--- a/docs/judgement-calls.xlsx
+++ b/docs/judgement-calls.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Decisions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$245</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B24" s="4">
-        <f>COUNTBLANK(Decisions!$I$4:$I$242)</f>
+        <f>COUNTBLANK(Decisions!$I$4:$I$245)</f>
         <v/>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J242"/>
+  <dimension ref="A1:J245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>983</v>
+        <v>1097</v>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>2798</v>
+        <v>3031</v>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2805</v>
+        <v>3038</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>5376</v>
+        <v>5524</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>5964</v>
+        <v>6117</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>3169</v>
+        <v>3463</v>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2431</v>
+        <v>2512</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>5925</v>
+        <v>6060</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>7632</v>
+        <v>7767</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>8384</v>
+        <v>8519</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>9521</v>
+        <v>9656</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>10571</v>
+        <v>10721</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>10572</v>
+        <v>10722</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>10573</v>
+        <v>10723</v>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>7767</v>
+        <v>7836</v>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>2344</v>
+        <v>2389</v>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2471</v>
+        <v>2516</v>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>4549</v>
+        <v>4600</v>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>637</v>
+        <v>697</v>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>725</v>
+        <v>785</v>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>726</v>
+        <v>786</v>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>756</v>
+        <v>816</v>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>765</v>
+        <v>831</v>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>768</v>
+        <v>834</v>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>778</v>
+        <v>927</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>1994</v>
+        <v>2090</v>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>4055</v>
+        <v>4156</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>659</v>
+        <v>749</v>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>1726</v>
+        <v>1852</v>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>942</v>
+        <v>1056</v>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>1818</v>
+        <v>1944</v>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>2813</v>
+        <v>3046</v>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>488</v>
+        <v>518</v>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>1838</v>
+        <v>1907</v>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>1841</v>
+        <v>1910</v>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>1844</v>
+        <v>1913</v>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>1885</v>
+        <v>1954</v>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>1888</v>
+        <v>1957</v>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>1891</v>
+        <v>1960</v>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>1936</v>
+        <v>2005</v>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>1975</v>
+        <v>2044</v>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>2194</v>
+        <v>2266</v>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>2197</v>
+        <v>2269</v>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>2273</v>
+        <v>2345</v>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>3332</v>
+        <v>3458</v>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>3524</v>
+        <v>3666</v>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>3610</v>
+        <v>3755</v>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>3697</v>
+        <v>3842</v>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>3889</v>
+        <v>4037</v>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>5694</v>
+        <v>5847</v>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>2239</v>
+        <v>2443</v>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>2989</v>
+        <v>3283</v>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>3003</v>
+        <v>3297</v>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>3037</v>
+        <v>3331</v>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>3490</v>
+        <v>3808</v>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>3769</v>
+        <v>4102</v>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>1906</v>
+        <v>1987</v>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>1961</v>
+        <v>2042</v>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="D64" s="8" t="n">
-        <v>2046</v>
+        <v>2127</v>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>2073</v>
+        <v>2154</v>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="D66" s="8" t="n">
-        <v>2361</v>
+        <v>2442</v>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>4017</v>
+        <v>4110</v>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>4621</v>
+        <v>4735</v>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>5327</v>
+        <v>5462</v>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>5328</v>
+        <v>5463</v>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>7333</v>
+        <v>7468</v>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>7722</v>
+        <v>7857</v>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>8690</v>
+        <v>8825</v>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="D74" s="8" t="n">
-        <v>9473</v>
+        <v>9608</v>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>10388</v>
+        <v>10538</v>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>518</v>
+        <v>548</v>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>648</v>
+        <v>684</v>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>1908</v>
+        <v>2010</v>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>1972</v>
+        <v>2074</v>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>2850</v>
+        <v>2952</v>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>3083</v>
+        <v>3185</v>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>3570</v>
+        <v>3673</v>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>2128</v>
+        <v>2287</v>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>2264</v>
+        <v>2423</v>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>1357</v>
+        <v>1375</v>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>1433</v>
+        <v>1451</v>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>1673</v>
+        <v>1694</v>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>1680</v>
+        <v>1701</v>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>1852</v>
+        <v>1873</v>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>1863</v>
+        <v>1884</v>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>1945</v>
+        <v>1966</v>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>2030</v>
+        <v>2054</v>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>2120</v>
+        <v>2144</v>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>2126</v>
+        <v>2150</v>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>2293</v>
+        <v>2317</v>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>2344</v>
+        <v>2368</v>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>2617</v>
+        <v>2641</v>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>2630</v>
+        <v>2654</v>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>3380</v>
+        <v>3404</v>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>3405</v>
+        <v>3429</v>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="D102" s="8" t="n">
-        <v>3004</v>
+        <v>3031</v>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>4215</v>
+        <v>4254</v>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>4698</v>
+        <v>4743</v>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>5034</v>
+        <v>5085</v>
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>5296</v>
+        <v>5350</v>
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>5300</v>
+        <v>5354</v>
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>5304</v>
+        <v>5358</v>
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>5307</v>
+        <v>5361</v>
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>5321</v>
+        <v>5375</v>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>5336</v>
+        <v>5390</v>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>6577</v>
+        <v>6646</v>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>7092</v>
+        <v>7161</v>
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="D114" s="8" t="n">
-        <v>7215</v>
+        <v>7284</v>
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>7519</v>
+        <v>7588</v>
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>7580</v>
+        <v>7649</v>
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>7757</v>
+        <v>7826</v>
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="D118" s="8" t="n">
-        <v>7815</v>
+        <v>7884</v>
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>620</v>
+        <v>635</v>
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="D122" s="8" t="n">
-        <v>1111</v>
+        <v>1141</v>
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>2347</v>
+        <v>2392</v>
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>2350</v>
+        <v>2395</v>
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>2353</v>
+        <v>2398</v>
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="D126" s="8" t="n">
-        <v>2387</v>
+        <v>2432</v>
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>2398</v>
+        <v>2443</v>
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>2466</v>
+        <v>2511</v>
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>2568</v>
+        <v>2613</v>
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>2990</v>
+        <v>3035</v>
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>3184</v>
+        <v>3232</v>
       </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>3273</v>
+        <v>3321</v>
       </c>
       <c r="E132" s="9" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>3363</v>
+        <v>3414</v>
       </c>
       <c r="E133" s="9" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="D134" s="8" t="n">
-        <v>3366</v>
+        <v>3417</v>
       </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>3660</v>
+        <v>3711</v>
       </c>
       <c r="E135" s="9" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="D136" s="8" t="n">
-        <v>4507</v>
+        <v>4558</v>
       </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>4533</v>
+        <v>4584</v>
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>4329</v>
+        <v>4417</v>
       </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="D140" s="8" t="n">
-        <v>5190</v>
+        <v>5281</v>
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>5210</v>
+        <v>5301</v>
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="D142" s="8" t="n">
-        <v>5221</v>
+        <v>5312</v>
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>5241</v>
+        <v>5332</v>
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="D144" s="8" t="n">
-        <v>5595</v>
+        <v>5686</v>
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>5762</v>
+        <v>5853</v>
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="D146" s="8" t="n">
-        <v>6293</v>
+        <v>6384</v>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>1659</v>
+        <v>1719</v>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="D148" s="8" t="n">
-        <v>3384</v>
+        <v>3623</v>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>641</v>
+        <v>701</v>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         </is>
       </c>
       <c r="D150" s="8" t="n">
-        <v>755</v>
+        <v>815</v>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
@@ -6876,16 +6876,16 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>Bolt Thrower</t>
+          <t>Gwytherc's Horn</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>757</v>
+        <v>3252</v>
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
-          <t>/unit/bolt-thrower (1.00)</t>
+          <t>/magic-item/gwytheres-horn (0.65)</t>
         </is>
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bolt-thrower</t>
+          <t>https://6th.whfb.app/magic-item/gwytheres-horn</t>
         </is>
       </c>
       <c r="I151" s="11" t="n"/>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Gwytherc's Horn</t>
+          <t>Stone of the Crystal Mere</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="D152" s="8" t="n">
-        <v>3156</v>
+        <v>3341</v>
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/gwytheres-horn (0.65)</t>
+          <t>/magic-item/stone-of-the-crystal-merex (0.90)</t>
         </is>
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/gwytheres-horn</t>
+          <t>https://6th.whfb.app/magic-item/stone-of-the-crystal-merex</t>
         </is>
       </c>
       <c r="I152" s="11" t="n"/>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>Stone of the Crystal Mere</t>
+          <t>Alter Kindred</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>3245</v>
+        <v>3961</v>
       </c>
       <c r="E153" s="9" t="inlineStr">
         <is>
@@ -6983,12 +6983,12 @@
       </c>
       <c r="G153" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/stone-of-the-crystal-merex (0.90)</t>
+          <t>/magic-item/the-alter-kindreds (0.80)</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/stone-of-the-crystal-merex</t>
+          <t>https://6th.whfb.app/magic-item/the-alter-kindreds</t>
         </is>
       </c>
       <c r="I153" s="11" t="n"/>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Alter Kindred</t>
+          <t>Strangle-Roots</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="D154" s="8" t="n">
-        <v>3865</v>
+        <v>4159</v>
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
@@ -7025,52 +7025,52 @@
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/the-alter-kindreds (0.80)</t>
-        </is>
-      </c>
-      <c r="H154" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/the-alter-kindreds</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H154" s="10" t="inlineStr"/>
       <c r="I154" s="11" t="n"/>
       <c r="J154" s="11" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>Strangle-Roots</t>
+          <t>Virtue of Stoicism</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>4058</v>
+        <v>2331</v>
       </c>
       <c r="E155" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G155" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H155" s="10" t="inlineStr"/>
+          <t>wiki: 35</t>
+        </is>
+      </c>
+      <c r="H155" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
+        </is>
+      </c>
       <c r="I155" s="11" t="n"/>
       <c r="J155" s="11" t="n"/>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Stoicism</t>
+          <t>Virtue of Noble Disdain</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
@@ -7091,7 +7091,7 @@
         </is>
       </c>
       <c r="D156" s="8" t="n">
-        <v>2199</v>
+        <v>2541</v>
       </c>
       <c r="E156" s="9" t="inlineStr">
         <is>
@@ -7100,17 +7100,17 @@
       </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
         </is>
       </c>
       <c r="I156" s="11" t="n"/>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Noble Disdain</t>
+          <t>Virtue of Purity</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>2409</v>
+        <v>2576</v>
       </c>
       <c r="E157" s="9" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
         </is>
       </c>
       <c r="I157" s="11" t="n"/>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Purity</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="D158" s="8" t="n">
-        <v>2444</v>
+        <v>2646</v>
       </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
@@ -7184,17 +7184,17 @@
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue: 30</t>
         </is>
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H158" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I158" s="11" t="n"/>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Audacity</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>2514</v>
+        <v>2751</v>
       </c>
       <c r="E159" s="9" t="inlineStr">
         <is>
@@ -7226,17 +7226,17 @@
       </c>
       <c r="F159" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 30</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 30</t>
         </is>
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
         </is>
       </c>
       <c r="I159" s="11" t="n"/>
@@ -7259,7 +7259,7 @@
         </is>
       </c>
       <c r="D160" s="8" t="n">
-        <v>2619</v>
+        <v>2793</v>
       </c>
       <c r="E160" s="9" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 90</t>
         </is>
       </c>
       <c r="G160" s="9" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Audacity</t>
+          <t>Virtue of Confidence</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="D161" s="8" t="n">
-        <v>2661</v>
+        <v>2835</v>
       </c>
       <c r="E161" s="9" t="inlineStr">
         <is>
@@ -7310,17 +7310,17 @@
       </c>
       <c r="F161" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue: 50</t>
         </is>
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
-          <t>wiki: 30</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
         </is>
       </c>
       <c r="I161" s="11" t="n"/>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="D162" s="8" t="n">
-        <v>2703</v>
+        <v>2870</v>
       </c>
       <c r="E162" s="9" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G162" s="9" t="inlineStr">
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="D163" s="8" t="n">
-        <v>2738</v>
+        <v>2912</v>
       </c>
       <c r="E163" s="9" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="F163" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 75</t>
         </is>
       </c>
       <c r="G163" s="9" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
+          <t>Virtue of Discipline</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="D164" s="8" t="n">
-        <v>2780</v>
+        <v>2954</v>
       </c>
       <c r="E164" s="9" t="inlineStr">
         <is>
@@ -7436,17 +7436,17 @@
       </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue: 90</t>
         </is>
       </c>
       <c r="G164" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H164" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I164" s="11" t="n"/>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="D165" s="8" t="n">
-        <v>2822</v>
+        <v>2996</v>
       </c>
       <c r="E165" s="9" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="F165" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue: 30</t>
         </is>
       </c>
       <c r="G165" s="9" t="inlineStr">
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="D166" s="8" t="n">
-        <v>2864</v>
+        <v>3031</v>
       </c>
       <c r="E166" s="9" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 30</t>
+          <t>catalogue: 45</t>
         </is>
       </c>
       <c r="G166" s="9" t="inlineStr">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="D167" s="8" t="n">
-        <v>2899</v>
+        <v>3066</v>
       </c>
       <c r="E167" s="9" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 45</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G167" s="9" t="inlineStr">
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="D168" s="8" t="n">
-        <v>2934</v>
+        <v>3108</v>
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 75</t>
         </is>
       </c>
       <c r="G168" s="9" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr">
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="D169" s="8" t="n">
-        <v>2976</v>
+        <v>3150</v>
       </c>
       <c r="E169" s="9" t="inlineStr">
         <is>
@@ -7646,17 +7646,17 @@
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue: 20</t>
         </is>
       </c>
       <c r="G169" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I169" s="11" t="n"/>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="D170" s="8" t="n">
-        <v>3018</v>
+        <v>3220</v>
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 20</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G170" s="9" t="inlineStr">
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="D171" s="8" t="n">
-        <v>3088</v>
+        <v>3255</v>
       </c>
       <c r="E171" s="9" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G171" s="9" t="inlineStr">
@@ -7763,7 +7763,7 @@
         </is>
       </c>
       <c r="D172" s="8" t="n">
-        <v>3123</v>
+        <v>3297</v>
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="F172" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 50</t>
         </is>
       </c>
       <c r="G172" s="9" t="inlineStr">
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="D173" s="8" t="n">
-        <v>3165</v>
+        <v>3332</v>
       </c>
       <c r="E173" s="9" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G173" s="9" t="inlineStr">
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="D174" s="8" t="n">
-        <v>3200</v>
+        <v>3374</v>
       </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="F174" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 70</t>
         </is>
       </c>
       <c r="G174" s="9" t="inlineStr">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="D175" s="8" t="n">
-        <v>3242</v>
+        <v>3416</v>
       </c>
       <c r="E175" s="9" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 70</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G175" s="9" t="inlineStr">
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="D176" s="8" t="n">
-        <v>3284</v>
+        <v>3458</v>
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="F176" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 90</t>
         </is>
       </c>
       <c r="G176" s="9" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Knightly Temper</t>
         </is>
       </c>
       <c r="C177" s="8" t="inlineStr">
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="D177" s="8" t="n">
-        <v>3326</v>
+        <v>3500</v>
       </c>
       <c r="E177" s="9" t="inlineStr">
         <is>
@@ -7982,17 +7982,17 @@
       </c>
       <c r="F177" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G177" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 40</t>
         </is>
       </c>
       <c r="H177" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-knightly-temper</t>
         </is>
       </c>
       <c r="I177" s="11" t="n"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Knightly Temper</t>
+          <t>Virtue of Noble Disdain</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="D178" s="8" t="n">
-        <v>3368</v>
+        <v>3542</v>
       </c>
       <c r="E178" s="9" t="inlineStr">
         <is>
@@ -8024,17 +8024,17 @@
       </c>
       <c r="F178" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G178" s="9" t="inlineStr">
         <is>
-          <t>wiki: 40</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H178" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-knightly-temper</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
         </is>
       </c>
       <c r="I178" s="11" t="n"/>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="D179" s="8" t="n">
-        <v>3410</v>
+        <v>3584</v>
       </c>
       <c r="E179" s="9" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G179" s="9" t="inlineStr">
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="D180" s="8" t="n">
-        <v>3452</v>
+        <v>3626</v>
       </c>
       <c r="E180" s="9" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="F180" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G180" s="9" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Noble Disdain</t>
+          <t>Virtue of Purity</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="D181" s="8" t="n">
-        <v>3494</v>
+        <v>3703</v>
       </c>
       <c r="E181" s="9" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="F181" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G181" s="9" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="H181" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
         </is>
       </c>
       <c r="I181" s="11" t="n"/>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="D182" s="8" t="n">
-        <v>3571</v>
+        <v>3745</v>
       </c>
       <c r="E182" s="9" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="F182" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G182" s="9" t="inlineStr">
@@ -8225,7 +8225,7 @@
         </is>
       </c>
       <c r="D183" s="8" t="n">
-        <v>3613</v>
+        <v>3787</v>
       </c>
       <c r="E183" s="9" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="F183" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G183" s="9" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Purity</t>
+          <t>Virtue of Heroism</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="D184" s="8" t="n">
-        <v>3655</v>
+        <v>3864</v>
       </c>
       <c r="E184" s="9" t="inlineStr">
         <is>
@@ -8281,12 +8281,12 @@
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 40</t>
         </is>
       </c>
       <c r="H184" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-heroism</t>
         </is>
       </c>
       <c r="I184" s="11" t="n"/>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Heroism</t>
+          <t>Virtue of Stoicism</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="D185" s="8" t="n">
-        <v>3732</v>
+        <v>3906</v>
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
@@ -8318,17 +8318,17 @@
       </c>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>wiki: 40</t>
+          <t>wiki: 35</t>
         </is>
       </c>
       <c r="H185" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-heroism</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
         </is>
       </c>
       <c r="I185" s="11" t="n"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Stoicism</t>
+          <t>Virtue of the Ideal</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="D186" s="8" t="n">
-        <v>3774</v>
+        <v>3941</v>
       </c>
       <c r="E186" s="9" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F186" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue: 70</t>
         </is>
       </c>
       <c r="G186" s="9" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="H186" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-ideal</t>
         </is>
       </c>
       <c r="I186" s="11" t="n"/>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Ideal</t>
+          <t>Virtue of the Impetuous Knight</t>
         </is>
       </c>
       <c r="C187" s="8" t="inlineStr">
@@ -8393,7 +8393,7 @@
         </is>
       </c>
       <c r="D187" s="8" t="n">
-        <v>3809</v>
+        <v>3983</v>
       </c>
       <c r="E187" s="9" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="H187" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-ideal</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-impetuous-knight</t>
         </is>
       </c>
       <c r="I187" s="11" t="n"/>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Impetuous Knight</t>
+          <t>Virtue of the Joust</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="D188" s="8" t="n">
-        <v>3851</v>
+        <v>4027</v>
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
@@ -8444,17 +8444,17 @@
       </c>
       <c r="F188" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 70</t>
+          <t>catalogue: 50</t>
         </is>
       </c>
       <c r="G188" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H188" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-impetuous-knight</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
         </is>
       </c>
       <c r="I188" s="11" t="n"/>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="D189" s="8" t="n">
-        <v>3895</v>
+        <v>4064</v>
       </c>
       <c r="E189" s="9" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="F189" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue: 75</t>
         </is>
       </c>
       <c r="G189" s="9" t="inlineStr">
@@ -8519,7 +8519,7 @@
         </is>
       </c>
       <c r="D190" s="8" t="n">
-        <v>3932</v>
+        <v>4108</v>
       </c>
       <c r="E190" s="9" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="F190" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G190" s="9" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Joust</t>
+          <t>Virtue of the Penitent</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="D191" s="8" t="n">
-        <v>3976</v>
+        <v>4152</v>
       </c>
       <c r="E191" s="9" t="inlineStr">
         <is>
@@ -8570,17 +8570,17 @@
       </c>
       <c r="F191" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G191" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: 40</t>
         </is>
       </c>
       <c r="H191" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-penitent</t>
         </is>
       </c>
       <c r="I191" s="11" t="n"/>
@@ -8594,16 +8594,16 @@
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Penitent</t>
+          <t>Power Stone</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="D192" s="8" t="n">
-        <v>4020</v>
+        <v>3347</v>
       </c>
       <c r="E192" s="9" t="inlineStr">
         <is>
@@ -8612,17 +8612,17 @@
       </c>
       <c r="F192" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 0</t>
         </is>
       </c>
       <c r="G192" s="9" t="inlineStr">
         <is>
-          <t>wiki: 40</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H192" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-penitent</t>
+          <t>https://6th.whfb.app/magic-item/power-stone</t>
         </is>
       </c>
       <c r="I192" s="11" t="n"/>
@@ -8631,40 +8631,40 @@
     <row r="193">
       <c r="A193" s="8" t="inlineStr">
         <is>
-          <t>Unit statline</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>Villein</t>
+          <t>Pure of Heart</t>
         </is>
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="D193" s="8" t="n">
-        <v>700</v>
+        <v>3536</v>
       </c>
       <c r="E193" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F193" s="9" t="inlineStr">
         <is>
-          <t>catalogue as is</t>
+          <t>catalogue: 0</t>
         </is>
       </c>
       <c r="G193" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;2, A 1-&gt;2</t>
+          <t>wiki: 500</t>
         </is>
       </c>
       <c r="H193" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/villein</t>
+          <t>https://6th.whfb.app/magic-item/pure-of-heart</t>
         </is>
       </c>
       <c r="I193" s="11" t="n"/>
@@ -8673,40 +8673,40 @@
     <row r="194">
       <c r="A194" s="8" t="inlineStr">
         <is>
-          <t>Unit statline</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>Pegasus</t>
+          <t>Ghal Maraz</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="D194" s="8" t="n">
-        <v>1071</v>
+        <v>5801</v>
       </c>
       <c r="E194" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F194" s="9" t="inlineStr">
         <is>
-          <t>catalogue as is</t>
+          <t>catalogue: 180</t>
         </is>
       </c>
       <c r="G194" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 7-&gt;6</t>
+          <t>wiki: 0</t>
         </is>
       </c>
       <c r="H194" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/pegasus</t>
+          <t>https://6th.whfb.app/magic-item/ghal-maraz</t>
         </is>
       </c>
       <c r="I194" s="11" t="n"/>
@@ -8715,40 +8715,40 @@
     <row r="195">
       <c r="A195" s="8" t="inlineStr">
         <is>
-          <t>Unit statline</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarf Sorcerer</t>
+          <t>Horn of the Wild Hunt</t>
         </is>
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarves.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="D195" s="8" t="n">
-        <v>104</v>
+        <v>1957</v>
       </c>
       <c r="E195" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F195" s="9" t="inlineStr">
         <is>
-          <t>catalogue as is</t>
+          <t>catalogue: 0</t>
         </is>
       </c>
       <c r="G195" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 4-&gt;3, T 5-&gt;4, W 3-&gt;2, I 1-&gt;2, Ld 10-&gt;9</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H195" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/chaos-dwarf-sorcerer</t>
+          <t>https://6th.whfb.app/magic-item/horn-of-the-wild-hunt</t>
         </is>
       </c>
       <c r="I195" s="11" t="n"/>
@@ -8762,20 +8762,20 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>Bull Centaur Hero</t>
+          <t>Villein</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarves.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="D196" s="8" t="n">
-        <v>520</v>
+        <v>793</v>
       </c>
       <c r="E196" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F196" s="9" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="G196" s="9" t="inlineStr">
         <is>
-          <t>wiki: T 4-&gt;5</t>
+          <t>wiki: WS 3-&gt;2, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H196" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bull-centaur-hero</t>
+          <t>https://6th.whfb.app/unit/villein</t>
         </is>
       </c>
       <c r="I196" s="11" t="n"/>
@@ -8804,16 +8804,16 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>Hobgoblin Crew</t>
+          <t>Pegasus</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarves.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="D197" s="8" t="n">
-        <v>1005</v>
+        <v>1179</v>
       </c>
       <c r="E197" s="9" t="inlineStr">
         <is>
@@ -8827,12 +8827,12 @@
       </c>
       <c r="G197" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 3-&gt;4</t>
+          <t>wiki: Ld 7-&gt;6</t>
         </is>
       </c>
       <c r="H197" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/hobgoblin-crew</t>
+          <t>https://6th.whfb.app/unit/pegasus</t>
         </is>
       </c>
       <c r="I197" s="11" t="n"/>
@@ -8846,20 +8846,20 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>Bloodletter</t>
+          <t>Chaos Dwarf Sorcerer</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="D198" s="8" t="n">
-        <v>780</v>
+        <v>107</v>
       </c>
       <c r="E198" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F198" s="9" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="G198" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: S 4-&gt;3, T 5-&gt;4, W 3-&gt;2, I 1-&gt;2, Ld 10-&gt;9</t>
         </is>
       </c>
       <c r="H198" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bloodletter</t>
+          <t>https://6th.whfb.app/unit/chaos-dwarf-sorcerer</t>
         </is>
       </c>
       <c r="I198" s="11" t="n"/>
@@ -8888,16 +8888,16 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>Horror</t>
+          <t>Bull Centaur Hero</t>
         </is>
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="D199" s="8" t="n">
-        <v>899</v>
+        <v>541</v>
       </c>
       <c r="E199" s="9" t="inlineStr">
         <is>
@@ -8911,12 +8911,12 @@
       </c>
       <c r="G199" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: T 4-&gt;5</t>
         </is>
       </c>
       <c r="H199" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/horror</t>
+          <t>https://6th.whfb.app/unit/bull-centaur-hero</t>
         </is>
       </c>
       <c r="I199" s="11" t="n"/>
@@ -8930,16 +8930,16 @@
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>Plaguebearer</t>
+          <t>Hobgoblin Crew</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="D200" s="8" t="n">
-        <v>999</v>
+        <v>1035</v>
       </c>
       <c r="E200" s="9" t="inlineStr">
         <is>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="G200" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: M 3-&gt;4</t>
         </is>
       </c>
       <c r="H200" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/plaguebearer</t>
+          <t>https://6th.whfb.app/unit/hobgoblin-crew</t>
         </is>
       </c>
       <c r="I200" s="11" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>Daemonette</t>
+          <t>Bloodletter</t>
         </is>
       </c>
       <c r="C201" s="8" t="inlineStr">
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="D201" s="8" t="n">
-        <v>1088</v>
+        <v>885</v>
       </c>
       <c r="E201" s="9" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="H201" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/daemonette</t>
+          <t>https://6th.whfb.app/unit/bloodletter</t>
         </is>
       </c>
       <c r="I201" s="11" t="n"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>Daemonette</t>
+          <t>Horror</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="D202" s="8" t="n">
-        <v>1186</v>
+        <v>1010</v>
       </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="H202" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/daemonette</t>
+          <t>https://6th.whfb.app/unit/horror</t>
         </is>
       </c>
       <c r="I202" s="11" t="n"/>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>Flamer</t>
+          <t>Plaguebearer</t>
         </is>
       </c>
       <c r="C203" s="8" t="inlineStr">
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="D203" s="8" t="n">
-        <v>1320</v>
+        <v>1113</v>
       </c>
       <c r="E203" s="9" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="H203" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/flamer</t>
+          <t>https://6th.whfb.app/unit/plaguebearer</t>
         </is>
       </c>
       <c r="I203" s="11" t="n"/>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t>Flesh Hound</t>
+          <t>Daemonette</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
@@ -9107,7 +9107,7 @@
         </is>
       </c>
       <c r="D204" s="8" t="n">
-        <v>1572</v>
+        <v>1208</v>
       </c>
       <c r="E204" s="9" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="H204" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/flesh-hound</t>
+          <t>https://6th.whfb.app/unit/daemonette</t>
         </is>
       </c>
       <c r="I204" s="11" t="n"/>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>Nurglings</t>
+          <t>Daemonette</t>
         </is>
       </c>
       <c r="C205" s="8" t="inlineStr">
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="D205" s="8" t="n">
-        <v>1632</v>
+        <v>1312</v>
       </c>
       <c r="E205" s="9" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="H205" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/nurglings</t>
+          <t>https://6th.whfb.app/unit/daemonette</t>
         </is>
       </c>
       <c r="I205" s="11" t="n"/>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t>Screamer</t>
+          <t>Flamer</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="D206" s="8" t="n">
-        <v>1690</v>
+        <v>1446</v>
       </c>
       <c r="E206" s="9" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="H206" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/screamer</t>
+          <t>https://6th.whfb.app/unit/flamer</t>
         </is>
       </c>
       <c r="I206" s="11" t="n"/>
@@ -9224,20 +9224,20 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Flesh Hound</t>
         </is>
       </c>
       <c r="C207" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="D207" s="8" t="n">
-        <v>1212</v>
+        <v>1698</v>
       </c>
       <c r="E207" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F207" s="9" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="G207" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 5-&gt;4, WS 5-&gt;4, BS 4-&gt;3, I 5-&gt;3, Ld 9-&gt;8</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H207" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/knight</t>
+          <t>https://6th.whfb.app/unit/flesh-hound</t>
         </is>
       </c>
       <c r="I207" s="11" t="n"/>
@@ -9266,16 +9266,16 @@
       </c>
       <c r="B208" s="8" t="inlineStr">
         <is>
-          <t>Hag</t>
+          <t>Nurglings</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="D208" s="8" t="n">
-        <v>1535</v>
+        <v>1758</v>
       </c>
       <c r="E208" s="9" t="inlineStr">
         <is>
@@ -9289,12 +9289,12 @@
       </c>
       <c r="G208" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 4-&gt;5</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H208" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/hag</t>
+          <t>https://6th.whfb.app/unit/nurglings</t>
         </is>
       </c>
       <c r="I208" s="11" t="n"/>
@@ -9308,20 +9308,20 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
+          <t>Screamer</t>
         </is>
       </c>
       <c r="C209" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="D209" s="8" t="n">
-        <v>2763</v>
+        <v>1816</v>
       </c>
       <c r="E209" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F209" s="9" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="G209" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H209" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
+          <t>https://6th.whfb.app/unit/screamer</t>
         </is>
       </c>
       <c r="I209" s="11" t="n"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t>Steed of Slaanesh</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="D210" s="8" t="n">
-        <v>2972</v>
+        <v>1263</v>
       </c>
       <c r="E210" s="9" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="G210" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
+          <t>wiki: M 5-&gt;4, WS 5-&gt;4, BS 4-&gt;3, I 5-&gt;3, Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H210" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
+          <t>https://6th.whfb.app/unit/knight</t>
         </is>
       </c>
       <c r="I210" s="11" t="n"/>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Hag</t>
         </is>
       </c>
       <c r="C211" s="8" t="inlineStr">
@@ -9401,11 +9401,11 @@
         </is>
       </c>
       <c r="D211" s="8" t="n">
-        <v>3170</v>
+        <v>1598</v>
       </c>
       <c r="E211" s="9" t="inlineStr">
         <is>
-          <t>4 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F211" s="9" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="G211" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
+          <t>wiki: WS 4-&gt;5</t>
         </is>
       </c>
       <c r="H211" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/knight</t>
+          <t>https://6th.whfb.app/unit/hag</t>
         </is>
       </c>
       <c r="I211" s="11" t="n"/>
@@ -9434,20 +9434,20 @@
       </c>
       <c r="B212" s="8" t="inlineStr">
         <is>
-          <t>Daddallo</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="D212" s="8" t="n">
-        <v>3084</v>
+        <v>2844</v>
       </c>
       <c r="E212" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F212" s="9" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="G212" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 2-&gt;1</t>
+          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
         </is>
       </c>
       <c r="H212" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/daddallo</t>
+          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
         </is>
       </c>
       <c r="I212" s="11" t="n"/>
@@ -9476,20 +9476,20 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>Warhorse</t>
+          <t>Steed of Slaanesh</t>
         </is>
       </c>
       <c r="C213" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="D213" s="8" t="n">
-        <v>4152</v>
+        <v>3065</v>
       </c>
       <c r="E213" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F213" s="9" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="G213" s="9" t="inlineStr">
         <is>
-          <t>wiki: BS 3-&gt;0</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H213" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warhorse</t>
+          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
         </is>
       </c>
       <c r="I213" s="11" t="n"/>
@@ -9518,20 +9518,20 @@
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="D214" s="8" t="n">
-        <v>507</v>
+        <v>3275</v>
       </c>
       <c r="E214" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>4 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F214" s="9" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="G214" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 2-&gt;1</t>
+          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
         </is>
       </c>
       <c r="H214" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/engineer</t>
+          <t>https://6th.whfb.app/unit/knight</t>
         </is>
       </c>
       <c r="I214" s="11" t="n"/>
@@ -9560,16 +9560,16 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>Bloodthirster</t>
+          <t>Daddallo</t>
         </is>
       </c>
       <c r="C215" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="D215" s="8" t="n">
-        <v>1462</v>
+        <v>3378</v>
       </c>
       <c r="E215" s="9" t="inlineStr">
         <is>
@@ -9583,12 +9583,12 @@
       </c>
       <c r="G215" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 7-&gt;6(7)</t>
+          <t>wiki: A 2-&gt;1</t>
         </is>
       </c>
       <c r="H215" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bloodthirster</t>
+          <t>https://6th.whfb.app/unit/daddallo</t>
         </is>
       </c>
       <c r="I215" s="11" t="n"/>
@@ -9602,20 +9602,20 @@
       </c>
       <c r="B216" s="8" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
+          <t>Warhorse</t>
         </is>
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="D216" s="8" t="n">
-        <v>1676</v>
+        <v>4491</v>
       </c>
       <c r="E216" s="9" t="inlineStr">
         <is>
-          <t>4 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F216" s="9" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="G216" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 6-&gt;8, WS 6-&gt;9, A 5-&gt;10, Ld 9-&gt;6</t>
+          <t>wiki: BS 3-&gt;0</t>
         </is>
       </c>
       <c r="H216" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
+          <t>https://6th.whfb.app/unit/warhorse</t>
         </is>
       </c>
       <c r="I216" s="11" t="n"/>
@@ -9644,20 +9644,20 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="C217" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Dwarfs.cat</t>
         </is>
       </c>
       <c r="D217" s="8" t="n">
-        <v>1784</v>
+        <v>528</v>
       </c>
       <c r="E217" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F217" s="9" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="G217" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
+          <t>wiki: A 2-&gt;1</t>
         </is>
       </c>
       <c r="H217" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
+          <t>https://6th.whfb.app/unit/engineer</t>
         </is>
       </c>
       <c r="I217" s="11" t="n"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Bloodthirster</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
@@ -9695,11 +9695,11 @@
         </is>
       </c>
       <c r="D218" s="8" t="n">
-        <v>3010</v>
+        <v>1483</v>
       </c>
       <c r="E218" s="9" t="inlineStr">
         <is>
-          <t>4 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F218" s="9" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="G218" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
+          <t>wiki: S 7-&gt;6(7)</t>
         </is>
       </c>
       <c r="H218" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/knight</t>
+          <t>https://6th.whfb.app/unit/bloodthirster</t>
         </is>
       </c>
       <c r="I218" s="11" t="n"/>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>Ungor</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="C219" s="8" t="inlineStr">
@@ -9737,11 +9737,11 @@
         </is>
       </c>
       <c r="D219" s="8" t="n">
-        <v>4100</v>
+        <v>1697</v>
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>4 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F219" s="9" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="G219" s="9" t="inlineStr">
         <is>
-          <t>wiki: T 4-&gt;3</t>
+          <t>wiki: M 6-&gt;8, WS 6-&gt;9, A 5-&gt;10, Ld 9-&gt;6</t>
         </is>
       </c>
       <c r="H219" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/ungor</t>
+          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
         </is>
       </c>
       <c r="I219" s="11" t="n"/>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="B220" s="8" t="inlineStr">
         <is>
-          <t>Troll</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
@@ -9779,11 +9779,11 @@
         </is>
       </c>
       <c r="D220" s="8" t="n">
-        <v>4441</v>
+        <v>1805</v>
       </c>
       <c r="E220" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F220" s="9" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="G220" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 4-&gt;3</t>
+          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
         </is>
       </c>
       <c r="H220" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/troll</t>
+          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
         </is>
       </c>
       <c r="I220" s="11" t="n"/>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>Centigor</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C221" s="8" t="inlineStr">
@@ -9821,11 +9821,11 @@
         </is>
       </c>
       <c r="D221" s="8" t="n">
-        <v>4770</v>
+        <v>3091</v>
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>4 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F221" s="9" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="G221" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 6-&gt;8, W 3-&gt;1, I 4-&gt;2, A 3-&gt;1(2), Ld 8-&gt;7</t>
+          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
         </is>
       </c>
       <c r="H221" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/centigor</t>
+          <t>https://6th.whfb.app/unit/knight</t>
         </is>
       </c>
       <c r="I221" s="11" t="n"/>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="B222" s="8" t="inlineStr">
         <is>
-          <t>Chaos Giant</t>
+          <t>Ungor</t>
         </is>
       </c>
       <c r="C222" s="8" t="inlineStr">
@@ -9863,7 +9863,7 @@
         </is>
       </c>
       <c r="D222" s="8" t="n">
-        <v>5291</v>
+        <v>4193</v>
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
@@ -9877,12 +9877,12 @@
       </c>
       <c r="G222" s="9" t="inlineStr">
         <is>
-          <t>wiki: A Special-&gt;*</t>
+          <t>wiki: T 4-&gt;3</t>
         </is>
       </c>
       <c r="H222" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/chaos-giant</t>
+          <t>https://6th.whfb.app/unit/ungor</t>
         </is>
       </c>
       <c r="I222" s="11" t="n"/>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>Steed of Slaanesh</t>
+          <t>Troll</t>
         </is>
       </c>
       <c r="C223" s="8" t="inlineStr">
@@ -9905,11 +9905,11 @@
         </is>
       </c>
       <c r="D223" s="8" t="n">
-        <v>5428</v>
+        <v>4546</v>
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="G223" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
+          <t>wiki: A 4-&gt;3</t>
         </is>
       </c>
       <c r="H223" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
+          <t>https://6th.whfb.app/unit/troll</t>
         </is>
       </c>
       <c r="I223" s="11" t="n"/>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>Tuskgor</t>
+          <t>Centigor</t>
         </is>
       </c>
       <c r="C224" s="8" t="inlineStr">
@@ -9947,11 +9947,11 @@
         </is>
       </c>
       <c r="D224" s="8" t="n">
-        <v>5478</v>
+        <v>4893</v>
       </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F224" s="9" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="G224" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 4-&gt;3</t>
+          <t>wiki: M 6-&gt;8, W 3-&gt;1, I 4-&gt;2, A 3-&gt;1(2), Ld 8-&gt;7</t>
         </is>
       </c>
       <c r="H224" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/tuskgor</t>
+          <t>https://6th.whfb.app/unit/centigor</t>
         </is>
       </c>
       <c r="I224" s="11" t="n"/>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>Ungor</t>
+          <t>Chaos Giant</t>
         </is>
       </c>
       <c r="C225" s="8" t="inlineStr">
@@ -9989,7 +9989,7 @@
         </is>
       </c>
       <c r="D225" s="8" t="n">
-        <v>5861</v>
+        <v>5426</v>
       </c>
       <c r="E225" s="9" t="inlineStr">
         <is>
@@ -10003,12 +10003,12 @@
       </c>
       <c r="G225" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 4-&gt;3</t>
+          <t>wiki: A Special-&gt;*</t>
         </is>
       </c>
       <c r="H225" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/ungor</t>
+          <t>https://6th.whfb.app/unit/chaos-giant</t>
         </is>
       </c>
       <c r="I225" s="11" t="n"/>
@@ -10022,20 +10022,20 @@
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t>Ellyrian Reaver</t>
+          <t>Steed of Slaanesh</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="D226" s="8" t="n">
-        <v>972</v>
+        <v>5563</v>
       </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="G226" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 1-&gt;2</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H226" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/ellyrian-reaver</t>
+          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
         </is>
       </c>
       <c r="I226" s="11" t="n"/>
@@ -10064,16 +10064,16 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>Harbinger</t>
+          <t>Tuskgor</t>
         </is>
       </c>
       <c r="C227" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="D227" s="8" t="n">
-        <v>1027</v>
+        <v>5613</v>
       </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="G227" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 1-&gt;2</t>
+          <t>wiki: S 4-&gt;3</t>
         </is>
       </c>
       <c r="H227" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/harbinger</t>
+          <t>https://6th.whfb.app/unit/tuskgor</t>
         </is>
       </c>
       <c r="I227" s="11" t="n"/>
@@ -10106,20 +10106,20 @@
       </c>
       <c r="B228" s="8" t="inlineStr">
         <is>
-          <t>Bladelord</t>
+          <t>Ungor</t>
         </is>
       </c>
       <c r="C228" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="D228" s="8" t="n">
-        <v>1586</v>
+        <v>5996</v>
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>3 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="G228" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 5-&gt;6, I 6-&gt;5, Ld 9-&gt;8</t>
+          <t>wiki: WS 4-&gt;3</t>
         </is>
       </c>
       <c r="H228" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bladelord</t>
+          <t>https://6th.whfb.app/unit/ungor</t>
         </is>
       </c>
       <c r="I228" s="11" t="n"/>
@@ -10148,16 +10148,16 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>Thunderfist</t>
+          <t>Ellyrian Reaver</t>
         </is>
       </c>
       <c r="C229" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="D229" s="8" t="n">
-        <v>1233</v>
+        <v>1029</v>
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>wiki: BS 2-&gt;3</t>
+          <t>wiki: A 1-&gt;2</t>
         </is>
       </c>
       <c r="H229" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/thunderfist</t>
+          <t>https://6th.whfb.app/unit/ellyrian-reaver</t>
         </is>
       </c>
       <c r="I229" s="11" t="n"/>
@@ -10190,16 +10190,16 @@
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t>Greyback</t>
+          <t>Harbinger</t>
         </is>
       </c>
       <c r="C230" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="D230" s="8" t="n">
-        <v>1333</v>
+        <v>1087</v>
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
@@ -10213,12 +10213,12 @@
       </c>
       <c r="G230" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 4-&gt;3</t>
+          <t>wiki: A 1-&gt;2</t>
         </is>
       </c>
       <c r="H230" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/greyback</t>
+          <t>https://6th.whfb.app/unit/harbinger</t>
         </is>
       </c>
       <c r="I230" s="11" t="n"/>
@@ -10232,20 +10232,20 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>Rhinox</t>
+          <t>Bladelord</t>
         </is>
       </c>
       <c r="C231" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="D231" s="8" t="n">
-        <v>1915</v>
+        <v>1682</v>
       </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>3 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="G231" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 7-&gt;6</t>
+          <t>wiki: WS 5-&gt;6, I 6-&gt;5, Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H231" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
+          <t>https://6th.whfb.app/unit/bladelord</t>
         </is>
       </c>
       <c r="I231" s="11" t="n"/>
@@ -10274,16 +10274,16 @@
       </c>
       <c r="B232" s="8" t="inlineStr">
         <is>
-          <t>Squig Hopper</t>
+          <t>Thunderfist</t>
         </is>
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="D232" s="8" t="n">
-        <v>3671</v>
+        <v>1248</v>
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
@@ -10297,12 +10297,12 @@
       </c>
       <c r="G232" s="9" t="inlineStr">
         <is>
-          <t>wiki: W 2-&gt;1</t>
+          <t>wiki: BS 2-&gt;3</t>
         </is>
       </c>
       <c r="H232" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/squig-hopper</t>
+          <t>https://6th.whfb.app/unit/thunderfist</t>
         </is>
       </c>
       <c r="I232" s="11" t="n"/>
@@ -10316,16 +10316,16 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>Giant</t>
+          <t>Greyback</t>
         </is>
       </c>
       <c r="C233" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="D233" s="8" t="n">
-        <v>4200</v>
+        <v>1351</v>
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
@@ -10339,12 +10339,12 @@
       </c>
       <c r="G233" s="9" t="inlineStr">
         <is>
-          <t>wiki: A Special-&gt;*</t>
+          <t>wiki: A 4-&gt;3</t>
         </is>
       </c>
       <c r="H233" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/giant</t>
+          <t>https://6th.whfb.app/unit/greyback</t>
         </is>
       </c>
       <c r="I233" s="11" t="n"/>
@@ -10358,16 +10358,16 @@
       </c>
       <c r="B234" s="8" t="inlineStr">
         <is>
-          <t>Boar Chariot</t>
+          <t>Rhinox</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="D234" s="8" t="n">
-        <v>6291</v>
+        <v>1936</v>
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
@@ -10381,12 +10381,12 @@
       </c>
       <c r="G234" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 5-&gt;3</t>
+          <t>wiki: M 7-&gt;6</t>
         </is>
       </c>
       <c r="H234" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/boar-chariot</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I234" s="11" t="n"/>
@@ -10400,16 +10400,16 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
+          <t>Squig Hopper</t>
         </is>
       </c>
       <c r="C235" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="D235" s="8" t="n">
-        <v>482</v>
+        <v>3710</v>
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
@@ -10423,12 +10423,12 @@
       </c>
       <c r="G235" s="9" t="inlineStr">
         <is>
-          <t>wiki: I 6-&gt;4</t>
+          <t>wiki: W 2-&gt;1</t>
         </is>
       </c>
       <c r="H235" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+          <t>https://6th.whfb.app/unit/squig-hopper</t>
         </is>
       </c>
       <c r="I235" s="11" t="n"/>
@@ -10442,20 +10442,20 @@
       </c>
       <c r="B236" s="8" t="inlineStr">
         <is>
-          <t>Clanrat Slave</t>
+          <t>Giant</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="D236" s="8" t="n">
-        <v>1400</v>
+        <v>4239</v>
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F236" s="9" t="inlineStr">
@@ -10465,12 +10465,12 @@
       </c>
       <c r="G236" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 6-&gt;5, I 5-&gt;4</t>
+          <t>wiki: A Special-&gt;*</t>
         </is>
       </c>
       <c r="H236" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/clanrat-slave</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I236" s="11" t="n"/>
@@ -10484,20 +10484,20 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
+          <t>Boar Chariot</t>
         </is>
       </c>
       <c r="C237" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="D237" s="8" t="n">
-        <v>2975</v>
+        <v>6360</v>
       </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>6 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F237" s="9" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="G237" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 4-&gt;3, T 4-&gt;3, W 3-&gt;2, I 5-&gt;4, A 2-&gt;1, Ld 7-&gt;5</t>
+          <t>wiki: S 5-&gt;3</t>
         </is>
       </c>
       <c r="H237" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+          <t>https://6th.whfb.app/unit/boar-chariot</t>
         </is>
       </c>
       <c r="I237" s="11" t="n"/>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="B238" s="8" t="inlineStr">
         <is>
-          <t>Plague Lord</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
@@ -10535,7 +10535,7 @@
         </is>
       </c>
       <c r="D238" s="8" t="n">
-        <v>3095</v>
+        <v>497</v>
       </c>
       <c r="E238" s="9" t="inlineStr">
         <is>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="G238" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 5-&gt;4</t>
+          <t>wiki: I 6-&gt;4</t>
         </is>
       </c>
       <c r="H238" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/plague-lord</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I238" s="11" t="n"/>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>Festering Chantor</t>
+          <t>Clanrat Slave</t>
         </is>
       </c>
       <c r="C239" s="8" t="inlineStr">
@@ -10577,11 +10577,11 @@
         </is>
       </c>
       <c r="D239" s="8" t="n">
-        <v>3169</v>
+        <v>1433</v>
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>7 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F239" s="9" t="inlineStr">
@@ -10591,12 +10591,12 @@
       </c>
       <c r="G239" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
+          <t>wiki: M 6-&gt;5, I 5-&gt;4</t>
         </is>
       </c>
       <c r="H239" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/festering-chantor</t>
+          <t>https://6th.whfb.app/unit/clanrat-slave</t>
         </is>
       </c>
       <c r="I239" s="11" t="n"/>
@@ -10610,20 +10610,20 @@
       </c>
       <c r="B240" s="8" t="inlineStr">
         <is>
-          <t>Skeleton</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>Tomb Kings.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="D240" s="8" t="n">
-        <v>637</v>
+        <v>3020</v>
       </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>6 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F240" s="9" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="G240" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 5-&gt;3</t>
+          <t>wiki: WS 4-&gt;3, T 4-&gt;3, W 3-&gt;2, I 5-&gt;4, A 2-&gt;1, Ld 7-&gt;5</t>
         </is>
       </c>
       <c r="H240" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/skeleton</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I240" s="11" t="n"/>
@@ -10652,16 +10652,16 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>Skeleton</t>
+          <t>Plague Lord</t>
         </is>
       </c>
       <c r="C241" s="8" t="inlineStr">
         <is>
-          <t>Tomb Kings.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="D241" s="8" t="n">
-        <v>728</v>
+        <v>3140</v>
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
@@ -10675,12 +10675,12 @@
       </c>
       <c r="G241" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 5-&gt;3</t>
+          <t>wiki: A 5-&gt;4</t>
         </is>
       </c>
       <c r="H241" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/skeleton</t>
+          <t>https://6th.whfb.app/unit/plague-lord</t>
         </is>
       </c>
       <c r="I241" s="11" t="n"/>
@@ -10694,20 +10694,20 @@
       </c>
       <c r="B242" s="8" t="inlineStr">
         <is>
-          <t>Skeleton Crew</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>Tomb Kings.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="D242" s="8" t="n">
-        <v>876</v>
+        <v>3217</v>
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>7 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F242" s="9" t="inlineStr">
@@ -10717,24 +10717,150 @@
       </c>
       <c r="G242" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;2, Ld 7-&gt;3</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
         </is>
       </c>
       <c r="H242" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/skeleton-crew</t>
+          <t>https://6th.whfb.app/unit/festering-chantor</t>
         </is>
       </c>
       <c r="I242" s="11" t="n"/>
       <c r="J242" s="11" t="n"/>
     </row>
+    <row r="243">
+      <c r="A243" s="8" t="inlineStr">
+        <is>
+          <t>Unit statline</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="inlineStr">
+        <is>
+          <t>Skeleton</t>
+        </is>
+      </c>
+      <c r="C243" s="8" t="inlineStr">
+        <is>
+          <t>Tomb Kings.cat</t>
+        </is>
+      </c>
+      <c r="D243" s="8" t="n">
+        <v>663</v>
+      </c>
+      <c r="E243" s="9" t="inlineStr">
+        <is>
+          <t>1 characteristic(s) differ</t>
+        </is>
+      </c>
+      <c r="F243" s="9" t="inlineStr">
+        <is>
+          <t>catalogue as is</t>
+        </is>
+      </c>
+      <c r="G243" s="9" t="inlineStr">
+        <is>
+          <t>wiki: Ld 5-&gt;3</t>
+        </is>
+      </c>
+      <c r="H243" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/skeleton</t>
+        </is>
+      </c>
+      <c r="I243" s="11" t="n"/>
+      <c r="J243" s="11" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="8" t="inlineStr">
+        <is>
+          <t>Unit statline</t>
+        </is>
+      </c>
+      <c r="B244" s="8" t="inlineStr">
+        <is>
+          <t>Skeleton</t>
+        </is>
+      </c>
+      <c r="C244" s="8" t="inlineStr">
+        <is>
+          <t>Tomb Kings.cat</t>
+        </is>
+      </c>
+      <c r="D244" s="8" t="n">
+        <v>765</v>
+      </c>
+      <c r="E244" s="9" t="inlineStr">
+        <is>
+          <t>1 characteristic(s) differ</t>
+        </is>
+      </c>
+      <c r="F244" s="9" t="inlineStr">
+        <is>
+          <t>catalogue as is</t>
+        </is>
+      </c>
+      <c r="G244" s="9" t="inlineStr">
+        <is>
+          <t>wiki: Ld 5-&gt;3</t>
+        </is>
+      </c>
+      <c r="H244" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/skeleton</t>
+        </is>
+      </c>
+      <c r="I244" s="11" t="n"/>
+      <c r="J244" s="11" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="8" t="inlineStr">
+        <is>
+          <t>Unit statline</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
+        <is>
+          <t>Skeleton Crew</t>
+        </is>
+      </c>
+      <c r="C245" s="8" t="inlineStr">
+        <is>
+          <t>Tomb Kings.cat</t>
+        </is>
+      </c>
+      <c r="D245" s="8" t="n">
+        <v>919</v>
+      </c>
+      <c r="E245" s="9" t="inlineStr">
+        <is>
+          <t>2 characteristic(s) differ</t>
+        </is>
+      </c>
+      <c r="F245" s="9" t="inlineStr">
+        <is>
+          <t>catalogue as is</t>
+        </is>
+      </c>
+      <c r="G245" s="9" t="inlineStr">
+        <is>
+          <t>wiki: WS 3-&gt;2, Ld 7-&gt;3</t>
+        </is>
+      </c>
+      <c r="H245" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/skeleton-crew</t>
+        </is>
+      </c>
+      <c r="I245" s="11" t="n"/>
+      <c r="J245" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:J242"/>
+  <autoFilter ref="A2:J245"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4:I242" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I245" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Option A,Option B,Leave as is,Rename catalogue,Needs more thought"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10869,7 +10995,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId134"/>
@@ -10957,6 +11083,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId221"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/judgement-calls.xlsx
+++ b/docs/judgement-calls.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -527,122 +527,160 @@
       <c r="A6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Category meanings:</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>'Used by' is what tells two same-named rules apart. For a rule that sits inside a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ambiguous match   the wiki has more than one page for this name and the texts differ</t>
+          <t>unit it reads as a path, outermost first: 'Plaguebearers &gt; Plaguebearer'. For one</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  No wiki coverage  no confident match. Often a catalogue spelling error - check the candidate</t>
+          <t>in &lt;sharedRules&gt; it lists every entry that links to it - so a rule showing</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Points cost       catalogue and wiki disagree. NB Bretonnian Virtues are priced per</t>
+          <t>'shared; used by Plaguebearers, Stream of Corruption' serves both the unit and the</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    character rank, so several rows per item is expected, not a bug</t>
+          <t>Daemonic Gift of the same name, which is the decision to make.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unit statline     characteristics differ. Only characteristics both sides state are compared</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Category meanings:</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Source: wiki scrape at C:/src/6eWikiScraper, indexed 2026-09-17T12:43:16+00:00</t>
+          <t xml:space="preserve">  Ambiguous match   the wiki has more than one page for this name and the texts differ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Generated by .claude/skills/bsdata-cat/scripts/wiki_xref.py</t>
+          <t xml:space="preserve">  No wiki coverage  no confident match. Often a catalogue spelling error - check the candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Points cost       catalogue and wiki disagree. NB Bretonnian Virtues are priced per</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                    character rank, so several rows per item is expected, not a bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unit statline     characteristics differ. Only characteristics both sides state are compared</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Counts by category</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous match</t>
-        </is>
-      </c>
-      <c r="B20" s="2">
-        <f>COUNTIF(Decisions!$A:$A,A20)</f>
-        <v/>
+          <t>Source: wiki scrape at C:/src/6eWikiScraper, indexed 2026-09-17T12:43:16+00:00</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
-        </is>
-      </c>
-      <c r="B21" s="2">
-        <f>COUNTIF(Decisions!$A:$A,A21)</f>
+          <t>Generated by .claude/skills/bsdata-cat/scripts/wiki_xref.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Counts by category</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous match</t>
+        </is>
+      </c>
+      <c r="B24" s="2">
+        <f>COUNTIF(Decisions!$A:$A,A24)</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>No wiki coverage</t>
+        </is>
+      </c>
+      <c r="B25" s="2">
+        <f>COUNTIF(Decisions!$A:$A,A25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Points cost</t>
         </is>
       </c>
-      <c r="B22" s="2">
-        <f>COUNTIF(Decisions!$A:$A,A22)</f>
+      <c r="B26" s="2">
+        <f>COUNTIF(Decisions!$A:$A,A26)</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Unit statline</t>
         </is>
       </c>
-      <c r="B23" s="2">
-        <f>COUNTIF(Decisions!$A:$A,A23)</f>
+      <c r="B27" s="2">
+        <f>COUNTIF(Decisions!$A:$A,A27)</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Still undecided</t>
         </is>
       </c>
-      <c r="B24" s="4">
+      <c r="B28" s="4">
         <f>COUNTBLANK(Decisions!$I$4:$I$245)</f>
         <v/>
       </c>
@@ -662,13 +700,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
@@ -676,7 +714,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Edit the yellow Decision column (and Notes). Row 2 is an example - delete it.</t>
+          <t>Edit the yellow Decision column (and Notes). Row 3 is an example - delete it.</t>
         </is>
       </c>
     </row>
@@ -693,12 +731,12 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
+          <t>Used by</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
           <t>File</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Line</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -740,17 +778,19 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>(example) Cloud of Flies</t>
+          <t>(example) Stream of Corruption</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
+          <t>shared; used by Plaguebearers, Stream of Corruption</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n">
-        <v>10571</v>
-      </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -758,17 +798,17 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>/magic-item/cloud-of-flies</t>
+          <t>/magic-item/stream-of-corruption</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>/special-rules/cloud-of-flies</t>
+          <t>/special-rules/stream-of-corruption</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/cloud-of-flies</t>
+          <t>https://6th.whfb.app/special-rules/stream-of-corruption</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr">
@@ -790,17 +830,19 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Stream of Corruption</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
+          <t>Aura of Slaanesh</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Chariot of Slaanesh, Daemonettes, Daemonic Gifts, Mounted Daemonettes, Pleasureseekers</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>1097</v>
-      </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -808,17 +850,17 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/stream-of-corruption</t>
+          <t>/magic-item/aura-of-slaanesh</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/stream-of-corruption</t>
+          <t>/special-rules/aura-of-slaanesh</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/stream-of-corruption</t>
+          <t>https://6th.whfb.app/magic-item/aura-of-slaanesh</t>
         </is>
       </c>
       <c r="I4" s="11" t="n"/>
@@ -832,17 +874,19 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Aura of Slaanesh</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
+          <t>Cloud of Flies</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Chariot of Nurgle, Daemonic Gifts, Nurglings, Plaguebearers, Plagueriders</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>3031</v>
-      </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -850,17 +894,17 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/aura-of-slaanesh</t>
+          <t>/magic-item/cloud-of-flies</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/aura-of-slaanesh</t>
+          <t>/special-rules/cloud-of-flies</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/aura-of-slaanesh</t>
+          <t>https://6th.whfb.app/magic-item/cloud-of-flies</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -874,17 +918,19 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Cloud of Flies</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
+          <t>Stream of Corruption</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Plaguebearers</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>3038</v>
-      </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -892,17 +938,17 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/cloud-of-flies</t>
+          <t>/magic-item/stream-of-corruption</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/cloud-of-flies</t>
+          <t>/special-rules/stream-of-corruption</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/cloud-of-flies</t>
+          <t>https://6th.whfb.app/magic-item/stream-of-corruption</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -916,17 +962,19 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Hand of Khaine</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
+          <t>Aura of Slaanesh</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Slaanesh Daemonic Gifts &gt; Aura of Slaanesh</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>5524</v>
-      </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -934,17 +982,17 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/hand-of-khaine-artefact-and-skill</t>
+          <t>/magic-item/aura-of-slaanesh</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/hand-of-khaine-malekith</t>
+          <t>/special-rules/aura-of-slaanesh</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/hand-of-khaine-artefact-and-skill</t>
+          <t>https://6th.whfb.app/magic-item/aura-of-slaanesh</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -958,17 +1006,19 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Aura of Slaanesh</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
+          <t>Hand of Khaine</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Artifacts and Skills &gt; Hand of Khaine</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>6117</v>
-      </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -976,17 +1026,17 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/aura-of-slaanesh</t>
+          <t>/magic-item/hand-of-khaine-artefact-and-skill</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/aura-of-slaanesh</t>
+          <t>/magic-item/hand-of-khaine-malekith</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/aura-of-slaanesh</t>
+          <t>https://6th.whfb.app/magic-item/hand-of-khaine-artefact-and-skill</t>
         </is>
       </c>
       <c r="I8" s="11" t="n"/>
@@ -1003,13 +1053,15 @@
           <t>Magic</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>The Giants of Albion &gt; Hengus the Druid</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Dogs of War.cat</t>
         </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>3463</v>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
@@ -1045,13 +1097,15 @@
           <t>Rune of Fire</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Weapon Runes &gt; Rune of Fire</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Dwarfs.cat</t>
         </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>2512</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
@@ -1084,17 +1138,19 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Axe of Khorne</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
+          <t>Aura of Slaanesh</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Aura of Slaanesh, Daemonettes, Mounted Daemonettes</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>6060</v>
-      </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -1102,17 +1158,17 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/axe-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>/magic-item/aura-of-slaanesh</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/axe-of-khorne-daemonic-gifts</t>
+          <t>/special-rules/aura-of-slaanesh</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/axe-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>https://6th.whfb.app/magic-item/aura-of-slaanesh</t>
         </is>
       </c>
       <c r="I11" s="11" t="n"/>
@@ -1129,13 +1185,15 @@
           <t>Axe of Khorne</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Magic Weapons &gt; Axe of Khorne</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>7767</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
@@ -1168,17 +1226,19 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Collar of Khorne</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
+          <t>Axe of Khorne</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
-        <v>8519</v>
-      </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -1186,17 +1246,17 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>/magic-item/axe-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/collar-of-khorne-daemonic-gifts</t>
+          <t>/magic-item/axe-of-khorne-daemonic-gifts</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>https://6th.whfb.app/magic-item/axe-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="I13" s="11" t="n"/>
@@ -1210,17 +1270,19 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Collar of Khorne</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
+          <t>Cloud of Flies</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Cloud of Flies, Nurglings, Plaguebearers</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n">
-        <v>9656</v>
-      </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -1228,17 +1290,17 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>/magic-item/cloud-of-flies</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/collar-of-khorne-daemonic-gifts</t>
+          <t>/special-rules/cloud-of-flies</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>https://6th.whfb.app/magic-item/cloud-of-flies</t>
         </is>
       </c>
       <c r="I14" s="11" t="n"/>
@@ -1252,17 +1314,19 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Cloud of Flies</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
+          <t>Collar of Khorne</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Talismans</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n">
-        <v>10721</v>
-      </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -1270,17 +1334,17 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/cloud-of-flies</t>
+          <t>/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/cloud-of-flies</t>
+          <t>/magic-item/collar-of-khorne-daemonic-gifts</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/cloud-of-flies</t>
+          <t>https://6th.whfb.app/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -1294,17 +1358,19 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Stream of Corruption</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
+          <t>Collar of Khorne</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Daemonic Gifts</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
-        <v>10722</v>
-      </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -1312,17 +1378,17 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/stream-of-corruption</t>
+          <t>/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/stream-of-corruption</t>
+          <t>/magic-item/collar-of-khorne-daemonic-gifts</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/stream-of-corruption</t>
+          <t>https://6th.whfb.app/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="I16" s="11" t="n"/>
@@ -1336,17 +1402,19 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Aura of Slaanesh</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
+          <t>Stream of Corruption</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Plaguebearers, Stream of Corruption</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n">
-        <v>10723</v>
-      </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -1354,17 +1422,17 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/aura-of-slaanesh</t>
+          <t>/magic-item/stream-of-corruption</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/aura-of-slaanesh</t>
+          <t>/special-rules/stream-of-corruption</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/aura-of-slaanesh</t>
+          <t>https://6th.whfb.app/magic-item/stream-of-corruption</t>
         </is>
       </c>
       <c r="I17" s="11" t="n"/>
@@ -1381,13 +1449,15 @@
           <t>'Eadbutt</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>7836</v>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
@@ -1423,13 +1493,15 @@
           <t>Daemonic Aura</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Vermin Lord</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>2389</v>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
@@ -1462,35 +1534,37 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Movement</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
+          <t>Expendable</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Clanrat Slaves, Rat Swarm</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
-        <v>2516</v>
-      </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>wiki has 3 candidate pages</t>
+          <t>wiki has 2 candidate pages</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>/faq/movement</t>
+          <t>/special-rules/expendable-clanrat-slaves</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>/movement</t>
+          <t>/special-rules/expendable-swarms</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/movement</t>
+          <t>https://6th.whfb.app/special-rules/expendable-clanrat-slaves</t>
         </is>
       </c>
       <c r="I20" s="11" t="n"/>
@@ -1504,35 +1578,37 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Expendable</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Doomwheel</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
-        <v>4600</v>
-      </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>wiki has 3 candidate pages</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/expendable-clanrat-slaves</t>
+          <t>/faq/movement</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/expendable-swarms</t>
+          <t>/movement</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/expendable-clanrat-slaves</t>
+          <t>https://6th.whfb.app/faq/movement</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -1546,17 +1622,19 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Skirmishers</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
+          <t>Cannon</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n">
-        <v>697</v>
-      </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -1564,17 +1642,17 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>/faq/skirmishers</t>
+          <t>/unit/cannon-dogs-of-war</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>/skirmishers</t>
+          <t>/unit/cannon-dwarfs</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/skirmishers</t>
+          <t>https://6th.whfb.app/unit/cannon-dogs-of-war</t>
         </is>
       </c>
       <c r="I22" s="11" t="n"/>
@@ -1588,35 +1666,33 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Fast Cavalry</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
+          <t>Chariot</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by (catalogue root)</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
-        <v>785</v>
-      </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>/special-rules/chariot-gorthor is Beasts of Chaos, not core rulebook - wrong for a shared rule</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>/faq/fast-cavalry</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>/fast-cavalry</t>
-        </is>
-      </c>
+          <t>/special-rules/chariot-gorthor</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/fast-cavalry</t>
+          <t>https://6th.whfb.app/special-rules/chariot-gorthor</t>
         </is>
       </c>
       <c r="I23" s="11" t="n"/>
@@ -1630,31 +1706,37 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Chariot</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
+          <t>Fast Cavalry</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
-        <v>786</v>
-      </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/chariot-gorthor is Beasts of Chaos, not core rulebook - wrong for a shared rule</t>
+          <t>wiki has 2 candidate pages</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/chariot-gorthor</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr"/>
+          <t>/faq/fast-cavalry</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>/fast-cavalry</t>
+        </is>
+      </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/chariot-gorthor</t>
+          <t>https://6th.whfb.app/faq/fast-cavalry</t>
         </is>
       </c>
       <c r="I24" s="11" t="n"/>
@@ -1668,17 +1750,19 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Cannon</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
+          <t>Skirmishers</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n">
-        <v>816</v>
-      </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
           <t>wiki has 2 candidate pages</t>
@@ -1686,17 +1770,17 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>/unit/cannon-dogs-of-war</t>
+          <t>/faq/skirmishers</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>/unit/cannon-dwarfs</t>
+          <t>/skirmishers</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/cannon-dogs-of-war</t>
+          <t>https://6th.whfb.app/faq/skirmishers</t>
         </is>
       </c>
       <c r="I25" s="11" t="n"/>
@@ -1713,13 +1797,15 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by (catalogue root)</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>831</v>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
@@ -1751,13 +1837,15 @@
           <t>Swarm</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by (catalogue root)</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>834</v>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
@@ -1793,13 +1881,15 @@
           <t>Undead</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>927</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
@@ -1835,13 +1925,15 @@
           <t>Tree Singing</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Drycha</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Wood Elves.cat</t>
         </is>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>2090</v>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
@@ -1877,13 +1969,15 @@
           <t>Tree Singing</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Treeman, Treeman Ancient</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Wood Elves.cat</t>
         </is>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>4156</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
@@ -1919,13 +2013,15 @@
           <t>Braziers</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Peasant Bowmen &gt; Braziers</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>749</v>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
@@ -1957,13 +2053,15 @@
           <t>The Fay Enchantress</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>The Fay Enchantress</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>1852</v>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
@@ -1996,17 +2094,19 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Lammasu</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
+          <t>Great Taurus</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Chaos Dwarf Lord &gt; Mount &gt; Great Taurus</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>Chaos Dwarves.cat</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n">
-        <v>149</v>
-      </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2019,12 +2119,12 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>/unit/lammasu (1.00)</t>
+          <t>/unit/great-taurus (1.00)</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/lammasu</t>
+          <t>https://6th.whfb.app/unit/great-taurus</t>
         </is>
       </c>
       <c r="I33" s="11" t="n"/>
@@ -2038,17 +2138,19 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Great Taurus</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
+          <t>Lammasu</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Sorcerer Lord &gt; Mount &gt; Lammasu</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Chaos Dwarves.cat</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n">
-        <v>327</v>
-      </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2061,12 +2163,12 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>/unit/great-taurus (1.00)</t>
+          <t>/unit/lammasu (1.00)</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/great-taurus</t>
+          <t>https://6th.whfb.app/unit/lammasu</t>
         </is>
       </c>
       <c r="I34" s="11" t="n"/>
@@ -2080,17 +2182,19 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Horror Champion</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
+          <t>Daemonic Legions Special Rules</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n">
-        <v>1056</v>
-      </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2103,12 +2207,12 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>/unit/horror (0.90)</t>
+          <t>/special-rules/daemonic (0.90)</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/horror</t>
+          <t>https://6th.whfb.app/special-rules/daemonic</t>
         </is>
       </c>
       <c r="I35" s="11" t="n"/>
@@ -2122,17 +2226,19 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions Special Rules</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
+          <t>Horror Champion</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Horrors &gt; Command &gt; Champion</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
       </c>
-      <c r="D36" s="8" t="n">
-        <v>1944</v>
-      </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2145,12 +2251,12 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/daemonic (0.90)</t>
+          <t>/unit/horror (0.90)</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/daemonic</t>
+          <t>https://6th.whfb.app/unit/horror</t>
         </is>
       </c>
       <c r="I36" s="11" t="n"/>
@@ -2167,13 +2273,15 @@
           <t>Scythed Wheels</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Chariot of Khorne, Chariot of Slaanesh</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
-      </c>
-      <c r="D37" s="8" t="n">
-        <v>3046</v>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
@@ -2206,17 +2314,19 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
+          <t>5+ Annointed Ward Save</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Druchii Annointed</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D38" s="8" t="n">
-        <v>518</v>
-      </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2229,12 +2339,12 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
+          <t>/special-rules/annointed-ward-save (0.80)</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
+          <t>https://6th.whfb.app/special-rules/annointed-ward-save</t>
         </is>
       </c>
       <c r="I38" s="11" t="n"/>
@@ -2248,16 +2358,18 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Acid Breath</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
+          <t>Accustomed to Battle</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>War Hydra &gt; Variant War Hydra &gt; Veteran War Hydra</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>1907</v>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
@@ -2286,16 +2398,18 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Splashback</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
+          <t>Acid Breath</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>War Hydra &gt; Variant War Hydra &gt; Royal War Hydra</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>1910</v>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
@@ -2324,17 +2438,19 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Mentally Scarred</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
+          <t>Beastmaster</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Beastmaster</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D41" s="8" t="n">
-        <v>1913</v>
-      </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2347,10 +2463,14 @@
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr"/>
+          <t>/unit/beastmaster (1.00)</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
+        </is>
+      </c>
       <c r="I41" s="11" t="n"/>
       <c r="J41" s="11" t="n"/>
     </row>
@@ -2362,17 +2482,19 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Daerlythe's Aura</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
+          <t>Chaos Daemon Sword (Keeper of Secrets) WS9 S6 I10 A6</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Chaos Daemon Sword</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D42" s="8" t="n">
-        <v>1954</v>
-      </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2385,10 +2507,14 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr"/>
+          <t>/magic-item/chaos-daemon-sword (0.90)</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/magic-item/chaos-daemon-sword</t>
+        </is>
+      </c>
       <c r="I42" s="11" t="n"/>
       <c r="J42" s="11" t="n"/>
     </row>
@@ -2400,17 +2526,19 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Physically Weakened</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
+          <t>Chosen of the Convents</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>War Hydra &gt; Variant War Hydra &gt; Spellthirster</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D43" s="8" t="n">
-        <v>1957</v>
-      </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2423,10 +2551,14 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr"/>
+          <t>/special-rules/chosen (0.90)</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/special-rules/chosen</t>
+        </is>
+      </c>
       <c r="I43" s="11" t="n"/>
       <c r="J43" s="11" t="n"/>
     </row>
@@ -2438,17 +2570,19 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Chosen of the Convents</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
+          <t>Cold One Chariot</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Cold One Chariot</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D44" s="8" t="n">
-        <v>1960</v>
-      </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2461,12 +2595,12 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/chosen (0.90)</t>
+          <t>/unit/cold-one-chariot (1.00)</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/chosen</t>
+          <t>https://6th.whfb.app/unit/cold-one-chariot</t>
         </is>
       </c>
       <c r="I44" s="11" t="n"/>
@@ -2480,17 +2614,19 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Veteran</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
+          <t>Daerlythe's Aura</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>War Hydra &gt; Variant War Hydra &gt; Spellthirster</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D45" s="8" t="n">
-        <v>2005</v>
-      </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2503,14 +2639,10 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>/unit/veteran (1.00)</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/veteran</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr"/>
       <c r="I45" s="11" t="n"/>
       <c r="J45" s="11" t="n"/>
     </row>
@@ -2522,17 +2654,19 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Accustomed to Battle</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
+          <t>Hate High Elves</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D46" s="8" t="n">
-        <v>2044</v>
-      </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2545,10 +2679,14 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr"/>
+          <t>/army/high-elves (0.80)</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/army/high-elves</t>
+        </is>
+      </c>
       <c r="I46" s="11" t="n"/>
       <c r="J46" s="11" t="n"/>
     </row>
@@ -2560,17 +2698,19 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Sorcerer</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
+          <t>Malekith's Weapons</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Malekith, Witch King of Naggaroth</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D47" s="8" t="n">
-        <v>2266</v>
-      </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2583,12 +2723,12 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>/unit/sorcerer (1.00)</t>
+          <t>/unit/malekith (0.90)</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/sorcerer</t>
+          <t>https://6th.whfb.app/unit/malekith</t>
         </is>
       </c>
       <c r="I47" s="11" t="n"/>
@@ -2602,17 +2742,19 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Malekith's Weapons</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
+          <t>Mentally Scarred</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>War Hydra &gt; Variant War Hydra &gt; Royal War Hydra</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D48" s="8" t="n">
-        <v>2269</v>
-      </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2625,14 +2767,10 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>/unit/malekith (0.90)</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/malekith</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr"/>
       <c r="I48" s="11" t="n"/>
       <c r="J48" s="11" t="n"/>
     </row>
@@ -2644,17 +2782,19 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>The Hand of Khaine</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
+          <t>Physically Weakened</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>War Hydra &gt; Variant War Hydra &gt; Spellthirster</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D49" s="8" t="n">
-        <v>2345</v>
-      </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2667,14 +2807,10 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/hand-of-khaine-artefact-and-skill (0.80)</t>
-        </is>
-      </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/hand-of-khaine-artefact-and-skill</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr"/>
       <c r="I49" s="11" t="n"/>
       <c r="J49" s="11" t="n"/>
     </row>
@@ -2686,17 +2822,19 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>5+ Annointed Ward Save</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
+          <t>Slaughterer's Blade</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Chaos Magic Items &gt; Magic Weapons &gt; Slaughterer's Blade</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D50" s="8" t="n">
-        <v>3458</v>
-      </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2709,12 +2847,12 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/annointed-ward-save (0.80)</t>
+          <t>/magic-item/slaughters-blade (0.66)</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/annointed-ward-save</t>
+          <t>https://6th.whfb.app/magic-item/slaughters-blade</t>
         </is>
       </c>
       <c r="I50" s="11" t="n"/>
@@ -2728,17 +2866,19 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Speed of Slaanesh (Mistress)</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
+          <t>Sorcerer</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Malekith, Witch King of Naggaroth</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D51" s="8" t="n">
-        <v>3666</v>
-      </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2751,12 +2891,12 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>/unit/mistress (0.80)</t>
+          <t>/unit/sorcerer (1.00)</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/mistress</t>
+          <t>https://6th.whfb.app/unit/sorcerer</t>
         </is>
       </c>
       <c r="I51" s="11" t="n"/>
@@ -2770,17 +2910,19 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Hate High Elves</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
+          <t>Speed of Slaanesh (Mistress)</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Devoted of Slaanesh &gt; Speed of Slaanesh (Mistress)</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D52" s="8" t="n">
-        <v>3755</v>
-      </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2793,12 +2935,12 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>/army/high-elves (0.80)</t>
+          <t>/unit/mistress (0.80)</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/army/high-elves</t>
+          <t>https://6th.whfb.app/unit/mistress</t>
         </is>
       </c>
       <c r="I52" s="11" t="n"/>
@@ -2812,17 +2954,19 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Cold One Chariot</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
+          <t>Splashback</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>War Hydra &gt; Variant War Hydra &gt; Royal War Hydra</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D53" s="8" t="n">
-        <v>3842</v>
-      </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2835,14 +2979,10 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>/unit/cold-one-chariot (1.00)</t>
-        </is>
-      </c>
-      <c r="H53" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/cold-one-chariot</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr"/>
       <c r="I53" s="11" t="n"/>
       <c r="J53" s="11" t="n"/>
     </row>
@@ -2854,17 +2994,19 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Chaos Daemon Sword (Keeper of Secrets) WS9 S6 I10 A6</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
+          <t>The Hand of Khaine</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Malekith, Witch King of Naggaroth &gt; The Hand of Khaine</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D54" s="8" t="n">
-        <v>4037</v>
-      </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2877,12 +3019,12 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/chaos-daemon-sword (0.90)</t>
+          <t>/magic-item/hand-of-khaine-artefact-and-skill (0.80)</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/chaos-daemon-sword</t>
+          <t>https://6th.whfb.app/magic-item/hand-of-khaine-artefact-and-skill</t>
         </is>
       </c>
       <c r="I54" s="11" t="n"/>
@@ -2896,17 +3038,19 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Slaughterer's Blade</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
+          <t>Veteran</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>War Hydra &gt; Variant War Hydra &gt; Veteran War Hydra</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D55" s="8" t="n">
-        <v>5847</v>
-      </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2919,12 +3063,12 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/slaughters-blade (0.66)</t>
+          <t>/unit/veteran (1.00)</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/slaughters-blade</t>
+          <t>https://6th.whfb.app/unit/veteran</t>
         </is>
       </c>
       <c r="I55" s="11" t="n"/>
@@ -2938,17 +3082,19 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Brazanga's Besiegers</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
+          <t>Birdmen of Catrazza</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Birdmen of Catrazza</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>Dogs of War.cat</t>
         </is>
       </c>
-      <c r="D56" s="8" t="n">
-        <v>2443</v>
-      </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -2961,12 +3107,12 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>/unit/besieger-braganzas-besiegers (0.80)</t>
+          <t>/unit/birdman-daddallos-birdmen-of-catrazza (0.80)</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/besieger-braganzas-besiegers</t>
+          <t>https://6th.whfb.app/unit/birdman-daddallos-birdmen-of-catrazza</t>
         </is>
       </c>
       <c r="I56" s="11" t="n"/>
@@ -2980,17 +3126,19 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Master Gunner Bronzino</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
+          <t>Brazanga's Besiegers</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Brazanga's Besiegers</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>Dogs of War.cat</t>
         </is>
       </c>
-      <c r="D57" s="8" t="n">
-        <v>3283</v>
-      </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3003,12 +3151,12 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>/unit/master (0.90)</t>
+          <t>/unit/besieger-braganzas-besiegers (0.80)</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/master</t>
+          <t>https://6th.whfb.app/unit/besieger-braganzas-besiegers</t>
         </is>
       </c>
       <c r="I57" s="11" t="n"/>
@@ -3022,17 +3170,19 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Galloper Gun Team</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
+          <t>Dark Emissary Spell List</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Dark Emissary</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>Dogs of War.cat</t>
         </is>
       </c>
-      <c r="D58" s="8" t="n">
-        <v>3297</v>
-      </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3045,12 +3195,12 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/galloper-gun (0.90)</t>
+          <t>/unit/dark-emissary (0.90)</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/galloper-gun</t>
+          <t>https://6th.whfb.app/unit/dark-emissary</t>
         </is>
       </c>
       <c r="I58" s="11" t="n"/>
@@ -3064,17 +3214,19 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Birdmen of Catrazza</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="inlineStr">
+          <t>Galloper Gun Team</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Bronzino's Galloper Guns &gt; Galloper Gun Team</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>Dogs of War.cat</t>
         </is>
       </c>
-      <c r="D59" s="8" t="n">
-        <v>3331</v>
-      </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3087,12 +3239,12 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>/unit/birdman-daddallos-birdmen-of-catrazza (0.80)</t>
+          <t>/special-rules/galloper-gun (0.90)</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/birdman-daddallos-birdmen-of-catrazza</t>
+          <t>https://6th.whfb.app/special-rules/galloper-gun</t>
         </is>
       </c>
       <c r="I59" s="11" t="n"/>
@@ -3106,17 +3258,19 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>The Bearmen of Urslo</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
+          <t>Master Gunner Bronzino</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Bronzino's Galloper Guns &gt; Master Gunner Bronzino</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>Dogs of War.cat</t>
         </is>
       </c>
-      <c r="D60" s="8" t="n">
-        <v>3808</v>
-      </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3129,12 +3283,12 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/for-hire-bearmen-of-urslo (0.59)</t>
+          <t>/unit/master (0.90)</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/for-hire-bearmen-of-urslo</t>
+          <t>https://6th.whfb.app/unit/master</t>
         </is>
       </c>
       <c r="I60" s="11" t="n"/>
@@ -3148,17 +3302,19 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Dark Emissary Spell List</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
+          <t>The Bearmen of Urslo</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Beorg Bearstruck and the Bearmen of Urslo</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>Dogs of War.cat</t>
         </is>
       </c>
-      <c r="D61" s="8" t="n">
-        <v>4102</v>
-      </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3171,12 +3327,12 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>/unit/dark-emissary (0.90)</t>
+          <t>/special-rules/for-hire-bearmen-of-urslo (0.59)</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/dark-emissary</t>
+          <t>https://6th.whfb.app/special-rules/for-hire-bearmen-of-urslo</t>
         </is>
       </c>
       <c r="I61" s="11" t="n"/>
@@ -3193,13 +3349,15 @@
           <t>Flame Cannon Misfire</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Flame Cannon</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Dwarfs.cat</t>
         </is>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>1987</v>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
@@ -3235,13 +3393,15 @@
           <t>Gyrocopter</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Gyrocopter</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>Dwarfs.cat</t>
         </is>
-      </c>
-      <c r="D63" s="8" t="n">
-        <v>2042</v>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
@@ -3274,17 +3434,19 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Organ Gun Misfire</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
+          <t>Master Rune of Switftness</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Weapon Runes &gt; Master Rune of Switftness</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>Dwarfs.cat</t>
         </is>
       </c>
-      <c r="D64" s="8" t="n">
-        <v>2127</v>
-      </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3297,12 +3459,12 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/organ-gun (0.90)</t>
+          <t>/unit/master (0.90)</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/organ-gun</t>
+          <t>https://6th.whfb.app/unit/master</t>
         </is>
       </c>
       <c r="I64" s="11" t="n"/>
@@ -3316,17 +3478,19 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Rule of Pride</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
+          <t>Organ Gun Misfire</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Organ Gun</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>Dwarfs.cat</t>
         </is>
       </c>
-      <c r="D65" s="8" t="n">
-        <v>2154</v>
-      </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3339,10 +3503,14 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H65" s="10" t="inlineStr"/>
+          <t>/special-rules/organ-gun (0.90)</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/special-rules/organ-gun</t>
+        </is>
+      </c>
       <c r="I65" s="11" t="n"/>
       <c r="J65" s="11" t="n"/>
     </row>
@@ -3354,17 +3522,19 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Master Rune of Switftness</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
+          <t>Rule of Pride</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>Dwarfs.cat</t>
         </is>
       </c>
-      <c r="D66" s="8" t="n">
-        <v>2442</v>
-      </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3377,14 +3547,10 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>/unit/master (0.90)</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/master</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr"/>
       <c r="I66" s="11" t="n"/>
       <c r="J66" s="11" t="n"/>
     </row>
@@ -3396,17 +3562,19 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Firewyrn of Tzeentch</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
+          <t>Centigors</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Centigors</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D67" s="8" t="n">
-        <v>4110</v>
-      </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3419,12 +3587,12 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/regeneration (0.90)</t>
+          <t>/unit/centigor (1.00)</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/regeneration</t>
+          <t>https://6th.whfb.app/unit/centigor</t>
         </is>
       </c>
       <c r="I67" s="11" t="n"/>
@@ -3438,17 +3606,19 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Centigors</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
+          <t>Diabolic Splendour</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Daemonic Gifts</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D68" s="8" t="n">
-        <v>4735</v>
-      </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3461,12 +3631,12 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>/unit/centigor (1.00)</t>
+          <t>/magic-item/diabolical-splendour (0.66)</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/centigor</t>
+          <t>https://6th.whfb.app/magic-item/diabolical-splendour</t>
         </is>
       </c>
       <c r="I68" s="11" t="n"/>
@@ -3480,17 +3650,19 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Giant Attacks</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
+          <t>Firewyrn of Tzeentch</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Spawn of Chaos &gt; Spawn of Chaos &gt; Spawn of the Gods &gt; Firewyrn of Tzeentch</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D69" s="8" t="n">
-        <v>5462</v>
-      </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3503,12 +3675,12 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (0.90)</t>
+          <t>/special-rules/regeneration (0.90)</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/giant</t>
+          <t>https://6th.whfb.app/special-rules/regeneration</t>
         </is>
       </c>
       <c r="I69" s="11" t="n"/>
@@ -3522,17 +3694,19 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Move Over Obstacles</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
+          <t>Giant Attacks</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Chaos Giant</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D70" s="8" t="n">
-        <v>5463</v>
-      </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3545,12 +3719,12 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/move-giants (0.90)</t>
+          <t>/unit/giant (0.90)</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/move-giants</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I70" s="11" t="n"/>
@@ -3564,17 +3738,19 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Slaughterer's Blade</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
+          <t>Move Over Obstacles</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Chaos Giant</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D71" s="8" t="n">
-        <v>7468</v>
-      </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3587,12 +3763,12 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/slaughters-blade (0.66)</t>
+          <t>/special-rules/move-giants (0.90)</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/slaughters-blade</t>
+          <t>https://6th.whfb.app/special-rules/move-giants</t>
         </is>
       </c>
       <c r="I71" s="11" t="n"/>
@@ -3606,17 +3782,19 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Two Breath Weapons</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
+          <t>Slaughterer's Blade</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Magic Weapons &gt; Slaughterer's Blade</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D72" s="8" t="n">
-        <v>7857</v>
-      </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3629,12 +3807,12 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/breath-weapons (0.80)</t>
+          <t>/magic-item/slaughters-blade (0.66)</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/breath-weapons</t>
+          <t>https://6th.whfb.app/magic-item/slaughters-blade</t>
         </is>
       </c>
       <c r="I72" s="11" t="n"/>
@@ -3648,17 +3826,19 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Vitriolic Totem</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
+          <t>Staff of Darkoath</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Arcane Items</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D73" s="8" t="n">
-        <v>8825</v>
-      </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3671,12 +3851,12 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/vitrolic-totem (0.68)</t>
+          <t>/magic-item/staff-of-darkoth (0.68)</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/vitrolic-totem</t>
+          <t>https://6th.whfb.app/magic-item/staff-of-darkoth</t>
         </is>
       </c>
       <c r="I73" s="11" t="n"/>
@@ -3690,17 +3870,19 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Diabolic Splendour</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
+          <t>Two Breath Weapons</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Mount &gt; Dragon of Chaos</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D74" s="8" t="n">
-        <v>9608</v>
-      </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3713,12 +3895,12 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/diabolical-splendour (0.66)</t>
+          <t>/special-rules/breath-weapons (0.80)</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/diabolical-splendour</t>
+          <t>https://6th.whfb.app/special-rules/breath-weapons</t>
         </is>
       </c>
       <c r="I74" s="11" t="n"/>
@@ -3732,17 +3914,19 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Staff of Darkoath</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
+          <t>Vitriolic Totem</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Magic Banners</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D75" s="8" t="n">
-        <v>10538</v>
-      </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3755,12 +3939,12 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/staff-of-darkoth (0.68)</t>
+          <t>/magic-item/vitrolic-totem (0.68)</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/staff-of-darkoth</t>
+          <t>https://6th.whfb.app/magic-item/vitrolic-totem</t>
         </is>
       </c>
       <c r="I75" s="11" t="n"/>
@@ -3774,17 +3958,19 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Fight In Three Ranks</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
+          <t>Banner of Ellyrion</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Magic Banners &gt; Banner of Ellyrion</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>High Elves.cat</t>
         </is>
       </c>
-      <c r="D76" s="8" t="n">
-        <v>548</v>
-      </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3797,12 +3983,12 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>/skirmishers/ranks-skirmishers (0.80)</t>
+          <t>/magic-item/banner-of-ellryion (0.66)</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/skirmishers/ranks-skirmishers</t>
+          <t>https://6th.whfb.app/magic-item/banner-of-ellryion</t>
         </is>
       </c>
       <c r="I76" s="11" t="n"/>
@@ -3816,17 +4002,19 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Fight In Three Ranks</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
+          <t>Bow of the Searfarer</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Magic Weapons &gt; Bow of the Searfarer</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>High Elves.cat</t>
         </is>
       </c>
-      <c r="D77" s="8" t="n">
-        <v>684</v>
-      </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3839,12 +4027,12 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>/skirmishers/ranks-skirmishers (0.80)</t>
+          <t>/weapons/bow (0.90)</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/skirmishers/ranks-skirmishers</t>
+          <t>https://6th.whfb.app/weapons/bow</t>
         </is>
       </c>
       <c r="I77" s="11" t="n"/>
@@ -3858,17 +4046,19 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Intruige at Court</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
+          <t>Channeler</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Honours &gt; Channeler</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>High Elves.cat</t>
         </is>
       </c>
-      <c r="D78" s="8" t="n">
-        <v>2010</v>
-      </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3881,12 +4071,12 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/intrigue-at-court (0.66)</t>
+          <t>/magic-item/channeller (0.66)</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/intrigue-at-court</t>
+          <t>https://6th.whfb.app/magic-item/channeller</t>
         </is>
       </c>
       <c r="I78" s="11" t="n"/>
@@ -3900,17 +4090,19 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Tiranoc Chariot</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr">
+          <t>Fight In Three Ranks</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Spearmen</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>High Elves.cat</t>
         </is>
       </c>
-      <c r="D79" s="8" t="n">
-        <v>2074</v>
-      </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3923,12 +4115,12 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>/unit/tiranoc-chariot (1.00)</t>
+          <t>/skirmishers/ranks-skirmishers (0.80)</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/tiranoc-chariot</t>
+          <t>https://6th.whfb.app/skirmishers/ranks-skirmishers</t>
         </is>
       </c>
       <c r="I79" s="11" t="n"/>
@@ -3942,17 +4134,19 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Bow of the Searfarer</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="inlineStr">
+          <t>Fight In Three Ranks</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Lothern Sea Guard</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>High Elves.cat</t>
         </is>
       </c>
-      <c r="D80" s="8" t="n">
-        <v>2952</v>
-      </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -3965,12 +4159,12 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>/weapons/bow (0.90)</t>
+          <t>/skirmishers/ranks-skirmishers (0.80)</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/bow</t>
+          <t>https://6th.whfb.app/skirmishers/ranks-skirmishers</t>
         </is>
       </c>
       <c r="I80" s="11" t="n"/>
@@ -3984,17 +4178,19 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Banner of Ellyrion</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
+          <t>Intruige at Court</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>High Elves.cat</t>
         </is>
       </c>
-      <c r="D81" s="8" t="n">
-        <v>3185</v>
-      </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4007,12 +4203,12 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/banner-of-ellryion (0.66)</t>
+          <t>/special-rules/intrigue-at-court (0.66)</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/banner-of-ellryion</t>
+          <t>https://6th.whfb.app/special-rules/intrigue-at-court</t>
         </is>
       </c>
       <c r="I81" s="11" t="n"/>
@@ -4026,17 +4222,19 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Channeler</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr">
+          <t>Tiranoc Chariot</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Tiranoc Chariot</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>High Elves.cat</t>
         </is>
       </c>
-      <c r="D82" s="8" t="n">
-        <v>3673</v>
-      </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4049,12 +4247,12 @@
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/channeller (0.66)</t>
+          <t>/unit/tiranoc-chariot (1.00)</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/channeller</t>
+          <t>https://6th.whfb.app/unit/tiranoc-chariot</t>
         </is>
       </c>
       <c r="I82" s="11" t="n"/>
@@ -4071,13 +4269,15 @@
           <t>Blessed Spawning of Tlzazcotl</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>Sacred Spawnings &gt; Blessed Spawning of Tlzazcotl</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>Lizardmen.cat</t>
         </is>
-      </c>
-      <c r="D83" s="8" t="n">
-        <v>2287</v>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
@@ -4113,13 +4313,15 @@
           <t>Cupped Hands of the Hold Ones</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Sacred Plaques &gt; Cupped Hands of the Hold Ones</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>Lizardmen.cat</t>
         </is>
-      </c>
-      <c r="D84" s="8" t="n">
-        <v>2423</v>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
@@ -4152,17 +4354,19 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Harpoon Crossbow</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr">
+          <t>Bull Rhinoxen</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>Rhinox Cavalry &gt; Bull Rhinox &gt; Bull Rhinox</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D85" s="8" t="n">
-        <v>507</v>
-      </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4175,12 +4379,12 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>/weapons/bow (0.80)</t>
+          <t>/unit/rhinox (0.80)</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/bow</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I85" s="11" t="n"/>
@@ -4194,17 +4398,19 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Yheetee Ice Weapons</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr">
+          <t>Greasus Goldtooth</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>Greasus Goldtooth</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D86" s="8" t="n">
-        <v>1375</v>
-      </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4217,12 +4423,12 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>/weapons/ice-weapons (0.80)</t>
+          <t>/unit/greasus-goldtooth (1.00)</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/ice-weapons</t>
+          <t>https://6th.whfb.app/unit/greasus-goldtooth</t>
         </is>
       </c>
       <c r="I86" s="11" t="n"/>
@@ -4236,17 +4442,19 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Scrap Launcher</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
+          <t>Gut Magic Miscast</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Butcher, Scrag the Slaughterer, Slaughtermaster</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D87" s="8" t="n">
-        <v>1451</v>
-      </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4259,12 +4467,12 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>/unit/scraplauncher (0.67)</t>
+          <t>/spell-lists/gut-magic (0.90)</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/scraplauncher</t>
+          <t>https://6th.whfb.app/spell-lists/gut-magic</t>
         </is>
       </c>
       <c r="I87" s="11" t="n"/>
@@ -4278,17 +4486,19 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Move Over Obstacles</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="inlineStr">
+          <t>Harpoon Crossbow</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Hunter &gt; Harpoon Crossbow</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D88" s="8" t="n">
-        <v>1694</v>
-      </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4301,12 +4511,12 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/move-giants (0.90)</t>
+          <t>/weapons/bow (0.80)</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/move-giants</t>
+          <t>https://6th.whfb.app/weapons/bow</t>
         </is>
       </c>
       <c r="I88" s="11" t="n"/>
@@ -4320,17 +4530,19 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Slavegiant Attacks</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
+          <t>Ironfist</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Bruiser, Ogre Bulls, Rhinox Cavalry, Tyrant</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D89" s="8" t="n">
-        <v>1701</v>
-      </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4343,12 +4555,12 @@
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>/unit/slavegiant (0.90)</t>
+          <t>/unit/garagrim-ironfist (0.80)</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/slavegiant</t>
+          <t>https://6th.whfb.app/unit/garagrim-ironfist</t>
         </is>
       </c>
       <c r="I89" s="11" t="n"/>
@@ -4362,17 +4574,19 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Thunderous Charge</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
+          <t>Ironfists (Rhinox Riders)</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Rhinox Cavalry &gt; Ironfists</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D90" s="8" t="n">
-        <v>1873</v>
-      </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4385,12 +4599,12 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish (0.80)</t>
+          <t>/unit/rhinox (0.80)</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I90" s="11" t="n"/>
@@ -4404,17 +4618,19 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
+          <t>Mawseeker</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>Big Names &gt; Mawseeker</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D91" s="8" t="n">
-        <v>1884</v>
-      </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4427,14 +4643,10 @@
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>/unit/rhinox (0.90)</t>
-        </is>
-      </c>
-      <c r="H91" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr"/>
       <c r="I91" s="11" t="n"/>
       <c r="J91" s="11" t="n"/>
     </row>
@@ -4446,17 +4658,19 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Ironfists (Rhinox Riders)</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
+          <t>Move Over Obstacles</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>Slavegiant</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D92" s="8" t="n">
-        <v>1966</v>
-      </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4469,12 +4683,12 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>/unit/rhinox (0.80)</t>
+          <t>/special-rules/move-giants (0.90)</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
+          <t>https://6th.whfb.app/special-rules/move-giants</t>
         </is>
       </c>
       <c r="I92" s="11" t="n"/>
@@ -4488,17 +4702,19 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Bull Rhinoxen</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
+          <t>Rhinox Cavalry</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>Rhinox Cavalry</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D93" s="8" t="n">
-        <v>2054</v>
-      </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4511,7 +4727,7 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>/unit/rhinox (0.80)</t>
+          <t>/unit/rhinox (0.90)</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
@@ -4530,17 +4746,19 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Stump-Blades</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr">
+          <t>Scrap Launcher</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>Gnoblar Scraplauncher</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D94" s="8" t="n">
-        <v>2144</v>
-      </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4553,10 +4771,14 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H94" s="10" t="inlineStr"/>
+          <t>/unit/scraplauncher (0.67)</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/scraplauncher</t>
+        </is>
+      </c>
       <c r="I94" s="11" t="n"/>
       <c r="J94" s="11" t="n"/>
     </row>
@@ -4571,13 +4793,15 @@
           <t>Skrag the Slaughterer</t>
         </is>
       </c>
-      <c r="C95" s="8" t="inlineStr">
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>Scrag the Slaughterer</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
-      </c>
-      <c r="D95" s="8" t="n">
-        <v>2150</v>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
@@ -4610,17 +4834,19 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Greasus Goldtooth</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="inlineStr">
+          <t>Slavegiant Attacks</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Slavegiant</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D96" s="8" t="n">
-        <v>2317</v>
-      </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4633,12 +4859,12 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>/unit/greasus-goldtooth (1.00)</t>
+          <t>/unit/slavegiant (0.90)</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/greasus-goldtooth</t>
+          <t>https://6th.whfb.app/unit/slavegiant</t>
         </is>
       </c>
       <c r="I96" s="11" t="n"/>
@@ -4652,17 +4878,19 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>The Scepter of the Titans</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="inlineStr">
+          <t>Stump-Blades</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>Scrag the Slaughterer</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D97" s="8" t="n">
-        <v>2368</v>
-      </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4675,14 +4903,10 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/sceptre-of-the-titans (0.61)</t>
-        </is>
-      </c>
-      <c r="H97" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/sceptre-of-the-titans</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr"/>
       <c r="I97" s="11" t="n"/>
       <c r="J97" s="11" t="n"/>
     </row>
@@ -4694,17 +4918,19 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Wallcrusher</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr">
+          <t>The Scepter of the Titans</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>Greasus Goldtooth &gt; The Scepter of the Titans</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D98" s="8" t="n">
-        <v>2641</v>
-      </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4717,12 +4943,12 @@
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>/unit/crusher (0.80)</t>
+          <t>/magic-item/sceptre-of-the-titans (0.61)</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/crusher</t>
+          <t>https://6th.whfb.app/magic-item/sceptre-of-the-titans</t>
         </is>
       </c>
       <c r="I98" s="11" t="n"/>
@@ -4736,17 +4962,19 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>Mawseeker</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="inlineStr">
+          <t>Thunderous Charge</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>Rhinox Cavalry</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D99" s="8" t="n">
-        <v>2654</v>
-      </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4759,10 +4987,14 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H99" s="10" t="inlineStr"/>
+          <t>/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish (0.80)</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish</t>
+        </is>
+      </c>
       <c r="I99" s="11" t="n"/>
       <c r="J99" s="11" t="n"/>
     </row>
@@ -4774,17 +5006,19 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Ironfist</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="inlineStr">
+          <t>Wallcrusher</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Big Names &gt; Wallcrusher</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D100" s="8" t="n">
-        <v>3404</v>
-      </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4797,12 +5031,12 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>/unit/garagrim-ironfist (0.80)</t>
+          <t>/unit/crusher (0.80)</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/garagrim-ironfist</t>
+          <t>https://6th.whfb.app/unit/crusher</t>
         </is>
       </c>
       <c r="I100" s="11" t="n"/>
@@ -4816,17 +5050,19 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>Gut Magic Miscast</t>
-        </is>
-      </c>
-      <c r="C101" s="8" t="inlineStr">
+          <t>Yheetee Ice Weapons</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>Yheetees &gt; Yheetee Ice Weapons</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D101" s="8" t="n">
-        <v>3429</v>
-      </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4839,12 +5075,12 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>/spell-lists/gut-magic (0.90)</t>
+          <t>/weapons/ice-weapons (0.80)</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/spell-lists/gut-magic</t>
+          <t>https://6th.whfb.app/weapons/ice-weapons</t>
         </is>
       </c>
       <c r="I101" s="11" t="n"/>
@@ -4858,17 +5094,19 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Moving Fanatics into Obstacles</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="inlineStr">
+          <t>'Eadbuttin' 'At</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>Enchanted Items &gt; 'Eadbuttin' 'At</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D102" s="8" t="n">
-        <v>3031</v>
-      </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4881,12 +5119,12 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>/skirmishers/moving (0.90)</t>
+          <t>/special-rules/eadbutt (0.90)</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/skirmishers/moving</t>
+          <t>https://6th.whfb.app/special-rules/eadbutt</t>
         </is>
       </c>
       <c r="I102" s="11" t="n"/>
@@ -4900,17 +5138,19 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>Giant</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="inlineStr">
+          <t>Fungus Buster Brew</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Shiny Stuff &gt; Fungus Buster Brew</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D103" s="8" t="n">
-        <v>4254</v>
-      </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4923,14 +5163,10 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (1.00)</t>
-        </is>
-      </c>
-      <c r="H103" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/giant</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H103" s="10" t="inlineStr"/>
       <c r="I103" s="11" t="n"/>
       <c r="J103" s="11" t="n"/>
     </row>
@@ -4942,17 +5178,19 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Giant Spiders</t>
-        </is>
-      </c>
-      <c r="C104" s="8" t="inlineStr">
+          <t>Giant</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>Giant</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D104" s="8" t="n">
-        <v>4743</v>
-      </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -4965,7 +5203,7 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (0.90)</t>
+          <t>/unit/giant (1.00)</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
@@ -4984,17 +5222,19 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>The Blasted Banner</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="inlineStr">
+          <t>Giant Spiders</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Goblin Spider Riders</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D105" s="8" t="n">
-        <v>5085</v>
-      </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5007,12 +5247,12 @@
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/the-beast-banner (0.62)</t>
+          <t>/unit/giant (0.90)</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/the-beast-banner</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I105" s="11" t="n"/>
@@ -5026,17 +5266,19 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Gobbla the Cave Squig</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="inlineStr">
+          <t>Giants Movement</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D106" s="8" t="n">
-        <v>5350</v>
-      </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5049,12 +5291,12 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>/unit/squig (0.80)</t>
+          <t>/unit/giant (0.90)</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/squig</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I106" s="11" t="n"/>
@@ -5068,17 +5310,19 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>Gobbla's Movement</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr">
+          <t>Gobbla the Cave Squig</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D107" s="8" t="n">
-        <v>5354</v>
-      </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5091,12 +5335,12 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/move-giants (0.80)</t>
+          <t>/unit/squig (0.80)</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/move-giants</t>
+          <t>https://6th.whfb.app/unit/squig</t>
         </is>
       </c>
       <c r="I107" s="11" t="n"/>
@@ -5110,17 +5354,19 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Insatiable Appetite</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr">
+          <t>Gobbla's Movement</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D108" s="8" t="n">
-        <v>5358</v>
-      </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5133,10 +5379,14 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H108" s="10" t="inlineStr"/>
+          <t>/special-rules/move-giants (0.80)</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/special-rules/move-giants</t>
+        </is>
+      </c>
       <c r="I108" s="11" t="n"/>
       <c r="J108" s="11" t="n"/>
     </row>
@@ -5148,17 +5398,19 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>Shooting at Skarsnik &amp; Gobbla</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr">
+          <t>Hate Dwarfs</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D109" s="8" t="n">
-        <v>5361</v>
-      </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5171,12 +5423,12 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>/faq/shooting (0.90)</t>
+          <t>/unit/dwarf (0.80)</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/shooting</t>
+          <t>https://6th.whfb.app/unit/dwarf</t>
         </is>
       </c>
       <c r="I109" s="11" t="n"/>
@@ -5190,16 +5442,18 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Skarsnik's Prodder</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr">
+          <t>Insatiable Appetite</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
-      </c>
-      <c r="D110" s="8" t="n">
-        <v>5375</v>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
@@ -5228,17 +5482,19 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>Skarsnik's Prodder</t>
-        </is>
-      </c>
-      <c r="C111" s="8" t="inlineStr">
+          <t>Moving Fanatics into Obstacles</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>Night Goblins &gt; Fanatics</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D111" s="8" t="n">
-        <v>5390</v>
-      </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5251,10 +5507,14 @@
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H111" s="10" t="inlineStr"/>
+          <t>/skirmishers/moving (0.90)</t>
+        </is>
+      </c>
+      <c r="H111" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/skirmishers/moving</t>
+        </is>
+      </c>
       <c r="I111" s="11" t="n"/>
       <c r="J111" s="11" t="n"/>
     </row>
@@ -5269,13 +5529,15 @@
           <t>Porko's Pigstikka</t>
         </is>
       </c>
-      <c r="C112" s="8" t="inlineStr">
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>Magic Weapons &gt; Porko's Pigstikka</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
-      </c>
-      <c r="D112" s="8" t="n">
-        <v>6646</v>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
@@ -5308,17 +5570,19 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>'Eadbuttin' 'At</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr">
+          <t>Shooting at Skarsnik &amp; Gobbla</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D113" s="8" t="n">
-        <v>7161</v>
-      </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5331,12 +5595,12 @@
       </c>
       <c r="G113" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/eadbutt (0.90)</t>
+          <t>/faq/shooting (0.90)</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/eadbutt</t>
+          <t>https://6th.whfb.app/faq/shooting</t>
         </is>
       </c>
       <c r="I113" s="11" t="n"/>
@@ -5350,17 +5614,19 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Warboss Umm's Best Big Boss 'At</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="inlineStr">
+          <t>Skarsnik's Prodder</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D114" s="8" t="n">
-        <v>7284</v>
-      </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5373,14 +5639,10 @@
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/warboss-umms-best-big-bosss-at (0.69)</t>
-        </is>
-      </c>
-      <c r="H114" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/warboss-umms-best-big-bosss-at</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H114" s="10" t="inlineStr"/>
       <c r="I114" s="11" t="n"/>
       <c r="J114" s="11" t="n"/>
     </row>
@@ -5392,16 +5654,18 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>Fungus Buster Brew</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr">
+          <t>Skarsnik's Prodder</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
-      </c>
-      <c r="D115" s="8" t="n">
-        <v>7588</v>
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
@@ -5433,13 +5697,15 @@
           <t>Staff of Badumm</t>
         </is>
       </c>
-      <c r="C116" s="8" t="inlineStr">
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>Arcane Items &gt; Unique Items &gt; Staff of Badumm</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
-      </c>
-      <c r="D116" s="8" t="n">
-        <v>7649</v>
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
@@ -5472,17 +5738,19 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>Hate Dwarfs</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
+          <t>The Blasted Banner</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>Grimgor Ironhide &gt; Bodyguard &gt; Da Immortulz &gt; The Blasted Banner</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D117" s="8" t="n">
-        <v>7826</v>
-      </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5495,12 +5763,12 @@
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>/unit/dwarf (0.80)</t>
+          <t>/magic-item/the-beast-banner (0.62)</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/dwarf</t>
+          <t>https://6th.whfb.app/magic-item/the-beast-banner</t>
         </is>
       </c>
       <c r="I117" s="11" t="n"/>
@@ -5514,17 +5782,19 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Giants Movement</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
+          <t>Warboss Umm's Best Big Boss 'At</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>Talismans &gt; Warboss Umm's Best Big Boss 'At</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D118" s="8" t="n">
-        <v>7884</v>
-      </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5537,12 +5807,12 @@
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (0.90)</t>
+          <t>/magic-item/warboss-umms-best-big-bosss-at (0.69)</t>
         </is>
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/giant</t>
+          <t>https://6th.whfb.app/magic-item/warboss-umms-best-big-bosss-at</t>
         </is>
       </c>
       <c r="I118" s="11" t="n"/>
@@ -5556,17 +5826,19 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>High Ranking</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
+          <t>Beastmaster</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>Master Moulder</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D119" s="8" t="n">
-        <v>203</v>
-      </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5579,10 +5851,14 @@
       </c>
       <c r="G119" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H119" s="10" t="inlineStr"/>
+          <t>/unit/beastmaster (1.00)</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
+        </is>
+      </c>
       <c r="I119" s="11" t="n"/>
       <c r="J119" s="11" t="n"/>
     </row>
@@ -5594,17 +5870,19 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
+          <t>Beastmaster</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>Master Mutator</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D120" s="8" t="n">
-        <v>512</v>
-      </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5617,12 +5895,12 @@
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>/unit/warlock-engineer (1.00)</t>
+          <t>/unit/beastmaster (1.00)</t>
         </is>
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
         </is>
       </c>
       <c r="I120" s="11" t="n"/>
@@ -5639,13 +5917,15 @@
           <t>Beastmaster</t>
         </is>
       </c>
-      <c r="C121" s="8" t="inlineStr">
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>Harbinger of Mutation</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
-      </c>
-      <c r="D121" s="8" t="n">
-        <v>635</v>
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
@@ -5678,17 +5958,19 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Plague Rats</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="inlineStr">
+          <t>Boneripper</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>Grey Seer Thanquol &amp; Boneripper</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D122" s="8" t="n">
-        <v>1141</v>
-      </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5701,12 +5983,12 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>/spell/plague (0.90)</t>
+          <t>/unit/boneripper (1.00)</t>
         </is>
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/spell/plague</t>
+          <t>https://6th.whfb.app/unit/boneripper</t>
         </is>
       </c>
       <c r="I122" s="11" t="n"/>
@@ -5720,17 +6002,19 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>Stands Alone</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
+          <t>Cursed Blade of Delerium</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>Magic Weapons &gt; Cursed Blade of Delerium</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D123" s="8" t="n">
-        <v>2392</v>
-      </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5743,10 +6027,14 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H123" s="10" t="inlineStr"/>
+          <t>/magic-item/cursed-blade-of-delirium (0.67)</t>
+        </is>
+      </c>
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/magic-item/cursed-blade-of-delirium</t>
+        </is>
+      </c>
       <c r="I123" s="11" t="n"/>
       <c r="J123" s="11" t="n"/>
     </row>
@@ -5758,17 +6046,19 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Horned Rat Incarnate</t>
-        </is>
-      </c>
-      <c r="C124" s="8" t="inlineStr">
+          <t>Daemonic Instability</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>Vermin Lord</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D124" s="8" t="n">
-        <v>2395</v>
-      </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5781,10 +6071,14 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H124" s="10" t="inlineStr"/>
+          <t>/special-rules/daemonic (0.90)</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/special-rules/daemonic</t>
+        </is>
+      </c>
       <c r="I124" s="11" t="n"/>
       <c r="J124" s="11" t="n"/>
     </row>
@@ -5799,13 +6093,15 @@
           <t>Doom Glaive</t>
         </is>
       </c>
-      <c r="C125" s="8" t="inlineStr">
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>Vermin Lord</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
-      </c>
-      <c r="D125" s="8" t="n">
-        <v>2398</v>
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
@@ -5834,17 +6130,19 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Instability</t>
-        </is>
-      </c>
-      <c r="C126" s="8" t="inlineStr">
+          <t>Doomwheel</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>Doomwheel</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D126" s="8" t="n">
-        <v>2432</v>
-      </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5857,12 +6155,12 @@
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/daemonic (0.90)</t>
+          <t>/movement/wheel (0.80)</t>
         </is>
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/daemonic</t>
+          <t>https://6th.whfb.app/movement/wheel</t>
         </is>
       </c>
       <c r="I126" s="11" t="n"/>
@@ -5876,17 +6174,19 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
-        </is>
-      </c>
-      <c r="C127" s="8" t="inlineStr">
+          <t>Festering Chantor</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>Festering Chantor</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D127" s="8" t="n">
-        <v>2443</v>
-      </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5899,10 +6199,14 @@
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H127" s="10" t="inlineStr"/>
+          <t>/unit/festering-chantor (1.00)</t>
+        </is>
+      </c>
+      <c r="H127" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/festering-chantor</t>
+        </is>
+      </c>
       <c r="I127" s="11" t="n"/>
       <c r="J127" s="11" t="n"/>
     </row>
@@ -5914,17 +6218,19 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Doomwheel</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="inlineStr">
+          <t>Harbinger of Mutation</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>Harbinger of Mutation</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D128" s="8" t="n">
-        <v>2511</v>
-      </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5937,12 +6243,12 @@
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>/movement/wheel (0.80)</t>
+          <t>/unit/harbinger (0.90)</t>
         </is>
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/movement/wheel</t>
+          <t>https://6th.whfb.app/unit/harbinger</t>
         </is>
       </c>
       <c r="I128" s="11" t="n"/>
@@ -5956,17 +6262,19 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>Boneripper</t>
-        </is>
-      </c>
-      <c r="C129" s="8" t="inlineStr">
+          <t>High Ranking</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>Grey Seer</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D129" s="8" t="n">
-        <v>2613</v>
-      </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -5979,14 +6287,10 @@
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>/unit/boneripper (1.00)</t>
-        </is>
-      </c>
-      <c r="H129" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/boneripper</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="inlineStr"/>
       <c r="I129" s="11" t="n"/>
       <c r="J129" s="11" t="n"/>
     </row>
@@ -5998,17 +6302,19 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="C130" s="8" t="inlineStr">
+          <t>Horned Rat Incarnate</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>Vermin Lord</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D130" s="8" t="n">
-        <v>3035</v>
-      </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6021,14 +6327,10 @@
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>/unit/warlock-engineer (1.00)</t>
-        </is>
-      </c>
-      <c r="H130" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H130" s="10" t="inlineStr"/>
       <c r="I130" s="11" t="n"/>
       <c r="J130" s="11" t="n"/>
     </row>
@@ -6040,17 +6342,19 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>Festering Chantor</t>
-        </is>
-      </c>
-      <c r="C131" s="8" t="inlineStr">
+          <t>Plague Rats</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>Rat Swarm &gt; Plague Rats</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D131" s="8" t="n">
-        <v>3232</v>
-      </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6063,12 +6367,12 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>/unit/festering-chantor (1.00)</t>
+          <t>/spell/plague (0.90)</t>
         </is>
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/festering-chantor</t>
+          <t>https://6th.whfb.app/spell/plague</t>
         </is>
       </c>
       <c r="I131" s="11" t="n"/>
@@ -6082,17 +6386,19 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
-        </is>
-      </c>
-      <c r="C132" s="8" t="inlineStr">
+          <t>Ratling Gun Misfire</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>Weapon Team &gt; Ratling Gun</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D132" s="8" t="n">
-        <v>3321</v>
-      </c>
       <c r="E132" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6105,12 +6411,12 @@
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
+          <t>/weapons/ratling-gun (0.90)</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
+          <t>https://6th.whfb.app/weapons/ratling-gun</t>
         </is>
       </c>
       <c r="I132" s="11" t="n"/>
@@ -6124,17 +6430,19 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
-        </is>
-      </c>
-      <c r="C133" s="8" t="inlineStr">
+          <t>Stands Alone</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>Vermin Lord</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D133" s="8" t="n">
-        <v>3414</v>
-      </c>
       <c r="E133" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6147,14 +6455,10 @@
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
-        </is>
-      </c>
-      <c r="H133" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H133" s="10" t="inlineStr"/>
       <c r="I133" s="11" t="n"/>
       <c r="J133" s="11" t="n"/>
     </row>
@@ -6166,17 +6470,19 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Harbinger of Mutation</t>
-        </is>
-      </c>
-      <c r="C134" s="8" t="inlineStr">
+          <t>Vermin Lord</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>Vermin Lord</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D134" s="8" t="n">
-        <v>3417</v>
-      </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6189,14 +6495,10 @@
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
-          <t>/unit/harbinger (0.90)</t>
-        </is>
-      </c>
-      <c r="H134" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/harbinger</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H134" s="10" t="inlineStr"/>
       <c r="I134" s="11" t="n"/>
       <c r="J134" s="11" t="n"/>
     </row>
@@ -6208,17 +6510,19 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>Cursed Blade of Delerium</t>
-        </is>
-      </c>
-      <c r="C135" s="8" t="inlineStr">
+          <t>Warlock Engineer</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>Warlock Engineer</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D135" s="8" t="n">
-        <v>3711</v>
-      </c>
       <c r="E135" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6231,12 +6535,12 @@
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/cursed-blade-of-delirium (0.67)</t>
+          <t>/unit/warlock-engineer (1.00)</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/cursed-blade-of-delirium</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I135" s="11" t="n"/>
@@ -6250,17 +6554,19 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Warpfire Thrower Misfire</t>
-        </is>
-      </c>
-      <c r="C136" s="8" t="inlineStr">
+          <t>Warlock Engineer</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>Warlock Master</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D136" s="8" t="n">
-        <v>4558</v>
-      </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6273,12 +6579,12 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>/weapons/warpfire-thrower (0.90)</t>
+          <t>/unit/warlock-engineer (1.00)</t>
         </is>
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/warpfire-thrower</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I136" s="11" t="n"/>
@@ -6292,17 +6598,19 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>Ratling Gun Misfire</t>
-        </is>
-      </c>
-      <c r="C137" s="8" t="inlineStr">
+          <t>Warpfire Thrower Misfire</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>Weapon Team &gt; Warpfire Thrower</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D137" s="8" t="n">
-        <v>4584</v>
-      </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6315,12 +6623,12 @@
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>/weapons/ratling-gun (0.90)</t>
+          <t>/weapons/warpfire-thrower (0.90)</t>
         </is>
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/ratling-gun</t>
+          <t>https://6th.whfb.app/weapons/warpfire-thrower</t>
         </is>
       </c>
       <c r="I137" s="11" t="n"/>
@@ -6334,17 +6642,19 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Electoral Banner</t>
-        </is>
-      </c>
-      <c r="C138" s="8" t="inlineStr">
+          <t>Athandin</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>Valten, Exalted of Sigmar &gt; Athandin</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
         <is>
           <t>The Empire.cat</t>
         </is>
       </c>
-      <c r="D138" s="8" t="n">
-        <v>15</v>
-      </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6357,10 +6667,14 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H138" s="10" t="inlineStr"/>
+          <t>/special-rules/althandin (0.66)</t>
+        </is>
+      </c>
+      <c r="H138" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/special-rules/althandin</t>
+        </is>
+      </c>
       <c r="I138" s="11" t="n"/>
       <c r="J138" s="11" t="n"/>
     </row>
@@ -6372,17 +6686,19 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>Fusilade</t>
-        </is>
-      </c>
-      <c r="C139" s="8" t="inlineStr">
+          <t>Charging with the Steam Tank</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>Steam Tank</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="inlineStr">
         <is>
           <t>The Empire.cat</t>
         </is>
       </c>
-      <c r="D139" s="8" t="n">
-        <v>4417</v>
-      </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6395,12 +6711,12 @@
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/fusillade (0.66)</t>
+          <t>/movement/charging (0.90)</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/fusillade</t>
+          <t>https://6th.whfb.app/movement/charging</t>
         </is>
       </c>
       <c r="I139" s="11" t="n"/>
@@ -6414,17 +6730,19 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Steam Points</t>
-        </is>
-      </c>
-      <c r="C140" s="8" t="inlineStr">
+          <t>Electoral Banner</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
         <is>
           <t>The Empire.cat</t>
         </is>
       </c>
-      <c r="D140" s="8" t="n">
-        <v>5281</v>
-      </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6437,14 +6755,10 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/building-up-steam-points (0.80)</t>
-        </is>
-      </c>
-      <c r="H140" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/special-rules/building-up-steam-points</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="inlineStr"/>
       <c r="I140" s="11" t="n"/>
       <c r="J140" s="11" t="n"/>
     </row>
@@ -6456,17 +6770,19 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>Shooting with the Steam Tank</t>
-        </is>
-      </c>
-      <c r="C141" s="8" t="inlineStr">
+          <t>Fusilade</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>Pistoliers</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
         <is>
           <t>The Empire.cat</t>
         </is>
       </c>
-      <c r="D141" s="8" t="n">
-        <v>5301</v>
-      </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6479,12 +6795,12 @@
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>/faq/shooting (0.90)</t>
+          <t>/special-rules/fusillade (0.66)</t>
         </is>
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/shooting</t>
+          <t>https://6th.whfb.app/special-rules/fusillade</t>
         </is>
       </c>
       <c r="I141" s="11" t="n"/>
@@ -6498,17 +6814,19 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Charging with the Steam Tank</t>
-        </is>
-      </c>
-      <c r="C142" s="8" t="inlineStr">
+          <t>Helm of the Skavenslayer</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>Magic Armour &gt; Magic Armour &gt; Helm of the Skavenslayer</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
         <is>
           <t>The Empire.cat</t>
         </is>
       </c>
-      <c r="D142" s="8" t="n">
-        <v>5312</v>
-      </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6521,12 +6839,12 @@
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>/movement/charging (0.90)</t>
+          <t>/army/skaven (0.80)</t>
         </is>
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/movement/charging</t>
+          <t>https://6th.whfb.app/army/skaven</t>
         </is>
       </c>
       <c r="I142" s="11" t="n"/>
@@ -6540,17 +6858,19 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>Shooting at the Steam Tank</t>
-        </is>
-      </c>
-      <c r="C143" s="8" t="inlineStr">
+          <t>Parent and Detachment Units</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
         <is>
           <t>The Empire.cat</t>
         </is>
       </c>
-      <c r="D143" s="8" t="n">
-        <v>5332</v>
-      </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6563,12 +6883,12 @@
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>/faq/shooting (0.90)</t>
+          <t>/warhammer-glossary/unit-warhammer-glossary (0.80)</t>
         </is>
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/shooting</t>
+          <t>https://6th.whfb.app/warhammer-glossary/unit-warhammer-glossary</t>
         </is>
       </c>
       <c r="I143" s="11" t="n"/>
@@ -6582,17 +6902,19 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Athandin</t>
-        </is>
-      </c>
-      <c r="C144" s="8" t="inlineStr">
+          <t>Shooting at the Steam Tank</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>Steam Tank</t>
+        </is>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
         <is>
           <t>The Empire.cat</t>
         </is>
       </c>
-      <c r="D144" s="8" t="n">
-        <v>5686</v>
-      </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6605,12 +6927,12 @@
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/althandin (0.66)</t>
+          <t>/faq/shooting (0.90)</t>
         </is>
       </c>
       <c r="H144" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/althandin</t>
+          <t>https://6th.whfb.app/faq/shooting</t>
         </is>
       </c>
       <c r="I144" s="11" t="n"/>
@@ -6624,17 +6946,19 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>Parent and Detachment Units</t>
-        </is>
-      </c>
-      <c r="C145" s="8" t="inlineStr">
+          <t>Shooting with the Steam Tank</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>Steam Tank</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
         <is>
           <t>The Empire.cat</t>
         </is>
       </c>
-      <c r="D145" s="8" t="n">
-        <v>5853</v>
-      </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6647,12 +6971,12 @@
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>/warhammer-glossary/unit-warhammer-glossary (0.80)</t>
+          <t>/faq/shooting (0.90)</t>
         </is>
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/warhammer-glossary/unit-warhammer-glossary</t>
+          <t>https://6th.whfb.app/faq/shooting</t>
         </is>
       </c>
       <c r="I145" s="11" t="n"/>
@@ -6666,17 +6990,19 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Helm of the Skavenslayer</t>
-        </is>
-      </c>
-      <c r="C146" s="8" t="inlineStr">
+          <t>Steam Points</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>Steam Tank</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
         <is>
           <t>The Empire.cat</t>
         </is>
       </c>
-      <c r="D146" s="8" t="n">
-        <v>6384</v>
-      </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6689,12 +7015,12 @@
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>/army/skaven (0.80)</t>
+          <t>/special-rules/building-up-steam-points (0.80)</t>
         </is>
       </c>
       <c r="H146" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/army/skaven</t>
+          <t>https://6th.whfb.app/special-rules/building-up-steam-points</t>
         </is>
       </c>
       <c r="I146" s="11" t="n"/>
@@ -6711,13 +7037,15 @@
           <t>Armour of Eternity</t>
         </is>
       </c>
-      <c r="C147" s="8" t="inlineStr">
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>Magic Armour &gt; Magic Armour</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
         <is>
           <t>Tomb Kings.cat</t>
         </is>
-      </c>
-      <c r="D147" s="8" t="n">
-        <v>1719</v>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
@@ -6753,13 +7081,15 @@
           <t>Ethereal Steeds</t>
         </is>
       </c>
-      <c r="C148" s="8" t="inlineStr">
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Black Knights</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="inlineStr">
         <is>
           <t>Vampire Counts.cat</t>
         </is>
-      </c>
-      <c r="D148" s="8" t="n">
-        <v>3623</v>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
@@ -6795,13 +7125,15 @@
           <t>Fly</t>
         </is>
       </c>
-      <c r="C149" s="8" t="inlineStr">
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D149" s="8" t="inlineStr">
         <is>
           <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
-      </c>
-      <c r="D149" s="8" t="n">
-        <v>701</v>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
@@ -6837,13 +7169,15 @@
           <t>Stone Thrower</t>
         </is>
       </c>
-      <c r="C150" s="8" t="inlineStr">
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>shared; nothing links to it</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
         <is>
           <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
-      </c>
-      <c r="D150" s="8" t="n">
-        <v>815</v>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
@@ -6876,17 +7210,19 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>Gwytherc's Horn</t>
-        </is>
-      </c>
-      <c r="C151" s="8" t="inlineStr">
+          <t>Alter Kindred</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>Wood Elf Kindred &gt; Alter Kindred</t>
+        </is>
+      </c>
+      <c r="D151" s="8" t="inlineStr">
         <is>
           <t>Wood Elves.cat</t>
         </is>
       </c>
-      <c r="D151" s="8" t="n">
-        <v>3252</v>
-      </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6899,12 +7235,12 @@
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/gwytheres-horn (0.65)</t>
+          <t>/magic-item/the-alter-kindreds (0.80)</t>
         </is>
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/gwytheres-horn</t>
+          <t>https://6th.whfb.app/magic-item/the-alter-kindreds</t>
         </is>
       </c>
       <c r="I151" s="11" t="n"/>
@@ -6918,17 +7254,19 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Stone of the Crystal Mere</t>
-        </is>
-      </c>
-      <c r="C152" s="8" t="inlineStr">
+          <t>Gwytherc's Horn</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>Enchanted Items &gt; Gwytherc's Horn</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
         <is>
           <t>Wood Elves.cat</t>
         </is>
       </c>
-      <c r="D152" s="8" t="n">
-        <v>3341</v>
-      </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6941,12 +7279,12 @@
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/stone-of-the-crystal-merex (0.90)</t>
+          <t>/magic-item/gwytheres-horn (0.65)</t>
         </is>
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/stone-of-the-crystal-merex</t>
+          <t>https://6th.whfb.app/magic-item/gwytheres-horn</t>
         </is>
       </c>
       <c r="I152" s="11" t="n"/>
@@ -6960,17 +7298,19 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>Alter Kindred</t>
-        </is>
-      </c>
-      <c r="C153" s="8" t="inlineStr">
+          <t>Stone of the Crystal Mere</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>Talismans &gt; Stone of the Crystal Mere</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="inlineStr">
         <is>
           <t>Wood Elves.cat</t>
         </is>
       </c>
-      <c r="D153" s="8" t="n">
-        <v>3961</v>
-      </c>
       <c r="E153" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
@@ -6983,12 +7323,12 @@
       </c>
       <c r="G153" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/the-alter-kindreds (0.80)</t>
+          <t>/magic-item/stone-of-the-crystal-merex (0.90)</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/the-alter-kindreds</t>
+          <t>https://6th.whfb.app/magic-item/stone-of-the-crystal-merex</t>
         </is>
       </c>
       <c r="I153" s="11" t="n"/>
@@ -7005,13 +7345,15 @@
           <t>Strangle-Roots</t>
         </is>
       </c>
-      <c r="C154" s="8" t="inlineStr">
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Treeman, Treeman Ancient</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
         <is>
           <t>Wood Elves.cat</t>
         </is>
-      </c>
-      <c r="D154" s="8" t="n">
-        <v>4159</v>
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
@@ -7040,17 +7382,19 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Stoicism</t>
-        </is>
-      </c>
-      <c r="C155" s="8" t="inlineStr">
+          <t>Virtue of Audacity</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D155" s="8" t="n">
-        <v>2331</v>
-      </c>
       <c r="E155" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7058,17 +7402,17 @@
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G155" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: 30</t>
         </is>
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
         </is>
       </c>
       <c r="I155" s="11" t="n"/>
@@ -7082,17 +7426,19 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Noble Disdain</t>
-        </is>
-      </c>
-      <c r="C156" s="8" t="inlineStr">
+          <t>Virtue of Audacity</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D156" s="8" t="n">
-        <v>2541</v>
-      </c>
       <c r="E156" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7100,17 +7446,17 @@
       </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue: 90</t>
         </is>
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 30</t>
         </is>
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
         </is>
       </c>
       <c r="I156" s="11" t="n"/>
@@ -7124,17 +7470,19 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Purity</t>
-        </is>
-      </c>
-      <c r="C157" s="8" t="inlineStr">
+          <t>Virtue of Confidence</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D157" s="8" t="n">
-        <v>2576</v>
-      </c>
       <c r="E157" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7142,17 +7490,17 @@
       </c>
       <c r="F157" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue: 50</t>
         </is>
       </c>
       <c r="G157" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
         </is>
       </c>
       <c r="I157" s="11" t="n"/>
@@ -7166,17 +7514,19 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
-        </is>
-      </c>
-      <c r="C158" s="8" t="inlineStr">
+          <t>Virtue of Confidence</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D158" s="8" t="n">
-        <v>2646</v>
-      </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7184,17 +7534,17 @@
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 30</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H158" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
         </is>
       </c>
       <c r="I158" s="11" t="n"/>
@@ -7208,17 +7558,19 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Audacity</t>
-        </is>
-      </c>
-      <c r="C159" s="8" t="inlineStr">
+          <t>Virtue of Confidence</t>
+        </is>
+      </c>
+      <c r="C159" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D159" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D159" s="8" t="n">
-        <v>2751</v>
-      </c>
       <c r="E159" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7226,17 +7578,17 @@
       </c>
       <c r="F159" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 75</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>wiki: 30</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
         </is>
       </c>
       <c r="I159" s="11" t="n"/>
@@ -7250,17 +7602,19 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Audacity</t>
-        </is>
-      </c>
-      <c r="C160" s="8" t="inlineStr">
+          <t>Virtue of Discipline</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D160" s="8" t="n">
-        <v>2793</v>
-      </c>
       <c r="E160" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7273,12 +7627,12 @@
       </c>
       <c r="G160" s="9" t="inlineStr">
         <is>
-          <t>wiki: 30</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H160" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I160" s="11" t="n"/>
@@ -7292,17 +7646,19 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
-        </is>
-      </c>
-      <c r="C161" s="8" t="inlineStr">
+          <t>Virtue of Discipline</t>
+        </is>
+      </c>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D161" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D161" s="8" t="n">
-        <v>2835</v>
-      </c>
       <c r="E161" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7310,17 +7666,17 @@
       </c>
       <c r="F161" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue: 30</t>
         </is>
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I161" s="11" t="n"/>
@@ -7334,17 +7690,19 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
-        </is>
-      </c>
-      <c r="C162" s="8" t="inlineStr">
+          <t>Virtue of Discipline</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D162" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D162" s="8" t="n">
-        <v>2870</v>
-      </c>
       <c r="E162" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7352,17 +7710,17 @@
       </c>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 45</t>
         </is>
       </c>
       <c r="G162" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I162" s="11" t="n"/>
@@ -7376,17 +7734,19 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
-        </is>
-      </c>
-      <c r="C163" s="8" t="inlineStr">
+          <t>Virtue of Discipline</t>
+        </is>
+      </c>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D163" s="8" t="n">
-        <v>2912</v>
-      </c>
       <c r="E163" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7394,17 +7754,17 @@
       </c>
       <c r="F163" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I163" s="11" t="n"/>
@@ -7421,14 +7781,16 @@
           <t>Virtue of Discipline</t>
         </is>
       </c>
-      <c r="C164" s="8" t="inlineStr">
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D164" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D164" s="8" t="n">
-        <v>2954</v>
-      </c>
       <c r="E164" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7436,7 +7798,7 @@
       </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue: 75</t>
         </is>
       </c>
       <c r="G164" s="9" t="inlineStr">
@@ -7460,17 +7822,19 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
-        </is>
-      </c>
-      <c r="C165" s="8" t="inlineStr">
+          <t>Virtue of Empathy</t>
+        </is>
+      </c>
+      <c r="C165" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D165" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D165" s="8" t="n">
-        <v>2996</v>
-      </c>
       <c r="E165" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7483,12 +7847,12 @@
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I165" s="11" t="n"/>
@@ -7502,17 +7866,19 @@
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
-        </is>
-      </c>
-      <c r="C166" s="8" t="inlineStr">
+          <t>Virtue of Empathy</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D166" s="8" t="n">
-        <v>3031</v>
-      </c>
       <c r="E166" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7520,17 +7886,17 @@
       </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 45</t>
+          <t>catalogue: 20</t>
         </is>
       </c>
       <c r="G166" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H166" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I166" s="11" t="n"/>
@@ -7544,17 +7910,19 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
-        </is>
-      </c>
-      <c r="C167" s="8" t="inlineStr">
+          <t>Virtue of Empathy</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D167" s="8" t="n">
-        <v>3066</v>
-      </c>
       <c r="E167" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7562,17 +7930,17 @@
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G167" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I167" s="11" t="n"/>
@@ -7586,17 +7954,19 @@
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
-        </is>
-      </c>
-      <c r="C168" s="8" t="inlineStr">
+          <t>Virtue of Empathy</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D168" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D168" s="8" t="n">
-        <v>3108</v>
-      </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7604,17 +7974,17 @@
       </c>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G168" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H168" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I168" s="11" t="n"/>
@@ -7631,14 +8001,16 @@
           <t>Virtue of Empathy</t>
         </is>
       </c>
-      <c r="C169" s="8" t="inlineStr">
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D169" s="8" t="n">
-        <v>3150</v>
-      </c>
       <c r="E169" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7646,7 +8018,7 @@
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 20</t>
+          <t>catalogue: 50</t>
         </is>
       </c>
       <c r="G169" s="9" t="inlineStr">
@@ -7673,14 +8045,16 @@
           <t>Virtue of Empathy</t>
         </is>
       </c>
-      <c r="C170" s="8" t="inlineStr">
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D170" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D170" s="8" t="n">
-        <v>3220</v>
-      </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7688,7 +8062,7 @@
       </c>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G170" s="9" t="inlineStr">
@@ -7715,14 +8089,16 @@
           <t>Virtue of Empathy</t>
         </is>
       </c>
-      <c r="C171" s="8" t="inlineStr">
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D171" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D171" s="8" t="n">
-        <v>3255</v>
-      </c>
       <c r="E171" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7730,7 +8106,7 @@
       </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 70</t>
         </is>
       </c>
       <c r="G171" s="9" t="inlineStr">
@@ -7757,14 +8133,16 @@
           <t>Virtue of Empathy</t>
         </is>
       </c>
-      <c r="C172" s="8" t="inlineStr">
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D172" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D172" s="8" t="n">
-        <v>3297</v>
-      </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7772,7 +8150,7 @@
       </c>
       <c r="F172" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G172" s="9" t="inlineStr">
@@ -7799,14 +8177,16 @@
           <t>Virtue of Empathy</t>
         </is>
       </c>
-      <c r="C173" s="8" t="inlineStr">
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D173" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D173" s="8" t="n">
-        <v>3332</v>
-      </c>
       <c r="E173" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7814,7 +8194,7 @@
       </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 90</t>
         </is>
       </c>
       <c r="G173" s="9" t="inlineStr">
@@ -7838,17 +8218,19 @@
       </c>
       <c r="B174" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
-        </is>
-      </c>
-      <c r="C174" s="8" t="inlineStr">
+          <t>Virtue of Heroism</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D174" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D174" s="8" t="n">
-        <v>3374</v>
-      </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7856,17 +8238,17 @@
       </c>
       <c r="F174" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 70</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G174" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 40</t>
         </is>
       </c>
       <c r="H174" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-heroism</t>
         </is>
       </c>
       <c r="I174" s="11" t="n"/>
@@ -7880,17 +8262,19 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
-        </is>
-      </c>
-      <c r="C175" s="8" t="inlineStr">
+          <t>Virtue of Knightly Temper</t>
+        </is>
+      </c>
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D175" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D175" s="8" t="n">
-        <v>3416</v>
-      </c>
       <c r="E175" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7903,12 +8287,12 @@
       </c>
       <c r="G175" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 40</t>
         </is>
       </c>
       <c r="H175" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-knightly-temper</t>
         </is>
       </c>
       <c r="I175" s="11" t="n"/>
@@ -7922,17 +8306,19 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
-        </is>
-      </c>
-      <c r="C176" s="8" t="inlineStr">
+          <t>Virtue of Noble Disdain</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D176" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D176" s="8" t="n">
-        <v>3458</v>
-      </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7940,17 +8326,17 @@
       </c>
       <c r="F176" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G176" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H176" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
         </is>
       </c>
       <c r="I176" s="11" t="n"/>
@@ -7964,17 +8350,19 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Knightly Temper</t>
-        </is>
-      </c>
-      <c r="C177" s="8" t="inlineStr">
+          <t>Virtue of Noble Disdain</t>
+        </is>
+      </c>
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D177" s="8" t="n">
-        <v>3500</v>
-      </c>
       <c r="E177" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -7982,17 +8370,17 @@
       </c>
       <c r="F177" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G177" s="9" t="inlineStr">
         <is>
-          <t>wiki: 40</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H177" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-knightly-temper</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
         </is>
       </c>
       <c r="I177" s="11" t="n"/>
@@ -8009,14 +8397,16 @@
           <t>Virtue of Noble Disdain</t>
         </is>
       </c>
-      <c r="C178" s="8" t="inlineStr">
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D178" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D178" s="8" t="n">
-        <v>3542</v>
-      </c>
       <c r="E178" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -8024,7 +8414,7 @@
       </c>
       <c r="F178" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G178" s="9" t="inlineStr">
@@ -8051,14 +8441,16 @@
           <t>Virtue of Noble Disdain</t>
         </is>
       </c>
-      <c r="C179" s="8" t="inlineStr">
+      <c r="C179" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D179" s="8" t="n">
-        <v>3584</v>
-      </c>
       <c r="E179" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -8066,7 +8458,7 @@
       </c>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G179" s="9" t="inlineStr">
@@ -8090,17 +8482,19 @@
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Noble Disdain</t>
-        </is>
-      </c>
-      <c r="C180" s="8" t="inlineStr">
+          <t>Virtue of Purity</t>
+        </is>
+      </c>
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D180" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D180" s="8" t="n">
-        <v>3626</v>
-      </c>
       <c r="E180" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -8108,7 +8502,7 @@
       </c>
       <c r="F180" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G180" s="9" t="inlineStr">
@@ -8118,7 +8512,7 @@
       </c>
       <c r="H180" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
         </is>
       </c>
       <c r="I180" s="11" t="n"/>
@@ -8135,13 +8529,15 @@
           <t>Virtue of Purity</t>
         </is>
       </c>
-      <c r="C181" s="8" t="inlineStr">
+      <c r="C181" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
-      </c>
-      <c r="D181" s="8" t="n">
-        <v>3703</v>
       </c>
       <c r="E181" s="9" t="inlineStr">
         <is>
@@ -8177,13 +8573,15 @@
           <t>Virtue of Purity</t>
         </is>
       </c>
-      <c r="C182" s="8" t="inlineStr">
+      <c r="C182" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D182" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
-      </c>
-      <c r="D182" s="8" t="n">
-        <v>3745</v>
       </c>
       <c r="E182" s="9" t="inlineStr">
         <is>
@@ -8219,13 +8617,15 @@
           <t>Virtue of Purity</t>
         </is>
       </c>
-      <c r="C183" s="8" t="inlineStr">
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D183" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
-      </c>
-      <c r="D183" s="8" t="n">
-        <v>3787</v>
       </c>
       <c r="E183" s="9" t="inlineStr">
         <is>
@@ -8258,17 +8658,19 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Heroism</t>
-        </is>
-      </c>
-      <c r="C184" s="8" t="inlineStr">
+          <t>Virtue of Stoicism</t>
+        </is>
+      </c>
+      <c r="C184" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D184" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D184" s="8" t="n">
-        <v>3864</v>
-      </c>
       <c r="E184" s="9" t="inlineStr">
         <is>
           <t>catalogue and wiki disagree on cost</t>
@@ -8281,12 +8683,12 @@
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>wiki: 40</t>
+          <t>wiki: 35</t>
         </is>
       </c>
       <c r="H184" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-heroism</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
         </is>
       </c>
       <c r="I184" s="11" t="n"/>
@@ -8303,13 +8705,15 @@
           <t>Virtue of Stoicism</t>
         </is>
       </c>
-      <c r="C185" s="8" t="inlineStr">
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D185" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
-      </c>
-      <c r="D185" s="8" t="n">
-        <v>3906</v>
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
@@ -8345,13 +8749,15 @@
           <t>Virtue of the Ideal</t>
         </is>
       </c>
-      <c r="C186" s="8" t="inlineStr">
+      <c r="C186" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D186" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
-      </c>
-      <c r="D186" s="8" t="n">
-        <v>3941</v>
       </c>
       <c r="E186" s="9" t="inlineStr">
         <is>
@@ -8387,13 +8793,15 @@
           <t>Virtue of the Impetuous Knight</t>
         </is>
       </c>
-      <c r="C187" s="8" t="inlineStr">
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D187" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
-      </c>
-      <c r="D187" s="8" t="n">
-        <v>3983</v>
       </c>
       <c r="E187" s="9" t="inlineStr">
         <is>
@@ -8429,13 +8837,15 @@
           <t>Virtue of the Joust</t>
         </is>
       </c>
-      <c r="C188" s="8" t="inlineStr">
+      <c r="C188" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D188" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
-      </c>
-      <c r="D188" s="8" t="n">
-        <v>4027</v>
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
@@ -8471,13 +8881,15 @@
           <t>Virtue of the Joust</t>
         </is>
       </c>
-      <c r="C189" s="8" t="inlineStr">
+      <c r="C189" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D189" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
-      </c>
-      <c r="D189" s="8" t="n">
-        <v>4064</v>
       </c>
       <c r="E189" s="9" t="inlineStr">
         <is>
@@ -8513,13 +8925,15 @@
           <t>Virtue of the Joust</t>
         </is>
       </c>
-      <c r="C190" s="8" t="inlineStr">
+      <c r="C190" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
-      </c>
-      <c r="D190" s="8" t="n">
-        <v>4108</v>
       </c>
       <c r="E190" s="9" t="inlineStr">
         <is>
@@ -8555,13 +8969,15 @@
           <t>Virtue of the Penitent</t>
         </is>
       </c>
-      <c r="C191" s="8" t="inlineStr">
+      <c r="C191" s="9" t="inlineStr">
+        <is>
+          <t>Chivalric Virtues</t>
+        </is>
+      </c>
+      <c r="D191" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
-      </c>
-      <c r="D191" s="8" t="n">
-        <v>4152</v>
       </c>
       <c r="E191" s="9" t="inlineStr">
         <is>
@@ -8597,13 +9013,15 @@
           <t>Power Stone</t>
         </is>
       </c>
-      <c r="C192" s="8" t="inlineStr">
+      <c r="C192" s="9" t="inlineStr">
+        <is>
+          <t>Arcane Items &gt; Unique Items</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="inlineStr">
         <is>
           <t>High Elves.cat</t>
         </is>
-      </c>
-      <c r="D192" s="8" t="n">
-        <v>3347</v>
       </c>
       <c r="E192" s="9" t="inlineStr">
         <is>
@@ -8639,13 +9057,15 @@
           <t>Pure of Heart</t>
         </is>
       </c>
-      <c r="C193" s="8" t="inlineStr">
+      <c r="C193" s="9" t="inlineStr">
+        <is>
+          <t>Honours</t>
+        </is>
+      </c>
+      <c r="D193" s="8" t="inlineStr">
         <is>
           <t>High Elves.cat</t>
         </is>
-      </c>
-      <c r="D193" s="8" t="n">
-        <v>3536</v>
       </c>
       <c r="E193" s="9" t="inlineStr">
         <is>
@@ -8681,13 +9101,15 @@
           <t>Ghal Maraz</t>
         </is>
       </c>
-      <c r="C194" s="8" t="inlineStr">
+      <c r="C194" s="9" t="inlineStr">
+        <is>
+          <t>Emperor Karl Franz &gt; Weapon</t>
+        </is>
+      </c>
+      <c r="D194" s="8" t="inlineStr">
         <is>
           <t>The Empire.cat</t>
         </is>
-      </c>
-      <c r="D194" s="8" t="n">
-        <v>5801</v>
       </c>
       <c r="E194" s="9" t="inlineStr">
         <is>
@@ -8723,13 +9145,15 @@
           <t>Horn of the Wild Hunt</t>
         </is>
       </c>
-      <c r="C195" s="8" t="inlineStr">
+      <c r="C195" s="9" t="inlineStr">
+        <is>
+          <t>Orion, the King in the Woods</t>
+        </is>
+      </c>
+      <c r="D195" s="8" t="inlineStr">
         <is>
           <t>Wood Elves.cat</t>
         </is>
-      </c>
-      <c r="D195" s="8" t="n">
-        <v>1957</v>
       </c>
       <c r="E195" s="9" t="inlineStr">
         <is>
@@ -8762,20 +9186,22 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>Villein</t>
-        </is>
-      </c>
-      <c r="C196" s="8" t="inlineStr">
+          <t>Pegasus</t>
+        </is>
+      </c>
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>Pegasus Knights &gt; Pegasus Knight</t>
+        </is>
+      </c>
+      <c r="D196" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D196" s="8" t="n">
-        <v>793</v>
-      </c>
       <c r="E196" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F196" s="9" t="inlineStr">
@@ -8785,12 +9211,12 @@
       </c>
       <c r="G196" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;2, A 1-&gt;2</t>
+          <t>wiki: Ld 7-&gt;6</t>
         </is>
       </c>
       <c r="H196" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/villein</t>
+          <t>https://6th.whfb.app/unit/pegasus</t>
         </is>
       </c>
       <c r="I196" s="11" t="n"/>
@@ -8804,20 +9230,22 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>Pegasus</t>
-        </is>
-      </c>
-      <c r="C197" s="8" t="inlineStr">
+          <t>Villein</t>
+        </is>
+      </c>
+      <c r="C197" s="9" t="inlineStr">
+        <is>
+          <t>Peasant Bowmen &gt; Command &gt; Villein</t>
+        </is>
+      </c>
+      <c r="D197" s="8" t="inlineStr">
         <is>
           <t>Bretonnians.cat</t>
         </is>
       </c>
-      <c r="D197" s="8" t="n">
-        <v>1179</v>
-      </c>
       <c r="E197" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F197" s="9" t="inlineStr">
@@ -8827,12 +9255,12 @@
       </c>
       <c r="G197" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 7-&gt;6</t>
+          <t>wiki: WS 3-&gt;2, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H197" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/pegasus</t>
+          <t>https://6th.whfb.app/unit/villein</t>
         </is>
       </c>
       <c r="I197" s="11" t="n"/>
@@ -8846,20 +9274,22 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarf Sorcerer</t>
-        </is>
-      </c>
-      <c r="C198" s="8" t="inlineStr">
+          <t>Bull Centaur Hero</t>
+        </is>
+      </c>
+      <c r="C198" s="9" t="inlineStr">
+        <is>
+          <t>Bull Centaur Hero</t>
+        </is>
+      </c>
+      <c r="D198" s="8" t="inlineStr">
         <is>
           <t>Chaos Dwarves.cat</t>
         </is>
       </c>
-      <c r="D198" s="8" t="n">
-        <v>107</v>
-      </c>
       <c r="E198" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F198" s="9" t="inlineStr">
@@ -8869,12 +9299,12 @@
       </c>
       <c r="G198" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 4-&gt;3, T 5-&gt;4, W 3-&gt;2, I 1-&gt;2, Ld 10-&gt;9</t>
+          <t>wiki: T 4-&gt;5</t>
         </is>
       </c>
       <c r="H198" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/chaos-dwarf-sorcerer</t>
+          <t>https://6th.whfb.app/unit/bull-centaur-hero</t>
         </is>
       </c>
       <c r="I198" s="11" t="n"/>
@@ -8888,20 +9318,22 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>Bull Centaur Hero</t>
-        </is>
-      </c>
-      <c r="C199" s="8" t="inlineStr">
+          <t>Chaos Dwarf Sorcerer</t>
+        </is>
+      </c>
+      <c r="C199" s="9" t="inlineStr">
+        <is>
+          <t>Sorcerer Lord</t>
+        </is>
+      </c>
+      <c r="D199" s="8" t="inlineStr">
         <is>
           <t>Chaos Dwarves.cat</t>
         </is>
       </c>
-      <c r="D199" s="8" t="n">
-        <v>541</v>
-      </c>
       <c r="E199" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F199" s="9" t="inlineStr">
@@ -8911,12 +9343,12 @@
       </c>
       <c r="G199" s="9" t="inlineStr">
         <is>
-          <t>wiki: T 4-&gt;5</t>
+          <t>wiki: S 4-&gt;3, T 5-&gt;4, W 3-&gt;2, I 1-&gt;2, Ld 10-&gt;9</t>
         </is>
       </c>
       <c r="H199" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bull-centaur-hero</t>
+          <t>https://6th.whfb.app/unit/chaos-dwarf-sorcerer</t>
         </is>
       </c>
       <c r="I199" s="11" t="n"/>
@@ -8933,13 +9365,15 @@
           <t>Hobgoblin Crew</t>
         </is>
       </c>
-      <c r="C200" s="8" t="inlineStr">
+      <c r="C200" s="9" t="inlineStr">
+        <is>
+          <t>Hobgoblin Bolt Thrower &gt; Hobgoblin Bolt Thrower</t>
+        </is>
+      </c>
+      <c r="D200" s="8" t="inlineStr">
         <is>
           <t>Chaos Dwarves.cat</t>
         </is>
-      </c>
-      <c r="D200" s="8" t="n">
-        <v>1035</v>
       </c>
       <c r="E200" s="9" t="inlineStr">
         <is>
@@ -8975,13 +9409,15 @@
           <t>Bloodletter</t>
         </is>
       </c>
-      <c r="C201" s="8" t="inlineStr">
+      <c r="C201" s="9" t="inlineStr">
+        <is>
+          <t>Bloodletters &gt; Bloodletters</t>
+        </is>
+      </c>
+      <c r="D201" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
-      </c>
-      <c r="D201" s="8" t="n">
-        <v>885</v>
       </c>
       <c r="E201" s="9" t="inlineStr">
         <is>
@@ -9014,17 +9450,19 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>Horror</t>
-        </is>
-      </c>
-      <c r="C202" s="8" t="inlineStr">
+          <t>Daemonette</t>
+        </is>
+      </c>
+      <c r="C202" s="9" t="inlineStr">
+        <is>
+          <t>Daemonettes &gt; Daemonettes</t>
+        </is>
+      </c>
+      <c r="D202" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
       </c>
-      <c r="D202" s="8" t="n">
-        <v>1010</v>
-      </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -9042,7 +9480,7 @@
       </c>
       <c r="H202" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/horror</t>
+          <t>https://6th.whfb.app/unit/daemonette</t>
         </is>
       </c>
       <c r="I202" s="11" t="n"/>
@@ -9056,17 +9494,19 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>Plaguebearer</t>
-        </is>
-      </c>
-      <c r="C203" s="8" t="inlineStr">
+          <t>Daemonette</t>
+        </is>
+      </c>
+      <c r="C203" s="9" t="inlineStr">
+        <is>
+          <t>Mounted Daemonettes &gt; Mounted Daemonette</t>
+        </is>
+      </c>
+      <c r="D203" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
       </c>
-      <c r="D203" s="8" t="n">
-        <v>1113</v>
-      </c>
       <c r="E203" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -9084,7 +9524,7 @@
       </c>
       <c r="H203" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/plaguebearer</t>
+          <t>https://6th.whfb.app/unit/daemonette</t>
         </is>
       </c>
       <c r="I203" s="11" t="n"/>
@@ -9098,17 +9538,19 @@
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t>Daemonette</t>
-        </is>
-      </c>
-      <c r="C204" s="8" t="inlineStr">
+          <t>Flamer</t>
+        </is>
+      </c>
+      <c r="C204" s="9" t="inlineStr">
+        <is>
+          <t>Flamers &gt; Flamer</t>
+        </is>
+      </c>
+      <c r="D204" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
       </c>
-      <c r="D204" s="8" t="n">
-        <v>1208</v>
-      </c>
       <c r="E204" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -9126,7 +9568,7 @@
       </c>
       <c r="H204" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/daemonette</t>
+          <t>https://6th.whfb.app/unit/flamer</t>
         </is>
       </c>
       <c r="I204" s="11" t="n"/>
@@ -9140,17 +9582,19 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>Daemonette</t>
-        </is>
-      </c>
-      <c r="C205" s="8" t="inlineStr">
+          <t>Flesh Hound</t>
+        </is>
+      </c>
+      <c r="C205" s="9" t="inlineStr">
+        <is>
+          <t>Flesh Hounds &gt; Flesh Hounds</t>
+        </is>
+      </c>
+      <c r="D205" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
       </c>
-      <c r="D205" s="8" t="n">
-        <v>1312</v>
-      </c>
       <c r="E205" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -9168,7 +9612,7 @@
       </c>
       <c r="H205" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/daemonette</t>
+          <t>https://6th.whfb.app/unit/flesh-hound</t>
         </is>
       </c>
       <c r="I205" s="11" t="n"/>
@@ -9182,17 +9626,19 @@
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t>Flamer</t>
-        </is>
-      </c>
-      <c r="C206" s="8" t="inlineStr">
+          <t>Horror</t>
+        </is>
+      </c>
+      <c r="C206" s="9" t="inlineStr">
+        <is>
+          <t>Horrors &gt; Horrors</t>
+        </is>
+      </c>
+      <c r="D206" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
       </c>
-      <c r="D206" s="8" t="n">
-        <v>1446</v>
-      </c>
       <c r="E206" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -9210,7 +9656,7 @@
       </c>
       <c r="H206" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/flamer</t>
+          <t>https://6th.whfb.app/unit/horror</t>
         </is>
       </c>
       <c r="I206" s="11" t="n"/>
@@ -9224,17 +9670,19 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>Flesh Hound</t>
-        </is>
-      </c>
-      <c r="C207" s="8" t="inlineStr">
+          <t>Nurglings</t>
+        </is>
+      </c>
+      <c r="C207" s="9" t="inlineStr">
+        <is>
+          <t>Nurglings &gt; Nurglings</t>
+        </is>
+      </c>
+      <c r="D207" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
       </c>
-      <c r="D207" s="8" t="n">
-        <v>1698</v>
-      </c>
       <c r="E207" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -9252,7 +9700,7 @@
       </c>
       <c r="H207" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/flesh-hound</t>
+          <t>https://6th.whfb.app/unit/nurglings</t>
         </is>
       </c>
       <c r="I207" s="11" t="n"/>
@@ -9266,17 +9714,19 @@
       </c>
       <c r="B208" s="8" t="inlineStr">
         <is>
-          <t>Nurglings</t>
-        </is>
-      </c>
-      <c r="C208" s="8" t="inlineStr">
+          <t>Plaguebearer</t>
+        </is>
+      </c>
+      <c r="C208" s="9" t="inlineStr">
+        <is>
+          <t>Plaguebearers &gt; Plaguebearers</t>
+        </is>
+      </c>
+      <c r="D208" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
       </c>
-      <c r="D208" s="8" t="n">
-        <v>1758</v>
-      </c>
       <c r="E208" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -9294,7 +9744,7 @@
       </c>
       <c r="H208" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/nurglings</t>
+          <t>https://6th.whfb.app/unit/plaguebearer</t>
         </is>
       </c>
       <c r="I208" s="11" t="n"/>
@@ -9311,13 +9761,15 @@
           <t>Screamer</t>
         </is>
       </c>
-      <c r="C209" s="8" t="inlineStr">
+      <c r="C209" s="9" t="inlineStr">
+        <is>
+          <t>Screamers of Tzeentch &gt; Screamer</t>
+        </is>
+      </c>
+      <c r="D209" s="8" t="inlineStr">
         <is>
           <t>Daemonic Legions.cat</t>
         </is>
-      </c>
-      <c r="D209" s="8" t="n">
-        <v>1816</v>
       </c>
       <c r="E209" s="9" t="inlineStr">
         <is>
@@ -9350,20 +9802,22 @@
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t>Knight</t>
-        </is>
-      </c>
-      <c r="C210" s="8" t="inlineStr">
+          <t>Hag</t>
+        </is>
+      </c>
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>Cauldron of Blood</t>
+        </is>
+      </c>
+      <c r="D210" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D210" s="8" t="n">
-        <v>1263</v>
-      </c>
       <c r="E210" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F210" s="9" t="inlineStr">
@@ -9373,12 +9827,12 @@
       </c>
       <c r="G210" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 5-&gt;4, WS 5-&gt;4, BS 4-&gt;3, I 5-&gt;3, Ld 9-&gt;8</t>
+          <t>wiki: WS 4-&gt;5</t>
         </is>
       </c>
       <c r="H210" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/knight</t>
+          <t>https://6th.whfb.app/unit/hag</t>
         </is>
       </c>
       <c r="I210" s="11" t="n"/>
@@ -9392,20 +9846,22 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>Hag</t>
-        </is>
-      </c>
-      <c r="C211" s="8" t="inlineStr">
+          <t>Keeper of Secrets</t>
+        </is>
+      </c>
+      <c r="C211" s="9" t="inlineStr">
+        <is>
+          <t>Keeper of Secrets</t>
+        </is>
+      </c>
+      <c r="D211" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D211" s="8" t="n">
-        <v>1598</v>
-      </c>
       <c r="E211" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F211" s="9" t="inlineStr">
@@ -9415,12 +9871,12 @@
       </c>
       <c r="G211" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 4-&gt;5</t>
+          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
         </is>
       </c>
       <c r="H211" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/hag</t>
+          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
         </is>
       </c>
       <c r="I211" s="11" t="n"/>
@@ -9434,20 +9890,22 @@
       </c>
       <c r="B212" s="8" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
-        </is>
-      </c>
-      <c r="C212" s="8" t="inlineStr">
+          <t>Knight</t>
+        </is>
+      </c>
+      <c r="C212" s="9" t="inlineStr">
+        <is>
+          <t>Cold One Knights &gt; Cold One Knights</t>
+        </is>
+      </c>
+      <c r="D212" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D212" s="8" t="n">
-        <v>2844</v>
-      </c>
       <c r="E212" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F212" s="9" t="inlineStr">
@@ -9457,12 +9915,12 @@
       </c>
       <c r="G212" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
+          <t>wiki: M 5-&gt;4, WS 5-&gt;4, BS 4-&gt;3, I 5-&gt;3, Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H212" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
+          <t>https://6th.whfb.app/unit/knight</t>
         </is>
       </c>
       <c r="I212" s="11" t="n"/>
@@ -9476,20 +9934,22 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>Steed of Slaanesh</t>
-        </is>
-      </c>
-      <c r="C213" s="8" t="inlineStr">
+          <t>Knight</t>
+        </is>
+      </c>
+      <c r="C213" s="9" t="inlineStr">
+        <is>
+          <t>Knights of Chaos &gt; Knights</t>
+        </is>
+      </c>
+      <c r="D213" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D213" s="8" t="n">
-        <v>3065</v>
-      </c>
       <c r="E213" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>4 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F213" s="9" t="inlineStr">
@@ -9499,12 +9959,12 @@
       </c>
       <c r="G213" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
+          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
         </is>
       </c>
       <c r="H213" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
+          <t>https://6th.whfb.app/unit/knight</t>
         </is>
       </c>
       <c r="I213" s="11" t="n"/>
@@ -9518,20 +9978,22 @@
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
-          <t>Knight</t>
-        </is>
-      </c>
-      <c r="C214" s="8" t="inlineStr">
+          <t>Steed of Slaanesh</t>
+        </is>
+      </c>
+      <c r="C214" s="9" t="inlineStr">
+        <is>
+          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
+        </is>
+      </c>
+      <c r="D214" s="8" t="inlineStr">
         <is>
           <t>Dark Elves.cat</t>
         </is>
       </c>
-      <c r="D214" s="8" t="n">
-        <v>3275</v>
-      </c>
       <c r="E214" s="9" t="inlineStr">
         <is>
-          <t>4 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F214" s="9" t="inlineStr">
@@ -9541,12 +10003,12 @@
       </c>
       <c r="G214" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H214" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/knight</t>
+          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
         </is>
       </c>
       <c r="I214" s="11" t="n"/>
@@ -9563,13 +10025,15 @@
           <t>Daddallo</t>
         </is>
       </c>
-      <c r="C215" s="8" t="inlineStr">
+      <c r="C215" s="9" t="inlineStr">
+        <is>
+          <t>Birdmen of Catrazza &gt; Daddallo</t>
+        </is>
+      </c>
+      <c r="D215" s="8" t="inlineStr">
         <is>
           <t>Dogs of War.cat</t>
         </is>
-      </c>
-      <c r="D215" s="8" t="n">
-        <v>3378</v>
       </c>
       <c r="E215" s="9" t="inlineStr">
         <is>
@@ -9605,13 +10069,15 @@
           <t>Warhorse</t>
         </is>
       </c>
-      <c r="C216" s="8" t="inlineStr">
+      <c r="C216" s="9" t="inlineStr">
+        <is>
+          <t>shared; used by Al Muktar's Desert Dogs, Bronzino's Galloper Guns</t>
+        </is>
+      </c>
+      <c r="D216" s="8" t="inlineStr">
         <is>
           <t>Dogs of War.cat</t>
         </is>
-      </c>
-      <c r="D216" s="8" t="n">
-        <v>4491</v>
       </c>
       <c r="E216" s="9" t="inlineStr">
         <is>
@@ -9647,13 +10113,15 @@
           <t>Engineer</t>
         </is>
       </c>
-      <c r="C217" s="8" t="inlineStr">
+      <c r="C217" s="9" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="D217" s="8" t="inlineStr">
         <is>
           <t>Dwarfs.cat</t>
         </is>
-      </c>
-      <c r="D217" s="8" t="n">
-        <v>528</v>
       </c>
       <c r="E217" s="9" t="inlineStr">
         <is>
@@ -9689,13 +10157,15 @@
           <t>Bloodthirster</t>
         </is>
       </c>
-      <c r="C218" s="8" t="inlineStr">
+      <c r="C218" s="9" t="inlineStr">
+        <is>
+          <t>Bloodthirster</t>
+        </is>
+      </c>
+      <c r="D218" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
-      </c>
-      <c r="D218" s="8" t="n">
-        <v>1483</v>
       </c>
       <c r="E218" s="9" t="inlineStr">
         <is>
@@ -9728,20 +10198,22 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
-        </is>
-      </c>
-      <c r="C219" s="8" t="inlineStr">
+          <t>Centigor</t>
+        </is>
+      </c>
+      <c r="C219" s="9" t="inlineStr">
+        <is>
+          <t>Minotaurs &gt; Minotaurs</t>
+        </is>
+      </c>
+      <c r="D219" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D219" s="8" t="n">
-        <v>1697</v>
-      </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>4 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F219" s="9" t="inlineStr">
@@ -9751,12 +10223,12 @@
       </c>
       <c r="G219" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 6-&gt;8, WS 6-&gt;9, A 5-&gt;10, Ld 9-&gt;6</t>
+          <t>wiki: M 6-&gt;8, W 3-&gt;1, I 4-&gt;2, A 3-&gt;1(2), Ld 8-&gt;7</t>
         </is>
       </c>
       <c r="H219" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
+          <t>https://6th.whfb.app/unit/centigor</t>
         </is>
       </c>
       <c r="I219" s="11" t="n"/>
@@ -9770,20 +10242,22 @@
       </c>
       <c r="B220" s="8" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
-        </is>
-      </c>
-      <c r="C220" s="8" t="inlineStr">
+          <t>Chaos Giant</t>
+        </is>
+      </c>
+      <c r="C220" s="9" t="inlineStr">
+        <is>
+          <t>Chaos Giant</t>
+        </is>
+      </c>
+      <c r="D220" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D220" s="8" t="n">
-        <v>1805</v>
-      </c>
       <c r="E220" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F220" s="9" t="inlineStr">
@@ -9793,12 +10267,12 @@
       </c>
       <c r="G220" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
+          <t>wiki: A Special-&gt;*</t>
         </is>
       </c>
       <c r="H220" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
+          <t>https://6th.whfb.app/unit/chaos-giant</t>
         </is>
       </c>
       <c r="I220" s="11" t="n"/>
@@ -9812,17 +10286,19 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>Knight</t>
-        </is>
-      </c>
-      <c r="C221" s="8" t="inlineStr">
+          <t>Keeper of Secrets</t>
+        </is>
+      </c>
+      <c r="C221" s="9" t="inlineStr">
+        <is>
+          <t>Lord of Change</t>
+        </is>
+      </c>
+      <c r="D221" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D221" s="8" t="n">
-        <v>3091</v>
-      </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
           <t>4 characteristic(s) differ</t>
@@ -9835,12 +10311,12 @@
       </c>
       <c r="G221" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
+          <t>wiki: M 6-&gt;8, WS 6-&gt;9, A 5-&gt;10, Ld 9-&gt;6</t>
         </is>
       </c>
       <c r="H221" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/knight</t>
+          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
         </is>
       </c>
       <c r="I221" s="11" t="n"/>
@@ -9854,20 +10330,22 @@
       </c>
       <c r="B222" s="8" t="inlineStr">
         <is>
-          <t>Ungor</t>
-        </is>
-      </c>
-      <c r="C222" s="8" t="inlineStr">
+          <t>Keeper of Secrets</t>
+        </is>
+      </c>
+      <c r="C222" s="9" t="inlineStr">
+        <is>
+          <t>Keeper of Secrets</t>
+        </is>
+      </c>
+      <c r="D222" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D222" s="8" t="n">
-        <v>4193</v>
-      </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F222" s="9" t="inlineStr">
@@ -9877,12 +10355,12 @@
       </c>
       <c r="G222" s="9" t="inlineStr">
         <is>
-          <t>wiki: T 4-&gt;3</t>
+          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
         </is>
       </c>
       <c r="H222" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/ungor</t>
+          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
         </is>
       </c>
       <c r="I222" s="11" t="n"/>
@@ -9896,20 +10374,22 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>Troll</t>
-        </is>
-      </c>
-      <c r="C223" s="8" t="inlineStr">
+          <t>Knight</t>
+        </is>
+      </c>
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>Knights of Chaos &gt; Knights</t>
+        </is>
+      </c>
+      <c r="D223" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D223" s="8" t="n">
-        <v>4546</v>
-      </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>4 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr">
@@ -9919,12 +10399,12 @@
       </c>
       <c r="G223" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 4-&gt;3</t>
+          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
         </is>
       </c>
       <c r="H223" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/troll</t>
+          <t>https://6th.whfb.app/unit/knight</t>
         </is>
       </c>
       <c r="I223" s="11" t="n"/>
@@ -9938,17 +10418,19 @@
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>Centigor</t>
-        </is>
-      </c>
-      <c r="C224" s="8" t="inlineStr">
+          <t>Steed of Slaanesh</t>
+        </is>
+      </c>
+      <c r="C224" s="9" t="inlineStr">
+        <is>
+          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
+        </is>
+      </c>
+      <c r="D224" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D224" s="8" t="n">
-        <v>4893</v>
-      </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
           <t>5 characteristic(s) differ</t>
@@ -9961,12 +10443,12 @@
       </c>
       <c r="G224" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 6-&gt;8, W 3-&gt;1, I 4-&gt;2, A 3-&gt;1(2), Ld 8-&gt;7</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H224" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/centigor</t>
+          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
         </is>
       </c>
       <c r="I224" s="11" t="n"/>
@@ -9980,17 +10462,19 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>Chaos Giant</t>
-        </is>
-      </c>
-      <c r="C225" s="8" t="inlineStr">
+          <t>Troll</t>
+        </is>
+      </c>
+      <c r="C225" s="9" t="inlineStr">
+        <is>
+          <t>Chaos Trolls &gt; Trolls</t>
+        </is>
+      </c>
+      <c r="D225" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D225" s="8" t="n">
-        <v>5426</v>
-      </c>
       <c r="E225" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -10003,12 +10487,12 @@
       </c>
       <c r="G225" s="9" t="inlineStr">
         <is>
-          <t>wiki: A Special-&gt;*</t>
+          <t>wiki: A 4-&gt;3</t>
         </is>
       </c>
       <c r="H225" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/chaos-giant</t>
+          <t>https://6th.whfb.app/unit/troll</t>
         </is>
       </c>
       <c r="I225" s="11" t="n"/>
@@ -10022,20 +10506,22 @@
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t>Steed of Slaanesh</t>
-        </is>
-      </c>
-      <c r="C226" s="8" t="inlineStr">
+          <t>Tuskgor</t>
+        </is>
+      </c>
+      <c r="C226" s="9" t="inlineStr">
+        <is>
+          <t>Gorthor the Beastlord</t>
+        </is>
+      </c>
+      <c r="D226" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D226" s="8" t="n">
-        <v>5563</v>
-      </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
@@ -10045,12 +10531,12 @@
       </c>
       <c r="G226" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
+          <t>wiki: S 4-&gt;3</t>
         </is>
       </c>
       <c r="H226" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
+          <t>https://6th.whfb.app/unit/tuskgor</t>
         </is>
       </c>
       <c r="I226" s="11" t="n"/>
@@ -10064,17 +10550,19 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>Tuskgor</t>
-        </is>
-      </c>
-      <c r="C227" s="8" t="inlineStr">
+          <t>Ungor</t>
+        </is>
+      </c>
+      <c r="C227" s="9" t="inlineStr">
+        <is>
+          <t>Beast Herd &gt; Ungors</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
       </c>
-      <c r="D227" s="8" t="n">
-        <v>5613</v>
-      </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -10087,12 +10575,12 @@
       </c>
       <c r="G227" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 4-&gt;3</t>
+          <t>wiki: T 4-&gt;3</t>
         </is>
       </c>
       <c r="H227" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/tuskgor</t>
+          <t>https://6th.whfb.app/unit/ungor</t>
         </is>
       </c>
       <c r="I227" s="11" t="n"/>
@@ -10109,13 +10597,15 @@
           <t>Ungor</t>
         </is>
       </c>
-      <c r="C228" s="8" t="inlineStr">
+      <c r="C228" s="9" t="inlineStr">
+        <is>
+          <t>Tuskgor Chariot</t>
+        </is>
+      </c>
+      <c r="D228" s="8" t="inlineStr">
         <is>
           <t>Forces of Chaos.cat</t>
         </is>
-      </c>
-      <c r="D228" s="8" t="n">
-        <v>5996</v>
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
@@ -10148,20 +10638,22 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>Ellyrian Reaver</t>
-        </is>
-      </c>
-      <c r="C229" s="8" t="inlineStr">
+          <t>Bladelord</t>
+        </is>
+      </c>
+      <c r="C229" s="9" t="inlineStr">
+        <is>
+          <t>Phoenix Guard &gt; Command &gt; Keeper of the Flame</t>
+        </is>
+      </c>
+      <c r="D229" s="8" t="inlineStr">
         <is>
           <t>High Elves.cat</t>
         </is>
       </c>
-      <c r="D229" s="8" t="n">
-        <v>1029</v>
-      </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>3 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
@@ -10171,12 +10663,12 @@
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 1-&gt;2</t>
+          <t>wiki: WS 5-&gt;6, I 6-&gt;5, Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H229" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/ellyrian-reaver</t>
+          <t>https://6th.whfb.app/unit/bladelord</t>
         </is>
       </c>
       <c r="I229" s="11" t="n"/>
@@ -10190,17 +10682,19 @@
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t>Harbinger</t>
-        </is>
-      </c>
-      <c r="C230" s="8" t="inlineStr">
+          <t>Ellyrian Reaver</t>
+        </is>
+      </c>
+      <c r="C230" s="9" t="inlineStr">
+        <is>
+          <t>Ellyrian Reavers &gt; Ellyrian Reavers</t>
+        </is>
+      </c>
+      <c r="D230" s="8" t="inlineStr">
         <is>
           <t>High Elves.cat</t>
         </is>
       </c>
-      <c r="D230" s="8" t="n">
-        <v>1087</v>
-      </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -10218,7 +10712,7 @@
       </c>
       <c r="H230" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/harbinger</t>
+          <t>https://6th.whfb.app/unit/ellyrian-reaver</t>
         </is>
       </c>
       <c r="I230" s="11" t="n"/>
@@ -10232,20 +10726,22 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>Bladelord</t>
-        </is>
-      </c>
-      <c r="C231" s="8" t="inlineStr">
+          <t>Harbinger</t>
+        </is>
+      </c>
+      <c r="C231" s="9" t="inlineStr">
+        <is>
+          <t>Ellyrian Reavers &gt; Command &gt; Harbinger</t>
+        </is>
+      </c>
+      <c r="D231" s="8" t="inlineStr">
         <is>
           <t>High Elves.cat</t>
         </is>
       </c>
-      <c r="D231" s="8" t="n">
-        <v>1682</v>
-      </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>3 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
@@ -10255,12 +10751,12 @@
       </c>
       <c r="G231" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 5-&gt;6, I 6-&gt;5, Ld 9-&gt;8</t>
+          <t>wiki: A 1-&gt;2</t>
         </is>
       </c>
       <c r="H231" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bladelord</t>
+          <t>https://6th.whfb.app/unit/harbinger</t>
         </is>
       </c>
       <c r="I231" s="11" t="n"/>
@@ -10274,17 +10770,19 @@
       </c>
       <c r="B232" s="8" t="inlineStr">
         <is>
-          <t>Thunderfist</t>
-        </is>
-      </c>
-      <c r="C232" s="8" t="inlineStr">
+          <t>Greyback</t>
+        </is>
+      </c>
+      <c r="C232" s="9" t="inlineStr">
+        <is>
+          <t>Yheetees &gt; Greyback</t>
+        </is>
+      </c>
+      <c r="D232" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D232" s="8" t="n">
-        <v>1248</v>
-      </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -10297,12 +10795,12 @@
       </c>
       <c r="G232" s="9" t="inlineStr">
         <is>
-          <t>wiki: BS 2-&gt;3</t>
+          <t>wiki: A 4-&gt;3</t>
         </is>
       </c>
       <c r="H232" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/thunderfist</t>
+          <t>https://6th.whfb.app/unit/greyback</t>
         </is>
       </c>
       <c r="I232" s="11" t="n"/>
@@ -10316,17 +10814,19 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>Greyback</t>
-        </is>
-      </c>
-      <c r="C233" s="8" t="inlineStr">
+          <t>Rhinox</t>
+        </is>
+      </c>
+      <c r="C233" s="9" t="inlineStr">
+        <is>
+          <t>Rhinox Cavalry &gt; Rhinox Riders</t>
+        </is>
+      </c>
+      <c r="D233" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D233" s="8" t="n">
-        <v>1351</v>
-      </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -10339,12 +10839,12 @@
       </c>
       <c r="G233" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 4-&gt;3</t>
+          <t>wiki: M 7-&gt;6</t>
         </is>
       </c>
       <c r="H233" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/greyback</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I233" s="11" t="n"/>
@@ -10358,17 +10858,19 @@
       </c>
       <c r="B234" s="8" t="inlineStr">
         <is>
-          <t>Rhinox</t>
-        </is>
-      </c>
-      <c r="C234" s="8" t="inlineStr">
+          <t>Thunderfist</t>
+        </is>
+      </c>
+      <c r="C234" s="9" t="inlineStr">
+        <is>
+          <t>Leadbelchers &gt; Command &gt; Thunderfist</t>
+        </is>
+      </c>
+      <c r="D234" s="8" t="inlineStr">
         <is>
           <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
-      <c r="D234" s="8" t="n">
-        <v>1936</v>
-      </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -10381,12 +10883,12 @@
       </c>
       <c r="G234" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 7-&gt;6</t>
+          <t>wiki: BS 2-&gt;3</t>
         </is>
       </c>
       <c r="H234" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
+          <t>https://6th.whfb.app/unit/thunderfist</t>
         </is>
       </c>
       <c r="I234" s="11" t="n"/>
@@ -10400,17 +10902,19 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>Squig Hopper</t>
-        </is>
-      </c>
-      <c r="C235" s="8" t="inlineStr">
+          <t>Boar Chariot</t>
+        </is>
+      </c>
+      <c r="C235" s="9" t="inlineStr">
+        <is>
+          <t>Savage Orc Boar Chariot</t>
+        </is>
+      </c>
+      <c r="D235" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D235" s="8" t="n">
-        <v>3710</v>
-      </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -10423,12 +10927,12 @@
       </c>
       <c r="G235" s="9" t="inlineStr">
         <is>
-          <t>wiki: W 2-&gt;1</t>
+          <t>wiki: S 5-&gt;3</t>
         </is>
       </c>
       <c r="H235" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/squig-hopper</t>
+          <t>https://6th.whfb.app/unit/boar-chariot</t>
         </is>
       </c>
       <c r="I235" s="11" t="n"/>
@@ -10445,13 +10949,15 @@
           <t>Giant</t>
         </is>
       </c>
-      <c r="C236" s="8" t="inlineStr">
+      <c r="C236" s="9" t="inlineStr">
+        <is>
+          <t>Giant</t>
+        </is>
+      </c>
+      <c r="D236" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
-      </c>
-      <c r="D236" s="8" t="n">
-        <v>4239</v>
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
@@ -10484,17 +10990,19 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>Boar Chariot</t>
-        </is>
-      </c>
-      <c r="C237" s="8" t="inlineStr">
+          <t>Squig Hopper</t>
+        </is>
+      </c>
+      <c r="C237" s="9" t="inlineStr">
+        <is>
+          <t>Night Goblin Squig Herd &gt; Unit &gt; Squig Hopper</t>
+        </is>
+      </c>
+      <c r="D237" s="8" t="inlineStr">
         <is>
           <t>Orcs and Goblins.cat</t>
         </is>
       </c>
-      <c r="D237" s="8" t="n">
-        <v>6360</v>
-      </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -10507,12 +11015,12 @@
       </c>
       <c r="G237" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 5-&gt;3</t>
+          <t>wiki: W 2-&gt;1</t>
         </is>
       </c>
       <c r="H237" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/boar-chariot</t>
+          <t>https://6th.whfb.app/unit/squig-hopper</t>
         </is>
       </c>
       <c r="I237" s="11" t="n"/>
@@ -10526,20 +11034,22 @@
       </c>
       <c r="B238" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="C238" s="8" t="inlineStr">
+          <t>Clanrat Slave</t>
+        </is>
+      </c>
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>Clanrat Slaves &gt; Clanrat Slaves</t>
+        </is>
+      </c>
+      <c r="D238" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D238" s="8" t="n">
-        <v>497</v>
-      </c>
       <c r="E238" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F238" s="9" t="inlineStr">
@@ -10549,12 +11059,12 @@
       </c>
       <c r="G238" s="9" t="inlineStr">
         <is>
-          <t>wiki: I 6-&gt;4</t>
+          <t>wiki: M 6-&gt;5, I 5-&gt;4</t>
         </is>
       </c>
       <c r="H238" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+          <t>https://6th.whfb.app/unit/clanrat-slave</t>
         </is>
       </c>
       <c r="I238" s="11" t="n"/>
@@ -10568,20 +11078,22 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>Clanrat Slave</t>
-        </is>
-      </c>
-      <c r="C239" s="8" t="inlineStr">
+          <t>Festering Chantor</t>
+        </is>
+      </c>
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>Festering Chantor</t>
+        </is>
+      </c>
+      <c r="D239" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D239" s="8" t="n">
-        <v>1433</v>
-      </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>7 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F239" s="9" t="inlineStr">
@@ -10591,12 +11103,12 @@
       </c>
       <c r="G239" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 6-&gt;5, I 5-&gt;4</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
         </is>
       </c>
       <c r="H239" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/clanrat-slave</t>
+          <t>https://6th.whfb.app/unit/festering-chantor</t>
         </is>
       </c>
       <c r="I239" s="11" t="n"/>
@@ -10610,20 +11122,22 @@
       </c>
       <c r="B240" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="C240" s="8" t="inlineStr">
+          <t>Plague Lord</t>
+        </is>
+      </c>
+      <c r="C240" s="9" t="inlineStr">
+        <is>
+          <t>Plague Lord</t>
+        </is>
+      </c>
+      <c r="D240" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D240" s="8" t="n">
-        <v>3020</v>
-      </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>6 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F240" s="9" t="inlineStr">
@@ -10633,12 +11147,12 @@
       </c>
       <c r="G240" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 4-&gt;3, T 4-&gt;3, W 3-&gt;2, I 5-&gt;4, A 2-&gt;1, Ld 7-&gt;5</t>
+          <t>wiki: A 5-&gt;4</t>
         </is>
       </c>
       <c r="H240" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+          <t>https://6th.whfb.app/unit/plague-lord</t>
         </is>
       </c>
       <c r="I240" s="11" t="n"/>
@@ -10652,17 +11166,19 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>Plague Lord</t>
-        </is>
-      </c>
-      <c r="C241" s="8" t="inlineStr">
+          <t>Warlock Engineer</t>
+        </is>
+      </c>
+      <c r="C241" s="9" t="inlineStr">
+        <is>
+          <t>Warlock Engineer</t>
+        </is>
+      </c>
+      <c r="D241" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D241" s="8" t="n">
-        <v>3140</v>
-      </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
           <t>1 characteristic(s) differ</t>
@@ -10675,12 +11191,12 @@
       </c>
       <c r="G241" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 5-&gt;4</t>
+          <t>wiki: I 6-&gt;4</t>
         </is>
       </c>
       <c r="H241" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/plague-lord</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I241" s="11" t="n"/>
@@ -10694,20 +11210,22 @@
       </c>
       <c r="B242" s="8" t="inlineStr">
         <is>
-          <t>Festering Chantor</t>
-        </is>
-      </c>
-      <c r="C242" s="8" t="inlineStr">
+          <t>Warlock Engineer</t>
+        </is>
+      </c>
+      <c r="C242" s="9" t="inlineStr">
+        <is>
+          <t>Warlock Master</t>
+        </is>
+      </c>
+      <c r="D242" s="8" t="inlineStr">
         <is>
           <t>Skaven.cat</t>
         </is>
       </c>
-      <c r="D242" s="8" t="n">
-        <v>3217</v>
-      </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>7 characteristic(s) differ</t>
+          <t>6 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F242" s="9" t="inlineStr">
@@ -10717,12 +11235,12 @@
       </c>
       <c r="G242" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
+          <t>wiki: WS 4-&gt;3, T 4-&gt;3, W 3-&gt;2, I 5-&gt;4, A 2-&gt;1, Ld 7-&gt;5</t>
         </is>
       </c>
       <c r="H242" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/festering-chantor</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I242" s="11" t="n"/>
@@ -10739,13 +11257,15 @@
           <t>Skeleton</t>
         </is>
       </c>
-      <c r="C243" s="8" t="inlineStr">
+      <c r="C243" s="9" t="inlineStr">
+        <is>
+          <t>Skeleton Light Horsemen &gt; Skeleton Horseman</t>
+        </is>
+      </c>
+      <c r="D243" s="8" t="inlineStr">
         <is>
           <t>Tomb Kings.cat</t>
         </is>
-      </c>
-      <c r="D243" s="8" t="n">
-        <v>663</v>
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
@@ -10781,13 +11301,15 @@
           <t>Skeleton</t>
         </is>
       </c>
-      <c r="C244" s="8" t="inlineStr">
+      <c r="C244" s="9" t="inlineStr">
+        <is>
+          <t>Skeleton Heavy Horsemen &gt; Skeleton Horseman</t>
+        </is>
+      </c>
+      <c r="D244" s="8" t="inlineStr">
         <is>
           <t>Tomb Kings.cat</t>
         </is>
-      </c>
-      <c r="D244" s="8" t="n">
-        <v>765</v>
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
@@ -10823,13 +11345,15 @@
           <t>Skeleton Crew</t>
         </is>
       </c>
-      <c r="C245" s="8" t="inlineStr">
+      <c r="C245" s="9" t="inlineStr">
+        <is>
+          <t>Chariots &gt; Chariot</t>
+        </is>
+      </c>
+      <c r="D245" s="8" t="inlineStr">
         <is>
           <t>Tomb Kings.cat</t>
         </is>
-      </c>
-      <c r="D245" s="8" t="n">
-        <v>919</v>
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
@@ -10899,15 +11423,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId46"/>
@@ -10919,7 +11443,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId58"/>
@@ -10944,44 +11468,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId120"/>

--- a/docs/judgement-calls.xlsx
+++ b/docs/judgement-calls.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Decisions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$236</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B28" s="4">
-        <f>COUNTBLANK(Decisions!$I$4:$I$245)</f>
+        <f>COUNTBLANK(Decisions!$I$4:$I$236)</f>
         <v/>
       </c>
     </row>
@@ -696,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J245"/>
+  <dimension ref="A1:J236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -830,17 +830,17 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Aura of Slaanesh</t>
+          <t>Hand of Khaine</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Chariot of Slaanesh, Daemonettes, Daemonic Gifts, Mounted Daemonettes, Pleasureseekers</t>
+          <t>Artifacts and Skills &gt; Hand of Khaine</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/aura-of-slaanesh</t>
+          <t>/magic-item/hand-of-khaine-artefact-and-skill</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/aura-of-slaanesh</t>
+          <t>/magic-item/hand-of-khaine-malekith</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/aura-of-slaanesh</t>
+          <t>https://6th.whfb.app/magic-item/hand-of-khaine-artefact-and-skill</t>
         </is>
       </c>
       <c r="I4" s="11" t="n"/>
@@ -874,37 +874,37 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Cloud of Flies</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Chariot of Nurgle, Daemonic Gifts, Nurglings, Plaguebearers, Plagueriders</t>
+          <t>The Giants of Albion &gt; Hengus the Druid</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>wiki has 3 candidate pages</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/cloud-of-flies</t>
+          <t>/faq/magic</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/cloud-of-flies</t>
+          <t>/magic</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/cloud-of-flies</t>
+          <t>https://6th.whfb.app/faq/magic</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -918,17 +918,17 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Stream of Corruption</t>
+          <t>Axe of Khorne</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Plaguebearers</t>
+          <t>Magic Weapons &gt; Axe of Khorne</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/stream-of-corruption</t>
+          <t>/magic-item/axe-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/stream-of-corruption</t>
+          <t>/magic-item/axe-of-khorne-daemonic-gifts</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/stream-of-corruption</t>
+          <t>https://6th.whfb.app/magic-item/axe-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -962,17 +962,17 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Aura of Slaanesh</t>
+          <t>Axe of Khorne</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Slaanesh Daemonic Gifts &gt; Aura of Slaanesh</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -982,17 +982,17 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/aura-of-slaanesh</t>
+          <t>/magic-item/axe-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/aura-of-slaanesh</t>
+          <t>/magic-item/axe-of-khorne-daemonic-gifts</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/aura-of-slaanesh</t>
+          <t>https://6th.whfb.app/magic-item/axe-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -1006,17 +1006,17 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Hand of Khaine</t>
+          <t>Collar of Khorne</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Artifacts and Skills &gt; Hand of Khaine</t>
+          <t>Talismans</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/hand-of-khaine-artefact-and-skill</t>
+          <t>/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/hand-of-khaine-malekith</t>
+          <t>/magic-item/collar-of-khorne-daemonic-gifts</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/hand-of-khaine-artefact-and-skill</t>
+          <t>https://6th.whfb.app/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="I8" s="11" t="n"/>
@@ -1050,37 +1050,37 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Collar of Khorne</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>The Giants of Albion &gt; Hengus the Druid</t>
+          <t>Daemonic Gifts</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>wiki has 3 candidate pages</t>
+          <t>wiki has 2 candidate pages</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>/faq/magic</t>
+          <t>/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>/magic</t>
+          <t>/magic-item/collar-of-khorne-daemonic-gifts</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/magic</t>
+          <t>https://6th.whfb.app/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
         </is>
       </c>
       <c r="I9" s="11" t="n"/>
@@ -1094,17 +1094,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Rune of Fire</t>
+          <t>'Eadbutt</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Weapon Runes &gt; Rune of Fire</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/rune-of-fire</t>
+          <t>/special-rules/eadbutt</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>/spell/rune-of-fire</t>
+          <t>/spell/eadbutt</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/rune-of-fire</t>
+          <t>https://6th.whfb.app/special-rules/eadbutt</t>
         </is>
       </c>
       <c r="I10" s="11" t="n"/>
@@ -1138,17 +1138,17 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Aura of Slaanesh</t>
+          <t>Daemonic Aura</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Aura of Slaanesh, Daemonettes, Mounted Daemonettes</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1158,17 +1158,17 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/aura-of-slaanesh</t>
+          <t>/army-lists/daemonic-daemonic-legion</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/aura-of-slaanesh</t>
+          <t>/special-rules/daemonic</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/aura-of-slaanesh</t>
+          <t>https://6th.whfb.app/army-lists/daemonic-daemonic-legion</t>
         </is>
       </c>
       <c r="I11" s="11" t="n"/>
@@ -1182,17 +1182,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Axe of Khorne</t>
+          <t>Expendable</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Magic Weapons &gt; Axe of Khorne</t>
+          <t>shared; used by Clanrat Slaves, Rat Swarm</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/axe-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>/special-rules/expendable-clanrat-slaves</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/axe-of-khorne-daemonic-gifts</t>
+          <t>/special-rules/expendable-swarms</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/axe-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>https://6th.whfb.app/special-rules/expendable-clanrat-slaves</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -1226,37 +1226,37 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Axe of Khorne</t>
+          <t>Movement</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Doomwheel</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>wiki has 3 candidate pages</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/axe-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>/faq/movement</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/axe-of-khorne-daemonic-gifts</t>
+          <t>/movement</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/axe-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>https://6th.whfb.app/faq/movement</t>
         </is>
       </c>
       <c r="I13" s="11" t="n"/>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Cloud of Flies</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Cloud of Flies, Nurglings, Plaguebearers</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1290,17 +1290,17 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/cloud-of-flies</t>
+          <t>/unit/cannon-dogs-of-war</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/cloud-of-flies</t>
+          <t>/unit/cannon-dwarfs</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/cloud-of-flies</t>
+          <t>https://6th.whfb.app/unit/cannon-dogs-of-war</t>
         </is>
       </c>
       <c r="I14" s="11" t="n"/>
@@ -1314,37 +1314,33 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Collar of Khorne</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Talismans</t>
+          <t>shared; used by (catalogue root)</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>/special-rules/chariot-gorthor is Beasts of Chaos, not core rulebook - wrong for a shared rule</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>/magic-item/collar-of-khorne-daemonic-gifts</t>
-        </is>
-      </c>
+          <t>/special-rules/chariot-gorthor</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr"/>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>https://6th.whfb.app/special-rules/chariot-gorthor</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -1358,17 +1354,17 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Collar of Khorne</t>
+          <t>Fast Cavalry</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Daemonic Gifts</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1378,17 +1374,17 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>/faq/fast-cavalry</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/collar-of-khorne-daemonic-gifts</t>
+          <t>/fast-cavalry</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/collar-of-khorne-artifacts-of-the-dark-gods</t>
+          <t>https://6th.whfb.app/faq/fast-cavalry</t>
         </is>
       </c>
       <c r="I16" s="11" t="n"/>
@@ -1402,17 +1398,17 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Stream of Corruption</t>
+          <t>Skirmishers</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Plaguebearers, Stream of Corruption</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1422,17 +1418,17 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/stream-of-corruption</t>
+          <t>/faq/skirmishers</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/stream-of-corruption</t>
+          <t>/skirmishers</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/stream-of-corruption</t>
+          <t>https://6th.whfb.app/faq/skirmishers</t>
         </is>
       </c>
       <c r="I17" s="11" t="n"/>
@@ -1446,37 +1442,33 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>'Eadbutt</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>shared; used by (catalogue root)</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>/special-rules/small is Lizardmen, Skaven, Tomb Kings, not core rulebook - wrong for a shared rule</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/eadbutt</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>/spell/eadbutt</t>
-        </is>
-      </c>
+          <t>/special-rules/small</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr"/>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/eadbutt</t>
+          <t>https://6th.whfb.app/special-rules/small</t>
         </is>
       </c>
       <c r="I18" s="11" t="n"/>
@@ -1490,37 +1482,37 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Aura</t>
+          <t>Swarm</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>shared; used by (catalogue root)</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>wiki has 6 candidate pages</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>/army-lists/daemonic-daemonic-legion</t>
+          <t>/special-rules/swarm-bat-swarms</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/daemonic</t>
+          <t>/special-rules/swarm-jungle-swarms</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/army-lists/daemonic-daemonic-legion</t>
+          <t>https://6th.whfb.app/special-rules/swarm-bat-swarms</t>
         </is>
       </c>
       <c r="I19" s="11" t="n"/>
@@ -1534,37 +1526,37 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Expendable</t>
+          <t>Undead</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Clanrat Slaves, Rat Swarm</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>wiki has 4 candidate pages</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/expendable-clanrat-slaves</t>
+          <t>/special-rules/undead-regiments-of-renown</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/expendable-swarms</t>
+          <t>/special-rules/undead-tomb-kings</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/expendable-clanrat-slaves</t>
+          <t>https://6th.whfb.app/special-rules/undead-regiments-of-renown</t>
         </is>
       </c>
       <c r="I20" s="11" t="n"/>
@@ -1578,37 +1570,37 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Tree Singing</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Doomwheel</t>
+          <t>Drycha</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>wiki has 3 candidate pages</t>
+          <t>wiki has 2 candidate pages</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>/faq/movement</t>
+          <t>/special-rules/tree-singing</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>/movement</t>
+          <t>/spell/tree-singing</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/movement</t>
+          <t>https://6th.whfb.app/special-rules/tree-singing</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -1617,82 +1609,82 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Ambiguous match</t>
+          <t>No wiki coverage</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Braziers</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Peasant Bowmen &gt; Braziers</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>no confident match; nearest candidate is not applied</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>/unit/cannon-dogs-of-war</t>
+          <t>leave as is</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>/unit/cannon-dwarfs</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/cannon-dogs-of-war</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr"/>
       <c r="I22" s="11" t="n"/>
       <c r="J22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Ambiguous match</t>
+          <t>No wiki coverage</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>The Fay Enchantress</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>shared; used by (catalogue root)</t>
+          <t>The Fay Enchantress</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/chariot-gorthor is Beasts of Chaos, not core rulebook - wrong for a shared rule</t>
+          <t>no confident match; nearest candidate is not applied</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/chariot-gorthor</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr"/>
+          <t>leave as is</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>/unit/the-fay-enchantress (1.00)</t>
+        </is>
+      </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/chariot-gorthor</t>
+          <t>https://6th.whfb.app/unit/the-fay-enchantress</t>
         </is>
       </c>
       <c r="I23" s="11" t="n"/>
@@ -1701,42 +1693,42 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Ambiguous match</t>
+          <t>No wiki coverage</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Fast Cavalry</t>
+          <t>Great Taurus</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Chaos Dwarf Lord &gt; Mount &gt; Great Taurus</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>no confident match; nearest candidate is not applied</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>/faq/fast-cavalry</t>
+          <t>leave as is</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>/fast-cavalry</t>
+          <t>/unit/great-taurus (1.00)</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/fast-cavalry</t>
+          <t>https://6th.whfb.app/unit/great-taurus</t>
         </is>
       </c>
       <c r="I24" s="11" t="n"/>
@@ -1745,42 +1737,42 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Ambiguous match</t>
+          <t>No wiki coverage</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Skirmishers</t>
+          <t>Lammasu</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Sorcerer Lord &gt; Mount &gt; Lammasu</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>no confident match; nearest candidate is not applied</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>/faq/skirmishers</t>
+          <t>leave as is</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>/skirmishers</t>
+          <t>/unit/lammasu (1.00)</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/skirmishers</t>
+          <t>https://6th.whfb.app/unit/lammasu</t>
         </is>
       </c>
       <c r="I25" s="11" t="n"/>
@@ -1789,38 +1781,42 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Ambiguous match</t>
+          <t>No wiki coverage</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Daemonic Legions Special Rules</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>shared; used by (catalogue root)</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/small is Lizardmen, Skaven, Tomb Kings, not core rulebook - wrong for a shared rule</t>
+          <t>no confident match; nearest candidate is not applied</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/small</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr"/>
+          <t>leave as is</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>/special-rules/daemonic (0.90)</t>
+        </is>
+      </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/small</t>
+          <t>https://6th.whfb.app/special-rules/daemonic</t>
         </is>
       </c>
       <c r="I26" s="11" t="n"/>
@@ -1829,42 +1825,42 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Ambiguous match</t>
+          <t>No wiki coverage</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Swarm</t>
+          <t>Horror Champion</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>shared; used by (catalogue root)</t>
+          <t>Horrors &gt; Command &gt; Champion</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>wiki has 6 candidate pages</t>
+          <t>no confident match; nearest candidate is not applied</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/swarm-bat-swarms</t>
+          <t>leave as is</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/swarm-jungle-swarms</t>
+          <t>/unit/horror (0.90)</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/swarm-bat-swarms</t>
+          <t>https://6th.whfb.app/unit/horror</t>
         </is>
       </c>
       <c r="I27" s="11" t="n"/>
@@ -1873,42 +1869,42 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Ambiguous match</t>
+          <t>No wiki coverage</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>Scythed Wheels</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>shared; used by Chariot of Khorne, Chariot of Slaanesh</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>wiki has 4 candidate pages</t>
+          <t>no confident match; nearest candidate is not applied</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/undead-regiments-of-renown</t>
+          <t>leave as is</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/undead-tomb-kings</t>
+          <t>/movement/wheel (0.80)</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/undead-regiments-of-renown</t>
+          <t>https://6th.whfb.app/movement/wheel</t>
         </is>
       </c>
       <c r="I28" s="11" t="n"/>
@@ -1917,42 +1913,42 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Ambiguous match</t>
+          <t>No wiki coverage</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Tree Singing</t>
+          <t>5+ Annointed Ward Save</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Drycha</t>
+          <t>Druchii Annointed</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>no confident match; nearest candidate is not applied</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/tree-singing</t>
+          <t>leave as is</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>/spell/tree-singing</t>
+          <t>/special-rules/annointed-ward-save (0.80)</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/tree-singing</t>
+          <t>https://6th.whfb.app/special-rules/annointed-ward-save</t>
         </is>
       </c>
       <c r="I29" s="11" t="n"/>
@@ -1961,44 +1957,40 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Ambiguous match</t>
+          <t>No wiki coverage</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Tree Singing</t>
+          <t>Accustomed to Battle</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Treeman, Treeman Ancient</t>
+          <t>War Hydra &gt; Variant War Hydra &gt; Veteran War Hydra</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>no confident match; nearest candidate is not applied</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/tree-singing</t>
+          <t>leave as is</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>/spell/tree-singing</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/special-rules/tree-singing</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr"/>
       <c r="I30" s="11" t="n"/>
       <c r="J30" s="11" t="n"/>
     </row>
@@ -2010,17 +2002,17 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Braziers</t>
+          <t>Acid Breath</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Peasant Bowmen &gt; Braziers</t>
+          <t>War Hydra &gt; Variant War Hydra &gt; Royal War Hydra</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -2050,17 +2042,17 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>The Fay Enchantress</t>
+          <t>Beastmaster</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>The Fay Enchantress</t>
+          <t>Beastmaster</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2075,12 +2067,12 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>/unit/the-fay-enchantress (1.00)</t>
+          <t>/unit/beastmaster (1.00)</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/the-fay-enchantress</t>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
         </is>
       </c>
       <c r="I32" s="11" t="n"/>
@@ -2094,17 +2086,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Great Taurus</t>
+          <t>Chaos Daemon Sword (Keeper of Secrets) WS9 S6 I10 A6</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Chaos Dwarf Lord &gt; Mount &gt; Great Taurus</t>
+          <t>Chaos Daemon Sword</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarves.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2119,12 +2111,12 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>/unit/great-taurus (1.00)</t>
+          <t>/magic-item/chaos-daemon-sword (0.90)</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/great-taurus</t>
+          <t>https://6th.whfb.app/magic-item/chaos-daemon-sword</t>
         </is>
       </c>
       <c r="I33" s="11" t="n"/>
@@ -2138,17 +2130,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Lammasu</t>
+          <t>Chosen of the Convents</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Sorcerer Lord &gt; Mount &gt; Lammasu</t>
+          <t>War Hydra &gt; Variant War Hydra &gt; Spellthirster</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarves.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2163,12 +2155,12 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>/unit/lammasu (1.00)</t>
+          <t>/special-rules/chosen (0.90)</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/lammasu</t>
+          <t>https://6th.whfb.app/special-rules/chosen</t>
         </is>
       </c>
       <c r="I34" s="11" t="n"/>
@@ -2182,17 +2174,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions Special Rules</t>
+          <t>Cold One Chariot</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Cold One Chariot</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2207,12 +2199,12 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/daemonic (0.90)</t>
+          <t>/unit/cold-one-chariot (1.00)</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/daemonic</t>
+          <t>https://6th.whfb.app/unit/cold-one-chariot</t>
         </is>
       </c>
       <c r="I35" s="11" t="n"/>
@@ -2226,17 +2218,17 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Horror Champion</t>
+          <t>Daerlythe's Aura</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Horrors &gt; Command &gt; Champion</t>
+          <t>War Hydra &gt; Variant War Hydra &gt; Spellthirster</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2251,14 +2243,10 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>/unit/horror (0.90)</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/horror</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr"/>
       <c r="I36" s="11" t="n"/>
       <c r="J36" s="11" t="n"/>
     </row>
@@ -2270,17 +2258,17 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Scythed Wheels</t>
+          <t>Hate High Elves</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Chariot of Khorne, Chariot of Slaanesh</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2295,12 +2283,12 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>/movement/wheel (0.80)</t>
+          <t>/army/high-elves (0.80)</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/movement/wheel</t>
+          <t>https://6th.whfb.app/army/high-elves</t>
         </is>
       </c>
       <c r="I37" s="11" t="n"/>
@@ -2314,12 +2302,12 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>5+ Annointed Ward Save</t>
+          <t>Malekith's Weapons</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Druchii Annointed</t>
+          <t>Malekith, Witch King of Naggaroth</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2339,12 +2327,12 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/annointed-ward-save (0.80)</t>
+          <t>/unit/malekith (0.90)</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/annointed-ward-save</t>
+          <t>https://6th.whfb.app/unit/malekith</t>
         </is>
       </c>
       <c r="I38" s="11" t="n"/>
@@ -2358,12 +2346,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Accustomed to Battle</t>
+          <t>Mentally Scarred</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>War Hydra &gt; Variant War Hydra &gt; Veteran War Hydra</t>
+          <t>War Hydra &gt; Variant War Hydra &gt; Royal War Hydra</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -2398,12 +2386,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Acid Breath</t>
+          <t>Physically Weakened</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>War Hydra &gt; Variant War Hydra &gt; Royal War Hydra</t>
+          <t>War Hydra &gt; Variant War Hydra &gt; Spellthirster</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2438,12 +2426,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
+          <t>Slaughterer's Blade</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
+          <t>Chaos Magic Items &gt; Magic Weapons &gt; Slaughterer's Blade</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -2463,12 +2451,12 @@
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
+          <t>/magic-item/slaughters-blade (0.66)</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
+          <t>https://6th.whfb.app/magic-item/slaughters-blade</t>
         </is>
       </c>
       <c r="I41" s="11" t="n"/>
@@ -2482,12 +2470,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Chaos Daemon Sword (Keeper of Secrets) WS9 S6 I10 A6</t>
+          <t>Sorcerer</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Chaos Daemon Sword</t>
+          <t>Malekith, Witch King of Naggaroth</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2507,12 +2495,12 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/chaos-daemon-sword (0.90)</t>
+          <t>/unit/sorcerer (1.00)</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/chaos-daemon-sword</t>
+          <t>https://6th.whfb.app/unit/sorcerer</t>
         </is>
       </c>
       <c r="I42" s="11" t="n"/>
@@ -2526,12 +2514,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Chosen of the Convents</t>
+          <t>Speed of Slaanesh (Mistress)</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>War Hydra &gt; Variant War Hydra &gt; Spellthirster</t>
+          <t>Devoted of Slaanesh &gt; Speed of Slaanesh (Mistress)</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -2551,12 +2539,12 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/chosen (0.90)</t>
+          <t>/unit/mistress (0.80)</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/chosen</t>
+          <t>https://6th.whfb.app/unit/mistress</t>
         </is>
       </c>
       <c r="I43" s="11" t="n"/>
@@ -2570,12 +2558,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Cold One Chariot</t>
+          <t>Splashback</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Cold One Chariot</t>
+          <t>War Hydra &gt; Variant War Hydra &gt; Royal War Hydra</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -2595,14 +2583,10 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>/unit/cold-one-chariot (1.00)</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/cold-one-chariot</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr"/>
       <c r="I44" s="11" t="n"/>
       <c r="J44" s="11" t="n"/>
     </row>
@@ -2614,12 +2598,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Daerlythe's Aura</t>
+          <t>The Hand of Khaine</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>War Hydra &gt; Variant War Hydra &gt; Spellthirster</t>
+          <t>Malekith, Witch King of Naggaroth &gt; The Hand of Khaine</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -2639,10 +2623,14 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr"/>
+          <t>/magic-item/hand-of-khaine-artefact-and-skill (0.80)</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/magic-item/hand-of-khaine-artefact-and-skill</t>
+        </is>
+      </c>
       <c r="I45" s="11" t="n"/>
       <c r="J45" s="11" t="n"/>
     </row>
@@ -2654,12 +2642,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Hate High Elves</t>
+          <t>Veteran</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>War Hydra &gt; Variant War Hydra &gt; Veteran War Hydra</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -2679,12 +2667,12 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>/army/high-elves (0.80)</t>
+          <t>/unit/veteran (1.00)</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/army/high-elves</t>
+          <t>https://6th.whfb.app/unit/veteran</t>
         </is>
       </c>
       <c r="I46" s="11" t="n"/>
@@ -2698,17 +2686,17 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Malekith's Weapons</t>
+          <t>Birdmen of Catrazza</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Malekith, Witch King of Naggaroth</t>
+          <t>Birdmen of Catrazza</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2723,12 +2711,12 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>/unit/malekith (0.90)</t>
+          <t>/unit/birdman-daddallos-birdmen-of-catrazza (0.80)</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/malekith</t>
+          <t>https://6th.whfb.app/unit/birdman-daddallos-birdmen-of-catrazza</t>
         </is>
       </c>
       <c r="I47" s="11" t="n"/>
@@ -2742,17 +2730,17 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Mentally Scarred</t>
+          <t>Brazanga's Besiegers</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>War Hydra &gt; Variant War Hydra &gt; Royal War Hydra</t>
+          <t>Brazanga's Besiegers</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -2767,10 +2755,14 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr"/>
+          <t>/unit/besieger-braganzas-besiegers (0.80)</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/besieger-braganzas-besiegers</t>
+        </is>
+      </c>
       <c r="I48" s="11" t="n"/>
       <c r="J48" s="11" t="n"/>
     </row>
@@ -2782,17 +2774,17 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Physically Weakened</t>
+          <t>Dark Emissary Spell List</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>War Hydra &gt; Variant War Hydra &gt; Spellthirster</t>
+          <t>Dark Emissary</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -2807,10 +2799,14 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H49" s="10" t="inlineStr"/>
+          <t>/unit/dark-emissary (0.90)</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/dark-emissary</t>
+        </is>
+      </c>
       <c r="I49" s="11" t="n"/>
       <c r="J49" s="11" t="n"/>
     </row>
@@ -2822,17 +2818,17 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Slaughterer's Blade</t>
+          <t>Galloper Gun Team</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Chaos Magic Items &gt; Magic Weapons &gt; Slaughterer's Blade</t>
+          <t>Bronzino's Galloper Guns &gt; Galloper Gun Team</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -2847,12 +2843,12 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/slaughters-blade (0.66)</t>
+          <t>/special-rules/galloper-gun (0.90)</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/slaughters-blade</t>
+          <t>https://6th.whfb.app/special-rules/galloper-gun</t>
         </is>
       </c>
       <c r="I50" s="11" t="n"/>
@@ -2866,17 +2862,17 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Sorcerer</t>
+          <t>Master Gunner Bronzino</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Malekith, Witch King of Naggaroth</t>
+          <t>Bronzino's Galloper Guns &gt; Master Gunner Bronzino</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2891,12 +2887,12 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>/unit/sorcerer (1.00)</t>
+          <t>/unit/master (0.90)</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/sorcerer</t>
+          <t>https://6th.whfb.app/unit/master</t>
         </is>
       </c>
       <c r="I51" s="11" t="n"/>
@@ -2910,17 +2906,17 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Speed of Slaanesh (Mistress)</t>
+          <t>The Bearmen of Urslo</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Devoted of Slaanesh &gt; Speed of Slaanesh (Mistress)</t>
+          <t>Beorg Bearstruck and the Bearmen of Urslo</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -2935,12 +2931,12 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>/unit/mistress (0.80)</t>
+          <t>/special-rules/for-hire-bearmen-of-urslo (0.59)</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/mistress</t>
+          <t>https://6th.whfb.app/special-rules/for-hire-bearmen-of-urslo</t>
         </is>
       </c>
       <c r="I52" s="11" t="n"/>
@@ -2954,17 +2950,17 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Splashback</t>
+          <t>Flame Cannon Misfire</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>War Hydra &gt; Variant War Hydra &gt; Royal War Hydra</t>
+          <t>Flame Cannon</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Dwarfs.cat</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -2979,10 +2975,14 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H53" s="10" t="inlineStr"/>
+          <t>/special-rules/flame-cannon (0.90)</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/special-rules/flame-cannon</t>
+        </is>
+      </c>
       <c r="I53" s="11" t="n"/>
       <c r="J53" s="11" t="n"/>
     </row>
@@ -2994,17 +2994,17 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>The Hand of Khaine</t>
+          <t>Gyrocopter</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Malekith, Witch King of Naggaroth &gt; The Hand of Khaine</t>
+          <t>Gyrocopter</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Dwarfs.cat</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/hand-of-khaine-artefact-and-skill (0.80)</t>
+          <t>/unit/gyrocopter (1.00)</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/hand-of-khaine-artefact-and-skill</t>
+          <t>https://6th.whfb.app/unit/gyrocopter</t>
         </is>
       </c>
       <c r="I54" s="11" t="n"/>
@@ -3038,17 +3038,17 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Veteran</t>
+          <t>Master Rune of Switftness</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>War Hydra &gt; Variant War Hydra &gt; Veteran War Hydra</t>
+          <t>Weapon Runes &gt; Master Rune of Switftness</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Dwarfs.cat</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>/unit/veteran (1.00)</t>
+          <t>/unit/master (0.90)</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/veteran</t>
+          <t>https://6th.whfb.app/unit/master</t>
         </is>
       </c>
       <c r="I55" s="11" t="n"/>
@@ -3082,17 +3082,17 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Birdmen of Catrazza</t>
+          <t>Organ Gun Misfire</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Birdmen of Catrazza</t>
+          <t>Organ Gun</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Dwarfs.cat</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>/unit/birdman-daddallos-birdmen-of-catrazza (0.80)</t>
+          <t>/special-rules/organ-gun (0.90)</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/birdman-daddallos-birdmen-of-catrazza</t>
+          <t>https://6th.whfb.app/special-rules/organ-gun</t>
         </is>
       </c>
       <c r="I56" s="11" t="n"/>
@@ -3126,17 +3126,17 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Brazanga's Besiegers</t>
+          <t>Rule of Pride</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Brazanga's Besiegers</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Dwarfs.cat</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -3151,14 +3151,10 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>/unit/besieger-braganzas-besiegers (0.80)</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/besieger-braganzas-besiegers</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr"/>
       <c r="I57" s="11" t="n"/>
       <c r="J57" s="11" t="n"/>
     </row>
@@ -3170,17 +3166,17 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Dark Emissary Spell List</t>
+          <t>Centigors</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Dark Emissary</t>
+          <t>Centigors</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -3195,12 +3191,12 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>/unit/dark-emissary (0.90)</t>
+          <t>/unit/centigor (1.00)</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/dark-emissary</t>
+          <t>https://6th.whfb.app/unit/centigor</t>
         </is>
       </c>
       <c r="I58" s="11" t="n"/>
@@ -3214,17 +3210,17 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Galloper Gun Team</t>
+          <t>Diabolic Splendour</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Bronzino's Galloper Guns &gt; Galloper Gun Team</t>
+          <t>Daemonic Gifts</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -3239,12 +3235,12 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/galloper-gun (0.90)</t>
+          <t>/magic-item/diabolical-splendour (0.66)</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/galloper-gun</t>
+          <t>https://6th.whfb.app/magic-item/diabolical-splendour</t>
         </is>
       </c>
       <c r="I59" s="11" t="n"/>
@@ -3258,17 +3254,17 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Master Gunner Bronzino</t>
+          <t>Firewyrn of Tzeentch</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Bronzino's Galloper Guns &gt; Master Gunner Bronzino</t>
+          <t>Spawn of Chaos &gt; Spawn of Chaos &gt; Spawn of the Gods &gt; Firewyrn of Tzeentch</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -3283,12 +3279,12 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>/unit/master (0.90)</t>
+          <t>/special-rules/regeneration (0.90)</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/master</t>
+          <t>https://6th.whfb.app/special-rules/regeneration</t>
         </is>
       </c>
       <c r="I60" s="11" t="n"/>
@@ -3302,17 +3298,17 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>The Bearmen of Urslo</t>
+          <t>Giant Attacks</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Beorg Bearstruck and the Bearmen of Urslo</t>
+          <t>Chaos Giant</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -3327,12 +3323,12 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/for-hire-bearmen-of-urslo (0.59)</t>
+          <t>/unit/giant (0.90)</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/for-hire-bearmen-of-urslo</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I61" s="11" t="n"/>
@@ -3346,17 +3342,17 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Flame Cannon Misfire</t>
+          <t>Move Over Obstacles</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Flame Cannon</t>
+          <t>Chaos Giant</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -3371,12 +3367,12 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/flame-cannon (0.90)</t>
+          <t>/special-rules/move-giants (0.90)</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/flame-cannon</t>
+          <t>https://6th.whfb.app/special-rules/move-giants</t>
         </is>
       </c>
       <c r="I62" s="11" t="n"/>
@@ -3390,17 +3386,17 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Gyrocopter</t>
+          <t>Slaughterer's Blade</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Gyrocopter</t>
+          <t>Magic Weapons &gt; Slaughterer's Blade</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -3415,12 +3411,12 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>/unit/gyrocopter (1.00)</t>
+          <t>/magic-item/slaughters-blade (0.66)</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/gyrocopter</t>
+          <t>https://6th.whfb.app/magic-item/slaughters-blade</t>
         </is>
       </c>
       <c r="I63" s="11" t="n"/>
@@ -3434,17 +3430,17 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Master Rune of Switftness</t>
+          <t>Staff of Darkoath</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Weapon Runes &gt; Master Rune of Switftness</t>
+          <t>Arcane Items</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3459,12 +3455,12 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>/unit/master (0.90)</t>
+          <t>/magic-item/staff-of-darkoth (0.68)</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/master</t>
+          <t>https://6th.whfb.app/magic-item/staff-of-darkoth</t>
         </is>
       </c>
       <c r="I64" s="11" t="n"/>
@@ -3478,17 +3474,17 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Organ Gun Misfire</t>
+          <t>Two Breath Weapons</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Organ Gun</t>
+          <t>Mount &gt; Dragon of Chaos</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -3503,12 +3499,12 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/organ-gun (0.90)</t>
+          <t>/special-rules/breath-weapons (0.80)</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/organ-gun</t>
+          <t>https://6th.whfb.app/special-rules/breath-weapons</t>
         </is>
       </c>
       <c r="I65" s="11" t="n"/>
@@ -3522,17 +3518,17 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Rule of Pride</t>
+          <t>Vitriolic Totem</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Magic Banners</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -3547,10 +3543,14 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr"/>
+          <t>/magic-item/vitrolic-totem (0.68)</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/magic-item/vitrolic-totem</t>
+        </is>
+      </c>
       <c r="I66" s="11" t="n"/>
       <c r="J66" s="11" t="n"/>
     </row>
@@ -3562,17 +3562,17 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Centigors</t>
+          <t>Banner of Ellyrion</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Centigors</t>
+          <t>Magic Banners &gt; Banner of Ellyrion</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>/unit/centigor (1.00)</t>
+          <t>/magic-item/banner-of-ellryion (0.66)</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/centigor</t>
+          <t>https://6th.whfb.app/magic-item/banner-of-ellryion</t>
         </is>
       </c>
       <c r="I67" s="11" t="n"/>
@@ -3606,17 +3606,17 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Diabolic Splendour</t>
+          <t>Bow of the Searfarer</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Daemonic Gifts</t>
+          <t>Magic Weapons &gt; Bow of the Searfarer</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/diabolical-splendour (0.66)</t>
+          <t>/weapons/bow (0.90)</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/diabolical-splendour</t>
+          <t>https://6th.whfb.app/weapons/bow</t>
         </is>
       </c>
       <c r="I68" s="11" t="n"/>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Firewyrn of Tzeentch</t>
+          <t>Channeler</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Spawn of Chaos &gt; Spawn of Chaos &gt; Spawn of the Gods &gt; Firewyrn of Tzeentch</t>
+          <t>Honours &gt; Channeler</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/regeneration (0.90)</t>
+          <t>/magic-item/channeller (0.66)</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/regeneration</t>
+          <t>https://6th.whfb.app/magic-item/channeller</t>
         </is>
       </c>
       <c r="I69" s="11" t="n"/>
@@ -3694,17 +3694,17 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Giant Attacks</t>
+          <t>Fight In Three Ranks</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Chaos Giant</t>
+          <t>Spearmen</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (0.90)</t>
+          <t>/skirmishers/ranks-skirmishers (0.80)</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/giant</t>
+          <t>https://6th.whfb.app/skirmishers/ranks-skirmishers</t>
         </is>
       </c>
       <c r="I70" s="11" t="n"/>
@@ -3738,17 +3738,17 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Move Over Obstacles</t>
+          <t>Fight In Three Ranks</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Chaos Giant</t>
+          <t>Lothern Sea Guard</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/move-giants (0.90)</t>
+          <t>/skirmishers/ranks-skirmishers (0.80)</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/move-giants</t>
+          <t>https://6th.whfb.app/skirmishers/ranks-skirmishers</t>
         </is>
       </c>
       <c r="I71" s="11" t="n"/>
@@ -3782,17 +3782,17 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Slaughterer's Blade</t>
+          <t>Intruige at Court</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Magic Weapons &gt; Slaughterer's Blade</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/slaughters-blade (0.66)</t>
+          <t>/special-rules/intrigue-at-court (0.66)</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/slaughters-blade</t>
+          <t>https://6th.whfb.app/special-rules/intrigue-at-court</t>
         </is>
       </c>
       <c r="I72" s="11" t="n"/>
@@ -3826,17 +3826,17 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Staff of Darkoath</t>
+          <t>Tiranoc Chariot</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Arcane Items</t>
+          <t>Tiranoc Chariot</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/staff-of-darkoth (0.68)</t>
+          <t>/unit/tiranoc-chariot (1.00)</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/staff-of-darkoth</t>
+          <t>https://6th.whfb.app/unit/tiranoc-chariot</t>
         </is>
       </c>
       <c r="I73" s="11" t="n"/>
@@ -3870,17 +3870,17 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Two Breath Weapons</t>
+          <t>Blessed Spawning of Tlzazcotl</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Mount &gt; Dragon of Chaos</t>
+          <t>Sacred Spawnings &gt; Blessed Spawning of Tlzazcotl</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Lizardmen.cat</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/breath-weapons (0.80)</t>
+          <t>/special-rules/pawn (0.80)</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/breath-weapons</t>
+          <t>https://6th.whfb.app/special-rules/pawn</t>
         </is>
       </c>
       <c r="I74" s="11" t="n"/>
@@ -3914,17 +3914,17 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Vitriolic Totem</t>
+          <t>Cupped Hands of the Hold Ones</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Magic Banners</t>
+          <t>Sacred Plaques &gt; Cupped Hands of the Hold Ones</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Lizardmen.cat</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/vitrolic-totem (0.68)</t>
+          <t>/movement/hold-movement (0.80)</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/vitrolic-totem</t>
+          <t>https://6th.whfb.app/movement/hold-movement</t>
         </is>
       </c>
       <c r="I75" s="11" t="n"/>
@@ -3958,17 +3958,17 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Banner of Ellyrion</t>
+          <t>Bull Rhinoxen</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Magic Banners &gt; Banner of Ellyrion</t>
+          <t>Rhinox Cavalry &gt; Bull Rhinox &gt; Bull Rhinox</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/banner-of-ellryion (0.66)</t>
+          <t>/unit/rhinox (0.80)</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/banner-of-ellryion</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I76" s="11" t="n"/>
@@ -4002,17 +4002,17 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Bow of the Searfarer</t>
+          <t>Greasus Goldtooth</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Magic Weapons &gt; Bow of the Searfarer</t>
+          <t>Greasus Goldtooth</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>/weapons/bow (0.90)</t>
+          <t>/unit/greasus-goldtooth (1.00)</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/bow</t>
+          <t>https://6th.whfb.app/unit/greasus-goldtooth</t>
         </is>
       </c>
       <c r="I77" s="11" t="n"/>
@@ -4046,17 +4046,17 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Channeler</t>
+          <t>Gut Magic Miscast</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Honours &gt; Channeler</t>
+          <t>shared; used by Butcher, Scrag the Slaughterer, Slaughtermaster</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/channeller (0.66)</t>
+          <t>/spell-lists/gut-magic (0.90)</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/channeller</t>
+          <t>https://6th.whfb.app/spell-lists/gut-magic</t>
         </is>
       </c>
       <c r="I78" s="11" t="n"/>
@@ -4090,17 +4090,17 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Fight In Three Ranks</t>
+          <t>Harpoon Crossbow</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Spearmen</t>
+          <t>Hunter &gt; Harpoon Crossbow</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>/skirmishers/ranks-skirmishers (0.80)</t>
+          <t>/weapons/bow (0.80)</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/skirmishers/ranks-skirmishers</t>
+          <t>https://6th.whfb.app/weapons/bow</t>
         </is>
       </c>
       <c r="I79" s="11" t="n"/>
@@ -4134,17 +4134,17 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Fight In Three Ranks</t>
+          <t>Ironfist</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Lothern Sea Guard</t>
+          <t>shared; used by Bruiser, Ogre Bulls, Rhinox Cavalry, Tyrant</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>/skirmishers/ranks-skirmishers (0.80)</t>
+          <t>/unit/garagrim-ironfist (0.80)</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/skirmishers/ranks-skirmishers</t>
+          <t>https://6th.whfb.app/unit/garagrim-ironfist</t>
         </is>
       </c>
       <c r="I80" s="11" t="n"/>
@@ -4178,17 +4178,17 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Intruige at Court</t>
+          <t>Ironfists (Rhinox Riders)</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Rhinox Cavalry &gt; Ironfists</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/intrigue-at-court (0.66)</t>
+          <t>/unit/rhinox (0.80)</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/intrigue-at-court</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I81" s="11" t="n"/>
@@ -4222,17 +4222,17 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Tiranoc Chariot</t>
+          <t>Mawseeker</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tiranoc Chariot</t>
+          <t>Big Names &gt; Mawseeker</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
@@ -4247,14 +4247,10 @@
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>/unit/tiranoc-chariot (1.00)</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/tiranoc-chariot</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr"/>
       <c r="I82" s="11" t="n"/>
       <c r="J82" s="11" t="n"/>
     </row>
@@ -4266,17 +4262,17 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Blessed Spawning of Tlzazcotl</t>
+          <t>Move Over Obstacles</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Sacred Spawnings &gt; Blessed Spawning of Tlzazcotl</t>
+          <t>Slavegiant</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Lizardmen.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
@@ -4291,12 +4287,12 @@
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/pawn (0.80)</t>
+          <t>/special-rules/move-giants (0.90)</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/pawn</t>
+          <t>https://6th.whfb.app/special-rules/move-giants</t>
         </is>
       </c>
       <c r="I83" s="11" t="n"/>
@@ -4310,17 +4306,17 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Cupped Hands of the Hold Ones</t>
+          <t>Rhinox Cavalry</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Sacred Plaques &gt; Cupped Hands of the Hold Ones</t>
+          <t>Rhinox Cavalry</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Lizardmen.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
@@ -4335,12 +4331,12 @@
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>/movement/hold-movement (0.80)</t>
+          <t>/unit/rhinox (0.90)</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/movement/hold-movement</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I84" s="11" t="n"/>
@@ -4354,12 +4350,12 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Bull Rhinoxen</t>
+          <t>Scrap Launcher</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry &gt; Bull Rhinox &gt; Bull Rhinox</t>
+          <t>Gnoblar Scraplauncher</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
@@ -4379,12 +4375,12 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>/unit/rhinox (0.80)</t>
+          <t>/unit/scraplauncher (0.67)</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
+          <t>https://6th.whfb.app/unit/scraplauncher</t>
         </is>
       </c>
       <c r="I85" s="11" t="n"/>
@@ -4398,12 +4394,12 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Greasus Goldtooth</t>
+          <t>Skrag the Slaughterer</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Greasus Goldtooth</t>
+          <t>Scrag the Slaughterer</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
@@ -4423,12 +4419,12 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>/unit/greasus-goldtooth (1.00)</t>
+          <t>/unit/skrag-the-slaughterer (1.00)</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/greasus-goldtooth</t>
+          <t>https://6th.whfb.app/unit/skrag-the-slaughterer</t>
         </is>
       </c>
       <c r="I86" s="11" t="n"/>
@@ -4442,12 +4438,12 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Gut Magic Miscast</t>
+          <t>Slavegiant Attacks</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Butcher, Scrag the Slaughterer, Slaughtermaster</t>
+          <t>Slavegiant</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -4467,12 +4463,12 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>/spell-lists/gut-magic (0.90)</t>
+          <t>/unit/slavegiant (0.90)</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/spell-lists/gut-magic</t>
+          <t>https://6th.whfb.app/unit/slavegiant</t>
         </is>
       </c>
       <c r="I87" s="11" t="n"/>
@@ -4486,12 +4482,12 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Harpoon Crossbow</t>
+          <t>Stump-Blades</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Hunter &gt; Harpoon Crossbow</t>
+          <t>Scrag the Slaughterer</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
@@ -4511,14 +4507,10 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>/weapons/bow (0.80)</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/weapons/bow</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr"/>
       <c r="I88" s="11" t="n"/>
       <c r="J88" s="11" t="n"/>
     </row>
@@ -4530,12 +4522,12 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Ironfist</t>
+          <t>The Scepter of the Titans</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Bruiser, Ogre Bulls, Rhinox Cavalry, Tyrant</t>
+          <t>Greasus Goldtooth &gt; The Scepter of the Titans</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -4555,12 +4547,12 @@
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>/unit/garagrim-ironfist (0.80)</t>
+          <t>/magic-item/sceptre-of-the-titans (0.61)</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/garagrim-ironfist</t>
+          <t>https://6th.whfb.app/magic-item/sceptre-of-the-titans</t>
         </is>
       </c>
       <c r="I89" s="11" t="n"/>
@@ -4574,12 +4566,12 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Ironfists (Rhinox Riders)</t>
+          <t>Thunderous Charge</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry &gt; Ironfists</t>
+          <t>Rhinox Cavalry</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
@@ -4599,12 +4591,12 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>/unit/rhinox (0.80)</t>
+          <t>/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish (0.80)</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
+          <t>https://6th.whfb.app/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish</t>
         </is>
       </c>
       <c r="I90" s="11" t="n"/>
@@ -4618,12 +4610,12 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>Mawseeker</t>
+          <t>Wallcrusher</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Big Names &gt; Mawseeker</t>
+          <t>Big Names &gt; Wallcrusher</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
@@ -4643,10 +4635,14 @@
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H91" s="10" t="inlineStr"/>
+          <t>/unit/crusher (0.80)</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/crusher</t>
+        </is>
+      </c>
       <c r="I91" s="11" t="n"/>
       <c r="J91" s="11" t="n"/>
     </row>
@@ -4658,12 +4654,12 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Move Over Obstacles</t>
+          <t>Yheetee Ice Weapons</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Slavegiant</t>
+          <t>Yheetees &gt; Yheetee Ice Weapons</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
@@ -4683,12 +4679,12 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/move-giants (0.90)</t>
+          <t>/weapons/ice-weapons (0.80)</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/move-giants</t>
+          <t>https://6th.whfb.app/weapons/ice-weapons</t>
         </is>
       </c>
       <c r="I92" s="11" t="n"/>
@@ -4702,17 +4698,17 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry</t>
+          <t>'Eadbuttin' 'At</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry</t>
+          <t>Enchanted Items &gt; 'Eadbuttin' 'At</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
@@ -4727,12 +4723,12 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>/unit/rhinox (0.90)</t>
+          <t>/special-rules/eadbutt (0.90)</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
+          <t>https://6th.whfb.app/special-rules/eadbutt</t>
         </is>
       </c>
       <c r="I93" s="11" t="n"/>
@@ -4746,17 +4742,17 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Scrap Launcher</t>
+          <t>Fungus Buster Brew</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Gnoblar Scraplauncher</t>
+          <t>Shiny Stuff &gt; Fungus Buster Brew</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
@@ -4771,14 +4767,10 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>/unit/scraplauncher (0.67)</t>
-        </is>
-      </c>
-      <c r="H94" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/scraplauncher</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr"/>
       <c r="I94" s="11" t="n"/>
       <c r="J94" s="11" t="n"/>
     </row>
@@ -4790,17 +4782,17 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Skrag the Slaughterer</t>
+          <t>Giant</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Scrag the Slaughterer</t>
+          <t>Giant</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
@@ -4815,12 +4807,12 @@
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>/unit/skrag-the-slaughterer (1.00)</t>
+          <t>/unit/giant (1.00)</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/skrag-the-slaughterer</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I95" s="11" t="n"/>
@@ -4834,17 +4826,17 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Slavegiant Attacks</t>
+          <t>Giant Spiders</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Slavegiant</t>
+          <t>Goblin Spider Riders</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
@@ -4859,12 +4851,12 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>/unit/slavegiant (0.90)</t>
+          <t>/unit/giant (0.90)</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/slavegiant</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I96" s="11" t="n"/>
@@ -4878,17 +4870,17 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>Stump-Blades</t>
+          <t>Giants Movement</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Scrag the Slaughterer</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
@@ -4903,10 +4895,14 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H97" s="10" t="inlineStr"/>
+          <t>/unit/giant (0.90)</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/giant</t>
+        </is>
+      </c>
       <c r="I97" s="11" t="n"/>
       <c r="J97" s="11" t="n"/>
     </row>
@@ -4918,17 +4914,17 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>The Scepter of the Titans</t>
+          <t>Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Greasus Goldtooth &gt; The Scepter of the Titans</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -4943,12 +4939,12 @@
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/sceptre-of-the-titans (0.61)</t>
+          <t>/unit/squig (0.80)</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/sceptre-of-the-titans</t>
+          <t>https://6th.whfb.app/unit/squig</t>
         </is>
       </c>
       <c r="I98" s="11" t="n"/>
@@ -4962,17 +4958,17 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>Thunderous Charge</t>
+          <t>Gobbla's Movement</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
@@ -4987,12 +4983,12 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish (0.80)</t>
+          <t>/special-rules/move-giants (0.80)</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish</t>
+          <t>https://6th.whfb.app/special-rules/move-giants</t>
         </is>
       </c>
       <c r="I99" s="11" t="n"/>
@@ -5006,17 +5002,17 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Wallcrusher</t>
+          <t>Hate Dwarfs</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Big Names &gt; Wallcrusher</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
@@ -5031,12 +5027,12 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>/unit/crusher (0.80)</t>
+          <t>/unit/dwarf (0.80)</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/crusher</t>
+          <t>https://6th.whfb.app/unit/dwarf</t>
         </is>
       </c>
       <c r="I100" s="11" t="n"/>
@@ -5050,17 +5046,17 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>Yheetee Ice Weapons</t>
+          <t>Insatiable Appetite</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Yheetees &gt; Yheetee Ice Weapons</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
@@ -5075,14 +5071,10 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>/weapons/ice-weapons (0.80)</t>
-        </is>
-      </c>
-      <c r="H101" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/weapons/ice-weapons</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H101" s="10" t="inlineStr"/>
       <c r="I101" s="11" t="n"/>
       <c r="J101" s="11" t="n"/>
     </row>
@@ -5094,12 +5086,12 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>'Eadbuttin' 'At</t>
+          <t>Moving Fanatics into Obstacles</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Enchanted Items &gt; 'Eadbuttin' 'At</t>
+          <t>Night Goblins &gt; Fanatics</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
@@ -5119,12 +5111,12 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/eadbutt (0.90)</t>
+          <t>/skirmishers/moving (0.90)</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/eadbutt</t>
+          <t>https://6th.whfb.app/skirmishers/moving</t>
         </is>
       </c>
       <c r="I102" s="11" t="n"/>
@@ -5138,12 +5130,12 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>Fungus Buster Brew</t>
+          <t>Porko's Pigstikka</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Shiny Stuff &gt; Fungus Buster Brew</t>
+          <t>Magic Weapons &gt; Porko's Pigstikka</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -5163,10 +5155,14 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H103" s="10" t="inlineStr"/>
+          <t>/magic-item/porks-pigstikka (0.68)</t>
+        </is>
+      </c>
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/magic-item/porks-pigstikka</t>
+        </is>
+      </c>
       <c r="I103" s="11" t="n"/>
       <c r="J103" s="11" t="n"/>
     </row>
@@ -5178,12 +5174,12 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Giant</t>
+          <t>Shooting at Skarsnik &amp; Gobbla</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Giant</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
@@ -5203,12 +5199,12 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (1.00)</t>
+          <t>/faq/shooting (0.90)</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/giant</t>
+          <t>https://6th.whfb.app/faq/shooting</t>
         </is>
       </c>
       <c r="I104" s="11" t="n"/>
@@ -5222,12 +5218,12 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>Giant Spiders</t>
+          <t>Skarsnik's Prodder</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Goblin Spider Riders</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -5247,14 +5243,10 @@
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (0.90)</t>
-        </is>
-      </c>
-      <c r="H105" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/giant</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr"/>
       <c r="I105" s="11" t="n"/>
       <c r="J105" s="11" t="n"/>
     </row>
@@ -5266,12 +5258,12 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Giants Movement</t>
+          <t>Skarsnik's Prodder</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
@@ -5291,14 +5283,10 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (0.90)</t>
-        </is>
-      </c>
-      <c r="H106" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/giant</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="inlineStr"/>
       <c r="I106" s="11" t="n"/>
       <c r="J106" s="11" t="n"/>
     </row>
@@ -5310,12 +5298,12 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>Gobbla the Cave Squig</t>
+          <t>Staff of Badumm</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+          <t>Arcane Items &gt; Unique Items &gt; Staff of Badumm</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
@@ -5335,12 +5323,12 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>/unit/squig (0.80)</t>
+          <t>/magic-item/staff-of-baduumm (0.68)</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/squig</t>
+          <t>https://6th.whfb.app/magic-item/staff-of-baduumm</t>
         </is>
       </c>
       <c r="I107" s="11" t="n"/>
@@ -5354,12 +5342,12 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Gobbla's Movement</t>
+          <t>The Blasted Banner</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+          <t>Grimgor Ironhide &gt; Bodyguard &gt; Da Immortulz &gt; The Blasted Banner</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
@@ -5379,12 +5367,12 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/move-giants (0.80)</t>
+          <t>/magic-item/the-beast-banner (0.62)</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/move-giants</t>
+          <t>https://6th.whfb.app/magic-item/the-beast-banner</t>
         </is>
       </c>
       <c r="I108" s="11" t="n"/>
@@ -5398,12 +5386,12 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>Hate Dwarfs</t>
+          <t>Warboss Umm's Best Big Boss 'At</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Talismans &gt; Warboss Umm's Best Big Boss 'At</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
@@ -5423,12 +5411,12 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>/unit/dwarf (0.80)</t>
+          <t>/magic-item/warboss-umms-best-big-bosss-at (0.69)</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/dwarf</t>
+          <t>https://6th.whfb.app/magic-item/warboss-umms-best-big-bosss-at</t>
         </is>
       </c>
       <c r="I109" s="11" t="n"/>
@@ -5442,17 +5430,17 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Insatiable Appetite</t>
+          <t>Beastmaster</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+          <t>Master Moulder</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
@@ -5467,10 +5455,14 @@
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H110" s="10" t="inlineStr"/>
+          <t>/unit/beastmaster (1.00)</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
+        </is>
+      </c>
       <c r="I110" s="11" t="n"/>
       <c r="J110" s="11" t="n"/>
     </row>
@@ -5482,17 +5474,17 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>Moving Fanatics into Obstacles</t>
+          <t>Beastmaster</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Night Goblins &gt; Fanatics</t>
+          <t>Master Mutator</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
@@ -5507,12 +5499,12 @@
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
-          <t>/skirmishers/moving (0.90)</t>
+          <t>/unit/beastmaster (1.00)</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/skirmishers/moving</t>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
         </is>
       </c>
       <c r="I111" s="11" t="n"/>
@@ -5526,17 +5518,17 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Porko's Pigstikka</t>
+          <t>Beastmaster</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Magic Weapons &gt; Porko's Pigstikka</t>
+          <t>Harbinger of Mutation</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
@@ -5551,12 +5543,12 @@
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/porks-pigstikka (0.68)</t>
+          <t>/unit/beastmaster (1.00)</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/porks-pigstikka</t>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
         </is>
       </c>
       <c r="I112" s="11" t="n"/>
@@ -5570,17 +5562,17 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>Shooting at Skarsnik &amp; Gobbla</t>
+          <t>Boneripper</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+          <t>Grey Seer Thanquol &amp; Boneripper</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
@@ -5595,12 +5587,12 @@
       </c>
       <c r="G113" s="9" t="inlineStr">
         <is>
-          <t>/faq/shooting (0.90)</t>
+          <t>/unit/boneripper (1.00)</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/shooting</t>
+          <t>https://6th.whfb.app/unit/boneripper</t>
         </is>
       </c>
       <c r="I113" s="11" t="n"/>
@@ -5614,17 +5606,17 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Skarsnik's Prodder</t>
+          <t>Cursed Blade of Delerium</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
+          <t>Magic Weapons &gt; Cursed Blade of Delerium</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
@@ -5639,10 +5631,14 @@
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H114" s="10" t="inlineStr"/>
+          <t>/magic-item/cursed-blade-of-delirium (0.67)</t>
+        </is>
+      </c>
+      <c r="H114" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/magic-item/cursed-blade-of-delirium</t>
+        </is>
+      </c>
       <c r="I114" s="11" t="n"/>
       <c r="J114" s="11" t="n"/>
     </row>
@@ -5654,17 +5650,17 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>Skarsnik's Prodder</t>
+          <t>Daemonic Instability</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
@@ -5679,10 +5675,14 @@
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H115" s="10" t="inlineStr"/>
+          <t>/special-rules/daemonic (0.90)</t>
+        </is>
+      </c>
+      <c r="H115" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/special-rules/daemonic</t>
+        </is>
+      </c>
       <c r="I115" s="11" t="n"/>
       <c r="J115" s="11" t="n"/>
     </row>
@@ -5694,17 +5694,17 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Staff of Badumm</t>
+          <t>Doom Glaive</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Arcane Items &gt; Unique Items &gt; Staff of Badumm</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
@@ -5719,14 +5719,10 @@
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/staff-of-baduumm (0.68)</t>
-        </is>
-      </c>
-      <c r="H116" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/staff-of-baduumm</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="inlineStr"/>
       <c r="I116" s="11" t="n"/>
       <c r="J116" s="11" t="n"/>
     </row>
@@ -5738,17 +5734,17 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>The Blasted Banner</t>
+          <t>Doomwheel</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Grimgor Ironhide &gt; Bodyguard &gt; Da Immortulz &gt; The Blasted Banner</t>
+          <t>Doomwheel</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
@@ -5763,12 +5759,12 @@
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/the-beast-banner (0.62)</t>
+          <t>/movement/wheel (0.80)</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/the-beast-banner</t>
+          <t>https://6th.whfb.app/movement/wheel</t>
         </is>
       </c>
       <c r="I117" s="11" t="n"/>
@@ -5782,17 +5778,17 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Warboss Umm's Best Big Boss 'At</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Talismans &gt; Warboss Umm's Best Big Boss 'At</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
@@ -5807,12 +5803,12 @@
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/warboss-umms-best-big-bosss-at (0.69)</t>
+          <t>/unit/festering-chantor (1.00)</t>
         </is>
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/warboss-umms-best-big-bosss-at</t>
+          <t>https://6th.whfb.app/unit/festering-chantor</t>
         </is>
       </c>
       <c r="I118" s="11" t="n"/>
@@ -5826,12 +5822,12 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
+          <t>Harbinger of Mutation</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Master Moulder</t>
+          <t>Harbinger of Mutation</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
@@ -5851,12 +5847,12 @@
       </c>
       <c r="G119" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
+          <t>/unit/harbinger (0.90)</t>
         </is>
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
+          <t>https://6th.whfb.app/unit/harbinger</t>
         </is>
       </c>
       <c r="I119" s="11" t="n"/>
@@ -5870,12 +5866,12 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
+          <t>High Ranking</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Master Mutator</t>
+          <t>Grey Seer</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
@@ -5895,14 +5891,10 @@
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
-        </is>
-      </c>
-      <c r="H120" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="inlineStr"/>
       <c r="I120" s="11" t="n"/>
       <c r="J120" s="11" t="n"/>
     </row>
@@ -5914,12 +5906,12 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
+          <t>Horned Rat Incarnate</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Harbinger of Mutation</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
@@ -5939,14 +5931,10 @@
       </c>
       <c r="G121" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
-        </is>
-      </c>
-      <c r="H121" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="inlineStr"/>
       <c r="I121" s="11" t="n"/>
       <c r="J121" s="11" t="n"/>
     </row>
@@ -5958,12 +5946,12 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Boneripper</t>
+          <t>Plague Rats</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Grey Seer Thanquol &amp; Boneripper</t>
+          <t>Rat Swarm &gt; Plague Rats</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
@@ -5983,12 +5971,12 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>/unit/boneripper (1.00)</t>
+          <t>/spell/plague (0.90)</t>
         </is>
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/boneripper</t>
+          <t>https://6th.whfb.app/spell/plague</t>
         </is>
       </c>
       <c r="I122" s="11" t="n"/>
@@ -6002,12 +5990,12 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>Cursed Blade of Delerium</t>
+          <t>Ratling Gun Misfire</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Magic Weapons &gt; Cursed Blade of Delerium</t>
+          <t>Weapon Team &gt; Ratling Gun</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
@@ -6027,12 +6015,12 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/cursed-blade-of-delirium (0.67)</t>
+          <t>/weapons/ratling-gun (0.90)</t>
         </is>
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/cursed-blade-of-delirium</t>
+          <t>https://6th.whfb.app/weapons/ratling-gun</t>
         </is>
       </c>
       <c r="I123" s="11" t="n"/>
@@ -6046,7 +6034,7 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Instability</t>
+          <t>Stands Alone</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
@@ -6071,14 +6059,10 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/daemonic (0.90)</t>
-        </is>
-      </c>
-      <c r="H124" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/special-rules/daemonic</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr"/>
       <c r="I124" s="11" t="n"/>
       <c r="J124" s="11" t="n"/>
     </row>
@@ -6090,7 +6074,7 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>Doom Glaive</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
@@ -6130,12 +6114,12 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Doomwheel</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Doomwheel</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
@@ -6155,12 +6139,12 @@
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>/movement/wheel (0.80)</t>
+          <t>/unit/warlock-engineer (1.00)</t>
         </is>
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/movement/wheel</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I126" s="11" t="n"/>
@@ -6174,12 +6158,12 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>Festering Chantor</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Festering Chantor</t>
+          <t>Warlock Master</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
@@ -6199,12 +6183,12 @@
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>/unit/festering-chantor (1.00)</t>
+          <t>/unit/warlock-engineer (1.00)</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/festering-chantor</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I127" s="11" t="n"/>
@@ -6218,12 +6202,12 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Harbinger of Mutation</t>
+          <t>Warpfire Thrower Misfire</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Harbinger of Mutation</t>
+          <t>Weapon Team &gt; Warpfire Thrower</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
@@ -6243,12 +6227,12 @@
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>/unit/harbinger (0.90)</t>
+          <t>/weapons/warpfire-thrower (0.90)</t>
         </is>
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/harbinger</t>
+          <t>https://6th.whfb.app/weapons/warpfire-thrower</t>
         </is>
       </c>
       <c r="I128" s="11" t="n"/>
@@ -6262,17 +6246,17 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>High Ranking</t>
+          <t>Athandin</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Grey Seer</t>
+          <t>Valten, Exalted of Sigmar &gt; Athandin</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E129" s="9" t="inlineStr">
@@ -6287,10 +6271,14 @@
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H129" s="10" t="inlineStr"/>
+          <t>/special-rules/althandin (0.66)</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/special-rules/althandin</t>
+        </is>
+      </c>
       <c r="I129" s="11" t="n"/>
       <c r="J129" s="11" t="n"/>
     </row>
@@ -6302,17 +6290,17 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Horned Rat Incarnate</t>
+          <t>Charging with the Steam Tank</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Steam Tank</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E130" s="9" t="inlineStr">
@@ -6327,10 +6315,14 @@
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H130" s="10" t="inlineStr"/>
+          <t>/movement/charging (0.90)</t>
+        </is>
+      </c>
+      <c r="H130" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/movement/charging</t>
+        </is>
+      </c>
       <c r="I130" s="11" t="n"/>
       <c r="J130" s="11" t="n"/>
     </row>
@@ -6342,17 +6334,17 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>Plague Rats</t>
+          <t>Electoral Banner</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Rat Swarm &gt; Plague Rats</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E131" s="9" t="inlineStr">
@@ -6367,14 +6359,10 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>/spell/plague (0.90)</t>
-        </is>
-      </c>
-      <c r="H131" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/spell/plague</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H131" s="10" t="inlineStr"/>
       <c r="I131" s="11" t="n"/>
       <c r="J131" s="11" t="n"/>
     </row>
@@ -6386,17 +6374,17 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Ratling Gun Misfire</t>
+          <t>Fusilade</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Weapon Team &gt; Ratling Gun</t>
+          <t>Pistoliers</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E132" s="9" t="inlineStr">
@@ -6411,12 +6399,12 @@
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>/weapons/ratling-gun (0.90)</t>
+          <t>/special-rules/fusillade (0.66)</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/ratling-gun</t>
+          <t>https://6th.whfb.app/special-rules/fusillade</t>
         </is>
       </c>
       <c r="I132" s="11" t="n"/>
@@ -6430,17 +6418,17 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>Stands Alone</t>
+          <t>Helm of the Skavenslayer</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Magic Armour &gt; Magic Armour &gt; Helm of the Skavenslayer</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E133" s="9" t="inlineStr">
@@ -6455,10 +6443,14 @@
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H133" s="10" t="inlineStr"/>
+          <t>/army/skaven (0.80)</t>
+        </is>
+      </c>
+      <c r="H133" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/army/skaven</t>
+        </is>
+      </c>
       <c r="I133" s="11" t="n"/>
       <c r="J133" s="11" t="n"/>
     </row>
@@ -6470,17 +6462,17 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Parent and Detachment Units</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E134" s="9" t="inlineStr">
@@ -6495,10 +6487,14 @@
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H134" s="10" t="inlineStr"/>
+          <t>/warhammer-glossary/unit-warhammer-glossary (0.80)</t>
+        </is>
+      </c>
+      <c r="H134" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/warhammer-glossary/unit-warhammer-glossary</t>
+        </is>
+      </c>
       <c r="I134" s="11" t="n"/>
       <c r="J134" s="11" t="n"/>
     </row>
@@ -6510,17 +6506,17 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
+          <t>Shooting at the Steam Tank</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
+          <t>Steam Tank</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E135" s="9" t="inlineStr">
@@ -6535,12 +6531,12 @@
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>/unit/warlock-engineer (1.00)</t>
+          <t>/faq/shooting (0.90)</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+          <t>https://6th.whfb.app/faq/shooting</t>
         </is>
       </c>
       <c r="I135" s="11" t="n"/>
@@ -6554,17 +6550,17 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
+          <t>Shooting with the Steam Tank</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Warlock Master</t>
+          <t>Steam Tank</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E136" s="9" t="inlineStr">
@@ -6579,12 +6575,12 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>/unit/warlock-engineer (1.00)</t>
+          <t>/faq/shooting (0.90)</t>
         </is>
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+          <t>https://6th.whfb.app/faq/shooting</t>
         </is>
       </c>
       <c r="I136" s="11" t="n"/>
@@ -6598,17 +6594,17 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>Warpfire Thrower Misfire</t>
+          <t>Steam Points</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>Weapon Team &gt; Warpfire Thrower</t>
+          <t>Steam Tank</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E137" s="9" t="inlineStr">
@@ -6623,12 +6619,12 @@
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>/weapons/warpfire-thrower (0.90)</t>
+          <t>/special-rules/building-up-steam-points (0.80)</t>
         </is>
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/warpfire-thrower</t>
+          <t>https://6th.whfb.app/special-rules/building-up-steam-points</t>
         </is>
       </c>
       <c r="I137" s="11" t="n"/>
@@ -6642,17 +6638,17 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Athandin</t>
+          <t>Armour of Eternity</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>Valten, Exalted of Sigmar &gt; Athandin</t>
+          <t>Magic Armour &gt; Magic Armour</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Tomb Kings.cat</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
@@ -6667,12 +6663,12 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/althandin (0.66)</t>
+          <t>/appendix-eight-sequence-of-play/4-shooting-p58 (0.90)</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/althandin</t>
+          <t>https://6th.whfb.app/appendix-eight-sequence-of-play/4-shooting-p58</t>
         </is>
       </c>
       <c r="I138" s="11" t="n"/>
@@ -6686,17 +6682,17 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>Charging with the Steam Tank</t>
+          <t>Ethereal Steeds</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>Steam Tank</t>
+          <t>shared; used by Black Knights</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Vampire Counts.cat</t>
         </is>
       </c>
       <c r="E139" s="9" t="inlineStr">
@@ -6711,12 +6707,12 @@
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>/movement/charging (0.90)</t>
+          <t>/special-rules/ethereal (0.90)</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/movement/charging</t>
+          <t>https://6th.whfb.app/special-rules/ethereal</t>
         </is>
       </c>
       <c r="I139" s="11" t="n"/>
@@ -6730,7 +6726,7 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Electoral Banner</t>
+          <t>Fly</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
@@ -6740,7 +6736,7 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
@@ -6755,10 +6751,14 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H140" s="10" t="inlineStr"/>
+          <t>/faq/flyers (0.90)</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/faq/flyers</t>
+        </is>
+      </c>
       <c r="I140" s="11" t="n"/>
       <c r="J140" s="11" t="n"/>
     </row>
@@ -6770,17 +6770,17 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>Fusilade</t>
+          <t>Stone Thrower</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>Pistoliers</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/fusillade (0.66)</t>
+          <t>/unit/stone-thrower (1.00)</t>
         </is>
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/fusillade</t>
+          <t>https://6th.whfb.app/unit/stone-thrower</t>
         </is>
       </c>
       <c r="I141" s="11" t="n"/>
@@ -6814,17 +6814,17 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Helm of the Skavenslayer</t>
+          <t>Alter Kindred</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>Magic Armour &gt; Magic Armour &gt; Helm of the Skavenslayer</t>
+          <t>Wood Elf Kindred &gt; Alter Kindred</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>/army/skaven (0.80)</t>
+          <t>/magic-item/the-alter-kindreds (0.80)</t>
         </is>
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/army/skaven</t>
+          <t>https://6th.whfb.app/magic-item/the-alter-kindreds</t>
         </is>
       </c>
       <c r="I142" s="11" t="n"/>
@@ -6858,17 +6858,17 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>Parent and Detachment Units</t>
+          <t>Gwytherc's Horn</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Enchanted Items &gt; Gwytherc's Horn</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E143" s="9" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>/warhammer-glossary/unit-warhammer-glossary (0.80)</t>
+          <t>/magic-item/gwytheres-horn (0.65)</t>
         </is>
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/warhammer-glossary/unit-warhammer-glossary</t>
+          <t>https://6th.whfb.app/magic-item/gwytheres-horn</t>
         </is>
       </c>
       <c r="I143" s="11" t="n"/>
@@ -6902,17 +6902,17 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Shooting at the Steam Tank</t>
+          <t>Stone of the Crystal Mere</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
         <is>
-          <t>Steam Tank</t>
+          <t>Talismans &gt; Stone of the Crystal Mere</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>/faq/shooting (0.90)</t>
+          <t>/magic-item/stone-of-the-crystal-merex (0.90)</t>
         </is>
       </c>
       <c r="H144" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/shooting</t>
+          <t>https://6th.whfb.app/magic-item/stone-of-the-crystal-merex</t>
         </is>
       </c>
       <c r="I144" s="11" t="n"/>
@@ -6946,17 +6946,17 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>Shooting with the Steam Tank</t>
+          <t>Strangle-Roots</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>Steam Tank</t>
+          <t>shared; used by Treeman, Treeman Ancient</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
@@ -6971,56 +6971,52 @@
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>/faq/shooting (0.90)</t>
-        </is>
-      </c>
-      <c r="H145" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/faq/shooting</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H145" s="10" t="inlineStr"/>
       <c r="I145" s="11" t="n"/>
       <c r="J145" s="11" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Steam Points</t>
+          <t>Virtue of Audacity</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>Steam Tank</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/building-up-steam-points (0.80)</t>
+          <t>wiki: 30</t>
         </is>
       </c>
       <c r="H146" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/building-up-steam-points</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
         </is>
       </c>
       <c r="I146" s="11" t="n"/>
@@ -7029,42 +7025,42 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>Armour of Eternity</t>
+          <t>Virtue of Audacity</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>Magic Armour &gt; Magic Armour</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>Tomb Kings.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 90</t>
         </is>
       </c>
       <c r="G147" s="9" t="inlineStr">
         <is>
-          <t>/appendix-eight-sequence-of-play/4-shooting-p58 (0.90)</t>
+          <t>wiki: 30</t>
         </is>
       </c>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/appendix-eight-sequence-of-play/4-shooting-p58</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
         </is>
       </c>
       <c r="I147" s="11" t="n"/>
@@ -7073,42 +7069,42 @@
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>Ethereal Steeds</t>
+          <t>Virtue of Confidence</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Black Knights</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Vampire Counts.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 50</t>
         </is>
       </c>
       <c r="G148" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/ethereal (0.90)</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H148" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/ethereal</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
         </is>
       </c>
       <c r="I148" s="11" t="n"/>
@@ -7117,42 +7113,42 @@
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>Fly</t>
+          <t>Virtue of Confidence</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G149" s="9" t="inlineStr">
         <is>
-          <t>/faq/flyers (0.90)</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/flyers</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
         </is>
       </c>
       <c r="I149" s="11" t="n"/>
@@ -7161,42 +7157,42 @@
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Stone Thrower</t>
+          <t>Virtue of Confidence</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 75</t>
         </is>
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
-          <t>/unit/stone-thrower (1.00)</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/stone-thrower</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
         </is>
       </c>
       <c r="I150" s="11" t="n"/>
@@ -7205,42 +7201,42 @@
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>Alter Kindred</t>
+          <t>Virtue of Discipline</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>Wood Elf Kindred &gt; Alter Kindred</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 90</t>
         </is>
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/the-alter-kindreds (0.80)</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/the-alter-kindreds</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I151" s="11" t="n"/>
@@ -7249,42 +7245,42 @@
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Gwytherc's Horn</t>
+          <t>Virtue of Discipline</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>Enchanted Items &gt; Gwytherc's Horn</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 30</t>
         </is>
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/gwytheres-horn (0.65)</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/gwytheres-horn</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I152" s="11" t="n"/>
@@ -7293,42 +7289,42 @@
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>Stone of the Crystal Mere</t>
+          <t>Virtue of Discipline</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>Talismans &gt; Stone of the Crystal Mere</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F153" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 45</t>
         </is>
       </c>
       <c r="G153" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/stone-of-the-crystal-merex (0.90)</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/stone-of-the-crystal-merex</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I153" s="11" t="n"/>
@@ -7337,40 +7333,44 @@
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Strangle-Roots</t>
+          <t>Virtue of Discipline</t>
         </is>
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Treeman, Treeman Ancient</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H154" s="10" t="inlineStr"/>
+          <t>wiki: 15</t>
+        </is>
+      </c>
+      <c r="H154" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+        </is>
+      </c>
       <c r="I154" s="11" t="n"/>
       <c r="J154" s="11" t="n"/>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Audacity</t>
+          <t>Virtue of Discipline</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
@@ -7402,17 +7402,17 @@
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 75</t>
         </is>
       </c>
       <c r="G155" s="9" t="inlineStr">
         <is>
-          <t>wiki: 30</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I155" s="11" t="n"/>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Audacity</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C156" s="9" t="inlineStr">
@@ -7446,17 +7446,17 @@
       </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue: 30</t>
         </is>
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
-          <t>wiki: 30</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I156" s="11" t="n"/>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C157" s="9" t="inlineStr">
@@ -7490,17 +7490,17 @@
       </c>
       <c r="F157" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue: 20</t>
         </is>
       </c>
       <c r="G157" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I157" s="11" t="n"/>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C158" s="9" t="inlineStr">
@@ -7534,17 +7534,17 @@
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H158" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I158" s="11" t="n"/>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
@@ -7578,17 +7578,17 @@
       </c>
       <c r="F159" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I159" s="11" t="n"/>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C160" s="9" t="inlineStr">
@@ -7622,17 +7622,17 @@
       </c>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue: 50</t>
         </is>
       </c>
       <c r="G160" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H160" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I160" s="11" t="n"/>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
@@ -7666,17 +7666,17 @@
       </c>
       <c r="F161" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 30</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I161" s="11" t="n"/>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C162" s="9" t="inlineStr">
@@ -7710,17 +7710,17 @@
       </c>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 45</t>
+          <t>catalogue: 70</t>
         </is>
       </c>
       <c r="G162" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I162" s="11" t="n"/>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C163" s="9" t="inlineStr">
@@ -7754,17 +7754,17 @@
       </c>
       <c r="F163" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I163" s="11" t="n"/>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C164" s="9" t="inlineStr">
@@ -7798,17 +7798,17 @@
       </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue: 90</t>
         </is>
       </c>
       <c r="G164" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H164" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I164" s="11" t="n"/>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Heroism</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
@@ -7842,17 +7842,17 @@
       </c>
       <c r="F165" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 30</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 40</t>
         </is>
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-heroism</t>
         </is>
       </c>
       <c r="I165" s="11" t="n"/>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Knightly Temper</t>
         </is>
       </c>
       <c r="C166" s="9" t="inlineStr">
@@ -7886,17 +7886,17 @@
       </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 20</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G166" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 40</t>
         </is>
       </c>
       <c r="H166" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-knightly-temper</t>
         </is>
       </c>
       <c r="I166" s="11" t="n"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Noble Disdain</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="G167" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
         </is>
       </c>
       <c r="I167" s="11" t="n"/>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Noble Disdain</t>
         </is>
       </c>
       <c r="C168" s="9" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="G168" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H168" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
         </is>
       </c>
       <c r="I168" s="11" t="n"/>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Noble Disdain</t>
         </is>
       </c>
       <c r="C169" s="9" t="inlineStr">
@@ -8018,17 +8018,17 @@
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G169" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
         </is>
       </c>
       <c r="I169" s="11" t="n"/>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Noble Disdain</t>
         </is>
       </c>
       <c r="C170" s="9" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="G170" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H170" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
         </is>
       </c>
       <c r="I170" s="11" t="n"/>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Purity</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
@@ -8106,17 +8106,17 @@
       </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 70</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G171" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H171" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
         </is>
       </c>
       <c r="I171" s="11" t="n"/>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Purity</t>
         </is>
       </c>
       <c r="C172" s="9" t="inlineStr">
@@ -8150,17 +8150,17 @@
       </c>
       <c r="F172" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G172" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H172" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
         </is>
       </c>
       <c r="I172" s="11" t="n"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Purity</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
@@ -8194,17 +8194,17 @@
       </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G173" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H173" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
         </is>
       </c>
       <c r="I173" s="11" t="n"/>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="B174" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Heroism</t>
+          <t>Virtue of Purity</t>
         </is>
       </c>
       <c r="C174" s="9" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="G174" s="9" t="inlineStr">
         <is>
-          <t>wiki: 40</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H174" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-heroism</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
         </is>
       </c>
       <c r="I174" s="11" t="n"/>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Knightly Temper</t>
+          <t>Virtue of Stoicism</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="G175" s="9" t="inlineStr">
         <is>
-          <t>wiki: 40</t>
+          <t>wiki: 35</t>
         </is>
       </c>
       <c r="H175" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-knightly-temper</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
         </is>
       </c>
       <c r="I175" s="11" t="n"/>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Noble Disdain</t>
+          <t>Virtue of Stoicism</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
@@ -8331,12 +8331,12 @@
       </c>
       <c r="G176" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 35</t>
         </is>
       </c>
       <c r="H176" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
         </is>
       </c>
       <c r="I176" s="11" t="n"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Noble Disdain</t>
+          <t>Virtue of the Ideal</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
@@ -8370,17 +8370,17 @@
       </c>
       <c r="F177" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 70</t>
         </is>
       </c>
       <c r="G177" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 35</t>
         </is>
       </c>
       <c r="H177" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-ideal</t>
         </is>
       </c>
       <c r="I177" s="11" t="n"/>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Noble Disdain</t>
+          <t>Virtue of the Impetuous Knight</t>
         </is>
       </c>
       <c r="C178" s="9" t="inlineStr">
@@ -8414,17 +8414,17 @@
       </c>
       <c r="F178" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 70</t>
         </is>
       </c>
       <c r="G178" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 35</t>
         </is>
       </c>
       <c r="H178" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-impetuous-knight</t>
         </is>
       </c>
       <c r="I178" s="11" t="n"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Noble Disdain</t>
+          <t>Virtue of the Joust</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
@@ -8458,17 +8458,17 @@
       </c>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 50</t>
         </is>
       </c>
       <c r="G179" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H179" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
         </is>
       </c>
       <c r="I179" s="11" t="n"/>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Purity</t>
+          <t>Virtue of the Joust</t>
         </is>
       </c>
       <c r="C180" s="9" t="inlineStr">
@@ -8502,17 +8502,17 @@
       </c>
       <c r="F180" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue: 75</t>
         </is>
       </c>
       <c r="G180" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H180" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
         </is>
       </c>
       <c r="I180" s="11" t="n"/>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Purity</t>
+          <t>Virtue of the Joust</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
@@ -8546,17 +8546,17 @@
       </c>
       <c r="F181" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G181" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H181" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
         </is>
       </c>
       <c r="I181" s="11" t="n"/>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Purity</t>
+          <t>Virtue of the Penitent</t>
         </is>
       </c>
       <c r="C182" s="9" t="inlineStr">
@@ -8590,17 +8590,17 @@
       </c>
       <c r="F182" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G182" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 40</t>
         </is>
       </c>
       <c r="H182" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-penitent</t>
         </is>
       </c>
       <c r="I182" s="11" t="n"/>
@@ -8614,17 +8614,17 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Purity</t>
+          <t>Power Stone</t>
         </is>
       </c>
       <c r="C183" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Arcane Items &gt; Unique Items</t>
         </is>
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E183" s="9" t="inlineStr">
@@ -8634,17 +8634,17 @@
       </c>
       <c r="F183" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 0</t>
         </is>
       </c>
       <c r="G183" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H183" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
+          <t>https://6th.whfb.app/magic-item/power-stone</t>
         </is>
       </c>
       <c r="I183" s="11" t="n"/>
@@ -8658,17 +8658,17 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Stoicism</t>
+          <t>Pure of Heart</t>
         </is>
       </c>
       <c r="C184" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Honours</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E184" s="9" t="inlineStr">
@@ -8678,17 +8678,17 @@
       </c>
       <c r="F184" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 0</t>
         </is>
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: 500</t>
         </is>
       </c>
       <c r="H184" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
+          <t>https://6th.whfb.app/magic-item/pure-of-heart</t>
         </is>
       </c>
       <c r="I184" s="11" t="n"/>
@@ -8702,17 +8702,17 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Stoicism</t>
+          <t>Ghal Maraz</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Emperor Karl Franz &gt; Weapon</t>
         </is>
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
@@ -8722,17 +8722,17 @@
       </c>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue: 180</t>
         </is>
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: 0</t>
         </is>
       </c>
       <c r="H185" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
+          <t>https://6th.whfb.app/magic-item/ghal-maraz</t>
         </is>
       </c>
       <c r="I185" s="11" t="n"/>
@@ -8746,17 +8746,17 @@
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Ideal</t>
+          <t>Horn of the Wild Hunt</t>
         </is>
       </c>
       <c r="C186" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Orion, the King in the Woods</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E186" s="9" t="inlineStr">
@@ -8766,17 +8766,17 @@
       </c>
       <c r="F186" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 70</t>
+          <t>catalogue: 0</t>
         </is>
       </c>
       <c r="G186" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H186" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-ideal</t>
+          <t>https://6th.whfb.app/magic-item/horn-of-the-wild-hunt</t>
         </is>
       </c>
       <c r="I186" s="11" t="n"/>
@@ -8785,17 +8785,17 @@
     <row r="187">
       <c r="A187" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Impetuous Knight</t>
+          <t>Pegasus</t>
         </is>
       </c>
       <c r="C187" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Pegasus Knights &gt; Pegasus Knight</t>
         </is>
       </c>
       <c r="D187" s="8" t="inlineStr">
@@ -8805,22 +8805,22 @@
       </c>
       <c r="E187" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F187" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 70</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G187" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: Ld 7-&gt;6</t>
         </is>
       </c>
       <c r="H187" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-impetuous-knight</t>
+          <t>https://6th.whfb.app/unit/pegasus</t>
         </is>
       </c>
       <c r="I187" s="11" t="n"/>
@@ -8829,17 +8829,17 @@
     <row r="188">
       <c r="A188" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Joust</t>
+          <t>Villein</t>
         </is>
       </c>
       <c r="C188" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Peasant Bowmen &gt; Command &gt; Villein</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
@@ -8849,22 +8849,22 @@
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F188" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G188" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: WS 3-&gt;2, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H188" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
+          <t>https://6th.whfb.app/unit/villein</t>
         </is>
       </c>
       <c r="I188" s="11" t="n"/>
@@ -8873,42 +8873,42 @@
     <row r="189">
       <c r="A189" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Joust</t>
+          <t>Bull Centaur Hero</t>
         </is>
       </c>
       <c r="C189" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Bull Centaur Hero</t>
         </is>
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="E189" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F189" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: T 4-&gt;5</t>
         </is>
       </c>
       <c r="H189" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
+          <t>https://6th.whfb.app/unit/bull-centaur-hero</t>
         </is>
       </c>
       <c r="I189" s="11" t="n"/>
@@ -8917,42 +8917,42 @@
     <row r="190">
       <c r="A190" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Joust</t>
+          <t>Chaos Dwarf Sorcerer</t>
         </is>
       </c>
       <c r="C190" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Sorcerer Lord</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="E190" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F190" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G190" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: S 4-&gt;3, T 5-&gt;4, W 3-&gt;2, I 1-&gt;2, Ld 10-&gt;9</t>
         </is>
       </c>
       <c r="H190" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
+          <t>https://6th.whfb.app/unit/chaos-dwarf-sorcerer</t>
         </is>
       </c>
       <c r="I190" s="11" t="n"/>
@@ -8961,42 +8961,42 @@
     <row r="191">
       <c r="A191" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Penitent</t>
+          <t>Hobgoblin Crew</t>
         </is>
       </c>
       <c r="C191" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Hobgoblin Bolt Thrower &gt; Hobgoblin Bolt Thrower</t>
         </is>
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="E191" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F191" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G191" s="9" t="inlineStr">
         <is>
-          <t>wiki: 40</t>
+          <t>wiki: M 3-&gt;4</t>
         </is>
       </c>
       <c r="H191" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-penitent</t>
+          <t>https://6th.whfb.app/unit/hobgoblin-crew</t>
         </is>
       </c>
       <c r="I191" s="11" t="n"/>
@@ -9005,42 +9005,42 @@
     <row r="192">
       <c r="A192" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>Power Stone</t>
+          <t>Bloodletter</t>
         </is>
       </c>
       <c r="C192" s="9" t="inlineStr">
         <is>
-          <t>Arcane Items &gt; Unique Items</t>
+          <t>Bloodletters &gt; Bloodletters</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E192" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F192" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 0</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G192" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H192" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/power-stone</t>
+          <t>https://6th.whfb.app/unit/bloodletter</t>
         </is>
       </c>
       <c r="I192" s="11" t="n"/>
@@ -9049,42 +9049,42 @@
     <row r="193">
       <c r="A193" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>Pure of Heart</t>
+          <t>Daemonette</t>
         </is>
       </c>
       <c r="C193" s="9" t="inlineStr">
         <is>
-          <t>Honours</t>
+          <t>Daemonettes &gt; Daemonettes</t>
         </is>
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E193" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F193" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 0</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G193" s="9" t="inlineStr">
         <is>
-          <t>wiki: 500</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H193" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/pure-of-heart</t>
+          <t>https://6th.whfb.app/unit/daemonette</t>
         </is>
       </c>
       <c r="I193" s="11" t="n"/>
@@ -9093,42 +9093,42 @@
     <row r="194">
       <c r="A194" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>Ghal Maraz</t>
+          <t>Daemonette</t>
         </is>
       </c>
       <c r="C194" s="9" t="inlineStr">
         <is>
-          <t>Emperor Karl Franz &gt; Weapon</t>
+          <t>Mounted Daemonettes &gt; Mounted Daemonette</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E194" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F194" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 180</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G194" s="9" t="inlineStr">
         <is>
-          <t>wiki: 0</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H194" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/ghal-maraz</t>
+          <t>https://6th.whfb.app/unit/daemonette</t>
         </is>
       </c>
       <c r="I194" s="11" t="n"/>
@@ -9137,42 +9137,42 @@
     <row r="195">
       <c r="A195" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>Horn of the Wild Hunt</t>
+          <t>Flamer</t>
         </is>
       </c>
       <c r="C195" s="9" t="inlineStr">
         <is>
-          <t>Orion, the King in the Woods</t>
+          <t>Flamers &gt; Flamer</t>
         </is>
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E195" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F195" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 0</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G195" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H195" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/horn-of-the-wild-hunt</t>
+          <t>https://6th.whfb.app/unit/flamer</t>
         </is>
       </c>
       <c r="I195" s="11" t="n"/>
@@ -9186,17 +9186,17 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>Pegasus</t>
+          <t>Flesh Hound</t>
         </is>
       </c>
       <c r="C196" s="9" t="inlineStr">
         <is>
-          <t>Pegasus Knights &gt; Pegasus Knight</t>
+          <t>Flesh Hounds &gt; Flesh Hounds</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E196" s="9" t="inlineStr">
@@ -9211,12 +9211,12 @@
       </c>
       <c r="G196" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 7-&gt;6</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H196" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/pegasus</t>
+          <t>https://6th.whfb.app/unit/flesh-hound</t>
         </is>
       </c>
       <c r="I196" s="11" t="n"/>
@@ -9230,22 +9230,22 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>Villein</t>
+          <t>Horror</t>
         </is>
       </c>
       <c r="C197" s="9" t="inlineStr">
         <is>
-          <t>Peasant Bowmen &gt; Command &gt; Villein</t>
+          <t>Horrors &gt; Horrors</t>
         </is>
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E197" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F197" s="9" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="G197" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;2, A 1-&gt;2</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H197" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/villein</t>
+          <t>https://6th.whfb.app/unit/horror</t>
         </is>
       </c>
       <c r="I197" s="11" t="n"/>
@@ -9274,17 +9274,17 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>Bull Centaur Hero</t>
+          <t>Nurglings</t>
         </is>
       </c>
       <c r="C198" s="9" t="inlineStr">
         <is>
-          <t>Bull Centaur Hero</t>
+          <t>Nurglings &gt; Nurglings</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E198" s="9" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="G198" s="9" t="inlineStr">
         <is>
-          <t>wiki: T 4-&gt;5</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H198" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bull-centaur-hero</t>
+          <t>https://6th.whfb.app/unit/nurglings</t>
         </is>
       </c>
       <c r="I198" s="11" t="n"/>
@@ -9318,22 +9318,22 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarf Sorcerer</t>
+          <t>Plaguebearer</t>
         </is>
       </c>
       <c r="C199" s="9" t="inlineStr">
         <is>
-          <t>Sorcerer Lord</t>
+          <t>Plaguebearers &gt; Plaguebearers</t>
         </is>
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E199" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F199" s="9" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="G199" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 4-&gt;3, T 5-&gt;4, W 3-&gt;2, I 1-&gt;2, Ld 10-&gt;9</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H199" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/chaos-dwarf-sorcerer</t>
+          <t>https://6th.whfb.app/unit/plaguebearer</t>
         </is>
       </c>
       <c r="I199" s="11" t="n"/>
@@ -9362,17 +9362,17 @@
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>Hobgoblin Crew</t>
+          <t>Screamer</t>
         </is>
       </c>
       <c r="C200" s="9" t="inlineStr">
         <is>
-          <t>Hobgoblin Bolt Thrower &gt; Hobgoblin Bolt Thrower</t>
+          <t>Screamers of Tzeentch &gt; Screamer</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E200" s="9" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="G200" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 3-&gt;4</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H200" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/hobgoblin-crew</t>
+          <t>https://6th.whfb.app/unit/screamer</t>
         </is>
       </c>
       <c r="I200" s="11" t="n"/>
@@ -9406,17 +9406,17 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>Bloodletter</t>
+          <t>Hag</t>
         </is>
       </c>
       <c r="C201" s="9" t="inlineStr">
         <is>
-          <t>Bloodletters &gt; Bloodletters</t>
+          <t>Cauldron of Blood</t>
         </is>
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E201" s="9" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="G201" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: WS 4-&gt;5</t>
         </is>
       </c>
       <c r="H201" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bloodletter</t>
+          <t>https://6th.whfb.app/unit/hag</t>
         </is>
       </c>
       <c r="I201" s="11" t="n"/>
@@ -9450,22 +9450,22 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>Daemonette</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="C202" s="9" t="inlineStr">
         <is>
-          <t>Daemonettes &gt; Daemonettes</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F202" s="9" t="inlineStr">
@@ -9475,12 +9475,12 @@
       </c>
       <c r="G202" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
         </is>
       </c>
       <c r="H202" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/daemonette</t>
+          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
         </is>
       </c>
       <c r="I202" s="11" t="n"/>
@@ -9494,22 +9494,22 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>Daemonette</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C203" s="9" t="inlineStr">
         <is>
-          <t>Mounted Daemonettes &gt; Mounted Daemonette</t>
+          <t>Cold One Knights &gt; Cold One Knights</t>
         </is>
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E203" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F203" s="9" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="G203" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: M 5-&gt;4, WS 5-&gt;4, BS 4-&gt;3, I 5-&gt;3, Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H203" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/daemonette</t>
+          <t>https://6th.whfb.app/unit/knight</t>
         </is>
       </c>
       <c r="I203" s="11" t="n"/>
@@ -9538,22 +9538,22 @@
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t>Flamer</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C204" s="9" t="inlineStr">
         <is>
-          <t>Flamers &gt; Flamer</t>
+          <t>Knights of Chaos &gt; Knights</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E204" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>4 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F204" s="9" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="G204" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
         </is>
       </c>
       <c r="H204" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/flamer</t>
+          <t>https://6th.whfb.app/unit/knight</t>
         </is>
       </c>
       <c r="I204" s="11" t="n"/>
@@ -9582,22 +9582,22 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>Flesh Hound</t>
+          <t>Steed of Slaanesh</t>
         </is>
       </c>
       <c r="C205" s="9" t="inlineStr">
         <is>
-          <t>Flesh Hounds &gt; Flesh Hounds</t>
+          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
         </is>
       </c>
       <c r="D205" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E205" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F205" s="9" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="G205" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H205" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/flesh-hound</t>
+          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
         </is>
       </c>
       <c r="I205" s="11" t="n"/>
@@ -9626,17 +9626,17 @@
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t>Horror</t>
+          <t>Daddallo</t>
         </is>
       </c>
       <c r="C206" s="9" t="inlineStr">
         <is>
-          <t>Horrors &gt; Horrors</t>
+          <t>Birdmen of Catrazza &gt; Daddallo</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E206" s="9" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="G206" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: A 2-&gt;1</t>
         </is>
       </c>
       <c r="H206" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/horror</t>
+          <t>https://6th.whfb.app/unit/daddallo</t>
         </is>
       </c>
       <c r="I206" s="11" t="n"/>
@@ -9670,17 +9670,17 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>Nurglings</t>
+          <t>Warhorse</t>
         </is>
       </c>
       <c r="C207" s="9" t="inlineStr">
         <is>
-          <t>Nurglings &gt; Nurglings</t>
+          <t>shared; used by Al Muktar's Desert Dogs, Bronzino's Galloper Guns</t>
         </is>
       </c>
       <c r="D207" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E207" s="9" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="G207" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: BS 3-&gt;0</t>
         </is>
       </c>
       <c r="H207" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/nurglings</t>
+          <t>https://6th.whfb.app/unit/warhorse</t>
         </is>
       </c>
       <c r="I207" s="11" t="n"/>
@@ -9714,17 +9714,17 @@
       </c>
       <c r="B208" s="8" t="inlineStr">
         <is>
-          <t>Plaguebearer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="C208" s="9" t="inlineStr">
         <is>
-          <t>Plaguebearers &gt; Plaguebearers</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dwarfs.cat</t>
         </is>
       </c>
       <c r="E208" s="9" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="G208" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: A 2-&gt;1</t>
         </is>
       </c>
       <c r="H208" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/plaguebearer</t>
+          <t>https://6th.whfb.app/unit/engineer</t>
         </is>
       </c>
       <c r="I208" s="11" t="n"/>
@@ -9758,17 +9758,17 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>Screamer</t>
+          <t>Bloodthirster</t>
         </is>
       </c>
       <c r="C209" s="9" t="inlineStr">
         <is>
-          <t>Screamers of Tzeentch &gt; Screamer</t>
+          <t>Bloodthirster</t>
         </is>
       </c>
       <c r="D209" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E209" s="9" t="inlineStr">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="G209" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: S 7-&gt;6(7)</t>
         </is>
       </c>
       <c r="H209" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/screamer</t>
+          <t>https://6th.whfb.app/unit/bloodthirster</t>
         </is>
       </c>
       <c r="I209" s="11" t="n"/>
@@ -9802,22 +9802,22 @@
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t>Hag</t>
+          <t>Centigor</t>
         </is>
       </c>
       <c r="C210" s="9" t="inlineStr">
         <is>
-          <t>Cauldron of Blood</t>
+          <t>Minotaurs &gt; Minotaurs</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E210" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F210" s="9" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="G210" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 4-&gt;5</t>
+          <t>wiki: M 6-&gt;8, W 3-&gt;1, I 4-&gt;2, A 3-&gt;1(2), Ld 8-&gt;7</t>
         </is>
       </c>
       <c r="H210" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/hag</t>
+          <t>https://6th.whfb.app/unit/centigor</t>
         </is>
       </c>
       <c r="I210" s="11" t="n"/>
@@ -9846,22 +9846,22 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
+          <t>Chaos Giant</t>
         </is>
       </c>
       <c r="C211" s="9" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
+          <t>Chaos Giant</t>
         </is>
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E211" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F211" s="9" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="G211" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
+          <t>wiki: A Special-&gt;*</t>
         </is>
       </c>
       <c r="H211" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
+          <t>https://6th.whfb.app/unit/chaos-giant</t>
         </is>
       </c>
       <c r="I211" s="11" t="n"/>
@@ -9890,22 +9890,22 @@
       </c>
       <c r="B212" s="8" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="C212" s="9" t="inlineStr">
         <is>
-          <t>Cold One Knights &gt; Cold One Knights</t>
+          <t>Lord of Change</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E212" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>4 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F212" s="9" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="G212" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 5-&gt;4, WS 5-&gt;4, BS 4-&gt;3, I 5-&gt;3, Ld 9-&gt;8</t>
+          <t>wiki: M 6-&gt;8, WS 6-&gt;9, A 5-&gt;10, Ld 9-&gt;6</t>
         </is>
       </c>
       <c r="H212" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/knight</t>
+          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
         </is>
       </c>
       <c r="I212" s="11" t="n"/>
@@ -9934,22 +9934,22 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="C213" s="9" t="inlineStr">
         <is>
-          <t>Knights of Chaos &gt; Knights</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="D213" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E213" s="9" t="inlineStr">
         <is>
-          <t>4 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F213" s="9" t="inlineStr">
@@ -9959,12 +9959,12 @@
       </c>
       <c r="G213" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
+          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
         </is>
       </c>
       <c r="H213" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/knight</t>
+          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
         </is>
       </c>
       <c r="I213" s="11" t="n"/>
@@ -9978,22 +9978,22 @@
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
-          <t>Steed of Slaanesh</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C214" s="9" t="inlineStr">
         <is>
-          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
+          <t>Knights of Chaos &gt; Knights</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E214" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>4 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F214" s="9" t="inlineStr">
@@ -10003,12 +10003,12 @@
       </c>
       <c r="G214" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
+          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
         </is>
       </c>
       <c r="H214" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
+          <t>https://6th.whfb.app/unit/knight</t>
         </is>
       </c>
       <c r="I214" s="11" t="n"/>
@@ -10022,22 +10022,22 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>Daddallo</t>
+          <t>Steed of Slaanesh</t>
         </is>
       </c>
       <c r="C215" s="9" t="inlineStr">
         <is>
-          <t>Birdmen of Catrazza &gt; Daddallo</t>
+          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
         </is>
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E215" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F215" s="9" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="G215" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 2-&gt;1</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H215" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/daddallo</t>
+          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
         </is>
       </c>
       <c r="I215" s="11" t="n"/>
@@ -10066,17 +10066,17 @@
       </c>
       <c r="B216" s="8" t="inlineStr">
         <is>
-          <t>Warhorse</t>
+          <t>Troll</t>
         </is>
       </c>
       <c r="C216" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Al Muktar's Desert Dogs, Bronzino's Galloper Guns</t>
+          <t>Chaos Trolls &gt; Trolls</t>
         </is>
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E216" s="9" t="inlineStr">
@@ -10091,12 +10091,12 @@
       </c>
       <c r="G216" s="9" t="inlineStr">
         <is>
-          <t>wiki: BS 3-&gt;0</t>
+          <t>wiki: A 4-&gt;3</t>
         </is>
       </c>
       <c r="H216" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warhorse</t>
+          <t>https://6th.whfb.app/unit/troll</t>
         </is>
       </c>
       <c r="I216" s="11" t="n"/>
@@ -10110,17 +10110,17 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Tuskgor</t>
         </is>
       </c>
       <c r="C217" s="9" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Gorthor the Beastlord</t>
         </is>
       </c>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E217" s="9" t="inlineStr">
@@ -10135,12 +10135,12 @@
       </c>
       <c r="G217" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 2-&gt;1</t>
+          <t>wiki: S 4-&gt;3</t>
         </is>
       </c>
       <c r="H217" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/engineer</t>
+          <t>https://6th.whfb.app/unit/tuskgor</t>
         </is>
       </c>
       <c r="I217" s="11" t="n"/>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t>Bloodthirster</t>
+          <t>Ungor</t>
         </is>
       </c>
       <c r="C218" s="9" t="inlineStr">
         <is>
-          <t>Bloodthirster</t>
+          <t>Beast Herd &gt; Ungors</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="G218" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 7-&gt;6(7)</t>
+          <t>wiki: T 4-&gt;3</t>
         </is>
       </c>
       <c r="H218" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bloodthirster</t>
+          <t>https://6th.whfb.app/unit/ungor</t>
         </is>
       </c>
       <c r="I218" s="11" t="n"/>
@@ -10198,12 +10198,12 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>Centigor</t>
+          <t>Ungor</t>
         </is>
       </c>
       <c r="C219" s="9" t="inlineStr">
         <is>
-          <t>Minotaurs &gt; Minotaurs</t>
+          <t>Tuskgor Chariot</t>
         </is>
       </c>
       <c r="D219" s="8" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F219" s="9" t="inlineStr">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="G219" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 6-&gt;8, W 3-&gt;1, I 4-&gt;2, A 3-&gt;1(2), Ld 8-&gt;7</t>
+          <t>wiki: WS 4-&gt;3</t>
         </is>
       </c>
       <c r="H219" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/centigor</t>
+          <t>https://6th.whfb.app/unit/ungor</t>
         </is>
       </c>
       <c r="I219" s="11" t="n"/>
@@ -10242,22 +10242,22 @@
       </c>
       <c r="B220" s="8" t="inlineStr">
         <is>
-          <t>Chaos Giant</t>
+          <t>Bladelord</t>
         </is>
       </c>
       <c r="C220" s="9" t="inlineStr">
         <is>
-          <t>Chaos Giant</t>
+          <t>Phoenix Guard &gt; Command &gt; Keeper of the Flame</t>
         </is>
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E220" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>3 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F220" s="9" t="inlineStr">
@@ -10267,12 +10267,12 @@
       </c>
       <c r="G220" s="9" t="inlineStr">
         <is>
-          <t>wiki: A Special-&gt;*</t>
+          <t>wiki: WS 5-&gt;6, I 6-&gt;5, Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H220" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/chaos-giant</t>
+          <t>https://6th.whfb.app/unit/bladelord</t>
         </is>
       </c>
       <c r="I220" s="11" t="n"/>
@@ -10286,22 +10286,22 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
+          <t>Ellyrian Reaver</t>
         </is>
       </c>
       <c r="C221" s="9" t="inlineStr">
         <is>
-          <t>Lord of Change</t>
+          <t>Ellyrian Reavers &gt; Ellyrian Reavers</t>
         </is>
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>4 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F221" s="9" t="inlineStr">
@@ -10311,12 +10311,12 @@
       </c>
       <c r="G221" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 6-&gt;8, WS 6-&gt;9, A 5-&gt;10, Ld 9-&gt;6</t>
+          <t>wiki: A 1-&gt;2</t>
         </is>
       </c>
       <c r="H221" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
+          <t>https://6th.whfb.app/unit/ellyrian-reaver</t>
         </is>
       </c>
       <c r="I221" s="11" t="n"/>
@@ -10330,22 +10330,22 @@
       </c>
       <c r="B222" s="8" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
+          <t>Harbinger</t>
         </is>
       </c>
       <c r="C222" s="9" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
+          <t>Ellyrian Reavers &gt; Command &gt; Harbinger</t>
         </is>
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F222" s="9" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="G222" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
+          <t>wiki: A 1-&gt;2</t>
         </is>
       </c>
       <c r="H222" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
+          <t>https://6th.whfb.app/unit/harbinger</t>
         </is>
       </c>
       <c r="I222" s="11" t="n"/>
@@ -10374,22 +10374,22 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Greyback</t>
         </is>
       </c>
       <c r="C223" s="9" t="inlineStr">
         <is>
-          <t>Knights of Chaos &gt; Knights</t>
+          <t>Yheetees &gt; Greyback</t>
         </is>
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>4 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr">
@@ -10399,12 +10399,12 @@
       </c>
       <c r="G223" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
+          <t>wiki: A 4-&gt;3</t>
         </is>
       </c>
       <c r="H223" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/knight</t>
+          <t>https://6th.whfb.app/unit/greyback</t>
         </is>
       </c>
       <c r="I223" s="11" t="n"/>
@@ -10418,22 +10418,22 @@
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>Steed of Slaanesh</t>
+          <t>Rhinox</t>
         </is>
       </c>
       <c r="C224" s="9" t="inlineStr">
         <is>
-          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
+          <t>Rhinox Cavalry &gt; Rhinox Riders</t>
         </is>
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F224" s="9" t="inlineStr">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="G224" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
+          <t>wiki: M 7-&gt;6</t>
         </is>
       </c>
       <c r="H224" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I224" s="11" t="n"/>
@@ -10462,17 +10462,17 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>Troll</t>
+          <t>Thunderfist</t>
         </is>
       </c>
       <c r="C225" s="9" t="inlineStr">
         <is>
-          <t>Chaos Trolls &gt; Trolls</t>
+          <t>Leadbelchers &gt; Command &gt; Thunderfist</t>
         </is>
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E225" s="9" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="G225" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 4-&gt;3</t>
+          <t>wiki: BS 2-&gt;3</t>
         </is>
       </c>
       <c r="H225" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/troll</t>
+          <t>https://6th.whfb.app/unit/thunderfist</t>
         </is>
       </c>
       <c r="I225" s="11" t="n"/>
@@ -10506,17 +10506,17 @@
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t>Tuskgor</t>
+          <t>Boar Chariot</t>
         </is>
       </c>
       <c r="C226" s="9" t="inlineStr">
         <is>
-          <t>Gorthor the Beastlord</t>
+          <t>Savage Orc Boar Chariot</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E226" s="9" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="G226" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 4-&gt;3</t>
+          <t>wiki: S 5-&gt;3</t>
         </is>
       </c>
       <c r="H226" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/tuskgor</t>
+          <t>https://6th.whfb.app/unit/boar-chariot</t>
         </is>
       </c>
       <c r="I226" s="11" t="n"/>
@@ -10550,17 +10550,17 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>Ungor</t>
+          <t>Giant</t>
         </is>
       </c>
       <c r="C227" s="9" t="inlineStr">
         <is>
-          <t>Beast Herd &gt; Ungors</t>
+          <t>Giant</t>
         </is>
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E227" s="9" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="G227" s="9" t="inlineStr">
         <is>
-          <t>wiki: T 4-&gt;3</t>
+          <t>wiki: A Special-&gt;*</t>
         </is>
       </c>
       <c r="H227" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/ungor</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I227" s="11" t="n"/>
@@ -10594,17 +10594,17 @@
       </c>
       <c r="B228" s="8" t="inlineStr">
         <is>
-          <t>Ungor</t>
+          <t>Squig Hopper</t>
         </is>
       </c>
       <c r="C228" s="9" t="inlineStr">
         <is>
-          <t>Tuskgor Chariot</t>
+          <t>Night Goblin Squig Herd &gt; Unit &gt; Squig Hopper</t>
         </is>
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E228" s="9" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="G228" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 4-&gt;3</t>
+          <t>wiki: W 2-&gt;1</t>
         </is>
       </c>
       <c r="H228" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/ungor</t>
+          <t>https://6th.whfb.app/unit/squig-hopper</t>
         </is>
       </c>
       <c r="I228" s="11" t="n"/>
@@ -10638,22 +10638,22 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>Bladelord</t>
+          <t>Clanrat Slave</t>
         </is>
       </c>
       <c r="C229" s="9" t="inlineStr">
         <is>
-          <t>Phoenix Guard &gt; Command &gt; Keeper of the Flame</t>
+          <t>Clanrat Slaves &gt; Clanrat Slaves</t>
         </is>
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>3 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 5-&gt;6, I 6-&gt;5, Ld 9-&gt;8</t>
+          <t>wiki: M 6-&gt;5, I 5-&gt;4</t>
         </is>
       </c>
       <c r="H229" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bladelord</t>
+          <t>https://6th.whfb.app/unit/clanrat-slave</t>
         </is>
       </c>
       <c r="I229" s="11" t="n"/>
@@ -10682,22 +10682,22 @@
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t>Ellyrian Reaver</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="C230" s="9" t="inlineStr">
         <is>
-          <t>Ellyrian Reavers &gt; Ellyrian Reavers</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>7 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
@@ -10707,12 +10707,12 @@
       </c>
       <c r="G230" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 1-&gt;2</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
         </is>
       </c>
       <c r="H230" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/ellyrian-reaver</t>
+          <t>https://6th.whfb.app/unit/festering-chantor</t>
         </is>
       </c>
       <c r="I230" s="11" t="n"/>
@@ -10726,17 +10726,17 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>Harbinger</t>
+          <t>Plague Lord</t>
         </is>
       </c>
       <c r="C231" s="9" t="inlineStr">
         <is>
-          <t>Ellyrian Reavers &gt; Command &gt; Harbinger</t>
+          <t>Plague Lord</t>
         </is>
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E231" s="9" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="G231" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 1-&gt;2</t>
+          <t>wiki: A 5-&gt;4</t>
         </is>
       </c>
       <c r="H231" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/harbinger</t>
+          <t>https://6th.whfb.app/unit/plague-lord</t>
         </is>
       </c>
       <c r="I231" s="11" t="n"/>
@@ -10770,17 +10770,17 @@
       </c>
       <c r="B232" s="8" t="inlineStr">
         <is>
-          <t>Greyback</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C232" s="9" t="inlineStr">
         <is>
-          <t>Yheetees &gt; Greyback</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E232" s="9" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="G232" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 4-&gt;3</t>
+          <t>wiki: I 6-&gt;4</t>
         </is>
       </c>
       <c r="H232" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/greyback</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I232" s="11" t="n"/>
@@ -10814,22 +10814,22 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>Rhinox</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C233" s="9" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry &gt; Rhinox Riders</t>
+          <t>Warlock Master</t>
         </is>
       </c>
       <c r="D233" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>6 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="G233" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 7-&gt;6</t>
+          <t>wiki: WS 4-&gt;3, T 4-&gt;3, W 3-&gt;2, I 5-&gt;4, A 2-&gt;1, Ld 7-&gt;5</t>
         </is>
       </c>
       <c r="H233" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I233" s="11" t="n"/>
@@ -10858,17 +10858,17 @@
       </c>
       <c r="B234" s="8" t="inlineStr">
         <is>
-          <t>Thunderfist</t>
+          <t>Skeleton</t>
         </is>
       </c>
       <c r="C234" s="9" t="inlineStr">
         <is>
-          <t>Leadbelchers &gt; Command &gt; Thunderfist</t>
+          <t>Skeleton Light Horsemen &gt; Skeleton Horseman</t>
         </is>
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Tomb Kings.cat</t>
         </is>
       </c>
       <c r="E234" s="9" t="inlineStr">
@@ -10883,12 +10883,12 @@
       </c>
       <c r="G234" s="9" t="inlineStr">
         <is>
-          <t>wiki: BS 2-&gt;3</t>
+          <t>wiki: Ld 5-&gt;3</t>
         </is>
       </c>
       <c r="H234" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/thunderfist</t>
+          <t>https://6th.whfb.app/unit/skeleton</t>
         </is>
       </c>
       <c r="I234" s="11" t="n"/>
@@ -10902,17 +10902,17 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>Boar Chariot</t>
+          <t>Skeleton</t>
         </is>
       </c>
       <c r="C235" s="9" t="inlineStr">
         <is>
-          <t>Savage Orc Boar Chariot</t>
+          <t>Skeleton Heavy Horsemen &gt; Skeleton Horseman</t>
         </is>
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Tomb Kings.cat</t>
         </is>
       </c>
       <c r="E235" s="9" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="G235" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 5-&gt;3</t>
+          <t>wiki: Ld 5-&gt;3</t>
         </is>
       </c>
       <c r="H235" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/boar-chariot</t>
+          <t>https://6th.whfb.app/unit/skeleton</t>
         </is>
       </c>
       <c r="I235" s="11" t="n"/>
@@ -10946,22 +10946,22 @@
       </c>
       <c r="B236" s="8" t="inlineStr">
         <is>
-          <t>Giant</t>
+          <t>Skeleton Crew</t>
         </is>
       </c>
       <c r="C236" s="9" t="inlineStr">
         <is>
-          <t>Giant</t>
+          <t>Chariots &gt; Chariot</t>
         </is>
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Tomb Kings.cat</t>
         </is>
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F236" s="9" t="inlineStr">
@@ -10971,420 +10971,24 @@
       </c>
       <c r="G236" s="9" t="inlineStr">
         <is>
-          <t>wiki: A Special-&gt;*</t>
+          <t>wiki: WS 3-&gt;2, Ld 7-&gt;3</t>
         </is>
       </c>
       <c r="H236" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/giant</t>
+          <t>https://6th.whfb.app/unit/skeleton-crew</t>
         </is>
       </c>
       <c r="I236" s="11" t="n"/>
       <c r="J236" s="11" t="n"/>
     </row>
-    <row r="237">
-      <c r="A237" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B237" s="8" t="inlineStr">
-        <is>
-          <t>Squig Hopper</t>
-        </is>
-      </c>
-      <c r="C237" s="9" t="inlineStr">
-        <is>
-          <t>Night Goblin Squig Herd &gt; Unit &gt; Squig Hopper</t>
-        </is>
-      </c>
-      <c r="D237" s="8" t="inlineStr">
-        <is>
-          <t>Orcs and Goblins.cat</t>
-        </is>
-      </c>
-      <c r="E237" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F237" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G237" s="9" t="inlineStr">
-        <is>
-          <t>wiki: W 2-&gt;1</t>
-        </is>
-      </c>
-      <c r="H237" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/squig-hopper</t>
-        </is>
-      </c>
-      <c r="I237" s="11" t="n"/>
-      <c r="J237" s="11" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B238" s="8" t="inlineStr">
-        <is>
-          <t>Clanrat Slave</t>
-        </is>
-      </c>
-      <c r="C238" s="9" t="inlineStr">
-        <is>
-          <t>Clanrat Slaves &gt; Clanrat Slaves</t>
-        </is>
-      </c>
-      <c r="D238" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E238" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F238" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G238" s="9" t="inlineStr">
-        <is>
-          <t>wiki: M 6-&gt;5, I 5-&gt;4</t>
-        </is>
-      </c>
-      <c r="H238" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/clanrat-slave</t>
-        </is>
-      </c>
-      <c r="I238" s="11" t="n"/>
-      <c r="J238" s="11" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B239" s="8" t="inlineStr">
-        <is>
-          <t>Festering Chantor</t>
-        </is>
-      </c>
-      <c r="C239" s="9" t="inlineStr">
-        <is>
-          <t>Festering Chantor</t>
-        </is>
-      </c>
-      <c r="D239" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E239" s="9" t="inlineStr">
-        <is>
-          <t>7 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F239" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G239" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
-        </is>
-      </c>
-      <c r="H239" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/festering-chantor</t>
-        </is>
-      </c>
-      <c r="I239" s="11" t="n"/>
-      <c r="J239" s="11" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B240" s="8" t="inlineStr">
-        <is>
-          <t>Plague Lord</t>
-        </is>
-      </c>
-      <c r="C240" s="9" t="inlineStr">
-        <is>
-          <t>Plague Lord</t>
-        </is>
-      </c>
-      <c r="D240" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E240" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F240" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G240" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 5-&gt;4</t>
-        </is>
-      </c>
-      <c r="H240" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/plague-lord</t>
-        </is>
-      </c>
-      <c r="I240" s="11" t="n"/>
-      <c r="J240" s="11" t="n"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B241" s="8" t="inlineStr">
-        <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="C241" s="9" t="inlineStr">
-        <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="D241" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E241" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F241" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G241" s="9" t="inlineStr">
-        <is>
-          <t>wiki: I 6-&gt;4</t>
-        </is>
-      </c>
-      <c r="H241" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
-        </is>
-      </c>
-      <c r="I241" s="11" t="n"/>
-      <c r="J241" s="11" t="n"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B242" s="8" t="inlineStr">
-        <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="C242" s="9" t="inlineStr">
-        <is>
-          <t>Warlock Master</t>
-        </is>
-      </c>
-      <c r="D242" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E242" s="9" t="inlineStr">
-        <is>
-          <t>6 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F242" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G242" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 4-&gt;3, T 4-&gt;3, W 3-&gt;2, I 5-&gt;4, A 2-&gt;1, Ld 7-&gt;5</t>
-        </is>
-      </c>
-      <c r="H242" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
-        </is>
-      </c>
-      <c r="I242" s="11" t="n"/>
-      <c r="J242" s="11" t="n"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B243" s="8" t="inlineStr">
-        <is>
-          <t>Skeleton</t>
-        </is>
-      </c>
-      <c r="C243" s="9" t="inlineStr">
-        <is>
-          <t>Skeleton Light Horsemen &gt; Skeleton Horseman</t>
-        </is>
-      </c>
-      <c r="D243" s="8" t="inlineStr">
-        <is>
-          <t>Tomb Kings.cat</t>
-        </is>
-      </c>
-      <c r="E243" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F243" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G243" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 5-&gt;3</t>
-        </is>
-      </c>
-      <c r="H243" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/skeleton</t>
-        </is>
-      </c>
-      <c r="I243" s="11" t="n"/>
-      <c r="J243" s="11" t="n"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B244" s="8" t="inlineStr">
-        <is>
-          <t>Skeleton</t>
-        </is>
-      </c>
-      <c r="C244" s="9" t="inlineStr">
-        <is>
-          <t>Skeleton Heavy Horsemen &gt; Skeleton Horseman</t>
-        </is>
-      </c>
-      <c r="D244" s="8" t="inlineStr">
-        <is>
-          <t>Tomb Kings.cat</t>
-        </is>
-      </c>
-      <c r="E244" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F244" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G244" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 5-&gt;3</t>
-        </is>
-      </c>
-      <c r="H244" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/skeleton</t>
-        </is>
-      </c>
-      <c r="I244" s="11" t="n"/>
-      <c r="J244" s="11" t="n"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B245" s="8" t="inlineStr">
-        <is>
-          <t>Skeleton Crew</t>
-        </is>
-      </c>
-      <c r="C245" s="9" t="inlineStr">
-        <is>
-          <t>Chariots &gt; Chariot</t>
-        </is>
-      </c>
-      <c r="D245" s="8" t="inlineStr">
-        <is>
-          <t>Tomb Kings.cat</t>
-        </is>
-      </c>
-      <c r="E245" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F245" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G245" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;2, Ld 7-&gt;3</t>
-        </is>
-      </c>
-      <c r="H245" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/skeleton-crew</t>
-        </is>
-      </c>
-      <c r="I245" s="11" t="n"/>
-      <c r="J245" s="11" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:J245"/>
+  <autoFilter ref="A2:J236"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4:I245" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I236" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Option A,Option B,Leave as is,Rename catalogue,Needs more thought"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11407,43 +11011,43 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId58"/>
@@ -11459,66 +11063,66 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId133"/>
@@ -11601,15 +11205,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId211"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId221"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/judgement-calls.xlsx
+++ b/docs/judgement-calls.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Decisions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -506,146 +506,142 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Fill in the Decision column on the 'Decisions' sheet. Nothing else needs editing.</t>
+          <t>Fill in the Decision column on the 'Decisions' sheet, or just write what should</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Decision cells are shaded yellow and offer a dropdown; you may also type free text.</t>
+          <t>happen in Notes - a note on its own counts as an answer and will be actioned.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>Decision cells are shaded yellow and offer a dropdown; you may also type free text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>Use the Notes column for anything an agent actioning this should know.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-    </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>'Used by' is what tells two same-named rules apart. For a rule that sits inside a</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>unit it reads as a path, outermost first: 'Plaguebearers &gt; Plaguebearer'. For one</t>
+          <t>'Used by' is what tells two same-named rules apart. For a rule that sits inside a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>in &lt;sharedRules&gt; it lists every entry that links to it - so a rule showing</t>
+          <t>unit it reads as a path, outermost first: 'Plaguebearers &gt; Plaguebearer'. For one</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>'shared; used by Plaguebearers, Stream of Corruption' serves both the unit and the</t>
+          <t>in &lt;sharedRules&gt; it lists every entry that links to it - so a rule showing</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>'shared; used by Plaguebearers, Stream of Corruption' serves both the unit and the</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Daemonic Gift of the same name, which is the decision to make.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Category meanings:</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Ambiguous match   the wiki has more than one page for this name and the texts differ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  No wiki coverage  no confident match. Often a catalogue spelling error - check the candidate</t>
+          <t xml:space="preserve">  Ambiguous match   the wiki has more than one page for this name and the texts differ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Points cost       catalogue and wiki disagree. NB Bretonnian Virtues are priced per</t>
+          <t xml:space="preserve">  No wiki coverage  no confident match. Often a catalogue spelling error - check the candidate</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    character rank, so several rows per item is expected, not a bug</t>
+          <t xml:space="preserve">  Points cost       catalogue and wiki disagree. NB Bretonnian Virtues are priced per</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">                    character rank, so several rows per item is expected, not a bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Unit statline     characteristics differ. Only characteristics both sides state are compared</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Source: wiki scrape at C:/src/6eWikiScraper, indexed 2026-09-17T12:43:16+00:00</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>Source: wiki scrape at C:/src/6eWikiScraper, indexed 2026-09-17T12:43:16+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>Generated by .claude/skills/bsdata-cat/scripts/wiki_xref.py</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Counts by category</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Ambiguous match</t>
-        </is>
-      </c>
-      <c r="B24" s="2">
-        <f>COUNTIF(Decisions!$A:$A,A24)</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Ambiguous match</t>
         </is>
       </c>
       <c r="B25" s="2">
@@ -656,7 +652,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>No wiki coverage</t>
         </is>
       </c>
       <c r="B26" s="2">
@@ -667,7 +663,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Unit statline</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B27" s="2">
@@ -676,13 +672,24 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Unit statline</t>
+        </is>
+      </c>
+      <c r="B28" s="2">
+        <f>COUNTIF(Decisions!$A:$A,A28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Still undecided</t>
         </is>
       </c>
-      <c r="B28" s="4">
-        <f>COUNTBLANK(Decisions!$I$4:$I$181)</f>
+      <c r="B29" s="4">
+        <f>COUNTBLANK(Decisions!$I$4:$I$170)</f>
         <v/>
       </c>
     </row>
@@ -697,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J181"/>
+  <dimension ref="A1:J170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -919,17 +926,17 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Expendable</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Clanrat Slaves, Rat Swarm</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -939,21 +946,29 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/expendable-clanrat-slaves</t>
+          <t>/unit/cannon-dogs-of-war</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/expendable-swarms</t>
+          <t>/unit/cannon-dwarfs</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/expendable-clanrat-slaves</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
+          <t>https://6th.whfb.app/unit/cannon-dogs-of-war</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>Needs more thought</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>Need to summarise the cannon rules https://6th.whfb.app/war-machines/cannons</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -963,12 +978,12 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>shared; used by (catalogue root)</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -978,22 +993,18 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>/special-rules/chariot-gorthor is Beasts of Chaos, not core rulebook - wrong for a shared rule</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>/unit/cannon-dogs-of-war</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>/unit/cannon-dwarfs</t>
-        </is>
-      </c>
+          <t>/special-rules/chariot-gorthor</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr"/>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/cannon-dogs-of-war</t>
+          <t>https://6th.whfb.app/special-rules/chariot-gorthor</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
@@ -1003,7 +1014,7 @@
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>Need to summarise the cannon rules https://6th.whfb.app/war-machines/cannons</t>
+          <t>Need to summarise the Chariot rules: https://6th.whfb.app/chariots</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1026,12 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Fast Cavalry</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>shared; used by (catalogue root)</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1030,18 +1041,22 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/chariot-gorthor is Beasts of Chaos, not core rulebook - wrong for a shared rule</t>
+          <t>wiki has 2 candidate pages</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/chariot-gorthor</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr"/>
+          <t>/faq/fast-cavalry</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>/fast-cavalry</t>
+        </is>
+      </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/chariot-gorthor</t>
+          <t>https://6th.whfb.app/faq/fast-cavalry</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
@@ -1051,7 +1066,7 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>Need to summarise the Chariot rules: https://6th.whfb.app/chariots</t>
+          <t>Need to summarise the Fast Cavalry rules https://6th.whfb.app/fast-cavalry</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1078,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Fast Cavalry</t>
+          <t>Skirmishers</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1083,17 +1098,17 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>/faq/fast-cavalry</t>
+          <t>/faq/skirmishers</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>/fast-cavalry</t>
+          <t>/skirmishers</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/fast-cavalry</t>
+          <t>https://6th.whfb.app/faq/skirmishers</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
@@ -1103,7 +1118,7 @@
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>Need to summarise the Fast Cavalry rules https://6th.whfb.app/fast-cavalry</t>
+          <t>Need to summarise the Skirmishers rules https://6th.whfb.app/skirmishers</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1130,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Skirmishers</t>
+          <t>Undead</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -1130,22 +1145,22 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>wiki has 2 candidate pages</t>
+          <t>wiki has 4 candidate pages</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>/faq/skirmishers</t>
+          <t>/special-rules/undead-regiments-of-renown</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>/skirmishers</t>
+          <t>/special-rules/undead-tomb-kings</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/skirmishers</t>
+          <t>https://6th.whfb.app/special-rules/undead-regiments-of-renown</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -1155,61 +1170,53 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>Need to summarise the Skirmishers rules https://6th.whfb.app/skirmishers</t>
+          <t>Need to validate that the implementation across TK &amp; VC is identical, and summarise it</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Ambiguous match</t>
+          <t>No wiki coverage</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>Diabolic Splendour</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Daemonic Gifts &gt; Diabolic Splendour</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>wiki has 4 candidate pages</t>
+          <t>no confident match; nearest candidate is not applied</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/undead-regiments-of-renown</t>
+          <t>leave as is</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/undead-tomb-kings</t>
+          <t>/magic-item/diabolical-splendour (0.66)</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/undead-regiments-of-renown</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>Needs more thought</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="inlineStr">
-        <is>
-          <t>Need to validate that the implementation across TK &amp; VC is identical, and summarise it</t>
-        </is>
-      </c>
+          <t>https://6th.whfb.app/magic-item/diabolical-splendour</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -1219,17 +1226,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Flame Cannon Misfire</t>
+          <t>Staff of Darkoath</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Flame Cannon</t>
+          <t>Arcane Items &gt; Staff of Darkoath</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1244,12 +1251,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/flame-cannon (0.90)</t>
+          <t>/magic-item/staff-of-darkoth (0.68)</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/flame-cannon</t>
+          <t>https://6th.whfb.app/magic-item/staff-of-darkoth</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -1263,17 +1270,17 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Gyrocopter</t>
+          <t>Vitriolic Totem</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Gyrocopter</t>
+          <t>Magic Banners &gt; Vitriolic Totem</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1288,12 +1295,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>/unit/gyrocopter (1.00)</t>
+          <t>/magic-item/vitrolic-totem (0.68)</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/gyrocopter</t>
+          <t>https://6th.whfb.app/magic-item/vitrolic-totem</t>
         </is>
       </c>
       <c r="I13" s="11" t="n"/>
@@ -1307,17 +1314,17 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Master Rune of Switftness</t>
+          <t>Ironfist</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Weapon Runes &gt; Master Rune of Switftness</t>
+          <t>shared; used by Bruiser, Ogre Bulls, Rhinox Cavalry, Tyrant</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1332,12 +1339,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>/unit/master (0.90)</t>
+          <t>/unit/garagrim-ironfist (0.80)</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/master</t>
+          <t>https://6th.whfb.app/unit/garagrim-ironfist</t>
         </is>
       </c>
       <c r="I14" s="11" t="n"/>
@@ -1351,17 +1358,17 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Organ Gun Misfire</t>
+          <t>Ironfists (Rhinox Riders)</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Organ Gun</t>
+          <t>Rhinox Cavalry &gt; Ironfists</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1376,12 +1383,12 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/organ-gun (0.90)</t>
+          <t>/unit/rhinox (0.80)</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/organ-gun</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -1395,17 +1402,17 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Rule of Pride</t>
+          <t>Mawseeker</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Big Names &gt; Mawseeker</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1435,17 +1442,17 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Diabolic Splendour</t>
+          <t>Move Over Obstacles</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Daemonic Gifts &gt; Diabolic Splendour</t>
+          <t>Slavegiant</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1460,12 +1467,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/diabolical-splendour (0.66)</t>
+          <t>/special-rules/move-giants (0.90)</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/diabolical-splendour</t>
+          <t>https://6th.whfb.app/special-rules/move-giants</t>
         </is>
       </c>
       <c r="I17" s="11" t="n"/>
@@ -1479,17 +1486,17 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Firewyrn of Tzeentch</t>
+          <t>Rhinox Cavalry</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Spawn of Chaos &gt; Spawn of Chaos &gt; Spawn of the Gods &gt; Firewyrn of Tzeentch</t>
+          <t>Rhinox Cavalry</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1504,12 +1511,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/regeneration (0.90)</t>
+          <t>/unit/rhinox (0.90)</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/regeneration</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I18" s="11" t="n"/>
@@ -1523,17 +1530,17 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Staff of Darkoath</t>
+          <t>Scrap Launcher</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Arcane Items &gt; Staff of Darkoath</t>
+          <t>Gnoblar Scraplauncher</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1548,12 +1555,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/staff-of-darkoth (0.68)</t>
+          <t>/unit/scraplauncher (0.67)</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/staff-of-darkoth</t>
+          <t>https://6th.whfb.app/unit/scraplauncher</t>
         </is>
       </c>
       <c r="I19" s="11" t="n"/>
@@ -1567,17 +1574,17 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Two Breath Weapons</t>
+          <t>Skrag the Slaughterer</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Mount &gt; Dragon of Chaos</t>
+          <t>Scrag the Slaughterer</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1592,12 +1599,12 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/breath-weapons (0.80)</t>
+          <t>/unit/skrag-the-slaughterer (1.00)</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/breath-weapons</t>
+          <t>https://6th.whfb.app/unit/skrag-the-slaughterer</t>
         </is>
       </c>
       <c r="I20" s="11" t="n"/>
@@ -1611,17 +1618,17 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Vitriolic Totem</t>
+          <t>Slavegiant Attacks</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Magic Banners &gt; Vitriolic Totem</t>
+          <t>Slavegiant</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1636,12 +1643,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/vitrolic-totem (0.68)</t>
+          <t>/unit/slavegiant (0.90)</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/vitrolic-totem</t>
+          <t>https://6th.whfb.app/unit/slavegiant</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -1655,17 +1662,17 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Bow of the Searfarer</t>
+          <t>Stump-Blades</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Magic Weapons &gt; Bow of the Searfarer</t>
+          <t>Scrag the Slaughterer</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1680,14 +1687,10 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>/weapons/bow (0.90)</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/weapons/bow</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr"/>
       <c r="I22" s="11" t="n"/>
       <c r="J22" s="11" t="n"/>
     </row>
@@ -1699,17 +1702,17 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Blessed Spawning of Tlzazcotl</t>
+          <t>The Scepter of the Titans</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Sacred Spawnings &gt; Blessed Spawning of Tlzazcotl</t>
+          <t>Greasus Goldtooth &gt; The Scepter of the Titans</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Lizardmen.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -1724,12 +1727,12 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/pawn (0.80)</t>
+          <t>/magic-item/sceptre-of-the-titans (0.61)</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/pawn</t>
+          <t>https://6th.whfb.app/magic-item/sceptre-of-the-titans</t>
         </is>
       </c>
       <c r="I23" s="11" t="n"/>
@@ -1743,17 +1746,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Cupped Hands of the Hold Ones</t>
+          <t>Thunderous Charge</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Sacred Plaques &gt; Cupped Hands of the Hold Ones</t>
+          <t>Rhinox Cavalry</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Lizardmen.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -1768,12 +1771,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>/movement/hold-movement (0.80)</t>
+          <t>/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish (0.80)</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/movement/hold-movement</t>
+          <t>https://6th.whfb.app/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish</t>
         </is>
       </c>
       <c r="I24" s="11" t="n"/>
@@ -1787,12 +1790,12 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Ironfist</t>
+          <t>Wallcrusher</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Bruiser, Ogre Bulls, Rhinox Cavalry, Tyrant</t>
+          <t>Big Names &gt; Wallcrusher</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1812,12 +1815,12 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>/unit/garagrim-ironfist (0.80)</t>
+          <t>/unit/crusher (0.80)</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/garagrim-ironfist</t>
+          <t>https://6th.whfb.app/unit/crusher</t>
         </is>
       </c>
       <c r="I25" s="11" t="n"/>
@@ -1831,12 +1834,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Ironfists (Rhinox Riders)</t>
+          <t>Yheetee Ice Weapons</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry &gt; Ironfists</t>
+          <t>Yheetees &gt; Yheetee Ice Weapons</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1856,12 +1859,12 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>/unit/rhinox (0.80)</t>
+          <t>/weapons/ice-weapons (0.80)</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
+          <t>https://6th.whfb.app/weapons/ice-weapons</t>
         </is>
       </c>
       <c r="I26" s="11" t="n"/>
@@ -1875,17 +1878,17 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Mawseeker</t>
+          <t>'Eadbuttin' 'At</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Big Names &gt; Mawseeker</t>
+          <t>Enchanted Items &gt; 'Eadbuttin' 'At</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1900,10 +1903,14 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr"/>
+          <t>/special-rules/eadbutt (0.90)</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/special-rules/eadbutt</t>
+        </is>
+      </c>
       <c r="I27" s="11" t="n"/>
       <c r="J27" s="11" t="n"/>
     </row>
@@ -1915,17 +1922,17 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Move Over Obstacles</t>
+          <t>Fungus Buster Brew</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Slavegiant</t>
+          <t>Shiny Stuff &gt; Fungus Buster Brew</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1940,14 +1947,10 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/move-giants (0.90)</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/special-rules/move-giants</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr"/>
       <c r="I28" s="11" t="n"/>
       <c r="J28" s="11" t="n"/>
     </row>
@@ -1959,17 +1962,17 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry</t>
+          <t>Giant</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry</t>
+          <t>Giant</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -1984,12 +1987,12 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>/unit/rhinox (0.90)</t>
+          <t>/unit/giant (1.00)</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I29" s="11" t="n"/>
@@ -2003,17 +2006,17 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Scrap Launcher</t>
+          <t>Giant Spiders</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Gnoblar Scraplauncher</t>
+          <t>Goblin Spider Riders</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2028,12 +2031,12 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>/unit/scraplauncher (0.67)</t>
+          <t>/unit/giant (0.90)</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/scraplauncher</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I30" s="11" t="n"/>
@@ -2047,17 +2050,17 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Skrag the Slaughterer</t>
+          <t>Giants Movement</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Scrag the Slaughterer</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -2072,12 +2075,12 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>/unit/skrag-the-slaughterer (1.00)</t>
+          <t>/unit/giant (0.90)</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/skrag-the-slaughterer</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I31" s="11" t="n"/>
@@ -2091,17 +2094,17 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Slavegiant Attacks</t>
+          <t>Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Slavegiant</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2116,12 +2119,12 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>/unit/slavegiant (0.90)</t>
+          <t>/unit/squig (0.80)</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/slavegiant</t>
+          <t>https://6th.whfb.app/unit/squig</t>
         </is>
       </c>
       <c r="I32" s="11" t="n"/>
@@ -2135,17 +2138,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Stump-Blades</t>
+          <t>Gobbla's Movement</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Scrag the Slaughterer</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2160,10 +2163,14 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr"/>
+          <t>/special-rules/move-giants (0.80)</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/special-rules/move-giants</t>
+        </is>
+      </c>
       <c r="I33" s="11" t="n"/>
       <c r="J33" s="11" t="n"/>
     </row>
@@ -2175,17 +2182,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>The Scepter of the Titans</t>
+          <t>Hate Dwarfs</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Greasus Goldtooth &gt; The Scepter of the Titans</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2200,12 +2207,12 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/sceptre-of-the-titans (0.61)</t>
+          <t>/unit/dwarf (0.80)</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/sceptre-of-the-titans</t>
+          <t>https://6th.whfb.app/unit/dwarf</t>
         </is>
       </c>
       <c r="I34" s="11" t="n"/>
@@ -2219,17 +2226,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Thunderous Charge</t>
+          <t>Insatiable Appetite</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2244,14 +2251,10 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish (0.80)</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr"/>
       <c r="I35" s="11" t="n"/>
       <c r="J35" s="11" t="n"/>
     </row>
@@ -2263,17 +2266,17 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Wallcrusher</t>
+          <t>Moving Fanatics into Obstacles</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Big Names &gt; Wallcrusher</t>
+          <t>Night Goblins &gt; Fanatics</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2288,12 +2291,12 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>/unit/crusher (0.80)</t>
+          <t>/skirmishers/moving (0.90)</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/crusher</t>
+          <t>https://6th.whfb.app/skirmishers/moving</t>
         </is>
       </c>
       <c r="I36" s="11" t="n"/>
@@ -2307,17 +2310,17 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Yheetee Ice Weapons</t>
+          <t>Porko's Pigstikka</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Yheetees &gt; Yheetee Ice Weapons</t>
+          <t>Magic Weapons &gt; Porko's Pigstikka</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2332,12 +2335,12 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>/weapons/ice-weapons (0.80)</t>
+          <t>/magic-item/porks-pigstikka (0.68)</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/ice-weapons</t>
+          <t>https://6th.whfb.app/magic-item/porks-pigstikka</t>
         </is>
       </c>
       <c r="I37" s="11" t="n"/>
@@ -2351,12 +2354,12 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>'Eadbuttin' 'At</t>
+          <t>Shooting at Skarsnik &amp; Gobbla</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Enchanted Items &gt; 'Eadbuttin' 'At</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2376,12 +2379,12 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/eadbutt (0.90)</t>
+          <t>/faq/shooting (0.90)</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/eadbutt</t>
+          <t>https://6th.whfb.app/faq/shooting</t>
         </is>
       </c>
       <c r="I38" s="11" t="n"/>
@@ -2395,12 +2398,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Fungus Buster Brew</t>
+          <t>Skarsnik's Prodder</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Shiny Stuff &gt; Fungus Buster Brew</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -2435,12 +2438,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Giant</t>
+          <t>Skarsnik's Prodder</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Giant</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2460,14 +2463,10 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (1.00)</t>
-        </is>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/giant</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr"/>
       <c r="I40" s="11" t="n"/>
       <c r="J40" s="11" t="n"/>
     </row>
@@ -2479,12 +2478,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Giant Spiders</t>
+          <t>Staff of Badumm</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Goblin Spider Riders</t>
+          <t>Arcane Items &gt; Unique Items &gt; Staff of Badumm</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -2504,12 +2503,12 @@
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (0.90)</t>
+          <t>/magic-item/staff-of-baduumm (0.68)</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/giant</t>
+          <t>https://6th.whfb.app/magic-item/staff-of-baduumm</t>
         </is>
       </c>
       <c r="I41" s="11" t="n"/>
@@ -2523,12 +2522,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Giants Movement</t>
+          <t>The Blasted Banner</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Grimgor Ironhide &gt; Bodyguard &gt; Da Immortulz &gt; The Blasted Banner</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2548,12 +2547,12 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (0.90)</t>
+          <t>/magic-item/the-beast-banner (0.62)</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/giant</t>
+          <t>https://6th.whfb.app/magic-item/the-beast-banner</t>
         </is>
       </c>
       <c r="I42" s="11" t="n"/>
@@ -2567,12 +2566,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Gobbla the Cave Squig</t>
+          <t>Warboss Umm's Best Big Boss 'At</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+          <t>Talismans &gt; Warboss Umm's Best Big Boss 'At</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -2592,12 +2591,12 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>/unit/squig (0.80)</t>
+          <t>/magic-item/warboss-umms-best-big-bosss-at (0.69)</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/squig</t>
+          <t>https://6th.whfb.app/magic-item/warboss-umms-best-big-bosss-at</t>
         </is>
       </c>
       <c r="I43" s="11" t="n"/>
@@ -2611,17 +2610,17 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Gobbla's Movement</t>
+          <t>Beastmaster</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+          <t>Master Moulder</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2636,12 +2635,12 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/move-giants (0.80)</t>
+          <t>/unit/beastmaster (1.00)</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/move-giants</t>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
         </is>
       </c>
       <c r="I44" s="11" t="n"/>
@@ -2655,17 +2654,17 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Hate Dwarfs</t>
+          <t>Beastmaster</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Master Mutator</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -2680,12 +2679,12 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>/unit/dwarf (0.80)</t>
+          <t>/unit/beastmaster (1.00)</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/dwarf</t>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
         </is>
       </c>
       <c r="I45" s="11" t="n"/>
@@ -2699,17 +2698,17 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Insatiable Appetite</t>
+          <t>Beastmaster</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+          <t>Harbinger of Mutation</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -2724,10 +2723,14 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr"/>
+          <t>/unit/beastmaster (1.00)</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
+        </is>
+      </c>
       <c r="I46" s="11" t="n"/>
       <c r="J46" s="11" t="n"/>
     </row>
@@ -2739,17 +2742,17 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Moving Fanatics into Obstacles</t>
+          <t>Boneripper</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Night Goblins &gt; Fanatics</t>
+          <t>Grey Seer Thanquol &amp; Boneripper</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2764,12 +2767,12 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>/skirmishers/moving (0.90)</t>
+          <t>/unit/boneripper (1.00)</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/skirmishers/moving</t>
+          <t>https://6th.whfb.app/unit/boneripper</t>
         </is>
       </c>
       <c r="I47" s="11" t="n"/>
@@ -2783,17 +2786,17 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Porko's Pigstikka</t>
+          <t>Cursed Blade of Delerium</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Magic Weapons &gt; Porko's Pigstikka</t>
+          <t>Magic Weapons &gt; Cursed Blade of Delerium</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -2808,12 +2811,12 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/porks-pigstikka (0.68)</t>
+          <t>/magic-item/cursed-blade-of-delirium (0.67)</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/porks-pigstikka</t>
+          <t>https://6th.whfb.app/magic-item/cursed-blade-of-delirium</t>
         </is>
       </c>
       <c r="I48" s="11" t="n"/>
@@ -2827,17 +2830,17 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Shooting at Skarsnik &amp; Gobbla</t>
+          <t>Daemonic Instability</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -2852,12 +2855,12 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>/faq/shooting (0.90)</t>
+          <t>/special-rules/daemonic (0.90)</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/shooting</t>
+          <t>https://6th.whfb.app/special-rules/daemonic</t>
         </is>
       </c>
       <c r="I49" s="11" t="n"/>
@@ -2871,17 +2874,17 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Skarsnik's Prodder</t>
+          <t>Doom Glaive</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -2911,17 +2914,17 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Skarsnik's Prodder</t>
+          <t>Doomwheel</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
+          <t>Doomwheel</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2936,10 +2939,14 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H51" s="10" t="inlineStr"/>
+          <t>/movement/wheel (0.80)</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/movement/wheel</t>
+        </is>
+      </c>
       <c r="I51" s="11" t="n"/>
       <c r="J51" s="11" t="n"/>
     </row>
@@ -2951,17 +2958,17 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Staff of Badumm</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Arcane Items &gt; Unique Items &gt; Staff of Badumm</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -2976,12 +2983,12 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/staff-of-baduumm (0.68)</t>
+          <t>/unit/festering-chantor (1.00)</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/staff-of-baduumm</t>
+          <t>https://6th.whfb.app/unit/festering-chantor</t>
         </is>
       </c>
       <c r="I52" s="11" t="n"/>
@@ -2995,17 +3002,17 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>The Blasted Banner</t>
+          <t>Harbinger of Mutation</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Grimgor Ironhide &gt; Bodyguard &gt; Da Immortulz &gt; The Blasted Banner</t>
+          <t>Harbinger of Mutation</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -3020,12 +3027,12 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/the-beast-banner (0.62)</t>
+          <t>/unit/harbinger (0.90)</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/the-beast-banner</t>
+          <t>https://6th.whfb.app/unit/harbinger</t>
         </is>
       </c>
       <c r="I53" s="11" t="n"/>
@@ -3039,17 +3046,17 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Warboss Umm's Best Big Boss 'At</t>
+          <t>High Ranking</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Talismans &gt; Warboss Umm's Best Big Boss 'At</t>
+          <t>Grey Seer</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -3064,14 +3071,10 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/warboss-umms-best-big-bosss-at (0.69)</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/warboss-umms-best-big-bosss-at</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr"/>
       <c r="I54" s="11" t="n"/>
       <c r="J54" s="11" t="n"/>
     </row>
@@ -3083,12 +3086,12 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
+          <t>Horned Rat Incarnate</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Master Moulder</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -3108,14 +3111,10 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
-        </is>
-      </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr"/>
       <c r="I55" s="11" t="n"/>
       <c r="J55" s="11" t="n"/>
     </row>
@@ -3127,12 +3126,12 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
+          <t>Plague Rats</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Master Mutator</t>
+          <t>Rat Swarm &gt; Plague Rats</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -3152,12 +3151,12 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
+          <t>/spell/plague (0.90)</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
+          <t>https://6th.whfb.app/spell/plague</t>
         </is>
       </c>
       <c r="I56" s="11" t="n"/>
@@ -3171,12 +3170,12 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
+          <t>Ratling Gun Misfire</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Harbinger of Mutation</t>
+          <t>Weapon Team &gt; Ratling Gun</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -3196,12 +3195,12 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
+          <t>/weapons/ratling-gun (0.90)</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
+          <t>https://6th.whfb.app/weapons/ratling-gun</t>
         </is>
       </c>
       <c r="I57" s="11" t="n"/>
@@ -3215,12 +3214,12 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Boneripper</t>
+          <t>Stands Alone</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Grey Seer Thanquol &amp; Boneripper</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -3240,14 +3239,10 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>/unit/boneripper (1.00)</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/boneripper</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr"/>
       <c r="I58" s="11" t="n"/>
       <c r="J58" s="11" t="n"/>
     </row>
@@ -3259,12 +3254,12 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Cursed Blade of Delerium</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Magic Weapons &gt; Cursed Blade of Delerium</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -3284,14 +3279,10 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/cursed-blade-of-delirium (0.67)</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/cursed-blade-of-delirium</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr"/>
       <c r="I59" s="11" t="n"/>
       <c r="J59" s="11" t="n"/>
     </row>
@@ -3303,12 +3294,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Instability</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -3328,12 +3319,12 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/daemonic (0.90)</t>
+          <t>/unit/warlock-engineer (1.00)</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/daemonic</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I60" s="11" t="n"/>
@@ -3347,12 +3338,12 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Doom Glaive</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Warlock Master</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -3372,10 +3363,14 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="inlineStr"/>
+          <t>/unit/warlock-engineer (1.00)</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+        </is>
+      </c>
       <c r="I61" s="11" t="n"/>
       <c r="J61" s="11" t="n"/>
     </row>
@@ -3387,12 +3382,12 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Doomwheel</t>
+          <t>Warpfire Thrower Misfire</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Doomwheel</t>
+          <t>Weapon Team &gt; Warpfire Thrower</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -3412,12 +3407,12 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>/movement/wheel (0.80)</t>
+          <t>/weapons/warpfire-thrower (0.90)</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/movement/wheel</t>
+          <t>https://6th.whfb.app/weapons/warpfire-thrower</t>
         </is>
       </c>
       <c r="I62" s="11" t="n"/>
@@ -3431,17 +3426,17 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Festering Chantor</t>
+          <t>Athandin</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Festering Chantor</t>
+          <t>Valten, Exalted of Sigmar &gt; Athandin</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -3456,12 +3451,12 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>/unit/festering-chantor (1.00)</t>
+          <t>/special-rules/althandin (0.66)</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/festering-chantor</t>
+          <t>https://6th.whfb.app/special-rules/althandin</t>
         </is>
       </c>
       <c r="I63" s="11" t="n"/>
@@ -3475,17 +3470,17 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Harbinger of Mutation</t>
+          <t>Charging with the Steam Tank</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Harbinger of Mutation</t>
+          <t>Steam Tank</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3500,12 +3495,12 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>/unit/harbinger (0.90)</t>
+          <t>/movement/charging (0.90)</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/harbinger</t>
+          <t>https://6th.whfb.app/movement/charging</t>
         </is>
       </c>
       <c r="I64" s="11" t="n"/>
@@ -3519,17 +3514,17 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>High Ranking</t>
+          <t>Electoral Banner</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Grey Seer</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -3559,17 +3554,17 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Horned Rat Incarnate</t>
+          <t>Fusilade</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Pistoliers</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -3584,10 +3579,14 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr"/>
+          <t>/special-rules/fusillade (0.66)</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/special-rules/fusillade</t>
+        </is>
+      </c>
       <c r="I66" s="11" t="n"/>
       <c r="J66" s="11" t="n"/>
     </row>
@@ -3599,17 +3598,17 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Plague Rats</t>
+          <t>Helm of the Skavenslayer</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Rat Swarm &gt; Plague Rats</t>
+          <t>Magic Armour &gt; Magic Armour &gt; Helm of the Skavenslayer</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3624,12 +3623,12 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>/spell/plague (0.90)</t>
+          <t>/army/skaven (0.80)</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/spell/plague</t>
+          <t>https://6th.whfb.app/army/skaven</t>
         </is>
       </c>
       <c r="I67" s="11" t="n"/>
@@ -3643,17 +3642,17 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Ratling Gun Misfire</t>
+          <t>Parent and Detachment Units</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Weapon Team &gt; Ratling Gun</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -3668,12 +3667,12 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>/weapons/ratling-gun (0.90)</t>
+          <t>/warhammer-glossary/unit-warhammer-glossary (0.80)</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/ratling-gun</t>
+          <t>https://6th.whfb.app/warhammer-glossary/unit-warhammer-glossary</t>
         </is>
       </c>
       <c r="I68" s="11" t="n"/>
@@ -3687,17 +3686,17 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Stands Alone</t>
+          <t>Shooting at the Steam Tank</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Steam Tank</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -3712,10 +3711,14 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr"/>
+          <t>/faq/shooting (0.90)</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/faq/shooting</t>
+        </is>
+      </c>
       <c r="I69" s="11" t="n"/>
       <c r="J69" s="11" t="n"/>
     </row>
@@ -3727,17 +3730,17 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Shooting with the Steam Tank</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Steam Tank</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -3752,10 +3755,14 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr"/>
+          <t>/faq/shooting (0.90)</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/faq/shooting</t>
+        </is>
+      </c>
       <c r="I70" s="11" t="n"/>
       <c r="J70" s="11" t="n"/>
     </row>
@@ -3767,17 +3774,17 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
+          <t>Steam Points</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
+          <t>Steam Tank</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
@@ -3792,12 +3799,12 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>/unit/warlock-engineer (1.00)</t>
+          <t>/special-rules/building-up-steam-points (0.80)</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+          <t>https://6th.whfb.app/special-rules/building-up-steam-points</t>
         </is>
       </c>
       <c r="I71" s="11" t="n"/>
@@ -3811,17 +3818,17 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
+          <t>Armour of Eternity</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Warlock Master</t>
+          <t>Magic Armour &gt; Magic Armour</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>Tomb Kings.cat</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -3836,12 +3843,12 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>/unit/warlock-engineer (1.00)</t>
+          <t>/appendix-eight-sequence-of-play/4-shooting-p58 (0.90)</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+          <t>https://6th.whfb.app/appendix-eight-sequence-of-play/4-shooting-p58</t>
         </is>
       </c>
       <c r="I72" s="11" t="n"/>
@@ -3855,17 +3862,17 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Warpfire Thrower Misfire</t>
+          <t>Ethereal Steeds</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Weapon Team &gt; Warpfire Thrower</t>
+          <t>shared; used by Black Knights</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>Vampire Counts.cat</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
@@ -3880,12 +3887,12 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>/weapons/warpfire-thrower (0.90)</t>
+          <t>/special-rules/ethereal (0.90)</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/warpfire-thrower</t>
+          <t>https://6th.whfb.app/special-rules/ethereal</t>
         </is>
       </c>
       <c r="I73" s="11" t="n"/>
@@ -3899,17 +3906,17 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Athandin</t>
+          <t>Fly</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Valten, Exalted of Sigmar &gt; Athandin</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -3924,12 +3931,12 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/althandin (0.66)</t>
+          <t>/faq/flyers (0.90)</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/althandin</t>
+          <t>https://6th.whfb.app/faq/flyers</t>
         </is>
       </c>
       <c r="I74" s="11" t="n"/>
@@ -3943,17 +3950,17 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Charging with the Steam Tank</t>
+          <t>Stone Thrower</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Steam Tank</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
@@ -3968,12 +3975,12 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>/movement/charging (0.90)</t>
+          <t>/unit/stone-thrower (1.00)</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/movement/charging</t>
+          <t>https://6th.whfb.app/unit/stone-thrower</t>
         </is>
       </c>
       <c r="I75" s="11" t="n"/>
@@ -3987,17 +3994,17 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Electoral Banner</t>
+          <t>Alter Kindred</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Wood Elf Kindred &gt; Alter Kindred</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -4012,10 +4019,14 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr"/>
+          <t>/magic-item/the-alter-kindreds (0.80)</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/magic-item/the-alter-kindreds</t>
+        </is>
+      </c>
       <c r="I76" s="11" t="n"/>
       <c r="J76" s="11" t="n"/>
     </row>
@@ -4027,17 +4038,17 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Fusilade</t>
+          <t>Gwytherc's Horn</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Pistoliers</t>
+          <t>Enchanted Items &gt; Gwytherc's Horn</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -4052,12 +4063,12 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/fusillade (0.66)</t>
+          <t>/magic-item/gwytheres-horn (0.65)</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/fusillade</t>
+          <t>https://6th.whfb.app/magic-item/gwytheres-horn</t>
         </is>
       </c>
       <c r="I77" s="11" t="n"/>
@@ -4071,17 +4082,17 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Helm of the Skavenslayer</t>
+          <t>Stone of the Crystal Mere</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Magic Armour &gt; Magic Armour &gt; Helm of the Skavenslayer</t>
+          <t>Talismans &gt; Stone of the Crystal Mere</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -4096,12 +4107,12 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>/army/skaven (0.80)</t>
+          <t>/magic-item/stone-of-the-crystal-merex (0.90)</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/army/skaven</t>
+          <t>https://6th.whfb.app/magic-item/stone-of-the-crystal-merex</t>
         </is>
       </c>
       <c r="I78" s="11" t="n"/>
@@ -4115,17 +4126,17 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Parent and Detachment Units</t>
+          <t>Strangle-Roots</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>shared; used by Treeman, Treeman Ancient</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -4140,56 +4151,52 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>/warhammer-glossary/unit-warhammer-glossary (0.80)</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/warhammer-glossary/unit-warhammer-glossary</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr"/>
       <c r="I79" s="11" t="n"/>
       <c r="J79" s="11" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Shooting at the Steam Tank</t>
+          <t>Virtue of Audacity</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Steam Tank</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>/faq/shooting (0.90)</t>
+          <t>wiki: 30</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/shooting</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
         </is>
       </c>
       <c r="I80" s="11" t="n"/>
@@ -4198,42 +4205,42 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Shooting with the Steam Tank</t>
+          <t>Virtue of Audacity</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Steam Tank</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 90</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>/faq/shooting (0.90)</t>
+          <t>wiki: 30</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/shooting</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
         </is>
       </c>
       <c r="I81" s="11" t="n"/>
@@ -4242,42 +4249,42 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Steam Points</t>
+          <t>Virtue of Confidence</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Steam Tank</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 50</t>
         </is>
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/building-up-steam-points (0.80)</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/building-up-steam-points</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
         </is>
       </c>
       <c r="I82" s="11" t="n"/>
@@ -4286,42 +4293,42 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Armour of Eternity</t>
+          <t>Virtue of Confidence</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Magic Armour &gt; Magic Armour</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Tomb Kings.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>/appendix-eight-sequence-of-play/4-shooting-p58 (0.90)</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/appendix-eight-sequence-of-play/4-shooting-p58</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
         </is>
       </c>
       <c r="I83" s="11" t="n"/>
@@ -4330,42 +4337,42 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Ethereal Steeds</t>
+          <t>Virtue of Confidence</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Black Knights</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Vampire Counts.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 75</t>
         </is>
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/ethereal (0.90)</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/ethereal</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
         </is>
       </c>
       <c r="I84" s="11" t="n"/>
@@ -4374,42 +4381,42 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Fly</t>
+          <t>Virtue of Discipline</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 90</t>
         </is>
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>/faq/flyers (0.90)</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/flyers</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I85" s="11" t="n"/>
@@ -4418,42 +4425,42 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Stone Thrower</t>
+          <t>Virtue of Discipline</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 30</t>
         </is>
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>/unit/stone-thrower (1.00)</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/stone-thrower</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I86" s="11" t="n"/>
@@ -4462,42 +4469,42 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Alter Kindred</t>
+          <t>Virtue of Discipline</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Wood Elf Kindred &gt; Alter Kindred</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 45</t>
         </is>
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/the-alter-kindreds (0.80)</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/the-alter-kindreds</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I87" s="11" t="n"/>
@@ -4506,42 +4513,42 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Gwytherc's Horn</t>
+          <t>Virtue of Discipline</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Enchanted Items &gt; Gwytherc's Horn</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/gwytheres-horn (0.65)</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/gwytheres-horn</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I88" s="11" t="n"/>
@@ -4550,42 +4557,42 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Stone of the Crystal Mere</t>
+          <t>Virtue of Discipline</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Talismans &gt; Stone of the Crystal Mere</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 75</t>
         </is>
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/stone-of-the-crystal-merex (0.90)</t>
+          <t>wiki: 15</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/stone-of-the-crystal-merex</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
         </is>
       </c>
       <c r="I89" s="11" t="n"/>
@@ -4594,40 +4601,44 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Strangle-Roots</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Treeman, Treeman Ancient</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 30</t>
         </is>
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H90" s="10" t="inlineStr"/>
+          <t>wiki: 10</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+        </is>
+      </c>
       <c r="I90" s="11" t="n"/>
       <c r="J90" s="11" t="n"/>
     </row>
@@ -4639,7 +4650,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Audacity</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
@@ -4659,17 +4670,17 @@
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 20</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>wiki: 30</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I91" s="11" t="n"/>
@@ -4683,7 +4694,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Audacity</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
@@ -4703,17 +4714,17 @@
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>wiki: 30</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I92" s="11" t="n"/>
@@ -4727,7 +4738,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
@@ -4747,17 +4758,17 @@
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I93" s="11" t="n"/>
@@ -4771,7 +4782,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
@@ -4791,17 +4802,17 @@
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 50</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I94" s="11" t="n"/>
@@ -4815,7 +4826,7 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
@@ -4835,17 +4846,17 @@
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I95" s="11" t="n"/>
@@ -4859,7 +4870,7 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
@@ -4879,17 +4890,17 @@
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue: 70</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I96" s="11" t="n"/>
@@ -4903,7 +4914,7 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
@@ -4923,17 +4934,17 @@
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 30</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I97" s="11" t="n"/>
@@ -4947,7 +4958,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Virtue of Empathy</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
@@ -4967,17 +4978,17 @@
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 45</t>
+          <t>catalogue: 90</t>
         </is>
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
         </is>
       </c>
       <c r="I98" s="11" t="n"/>
@@ -4991,7 +5002,7 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Virtue of Heroism</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
@@ -5011,17 +5022,17 @@
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 40</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-heroism</t>
         </is>
       </c>
       <c r="I99" s="11" t="n"/>
@@ -5035,7 +5046,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Virtue of Knightly Temper</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
@@ -5055,17 +5066,17 @@
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: 40</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-knightly-temper</t>
         </is>
       </c>
       <c r="I100" s="11" t="n"/>
@@ -5079,7 +5090,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Noble Disdain</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
@@ -5099,17 +5110,17 @@
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 30</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
         </is>
       </c>
       <c r="I101" s="11" t="n"/>
@@ -5123,7 +5134,7 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Noble Disdain</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
@@ -5143,17 +5154,17 @@
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 20</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
         </is>
       </c>
       <c r="I102" s="11" t="n"/>
@@ -5167,7 +5178,7 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Noble Disdain</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
@@ -5187,17 +5198,17 @@
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
         </is>
       </c>
       <c r="I103" s="11" t="n"/>
@@ -5211,7 +5222,7 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Noble Disdain</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
@@ -5231,17 +5242,17 @@
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
         </is>
       </c>
       <c r="I104" s="11" t="n"/>
@@ -5255,7 +5266,7 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Purity</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
@@ -5275,17 +5286,17 @@
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
         </is>
       </c>
       <c r="I105" s="11" t="n"/>
@@ -5299,7 +5310,7 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Purity</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
@@ -5319,17 +5330,17 @@
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 60</t>
         </is>
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
         </is>
       </c>
       <c r="I106" s="11" t="n"/>
@@ -5343,7 +5354,7 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Purity</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
@@ -5363,17 +5374,17 @@
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 70</t>
+          <t>catalogue: 100</t>
         </is>
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
         </is>
       </c>
       <c r="I107" s="11" t="n"/>
@@ -5387,7 +5398,7 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Purity</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
@@ -5412,12 +5423,12 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 20</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
         </is>
       </c>
       <c r="I108" s="11" t="n"/>
@@ -5431,7 +5442,7 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Virtue of Stoicism</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
@@ -5451,17 +5462,17 @@
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: 35</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
         </is>
       </c>
       <c r="I109" s="11" t="n"/>
@@ -5475,7 +5486,7 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Heroism</t>
+          <t>Virtue of Stoicism</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
@@ -5495,17 +5506,17 @@
       </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>wiki: 40</t>
+          <t>wiki: 35</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-heroism</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
         </is>
       </c>
       <c r="I110" s="11" t="n"/>
@@ -5519,7 +5530,7 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Knightly Temper</t>
+          <t>Virtue of the Ideal</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
@@ -5539,17 +5550,17 @@
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 70</t>
         </is>
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
-          <t>wiki: 40</t>
+          <t>wiki: 35</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-knightly-temper</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-ideal</t>
         </is>
       </c>
       <c r="I111" s="11" t="n"/>
@@ -5563,7 +5574,7 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Noble Disdain</t>
+          <t>Virtue of the Impetuous Knight</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
@@ -5583,17 +5594,17 @@
       </c>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue: 70</t>
         </is>
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 35</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-impetuous-knight</t>
         </is>
       </c>
       <c r="I112" s="11" t="n"/>
@@ -5607,7 +5618,7 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Noble Disdain</t>
+          <t>Virtue of the Joust</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
@@ -5627,17 +5638,17 @@
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 50</t>
         </is>
       </c>
       <c r="G113" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
         </is>
       </c>
       <c r="I113" s="11" t="n"/>
@@ -5651,7 +5662,7 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Noble Disdain</t>
+          <t>Virtue of the Joust</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
@@ -5671,17 +5682,17 @@
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 75</t>
         </is>
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
         </is>
       </c>
       <c r="I114" s="11" t="n"/>
@@ -5695,7 +5706,7 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Noble Disdain</t>
+          <t>Virtue of the Joust</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
@@ -5720,12 +5731,12 @@
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
         </is>
       </c>
       <c r="I115" s="11" t="n"/>
@@ -5739,7 +5750,7 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Purity</t>
+          <t>Virtue of the Penitent</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
@@ -5759,17 +5770,17 @@
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 40</t>
         </is>
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-the-penitent</t>
         </is>
       </c>
       <c r="I116" s="11" t="n"/>
@@ -5783,17 +5794,17 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Purity</t>
+          <t>Power Stone</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Arcane Items &gt; Unique Items</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
@@ -5803,17 +5814,17 @@
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue: 0</t>
         </is>
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 25</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
+          <t>https://6th.whfb.app/magic-item/power-stone</t>
         </is>
       </c>
       <c r="I117" s="11" t="n"/>
@@ -5827,17 +5838,17 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Purity</t>
+          <t>Pure of Heart</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Honours</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
@@ -5847,17 +5858,17 @@
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue: 0</t>
         </is>
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 500</t>
         </is>
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
+          <t>https://6th.whfb.app/magic-item/pure-of-heart</t>
         </is>
       </c>
       <c r="I118" s="11" t="n"/>
@@ -5871,17 +5882,17 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Purity</t>
+          <t>Ghal Maraz</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Emperor Karl Franz &gt; Weapon</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
@@ -5891,17 +5902,17 @@
       </c>
       <c r="F119" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 180</t>
         </is>
       </c>
       <c r="G119" s="9" t="inlineStr">
         <is>
-          <t>wiki: 20</t>
+          <t>wiki: 0</t>
         </is>
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
+          <t>https://6th.whfb.app/magic-item/ghal-maraz</t>
         </is>
       </c>
       <c r="I119" s="11" t="n"/>
@@ -5915,17 +5926,17 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Stoicism</t>
+          <t>Horn of the Wild Hunt</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Orion, the King in the Woods</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
@@ -5935,17 +5946,17 @@
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 0</t>
         </is>
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: 10</t>
         </is>
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
+          <t>https://6th.whfb.app/magic-item/horn-of-the-wild-hunt</t>
         </is>
       </c>
       <c r="I120" s="11" t="n"/>
@@ -5954,17 +5965,17 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Stoicism</t>
+          <t>Pegasus</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Pegasus Knights &gt; Pegasus Knight</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
@@ -5974,22 +5985,22 @@
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G121" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: Ld 7-&gt;6</t>
         </is>
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
+          <t>https://6th.whfb.app/unit/pegasus</t>
         </is>
       </c>
       <c r="I121" s="11" t="n"/>
@@ -5998,17 +6009,17 @@
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Ideal</t>
+          <t>Villein</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Peasant Bowmen &gt; Command &gt; Villein</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
@@ -6018,22 +6029,22 @@
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 70</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: WS 3-&gt;2, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-ideal</t>
+          <t>https://6th.whfb.app/unit/villein</t>
         </is>
       </c>
       <c r="I122" s="11" t="n"/>
@@ -6042,42 +6053,42 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Impetuous Knight</t>
+          <t>Bull Centaur Hero</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Bull Centaur Hero</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 70</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: T 4-&gt;5</t>
         </is>
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-impetuous-knight</t>
+          <t>https://6th.whfb.app/unit/bull-centaur-hero</t>
         </is>
       </c>
       <c r="I123" s="11" t="n"/>
@@ -6086,42 +6097,42 @@
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Joust</t>
+          <t>Chaos Dwarf Sorcerer</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Sorcerer Lord</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: S 4-&gt;3, T 5-&gt;4, W 3-&gt;2, I 1-&gt;2, Ld 10-&gt;9</t>
         </is>
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
+          <t>https://6th.whfb.app/unit/chaos-dwarf-sorcerer</t>
         </is>
       </c>
       <c r="I124" s="11" t="n"/>
@@ -6130,42 +6141,42 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Joust</t>
+          <t>Hobgoblin Crew</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Hobgoblin Bolt Thrower &gt; Hobgoblin Bolt Thrower</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: M 3-&gt;4</t>
         </is>
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
+          <t>https://6th.whfb.app/unit/hobgoblin-crew</t>
         </is>
       </c>
       <c r="I125" s="11" t="n"/>
@@ -6174,42 +6185,42 @@
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Joust</t>
+          <t>Bloodletter</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Bloodletters &gt; Bloodletters</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
+          <t>https://6th.whfb.app/unit/bloodletter</t>
         </is>
       </c>
       <c r="I126" s="11" t="n"/>
@@ -6218,42 +6229,42 @@
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>Virtue of the Penitent</t>
+          <t>Daemonette</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Daemonettes &gt; Daemonettes</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>wiki: 40</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-penitent</t>
+          <t>https://6th.whfb.app/unit/daemonette</t>
         </is>
       </c>
       <c r="I127" s="11" t="n"/>
@@ -6262,42 +6273,42 @@
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Power Stone</t>
+          <t>Daemonette</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Arcane Items &gt; Unique Items</t>
+          <t>Mounted Daemonettes &gt; Mounted Daemonette</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 0</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/power-stone</t>
+          <t>https://6th.whfb.app/unit/daemonette</t>
         </is>
       </c>
       <c r="I128" s="11" t="n"/>
@@ -6306,42 +6317,42 @@
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>Pure of Heart</t>
+          <t>Flamer</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Honours</t>
+          <t>Flamers &gt; Flamer</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 0</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>wiki: 500</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/pure-of-heart</t>
+          <t>https://6th.whfb.app/unit/flamer</t>
         </is>
       </c>
       <c r="I129" s="11" t="n"/>
@@ -6350,42 +6361,42 @@
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Ghal Maraz</t>
+          <t>Flesh Hound</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Emperor Karl Franz &gt; Weapon</t>
+          <t>Flesh Hounds &gt; Flesh Hounds</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 180</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>wiki: 0</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/ghal-maraz</t>
+          <t>https://6th.whfb.app/unit/flesh-hound</t>
         </is>
       </c>
       <c r="I130" s="11" t="n"/>
@@ -6394,42 +6405,42 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>Horn of the Wild Hunt</t>
+          <t>Horror</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Orion, the King in the Woods</t>
+          <t>Horrors &gt; Horrors</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 0</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/horn-of-the-wild-hunt</t>
+          <t>https://6th.whfb.app/unit/horror</t>
         </is>
       </c>
       <c r="I131" s="11" t="n"/>
@@ -6443,17 +6454,17 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Pegasus</t>
+          <t>Nurglings</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Pegasus Knights &gt; Pegasus Knight</t>
+          <t>Nurglings &gt; Nurglings</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E132" s="9" t="inlineStr">
@@ -6468,12 +6479,12 @@
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 7-&gt;6</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/pegasus</t>
+          <t>https://6th.whfb.app/unit/nurglings</t>
         </is>
       </c>
       <c r="I132" s="11" t="n"/>
@@ -6487,22 +6498,22 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>Villein</t>
+          <t>Plaguebearer</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Peasant Bowmen &gt; Command &gt; Villein</t>
+          <t>Plaguebearers &gt; Plaguebearers</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E133" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr">
@@ -6512,12 +6523,12 @@
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;2, A 1-&gt;2</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/villein</t>
+          <t>https://6th.whfb.app/unit/plaguebearer</t>
         </is>
       </c>
       <c r="I133" s="11" t="n"/>
@@ -6531,17 +6542,17 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Bull Centaur Hero</t>
+          <t>Screamer</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Bull Centaur Hero</t>
+          <t>Screamers of Tzeentch &gt; Screamer</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarves.cat</t>
+          <t>Daemonic Legions.cat</t>
         </is>
       </c>
       <c r="E134" s="9" t="inlineStr">
@@ -6556,12 +6567,12 @@
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
-          <t>wiki: T 4-&gt;5</t>
+          <t>wiki: Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bull-centaur-hero</t>
+          <t>https://6th.whfb.app/unit/screamer</t>
         </is>
       </c>
       <c r="I134" s="11" t="n"/>
@@ -6575,22 +6586,22 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarf Sorcerer</t>
+          <t>Hag</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Sorcerer Lord</t>
+          <t>Cauldron of Blood</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarves.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E135" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr">
@@ -6600,12 +6611,12 @@
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 4-&gt;3, T 5-&gt;4, W 3-&gt;2, I 1-&gt;2, Ld 10-&gt;9</t>
+          <t>wiki: WS 4-&gt;5</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/chaos-dwarf-sorcerer</t>
+          <t>https://6th.whfb.app/unit/hag</t>
         </is>
       </c>
       <c r="I135" s="11" t="n"/>
@@ -6619,22 +6630,22 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Hobgoblin Crew</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Hobgoblin Bolt Thrower &gt; Hobgoblin Bolt Thrower</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Chaos Dwarves.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F136" s="9" t="inlineStr">
@@ -6644,12 +6655,12 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 3-&gt;4</t>
+          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
         </is>
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/hobgoblin-crew</t>
+          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
         </is>
       </c>
       <c r="I136" s="11" t="n"/>
@@ -6663,22 +6674,22 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>Bloodletter</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>Bloodletters &gt; Bloodletters</t>
+          <t>Cold One Knights &gt; Cold One Knights</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr">
@@ -6688,12 +6699,12 @@
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: M 5-&gt;4, WS 5-&gt;4, BS 4-&gt;3, I 5-&gt;3, Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bloodletter</t>
+          <t>https://6th.whfb.app/unit/knight</t>
         </is>
       </c>
       <c r="I137" s="11" t="n"/>
@@ -6707,22 +6718,22 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Daemonette</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>Daemonettes &gt; Daemonettes</t>
+          <t>Knights of Chaos &gt; Knights</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>4 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr">
@@ -6732,12 +6743,12 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/daemonette</t>
+          <t>https://6th.whfb.app/unit/knight</t>
         </is>
       </c>
       <c r="I138" s="11" t="n"/>
@@ -6751,22 +6762,22 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>Daemonette</t>
+          <t>Steed of Slaanesh</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>Mounted Daemonettes &gt; Mounted Daemonette</t>
+          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F139" s="9" t="inlineStr">
@@ -6776,12 +6787,12 @@
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/daemonette</t>
+          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
         </is>
       </c>
       <c r="I139" s="11" t="n"/>
@@ -6795,17 +6806,17 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Flamer</t>
+          <t>Daddallo</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>Flamers &gt; Flamer</t>
+          <t>Birdmen of Catrazza &gt; Daddallo</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
@@ -6820,12 +6831,12 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: A 2-&gt;1</t>
         </is>
       </c>
       <c r="H140" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/flamer</t>
+          <t>https://6th.whfb.app/unit/daddallo</t>
         </is>
       </c>
       <c r="I140" s="11" t="n"/>
@@ -6839,17 +6850,17 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>Flesh Hound</t>
+          <t>Warhorse</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>Flesh Hounds &gt; Flesh Hounds</t>
+          <t>shared; used by Al Muktar's Desert Dogs, Bronzino's Galloper Guns</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
@@ -6864,12 +6875,12 @@
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: BS 3-&gt;0</t>
         </is>
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/flesh-hound</t>
+          <t>https://6th.whfb.app/unit/warhorse</t>
         </is>
       </c>
       <c r="I141" s="11" t="n"/>
@@ -6883,17 +6894,17 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Horror</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>Horrors &gt; Horrors</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Dwarfs.cat</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
@@ -6908,12 +6919,12 @@
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: A 2-&gt;1</t>
         </is>
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/horror</t>
+          <t>https://6th.whfb.app/unit/engineer</t>
         </is>
       </c>
       <c r="I142" s="11" t="n"/>
@@ -6927,17 +6938,17 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>Nurglings</t>
+          <t>Bloodthirster</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>Nurglings &gt; Nurglings</t>
+          <t>Bloodthirster</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E143" s="9" t="inlineStr">
@@ -6952,12 +6963,12 @@
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: S 7-&gt;6(7)</t>
         </is>
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/nurglings</t>
+          <t>https://6th.whfb.app/unit/bloodthirster</t>
         </is>
       </c>
       <c r="I143" s="11" t="n"/>
@@ -6971,22 +6982,22 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Plaguebearer</t>
+          <t>Centigor</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
         <is>
-          <t>Plaguebearers &gt; Plaguebearers</t>
+          <t>Minotaurs &gt; Minotaurs</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr">
@@ -6996,12 +7007,12 @@
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: M 6-&gt;8, W 3-&gt;1, I 4-&gt;2, A 3-&gt;1(2), Ld 8-&gt;7</t>
         </is>
       </c>
       <c r="H144" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/plaguebearer</t>
+          <t>https://6th.whfb.app/unit/centigor</t>
         </is>
       </c>
       <c r="I144" s="11" t="n"/>
@@ -7015,17 +7026,17 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>Screamer</t>
+          <t>Chaos Giant</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>Screamers of Tzeentch &gt; Screamer</t>
+          <t>Chaos Giant</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Legions.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
@@ -7040,12 +7051,12 @@
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>wiki: Ld 9-&gt;8</t>
+          <t>wiki: A Special-&gt;*</t>
         </is>
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/screamer</t>
+          <t>https://6th.whfb.app/unit/chaos-giant</t>
         </is>
       </c>
       <c r="I145" s="11" t="n"/>
@@ -7059,22 +7070,22 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Hag</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>Cauldron of Blood</t>
+          <t>Lord of Change</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>4 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr">
@@ -7084,12 +7095,12 @@
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 4-&gt;5</t>
+          <t>wiki: M 6-&gt;8, WS 6-&gt;9, A 5-&gt;10, Ld 9-&gt;6</t>
         </is>
       </c>
       <c r="H146" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/hag</t>
+          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
         </is>
       </c>
       <c r="I146" s="11" t="n"/>
@@ -7113,7 +7124,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
@@ -7152,17 +7163,17 @@
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>Cold One Knights &gt; Cold One Knights</t>
+          <t>Knights of Chaos &gt; Knights</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>4 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr">
@@ -7172,7 +7183,7 @@
       </c>
       <c r="G148" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 5-&gt;4, WS 5-&gt;4, BS 4-&gt;3, I 5-&gt;3, Ld 9-&gt;8</t>
+          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
         </is>
       </c>
       <c r="H148" s="10" t="inlineStr">
@@ -7191,22 +7202,22 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Steed of Slaanesh</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>Knights of Chaos &gt; Knights</t>
+          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>4 characteristic(s) differ</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr">
@@ -7216,12 +7227,12 @@
       </c>
       <c r="G149" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/knight</t>
+          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
         </is>
       </c>
       <c r="I149" s="11" t="n"/>
@@ -7235,22 +7246,22 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Steed of Slaanesh</t>
+          <t>Troll</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
+          <t>Chaos Trolls &gt; Trolls</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Dark Elves.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr">
@@ -7260,12 +7271,12 @@
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
+          <t>wiki: A 4-&gt;3</t>
         </is>
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
+          <t>https://6th.whfb.app/unit/troll</t>
         </is>
       </c>
       <c r="I150" s="11" t="n"/>
@@ -7279,17 +7290,17 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>Daddallo</t>
+          <t>Tuskgor</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>Birdmen of Catrazza &gt; Daddallo</t>
+          <t>Gorthor the Beastlord</t>
         </is>
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E151" s="9" t="inlineStr">
@@ -7304,12 +7315,12 @@
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 2-&gt;1</t>
+          <t>wiki: S 4-&gt;3</t>
         </is>
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/daddallo</t>
+          <t>https://6th.whfb.app/unit/tuskgor</t>
         </is>
       </c>
       <c r="I151" s="11" t="n"/>
@@ -7323,17 +7334,17 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Warhorse</t>
+          <t>Ungor</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Al Muktar's Desert Dogs, Bronzino's Galloper Guns</t>
+          <t>Beast Herd &gt; Ungors</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Dogs of War.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E152" s="9" t="inlineStr">
@@ -7348,12 +7359,12 @@
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>wiki: BS 3-&gt;0</t>
+          <t>wiki: T 4-&gt;3</t>
         </is>
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warhorse</t>
+          <t>https://6th.whfb.app/unit/ungor</t>
         </is>
       </c>
       <c r="I152" s="11" t="n"/>
@@ -7367,17 +7378,17 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Ungor</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Tuskgor Chariot</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>Dwarfs.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
@@ -7392,12 +7403,12 @@
       </c>
       <c r="G153" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 2-&gt;1</t>
+          <t>wiki: WS 4-&gt;3</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/engineer</t>
+          <t>https://6th.whfb.app/unit/ungor</t>
         </is>
       </c>
       <c r="I153" s="11" t="n"/>
@@ -7411,22 +7422,22 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Bloodthirster</t>
+          <t>Bladelord</t>
         </is>
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>Bloodthirster</t>
+          <t>Phoenix Guard &gt; Command &gt; Keeper of the Flame</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>3 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr">
@@ -7436,12 +7447,12 @@
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 7-&gt;6(7)</t>
+          <t>wiki: WS 5-&gt;6, I 6-&gt;5, Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H154" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bloodthirster</t>
+          <t>https://6th.whfb.app/unit/bladelord</t>
         </is>
       </c>
       <c r="I154" s="11" t="n"/>
@@ -7455,22 +7466,22 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>Centigor</t>
+          <t>Ellyrian Reaver</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
         <is>
-          <t>Minotaurs &gt; Minotaurs</t>
+          <t>Ellyrian Reavers &gt; Ellyrian Reavers</t>
         </is>
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E155" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F155" s="9" t="inlineStr">
@@ -7480,12 +7491,12 @@
       </c>
       <c r="G155" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 6-&gt;8, W 3-&gt;1, I 4-&gt;2, A 3-&gt;1(2), Ld 8-&gt;7</t>
+          <t>wiki: A 1-&gt;2</t>
         </is>
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/centigor</t>
+          <t>https://6th.whfb.app/unit/ellyrian-reaver</t>
         </is>
       </c>
       <c r="I155" s="11" t="n"/>
@@ -7499,17 +7510,17 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Chaos Giant</t>
+          <t>Harbinger</t>
         </is>
       </c>
       <c r="C156" s="9" t="inlineStr">
         <is>
-          <t>Chaos Giant</t>
+          <t>Ellyrian Reavers &gt; Command &gt; Harbinger</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E156" s="9" t="inlineStr">
@@ -7524,12 +7535,12 @@
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
-          <t>wiki: A Special-&gt;*</t>
+          <t>wiki: A 1-&gt;2</t>
         </is>
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/chaos-giant</t>
+          <t>https://6th.whfb.app/unit/harbinger</t>
         </is>
       </c>
       <c r="I156" s="11" t="n"/>
@@ -7543,22 +7554,22 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
+          <t>Greyback</t>
         </is>
       </c>
       <c r="C157" s="9" t="inlineStr">
         <is>
-          <t>Lord of Change</t>
+          <t>Yheetees &gt; Greyback</t>
         </is>
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E157" s="9" t="inlineStr">
         <is>
-          <t>4 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F157" s="9" t="inlineStr">
@@ -7568,12 +7579,12 @@
       </c>
       <c r="G157" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 6-&gt;8, WS 6-&gt;9, A 5-&gt;10, Ld 9-&gt;6</t>
+          <t>wiki: A 4-&gt;3</t>
         </is>
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
+          <t>https://6th.whfb.app/unit/greyback</t>
         </is>
       </c>
       <c r="I157" s="11" t="n"/>
@@ -7587,22 +7598,22 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
+          <t>Rhinox</t>
         </is>
       </c>
       <c r="C158" s="9" t="inlineStr">
         <is>
-          <t>Keeper of Secrets</t>
+          <t>Rhinox Cavalry &gt; Rhinox Riders</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
-          <t>2 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F158" s="9" t="inlineStr">
@@ -7612,12 +7623,12 @@
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
+          <t>wiki: M 7-&gt;6</t>
         </is>
       </c>
       <c r="H158" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I158" s="11" t="n"/>
@@ -7631,22 +7642,22 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Thunderfist</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
         <is>
-          <t>Knights of Chaos &gt; Knights</t>
+          <t>Leadbelchers &gt; Command &gt; Thunderfist</t>
         </is>
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E159" s="9" t="inlineStr">
         <is>
-          <t>4 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F159" s="9" t="inlineStr">
@@ -7656,12 +7667,12 @@
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
+          <t>wiki: BS 2-&gt;3</t>
         </is>
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/knight</t>
+          <t>https://6th.whfb.app/unit/thunderfist</t>
         </is>
       </c>
       <c r="I159" s="11" t="n"/>
@@ -7675,22 +7686,22 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>Steed of Slaanesh</t>
+          <t>Boar Chariot</t>
         </is>
       </c>
       <c r="C160" s="9" t="inlineStr">
         <is>
-          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
+          <t>Savage Orc Boar Chariot</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E160" s="9" t="inlineStr">
         <is>
-          <t>5 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F160" s="9" t="inlineStr">
@@ -7700,12 +7711,12 @@
       </c>
       <c r="G160" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
+          <t>wiki: S 5-&gt;3</t>
         </is>
       </c>
       <c r="H160" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
+          <t>https://6th.whfb.app/unit/boar-chariot</t>
         </is>
       </c>
       <c r="I160" s="11" t="n"/>
@@ -7719,17 +7730,17 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>Troll</t>
+          <t>Giant</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
         <is>
-          <t>Chaos Trolls &gt; Trolls</t>
+          <t>Giant</t>
         </is>
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E161" s="9" t="inlineStr">
@@ -7744,12 +7755,12 @@
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 4-&gt;3</t>
+          <t>wiki: A Special-&gt;*</t>
         </is>
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/troll</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I161" s="11" t="n"/>
@@ -7763,17 +7774,17 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>Tuskgor</t>
+          <t>Squig Hopper</t>
         </is>
       </c>
       <c r="C162" s="9" t="inlineStr">
         <is>
-          <t>Gorthor the Beastlord</t>
+          <t>Night Goblin Squig Herd &gt; Unit &gt; Squig Hopper</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E162" s="9" t="inlineStr">
@@ -7788,12 +7799,12 @@
       </c>
       <c r="G162" s="9" t="inlineStr">
         <is>
-          <t>wiki: S 4-&gt;3</t>
+          <t>wiki: W 2-&gt;1</t>
         </is>
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/tuskgor</t>
+          <t>https://6th.whfb.app/unit/squig-hopper</t>
         </is>
       </c>
       <c r="I162" s="11" t="n"/>
@@ -7807,22 +7818,22 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>Ungor</t>
+          <t>Clanrat Slave</t>
         </is>
       </c>
       <c r="C163" s="9" t="inlineStr">
         <is>
-          <t>Beast Herd &gt; Ungors</t>
+          <t>Clanrat Slaves &gt; Clanrat Slaves</t>
         </is>
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E163" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F163" s="9" t="inlineStr">
@@ -7832,12 +7843,12 @@
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>wiki: T 4-&gt;3</t>
+          <t>wiki: M 6-&gt;5, I 5-&gt;4</t>
         </is>
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/ungor</t>
+          <t>https://6th.whfb.app/unit/clanrat-slave</t>
         </is>
       </c>
       <c r="I163" s="11" t="n"/>
@@ -7851,22 +7862,22 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Ungor</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="C164" s="9" t="inlineStr">
         <is>
-          <t>Tuskgor Chariot</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E164" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>7 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F164" s="9" t="inlineStr">
@@ -7876,12 +7887,12 @@
       </c>
       <c r="G164" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 4-&gt;3</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
         </is>
       </c>
       <c r="H164" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/ungor</t>
+          <t>https://6th.whfb.app/unit/festering-chantor</t>
         </is>
       </c>
       <c r="I164" s="11" t="n"/>
@@ -7895,22 +7906,22 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>Bladelord</t>
+          <t>Plague Lord</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
         <is>
-          <t>Phoenix Guard &gt; Command &gt; Keeper of the Flame</t>
+          <t>Plague Lord</t>
         </is>
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E165" s="9" t="inlineStr">
         <is>
-          <t>3 characteristic(s) differ</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F165" s="9" t="inlineStr">
@@ -7920,12 +7931,12 @@
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>wiki: WS 5-&gt;6, I 6-&gt;5, Ld 9-&gt;8</t>
+          <t>wiki: A 5-&gt;4</t>
         </is>
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/bladelord</t>
+          <t>https://6th.whfb.app/unit/plague-lord</t>
         </is>
       </c>
       <c r="I165" s="11" t="n"/>
@@ -7939,17 +7950,17 @@
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>Ellyrian Reaver</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C166" s="9" t="inlineStr">
         <is>
-          <t>Ellyrian Reavers &gt; Ellyrian Reavers</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E166" s="9" t="inlineStr">
@@ -7964,12 +7975,12 @@
       </c>
       <c r="G166" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 1-&gt;2</t>
+          <t>wiki: I 6-&gt;4</t>
         </is>
       </c>
       <c r="H166" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/ellyrian-reaver</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I166" s="11" t="n"/>
@@ -7983,22 +7994,22 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>Harbinger</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
         <is>
-          <t>Ellyrian Reavers &gt; Command &gt; Harbinger</t>
+          <t>Warlock Master</t>
         </is>
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>High Elves.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E167" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>6 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F167" s="9" t="inlineStr">
@@ -8008,12 +8019,12 @@
       </c>
       <c r="G167" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 1-&gt;2</t>
+          <t>wiki: WS 4-&gt;3, T 4-&gt;3, W 3-&gt;2, I 5-&gt;4, A 2-&gt;1, Ld 7-&gt;5</t>
         </is>
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/harbinger</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I167" s="11" t="n"/>
@@ -8027,17 +8038,17 @@
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t>Greyback</t>
+          <t>Skeleton</t>
         </is>
       </c>
       <c r="C168" s="9" t="inlineStr">
         <is>
-          <t>Yheetees &gt; Greyback</t>
+          <t>Skeleton Light Horsemen &gt; Skeleton Horseman</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Tomb Kings.cat</t>
         </is>
       </c>
       <c r="E168" s="9" t="inlineStr">
@@ -8052,12 +8063,12 @@
       </c>
       <c r="G168" s="9" t="inlineStr">
         <is>
-          <t>wiki: A 4-&gt;3</t>
+          <t>wiki: Ld 5-&gt;3</t>
         </is>
       </c>
       <c r="H168" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/greyback</t>
+          <t>https://6th.whfb.app/unit/skeleton</t>
         </is>
       </c>
       <c r="I168" s="11" t="n"/>
@@ -8071,17 +8082,17 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>Rhinox</t>
+          <t>Skeleton</t>
         </is>
       </c>
       <c r="C169" s="9" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry &gt; Rhinox Riders</t>
+          <t>Skeleton Heavy Horsemen &gt; Skeleton Horseman</t>
         </is>
       </c>
       <c r="D169" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Tomb Kings.cat</t>
         </is>
       </c>
       <c r="E169" s="9" t="inlineStr">
@@ -8096,12 +8107,12 @@
       </c>
       <c r="G169" s="9" t="inlineStr">
         <is>
-          <t>wiki: M 7-&gt;6</t>
+          <t>wiki: Ld 5-&gt;3</t>
         </is>
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
+          <t>https://6th.whfb.app/unit/skeleton</t>
         </is>
       </c>
       <c r="I169" s="11" t="n"/>
@@ -8115,22 +8126,22 @@
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
-          <t>Thunderfist</t>
+          <t>Skeleton Crew</t>
         </is>
       </c>
       <c r="C170" s="9" t="inlineStr">
         <is>
-          <t>Leadbelchers &gt; Command &gt; Thunderfist</t>
+          <t>Chariots &gt; Chariot</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Tomb Kings.cat</t>
         </is>
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>1 characteristic(s) differ</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F170" s="9" t="inlineStr">
@@ -8140,508 +8151,24 @@
       </c>
       <c r="G170" s="9" t="inlineStr">
         <is>
-          <t>wiki: BS 2-&gt;3</t>
+          <t>wiki: WS 3-&gt;2, Ld 7-&gt;3</t>
         </is>
       </c>
       <c r="H170" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/thunderfist</t>
+          <t>https://6th.whfb.app/unit/skeleton-crew</t>
         </is>
       </c>
       <c r="I170" s="11" t="n"/>
       <c r="J170" s="11" t="n"/>
     </row>
-    <row r="171">
-      <c r="A171" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B171" s="8" t="inlineStr">
-        <is>
-          <t>Boar Chariot</t>
-        </is>
-      </c>
-      <c r="C171" s="9" t="inlineStr">
-        <is>
-          <t>Savage Orc Boar Chariot</t>
-        </is>
-      </c>
-      <c r="D171" s="8" t="inlineStr">
-        <is>
-          <t>Orcs and Goblins.cat</t>
-        </is>
-      </c>
-      <c r="E171" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F171" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G171" s="9" t="inlineStr">
-        <is>
-          <t>wiki: S 5-&gt;3</t>
-        </is>
-      </c>
-      <c r="H171" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/boar-chariot</t>
-        </is>
-      </c>
-      <c r="I171" s="11" t="n"/>
-      <c r="J171" s="11" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B172" s="8" t="inlineStr">
-        <is>
-          <t>Giant</t>
-        </is>
-      </c>
-      <c r="C172" s="9" t="inlineStr">
-        <is>
-          <t>Giant</t>
-        </is>
-      </c>
-      <c r="D172" s="8" t="inlineStr">
-        <is>
-          <t>Orcs and Goblins.cat</t>
-        </is>
-      </c>
-      <c r="E172" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F172" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G172" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A Special-&gt;*</t>
-        </is>
-      </c>
-      <c r="H172" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/giant</t>
-        </is>
-      </c>
-      <c r="I172" s="11" t="n"/>
-      <c r="J172" s="11" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B173" s="8" t="inlineStr">
-        <is>
-          <t>Squig Hopper</t>
-        </is>
-      </c>
-      <c r="C173" s="9" t="inlineStr">
-        <is>
-          <t>Night Goblin Squig Herd &gt; Unit &gt; Squig Hopper</t>
-        </is>
-      </c>
-      <c r="D173" s="8" t="inlineStr">
-        <is>
-          <t>Orcs and Goblins.cat</t>
-        </is>
-      </c>
-      <c r="E173" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F173" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G173" s="9" t="inlineStr">
-        <is>
-          <t>wiki: W 2-&gt;1</t>
-        </is>
-      </c>
-      <c r="H173" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/squig-hopper</t>
-        </is>
-      </c>
-      <c r="I173" s="11" t="n"/>
-      <c r="J173" s="11" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B174" s="8" t="inlineStr">
-        <is>
-          <t>Clanrat Slave</t>
-        </is>
-      </c>
-      <c r="C174" s="9" t="inlineStr">
-        <is>
-          <t>Clanrat Slaves &gt; Clanrat Slaves</t>
-        </is>
-      </c>
-      <c r="D174" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E174" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F174" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G174" s="9" t="inlineStr">
-        <is>
-          <t>wiki: M 6-&gt;5, I 5-&gt;4</t>
-        </is>
-      </c>
-      <c r="H174" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/clanrat-slave</t>
-        </is>
-      </c>
-      <c r="I174" s="11" t="n"/>
-      <c r="J174" s="11" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B175" s="8" t="inlineStr">
-        <is>
-          <t>Festering Chantor</t>
-        </is>
-      </c>
-      <c r="C175" s="9" t="inlineStr">
-        <is>
-          <t>Festering Chantor</t>
-        </is>
-      </c>
-      <c r="D175" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E175" s="9" t="inlineStr">
-        <is>
-          <t>7 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F175" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G175" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
-        </is>
-      </c>
-      <c r="H175" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/festering-chantor</t>
-        </is>
-      </c>
-      <c r="I175" s="11" t="n"/>
-      <c r="J175" s="11" t="n"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B176" s="8" t="inlineStr">
-        <is>
-          <t>Plague Lord</t>
-        </is>
-      </c>
-      <c r="C176" s="9" t="inlineStr">
-        <is>
-          <t>Plague Lord</t>
-        </is>
-      </c>
-      <c r="D176" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E176" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F176" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G176" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 5-&gt;4</t>
-        </is>
-      </c>
-      <c r="H176" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/plague-lord</t>
-        </is>
-      </c>
-      <c r="I176" s="11" t="n"/>
-      <c r="J176" s="11" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B177" s="8" t="inlineStr">
-        <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="C177" s="9" t="inlineStr">
-        <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="D177" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E177" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F177" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G177" s="9" t="inlineStr">
-        <is>
-          <t>wiki: I 6-&gt;4</t>
-        </is>
-      </c>
-      <c r="H177" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
-        </is>
-      </c>
-      <c r="I177" s="11" t="n"/>
-      <c r="J177" s="11" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B178" s="8" t="inlineStr">
-        <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="C178" s="9" t="inlineStr">
-        <is>
-          <t>Warlock Master</t>
-        </is>
-      </c>
-      <c r="D178" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E178" s="9" t="inlineStr">
-        <is>
-          <t>6 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F178" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G178" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 4-&gt;3, T 4-&gt;3, W 3-&gt;2, I 5-&gt;4, A 2-&gt;1, Ld 7-&gt;5</t>
-        </is>
-      </c>
-      <c r="H178" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
-        </is>
-      </c>
-      <c r="I178" s="11" t="n"/>
-      <c r="J178" s="11" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B179" s="8" t="inlineStr">
-        <is>
-          <t>Skeleton</t>
-        </is>
-      </c>
-      <c r="C179" s="9" t="inlineStr">
-        <is>
-          <t>Skeleton Light Horsemen &gt; Skeleton Horseman</t>
-        </is>
-      </c>
-      <c r="D179" s="8" t="inlineStr">
-        <is>
-          <t>Tomb Kings.cat</t>
-        </is>
-      </c>
-      <c r="E179" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F179" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G179" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 5-&gt;3</t>
-        </is>
-      </c>
-      <c r="H179" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/skeleton</t>
-        </is>
-      </c>
-      <c r="I179" s="11" t="n"/>
-      <c r="J179" s="11" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B180" s="8" t="inlineStr">
-        <is>
-          <t>Skeleton</t>
-        </is>
-      </c>
-      <c r="C180" s="9" t="inlineStr">
-        <is>
-          <t>Skeleton Heavy Horsemen &gt; Skeleton Horseman</t>
-        </is>
-      </c>
-      <c r="D180" s="8" t="inlineStr">
-        <is>
-          <t>Tomb Kings.cat</t>
-        </is>
-      </c>
-      <c r="E180" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F180" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G180" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 5-&gt;3</t>
-        </is>
-      </c>
-      <c r="H180" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/skeleton</t>
-        </is>
-      </c>
-      <c r="I180" s="11" t="n"/>
-      <c r="J180" s="11" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B181" s="8" t="inlineStr">
-        <is>
-          <t>Skeleton Crew</t>
-        </is>
-      </c>
-      <c r="C181" s="9" t="inlineStr">
-        <is>
-          <t>Chariots &gt; Chariot</t>
-        </is>
-      </c>
-      <c r="D181" s="8" t="inlineStr">
-        <is>
-          <t>Tomb Kings.cat</t>
-        </is>
-      </c>
-      <c r="E181" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F181" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G181" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;2, Ld 7-&gt;3</t>
-        </is>
-      </c>
-      <c r="H181" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/skeleton-crew</t>
-        </is>
-      </c>
-      <c r="I181" s="11" t="n"/>
-      <c r="J181" s="11" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:J181"/>
+  <autoFilter ref="A2:J170"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4:I181" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Option A,Option B,Leave as is,Rename catalogue,Needs more thought"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8663,52 +8190,52 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId66"/>
@@ -8719,97 +8246,87 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId154"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/judgement-calls.xlsx
+++ b/docs/judgement-calls.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Decisions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B29" s="4">
-        <f>COUNTBLANK(Decisions!$I$4:$I$170)</f>
+        <f>COUNTBLANK(Decisions!$I$4:$I$98)</f>
         <v/>
       </c>
     </row>
@@ -704,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J170"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1182,17 +1182,17 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Diabolic Splendour</t>
+          <t>Ironfist</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Daemonic Gifts &gt; Diabolic Splendour</t>
+          <t>shared; used by Bruiser, Ogre Bulls, Rhinox Cavalry, Tyrant</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/diabolical-splendour (0.66)</t>
+          <t>/unit/garagrim-ironfist (0.80)</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/diabolical-splendour</t>
+          <t>https://6th.whfb.app/unit/garagrim-ironfist</t>
         </is>
       </c>
       <c r="I11" s="11" t="n"/>
@@ -1226,17 +1226,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Staff of Darkoath</t>
+          <t>Ironfists (Rhinox Riders)</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Arcane Items &gt; Staff of Darkoath</t>
+          <t>Rhinox Cavalry &gt; Ironfists</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/staff-of-darkoth (0.68)</t>
+          <t>/unit/rhinox (0.80)</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/staff-of-darkoth</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Vitriolic Totem</t>
+          <t>Mawseeker</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Magic Banners &gt; Vitriolic Totem</t>
+          <t>Big Names &gt; Mawseeker</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Forces of Chaos.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1295,14 +1295,10 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/vitrolic-totem (0.68)</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/vitrolic-totem</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr"/>
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="11" t="n"/>
     </row>
@@ -1314,12 +1310,12 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Ironfist</t>
+          <t>Rhinox Cavalry</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Bruiser, Ogre Bulls, Rhinox Cavalry, Tyrant</t>
+          <t>Rhinox Cavalry</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1339,12 +1335,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>/unit/garagrim-ironfist (0.80)</t>
+          <t>/unit/rhinox (0.90)</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/garagrim-ironfist</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I14" s="11" t="n"/>
@@ -1358,12 +1354,12 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Ironfists (Rhinox Riders)</t>
+          <t>Scrap Launcher</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry &gt; Ironfists</t>
+          <t>Gnoblar Scraplauncher</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1383,12 +1379,12 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>/unit/rhinox (0.80)</t>
+          <t>/unit/scraplauncher (0.67)</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
+          <t>https://6th.whfb.app/unit/scraplauncher</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -1402,12 +1398,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Mawseeker</t>
+          <t>Skrag the Slaughterer</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Big Names &gt; Mawseeker</t>
+          <t>Scrag the Slaughterer</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1427,10 +1423,14 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
+          <t>/unit/skrag-the-slaughterer (1.00)</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/skrag-the-slaughterer</t>
+        </is>
+      </c>
       <c r="I16" s="11" t="n"/>
       <c r="J16" s="11" t="n"/>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Move Over Obstacles</t>
+          <t>Slavegiant Attacks</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/move-giants (0.90)</t>
+          <t>/unit/slavegiant (0.90)</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/move-giants</t>
+          <t>https://6th.whfb.app/unit/slavegiant</t>
         </is>
       </c>
       <c r="I17" s="11" t="n"/>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry</t>
+          <t>Stump-Blades</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry</t>
+          <t>Scrag the Slaughterer</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1511,14 +1511,10 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>/unit/rhinox (0.90)</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr"/>
       <c r="I18" s="11" t="n"/>
       <c r="J18" s="11" t="n"/>
     </row>
@@ -1530,12 +1526,12 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Scrap Launcher</t>
+          <t>Thunderous Charge</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Gnoblar Scraplauncher</t>
+          <t>Rhinox Cavalry</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1555,12 +1551,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>/unit/scraplauncher (0.67)</t>
+          <t>/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish (0.80)</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/scraplauncher</t>
+          <t>https://6th.whfb.app/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish</t>
         </is>
       </c>
       <c r="I19" s="11" t="n"/>
@@ -1574,12 +1570,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Skrag the Slaughterer</t>
+          <t>Wallcrusher</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Scrag the Slaughterer</t>
+          <t>Big Names &gt; Wallcrusher</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1599,12 +1595,12 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>/unit/skrag-the-slaughterer (1.00)</t>
+          <t>/unit/crusher (0.80)</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/skrag-the-slaughterer</t>
+          <t>https://6th.whfb.app/unit/crusher</t>
         </is>
       </c>
       <c r="I20" s="11" t="n"/>
@@ -1618,17 +1614,17 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Slavegiant Attacks</t>
+          <t>'Eadbuttin' 'At</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Slavegiant</t>
+          <t>Enchanted Items &gt; 'Eadbuttin' 'At</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1643,12 +1639,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>/unit/slavegiant (0.90)</t>
+          <t>/special-rules/eadbutt (0.90)</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/slavegiant</t>
+          <t>https://6th.whfb.app/special-rules/eadbutt</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -1662,17 +1658,17 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Stump-Blades</t>
+          <t>Fungus Buster Brew</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Scrag the Slaughterer</t>
+          <t>Shiny Stuff &gt; Fungus Buster Brew</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1702,17 +1698,17 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>The Scepter of the Titans</t>
+          <t>Giant</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Greasus Goldtooth &gt; The Scepter of the Titans</t>
+          <t>Giant</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -1727,12 +1723,12 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/sceptre-of-the-titans (0.61)</t>
+          <t>/unit/giant (1.00)</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/sceptre-of-the-titans</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I23" s="11" t="n"/>
@@ -1746,17 +1742,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Thunderous Charge</t>
+          <t>Giant Spiders</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Rhinox Cavalry</t>
+          <t>Goblin Spider Riders</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -1771,12 +1767,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish (0.80)</t>
+          <t>/unit/giant (0.90)</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/appendix-three-warhammer-skirmish/charge-appendix-three-warhammer-skirmish</t>
+          <t>https://6th.whfb.app/unit/giant</t>
         </is>
       </c>
       <c r="I24" s="11" t="n"/>
@@ -1790,17 +1786,17 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Wallcrusher</t>
+          <t>Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Big Names &gt; Wallcrusher</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -1815,12 +1811,12 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>/unit/crusher (0.80)</t>
+          <t>/unit/squig (0.80)</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/crusher</t>
+          <t>https://6th.whfb.app/unit/squig</t>
         </is>
       </c>
       <c r="I25" s="11" t="n"/>
@@ -1834,17 +1830,17 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Yheetee Ice Weapons</t>
+          <t>Gobbla's Movement</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Yheetees &gt; Yheetee Ice Weapons</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Ogre Kingdoms.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1859,12 +1855,12 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>/weapons/ice-weapons (0.80)</t>
+          <t>/special-rules/move-giants (0.80)</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/ice-weapons</t>
+          <t>https://6th.whfb.app/special-rules/move-giants</t>
         </is>
       </c>
       <c r="I26" s="11" t="n"/>
@@ -1878,12 +1874,12 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>'Eadbuttin' 'At</t>
+          <t>Hate Dwarfs</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Enchanted Items &gt; 'Eadbuttin' 'At</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -1903,12 +1899,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/eadbutt (0.90)</t>
+          <t>/unit/dwarf (0.80)</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/eadbutt</t>
+          <t>https://6th.whfb.app/unit/dwarf</t>
         </is>
       </c>
       <c r="I27" s="11" t="n"/>
@@ -1922,12 +1918,12 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Fungus Buster Brew</t>
+          <t>Insatiable Appetite</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Shiny Stuff &gt; Fungus Buster Brew</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1962,12 +1958,12 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Giant</t>
+          <t>Moving Fanatics into Obstacles</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Giant</t>
+          <t>Night Goblins &gt; Fanatics</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -1987,12 +1983,12 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (1.00)</t>
+          <t>/skirmishers/moving (0.90)</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/giant</t>
+          <t>https://6th.whfb.app/skirmishers/moving</t>
         </is>
       </c>
       <c r="I29" s="11" t="n"/>
@@ -2006,12 +2002,12 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Giant Spiders</t>
+          <t>Porko's Pigstikka</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Goblin Spider Riders</t>
+          <t>Magic Weapons &gt; Porko's Pigstikka</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -2031,12 +2027,12 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (0.90)</t>
+          <t>/magic-item/porks-pigstikka (0.68)</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/giant</t>
+          <t>https://6th.whfb.app/magic-item/porks-pigstikka</t>
         </is>
       </c>
       <c r="I30" s="11" t="n"/>
@@ -2050,12 +2046,12 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Giants Movement</t>
+          <t>Shooting at Skarsnik &amp; Gobbla</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -2075,12 +2071,12 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>/unit/giant (0.90)</t>
+          <t>/faq/shooting (0.90)</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/giant</t>
+          <t>https://6th.whfb.app/faq/shooting</t>
         </is>
       </c>
       <c r="I31" s="11" t="n"/>
@@ -2094,12 +2090,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Gobbla the Cave Squig</t>
+          <t>Skarsnik's Prodder</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -2119,14 +2115,10 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>/unit/squig (0.80)</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/squig</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr"/>
       <c r="I32" s="11" t="n"/>
       <c r="J32" s="11" t="n"/>
     </row>
@@ -2138,12 +2130,12 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Gobbla's Movement</t>
+          <t>Skarsnik's Prodder</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -2163,14 +2155,10 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/move-giants (0.80)</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/special-rules/move-giants</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr"/>
       <c r="I33" s="11" t="n"/>
       <c r="J33" s="11" t="n"/>
     </row>
@@ -2182,12 +2170,12 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Hate Dwarfs</t>
+          <t>Staff of Badumm</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Arcane Items &gt; Unique Items &gt; Staff of Badumm</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -2207,12 +2195,12 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>/unit/dwarf (0.80)</t>
+          <t>/magic-item/staff-of-baduumm (0.68)</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/dwarf</t>
+          <t>https://6th.whfb.app/magic-item/staff-of-baduumm</t>
         </is>
       </c>
       <c r="I34" s="11" t="n"/>
@@ -2226,12 +2214,12 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Insatiable Appetite</t>
+          <t>The Blasted Banner</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+          <t>Grimgor Ironhide &gt; Bodyguard &gt; Da Immortulz &gt; The Blasted Banner</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -2251,10 +2239,14 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr"/>
+          <t>/magic-item/the-beast-banner (0.62)</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/magic-item/the-beast-banner</t>
+        </is>
+      </c>
       <c r="I35" s="11" t="n"/>
       <c r="J35" s="11" t="n"/>
     </row>
@@ -2266,12 +2258,12 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Moving Fanatics into Obstacles</t>
+          <t>Warboss Umm's Best Big Boss 'At</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Night Goblins &gt; Fanatics</t>
+          <t>Talismans &gt; Warboss Umm's Best Big Boss 'At</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2291,12 +2283,12 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>/skirmishers/moving (0.90)</t>
+          <t>/magic-item/warboss-umms-best-big-bosss-at (0.69)</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/skirmishers/moving</t>
+          <t>https://6th.whfb.app/magic-item/warboss-umms-best-big-bosss-at</t>
         </is>
       </c>
       <c r="I36" s="11" t="n"/>
@@ -2310,17 +2302,17 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Porko's Pigstikka</t>
+          <t>Beastmaster</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Magic Weapons &gt; Porko's Pigstikka</t>
+          <t>Master Moulder</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2335,12 +2327,12 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/porks-pigstikka (0.68)</t>
+          <t>/unit/beastmaster (1.00)</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/porks-pigstikka</t>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
         </is>
       </c>
       <c r="I37" s="11" t="n"/>
@@ -2354,17 +2346,17 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Shooting at Skarsnik &amp; Gobbla</t>
+          <t>Beastmaster</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Gobbla the Cave Squig</t>
+          <t>Master Mutator</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2379,12 +2371,12 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>/faq/shooting (0.90)</t>
+          <t>/unit/beastmaster (1.00)</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/shooting</t>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
         </is>
       </c>
       <c r="I38" s="11" t="n"/>
@@ -2398,17 +2390,17 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Skarsnik's Prodder</t>
+          <t>Beastmaster</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
+          <t>Harbinger of Mutation</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -2423,10 +2415,14 @@
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr"/>
+          <t>/unit/beastmaster (1.00)</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/beastmaster</t>
+        </is>
+      </c>
       <c r="I39" s="11" t="n"/>
       <c r="J39" s="11" t="n"/>
     </row>
@@ -2438,17 +2434,17 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Skarsnik's Prodder</t>
+          <t>Boneripper</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Skarsnik, Warlord of Karak Eight Peaks &gt; Skarsnik's Prodder</t>
+          <t>Grey Seer Thanquol &amp; Boneripper</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -2463,10 +2459,14 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H40" s="10" t="inlineStr"/>
+          <t>/unit/boneripper (1.00)</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/boneripper</t>
+        </is>
+      </c>
       <c r="I40" s="11" t="n"/>
       <c r="J40" s="11" t="n"/>
     </row>
@@ -2478,17 +2478,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Staff of Badumm</t>
+          <t>Cursed Blade of Delerium</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Arcane Items &gt; Unique Items &gt; Staff of Badumm</t>
+          <t>Magic Weapons &gt; Cursed Blade of Delerium</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/staff-of-baduumm (0.68)</t>
+          <t>/magic-item/cursed-blade-of-delirium (0.67)</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/staff-of-baduumm</t>
+          <t>https://6th.whfb.app/magic-item/cursed-blade-of-delirium</t>
         </is>
       </c>
       <c r="I41" s="11" t="n"/>
@@ -2522,17 +2522,17 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>The Blasted Banner</t>
+          <t>Daemonic Instability</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Grimgor Ironhide &gt; Bodyguard &gt; Da Immortulz &gt; The Blasted Banner</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/the-beast-banner (0.62)</t>
+          <t>/special-rules/daemonic (0.90)</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/the-beast-banner</t>
+          <t>https://6th.whfb.app/special-rules/daemonic</t>
         </is>
       </c>
       <c r="I42" s="11" t="n"/>
@@ -2566,17 +2566,17 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Warboss Umm's Best Big Boss 'At</t>
+          <t>Doom Glaive</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Talismans &gt; Warboss Umm's Best Big Boss 'At</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Orcs and Goblins.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -2591,14 +2591,10 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/warboss-umms-best-big-bosss-at (0.69)</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/warboss-umms-best-big-bosss-at</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr"/>
       <c r="I43" s="11" t="n"/>
       <c r="J43" s="11" t="n"/>
     </row>
@@ -2610,12 +2606,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
+          <t>Doomwheel</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Master Moulder</t>
+          <t>Doomwheel</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -2635,12 +2631,12 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
+          <t>/movement/wheel (0.80)</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
+          <t>https://6th.whfb.app/movement/wheel</t>
         </is>
       </c>
       <c r="I44" s="11" t="n"/>
@@ -2654,12 +2650,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Master Mutator</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -2679,12 +2675,12 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
+          <t>/unit/festering-chantor (1.00)</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
+          <t>https://6th.whfb.app/unit/festering-chantor</t>
         </is>
       </c>
       <c r="I45" s="11" t="n"/>
@@ -2698,7 +2694,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Beastmaster</t>
+          <t>Harbinger of Mutation</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
@@ -2723,12 +2719,12 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>/unit/beastmaster (1.00)</t>
+          <t>/unit/harbinger (0.90)</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/beastmaster</t>
+          <t>https://6th.whfb.app/unit/harbinger</t>
         </is>
       </c>
       <c r="I46" s="11" t="n"/>
@@ -2742,12 +2738,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Boneripper</t>
+          <t>High Ranking</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Grey Seer Thanquol &amp; Boneripper</t>
+          <t>Grey Seer</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -2767,14 +2763,10 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>/unit/boneripper (1.00)</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/boneripper</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr"/>
       <c r="I47" s="11" t="n"/>
       <c r="J47" s="11" t="n"/>
     </row>
@@ -2786,12 +2778,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Cursed Blade of Delerium</t>
+          <t>Horned Rat Incarnate</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Magic Weapons &gt; Cursed Blade of Delerium</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -2811,14 +2803,10 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/cursed-blade-of-delirium (0.67)</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/cursed-blade-of-delirium</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr"/>
       <c r="I48" s="11" t="n"/>
       <c r="J48" s="11" t="n"/>
     </row>
@@ -2830,12 +2818,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Daemonic Instability</t>
+          <t>Plague Rats</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Rat Swarm &gt; Plague Rats</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -2855,12 +2843,12 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/daemonic (0.90)</t>
+          <t>/spell/plague (0.90)</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/daemonic</t>
+          <t>https://6th.whfb.app/spell/plague</t>
         </is>
       </c>
       <c r="I49" s="11" t="n"/>
@@ -2874,12 +2862,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Doom Glaive</t>
+          <t>Ratling Gun Misfire</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Weapon Team &gt; Ratling Gun</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -2899,10 +2887,14 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H50" s="10" t="inlineStr"/>
+          <t>/weapons/ratling-gun (0.90)</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/weapons/ratling-gun</t>
+        </is>
+      </c>
       <c r="I50" s="11" t="n"/>
       <c r="J50" s="11" t="n"/>
     </row>
@@ -2914,12 +2906,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Doomwheel</t>
+          <t>Stands Alone</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Doomwheel</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -2939,14 +2931,10 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>/movement/wheel (0.80)</t>
-        </is>
-      </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/movement/wheel</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr"/>
       <c r="I51" s="11" t="n"/>
       <c r="J51" s="11" t="n"/>
     </row>
@@ -2958,12 +2946,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Festering Chantor</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Festering Chantor</t>
+          <t>Vermin Lord</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -2983,14 +2971,10 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>/unit/festering-chantor (1.00)</t>
-        </is>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/festering-chantor</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr"/>
       <c r="I52" s="11" t="n"/>
       <c r="J52" s="11" t="n"/>
     </row>
@@ -3002,12 +2986,12 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Harbinger of Mutation</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Harbinger of Mutation</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -3027,12 +3011,12 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>/unit/harbinger (0.90)</t>
+          <t>/unit/warlock-engineer (1.00)</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/harbinger</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I53" s="11" t="n"/>
@@ -3046,12 +3030,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>High Ranking</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Grey Seer</t>
+          <t>Warlock Master</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3071,10 +3055,14 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="inlineStr"/>
+          <t>/unit/warlock-engineer (1.00)</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+        </is>
+      </c>
       <c r="I54" s="11" t="n"/>
       <c r="J54" s="11" t="n"/>
     </row>
@@ -3086,12 +3074,12 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Horned Rat Incarnate</t>
+          <t>Warpfire Thrower Misfire</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Weapon Team &gt; Warpfire Thrower</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -3111,10 +3099,14 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H55" s="10" t="inlineStr"/>
+          <t>/weapons/warpfire-thrower (0.90)</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/weapons/warpfire-thrower</t>
+        </is>
+      </c>
       <c r="I55" s="11" t="n"/>
       <c r="J55" s="11" t="n"/>
     </row>
@@ -3126,17 +3118,17 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Plague Rats</t>
+          <t>Charging with the Steam Tank</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Rat Swarm &gt; Plague Rats</t>
+          <t>Steam Tank</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -3151,12 +3143,12 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>/spell/plague (0.90)</t>
+          <t>/movement/charging (0.90)</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/spell/plague</t>
+          <t>https://6th.whfb.app/movement/charging</t>
         </is>
       </c>
       <c r="I56" s="11" t="n"/>
@@ -3170,17 +3162,17 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Ratling Gun Misfire</t>
+          <t>Electoral Banner</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Weapon Team &gt; Ratling Gun</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -3195,14 +3187,10 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>/weapons/ratling-gun (0.90)</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/weapons/ratling-gun</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr"/>
       <c r="I57" s="11" t="n"/>
       <c r="J57" s="11" t="n"/>
     </row>
@@ -3214,17 +3202,17 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Stands Alone</t>
+          <t>Helm of the Skavenslayer</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Magic Armour &gt; Magic Armour &gt; Helm of the Skavenslayer</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -3239,10 +3227,14 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr"/>
+          <t>/army/skaven (0.80)</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/army/skaven</t>
+        </is>
+      </c>
       <c r="I58" s="11" t="n"/>
       <c r="J58" s="11" t="n"/>
     </row>
@@ -3254,17 +3246,17 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>Parent and Detachment Units</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Vermin Lord</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -3279,10 +3271,14 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="inlineStr"/>
+          <t>/warhammer-glossary/unit-warhammer-glossary (0.80)</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/warhammer-glossary/unit-warhammer-glossary</t>
+        </is>
+      </c>
       <c r="I59" s="11" t="n"/>
       <c r="J59" s="11" t="n"/>
     </row>
@@ -3294,17 +3290,17 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
+          <t>Shooting at the Steam Tank</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
+          <t>Steam Tank</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -3319,12 +3315,12 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>/unit/warlock-engineer (1.00)</t>
+          <t>/faq/shooting (0.90)</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+          <t>https://6th.whfb.app/faq/shooting</t>
         </is>
       </c>
       <c r="I60" s="11" t="n"/>
@@ -3338,17 +3334,17 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
+          <t>Shooting with the Steam Tank</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Warlock Master</t>
+          <t>Steam Tank</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -3363,12 +3359,12 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>/unit/warlock-engineer (1.00)</t>
+          <t>/faq/shooting (0.90)</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+          <t>https://6th.whfb.app/faq/shooting</t>
         </is>
       </c>
       <c r="I61" s="11" t="n"/>
@@ -3382,17 +3378,17 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Warpfire Thrower Misfire</t>
+          <t>Steam Points</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Weapon Team &gt; Warpfire Thrower</t>
+          <t>Steam Tank</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Skaven.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -3407,12 +3403,12 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>/weapons/warpfire-thrower (0.90)</t>
+          <t>/special-rules/building-up-steam-points (0.80)</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/weapons/warpfire-thrower</t>
+          <t>https://6th.whfb.app/special-rules/building-up-steam-points</t>
         </is>
       </c>
       <c r="I62" s="11" t="n"/>
@@ -3426,17 +3422,17 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Athandin</t>
+          <t>Armour of Eternity</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Valten, Exalted of Sigmar &gt; Athandin</t>
+          <t>Magic Armour &gt; Magic Armour</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Tomb Kings.cat</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -3451,12 +3447,12 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/althandin (0.66)</t>
+          <t>/appendix-eight-sequence-of-play/4-shooting-p58 (0.90)</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/althandin</t>
+          <t>https://6th.whfb.app/appendix-eight-sequence-of-play/4-shooting-p58</t>
         </is>
       </c>
       <c r="I63" s="11" t="n"/>
@@ -3470,17 +3466,17 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Charging with the Steam Tank</t>
+          <t>Ethereal Steeds</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Steam Tank</t>
+          <t>shared; used by Black Knights</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Vampire Counts.cat</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3495,12 +3491,12 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>/movement/charging (0.90)</t>
+          <t>/special-rules/ethereal (0.90)</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/movement/charging</t>
+          <t>https://6th.whfb.app/special-rules/ethereal</t>
         </is>
       </c>
       <c r="I64" s="11" t="n"/>
@@ -3514,7 +3510,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Electoral Banner</t>
+          <t>Fly</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -3524,7 +3520,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -3539,10 +3535,14 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H65" s="10" t="inlineStr"/>
+          <t>/faq/flyers (0.90)</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/faq/flyers</t>
+        </is>
+      </c>
       <c r="I65" s="11" t="n"/>
       <c r="J65" s="11" t="n"/>
     </row>
@@ -3554,17 +3554,17 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Fusilade</t>
+          <t>Stone Thrower</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Pistoliers</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/fusillade (0.66)</t>
+          <t>/unit/stone-thrower (1.00)</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/fusillade</t>
+          <t>https://6th.whfb.app/unit/stone-thrower</t>
         </is>
       </c>
       <c r="I66" s="11" t="n"/>
@@ -3598,17 +3598,17 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Helm of the Skavenslayer</t>
+          <t>Alter Kindred</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Magic Armour &gt; Magic Armour &gt; Helm of the Skavenslayer</t>
+          <t>Wood Elf Kindred &gt; Alter Kindred</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>/army/skaven (0.80)</t>
+          <t>/magic-item/the-alter-kindreds (0.80)</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/army/skaven</t>
+          <t>https://6th.whfb.app/magic-item/the-alter-kindreds</t>
         </is>
       </c>
       <c r="I67" s="11" t="n"/>
@@ -3642,17 +3642,17 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Parent and Detachment Units</t>
+          <t>Strangle-Roots</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>shared; used by Treeman, Treeman Ancient</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -3667,56 +3667,52 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>/warhammer-glossary/unit-warhammer-glossary (0.80)</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/warhammer-glossary/unit-warhammer-glossary</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr"/>
       <c r="I68" s="11" t="n"/>
       <c r="J68" s="11" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Shooting at the Steam Tank</t>
+          <t>Virtue of Stoicism</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Steam Tank</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 80</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>/faq/shooting (0.90)</t>
+          <t>wiki: 35</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/shooting</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
         </is>
       </c>
       <c r="I69" s="11" t="n"/>
@@ -3725,42 +3721,42 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Shooting with the Steam Tank</t>
+          <t>Virtue of Stoicism</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Steam Tank</t>
+          <t>Chivalric Virtues</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 40</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>/faq/shooting (0.90)</t>
+          <t>wiki: 35</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/shooting</t>
+          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
         </is>
       </c>
       <c r="I70" s="11" t="n"/>
@@ -3769,17 +3765,17 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Steam Points</t>
+          <t>Ghal Maraz</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Steam Tank</t>
+          <t>Emperor Karl Franz &gt; Weapon</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -3789,22 +3785,22 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 180</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/building-up-steam-points (0.80)</t>
+          <t>wiki: 0</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/building-up-steam-points</t>
+          <t>https://6th.whfb.app/magic-item/ghal-maraz</t>
         </is>
       </c>
       <c r="I71" s="11" t="n"/>
@@ -3813,42 +3809,42 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Armour of Eternity</t>
+          <t>Villein</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Magic Armour &gt; Magic Armour</t>
+          <t>Peasant Bowmen &gt; Command &gt; Villein</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Tomb Kings.cat</t>
+          <t>Bretonnians.cat</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>/appendix-eight-sequence-of-play/4-shooting-p58 (0.90)</t>
+          <t>wiki: WS 3-&gt;2, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/appendix-eight-sequence-of-play/4-shooting-p58</t>
+          <t>https://6th.whfb.app/unit/villein</t>
         </is>
       </c>
       <c r="I72" s="11" t="n"/>
@@ -3857,42 +3853,42 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Ethereal Steeds</t>
+          <t>Bull Centaur Hero</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Black Knights</t>
+          <t>Bull Centaur Hero</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Vampire Counts.cat</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/ethereal (0.90)</t>
+          <t>wiki: T 4-&gt;5</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/ethereal</t>
+          <t>https://6th.whfb.app/unit/bull-centaur-hero</t>
         </is>
       </c>
       <c r="I73" s="11" t="n"/>
@@ -3901,42 +3897,42 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Fly</t>
+          <t>Chaos Dwarf Sorcerer</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Sorcerer Lord</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>/faq/flyers (0.90)</t>
+          <t>wiki: S 4-&gt;3, T 5-&gt;4, W 3-&gt;2, I 1-&gt;2, Ld 10-&gt;9</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/flyers</t>
+          <t>https://6th.whfb.app/unit/chaos-dwarf-sorcerer</t>
         </is>
       </c>
       <c r="I74" s="11" t="n"/>
@@ -3945,42 +3941,42 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Stone Thrower</t>
+          <t>Hobgoblin Crew</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Hobgoblin Bolt Thrower &gt; Hobgoblin Bolt Thrower</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Chaos Dwarves.cat</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>/unit/stone-thrower (1.00)</t>
+          <t>wiki: M 3-&gt;4</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/stone-thrower</t>
+          <t>https://6th.whfb.app/unit/hobgoblin-crew</t>
         </is>
       </c>
       <c r="I75" s="11" t="n"/>
@@ -3989,42 +3985,42 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Alter Kindred</t>
+          <t>Hag</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Wood Elf Kindred &gt; Alter Kindred</t>
+          <t>Cauldron of Blood</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Dark Elves.cat</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/the-alter-kindreds (0.80)</t>
+          <t>wiki: WS 4-&gt;5</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/the-alter-kindreds</t>
+          <t>https://6th.whfb.app/unit/hag</t>
         </is>
       </c>
       <c r="I76" s="11" t="n"/>
@@ -4033,42 +4029,42 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Gwytherc's Horn</t>
+          <t>Daddallo</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Enchanted Items &gt; Gwytherc's Horn</t>
+          <t>Birdmen of Catrazza &gt; Daddallo</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/gwytheres-horn (0.65)</t>
+          <t>wiki: A 2-&gt;1</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/gwytheres-horn</t>
+          <t>https://6th.whfb.app/unit/daddallo</t>
         </is>
       </c>
       <c r="I77" s="11" t="n"/>
@@ -4077,42 +4073,42 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Stone of the Crystal Mere</t>
+          <t>Warhorse</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Talismans &gt; Stone of the Crystal Mere</t>
+          <t>shared; used by Al Muktar's Desert Dogs, Bronzino's Galloper Guns</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Dogs of War.cat</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/stone-of-the-crystal-merex (0.90)</t>
+          <t>wiki: BS 3-&gt;0</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/stone-of-the-crystal-merex</t>
+          <t>https://6th.whfb.app/unit/warhorse</t>
         </is>
       </c>
       <c r="I78" s="11" t="n"/>
@@ -4121,82 +4117,86 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Strangle-Roots</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Treeman, Treeman Ancient</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>Dwarfs.cat</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr"/>
+          <t>wiki: A 2-&gt;1</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/engineer</t>
+        </is>
+      </c>
       <c r="I79" s="11" t="n"/>
       <c r="J79" s="11" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Audacity</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Keeper of Secrets</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>wiki: 30</t>
+          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
+          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
         </is>
       </c>
       <c r="I80" s="11" t="n"/>
@@ -4205,42 +4205,42 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Audacity</t>
+          <t>Steed of Slaanesh</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>wiki: 30</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-audacity</t>
+          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
         </is>
       </c>
       <c r="I81" s="11" t="n"/>
@@ -4249,42 +4249,42 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
+          <t>Tuskgor</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Gorthor the Beastlord</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: S 4-&gt;3</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/unit/tuskgor</t>
         </is>
       </c>
       <c r="I82" s="11" t="n"/>
@@ -4293,42 +4293,42 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
+          <t>Ungor</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Beast Herd &gt; Ungors</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: T 4-&gt;3</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/unit/ungor</t>
         </is>
       </c>
       <c r="I83" s="11" t="n"/>
@@ -4337,42 +4337,42 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Confidence</t>
+          <t>Ungor</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Tuskgor Chariot</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>wiki: 25</t>
+          <t>wiki: WS 4-&gt;3</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-confidence</t>
+          <t>https://6th.whfb.app/unit/ungor</t>
         </is>
       </c>
       <c r="I84" s="11" t="n"/>
@@ -4381,42 +4381,42 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Bladelord</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Phoenix Guard &gt; Command &gt; Keeper of the Flame</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>3 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: WS 5-&gt;6, I 6-&gt;5, Ld 9-&gt;8</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/unit/bladelord</t>
         </is>
       </c>
       <c r="I85" s="11" t="n"/>
@@ -4425,42 +4425,42 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Ellyrian Reaver</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Ellyrian Reavers &gt; Ellyrian Reavers</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 30</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: A 1-&gt;2</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/unit/ellyrian-reaver</t>
         </is>
       </c>
       <c r="I86" s="11" t="n"/>
@@ -4469,42 +4469,42 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Harbinger</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Ellyrian Reavers &gt; Command &gt; Harbinger</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>High Elves.cat</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 45</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: A 1-&gt;2</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/unit/harbinger</t>
         </is>
       </c>
       <c r="I87" s="11" t="n"/>
@@ -4513,42 +4513,42 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Greyback</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Yheetees &gt; Greyback</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: A 4-&gt;3</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/unit/greyback</t>
         </is>
       </c>
       <c r="I88" s="11" t="n"/>
@@ -4557,42 +4557,42 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Discipline</t>
+          <t>Rhinox</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Rhinox Cavalry &gt; Rhinox Riders</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 75</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>wiki: 15</t>
+          <t>wiki: M 7-&gt;6</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-discipline</t>
+          <t>https://6th.whfb.app/unit/rhinox</t>
         </is>
       </c>
       <c r="I89" s="11" t="n"/>
@@ -4601,42 +4601,42 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Thunderfist</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Leadbelchers &gt; Command &gt; Thunderfist</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Ogre Kingdoms.cat</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 30</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: BS 2-&gt;3</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/unit/thunderfist</t>
         </is>
       </c>
       <c r="I90" s="11" t="n"/>
@@ -4645,42 +4645,42 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Boar Chariot</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Savage Orc Boar Chariot</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 20</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: S 5-&gt;3</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/unit/boar-chariot</t>
         </is>
       </c>
       <c r="I91" s="11" t="n"/>
@@ -4689,42 +4689,42 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Squig Hopper</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Night Goblin Squig Herd &gt; Unit &gt; Squig Hopper</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Orcs and Goblins.cat</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: W 2-&gt;1</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/unit/squig-hopper</t>
         </is>
       </c>
       <c r="I92" s="11" t="n"/>
@@ -4733,42 +4733,42 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Clanrat Slave</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Clanrat Slaves &gt; Clanrat Slaves</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 60</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: M 6-&gt;5, I 5-&gt;4</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/unit/clanrat-slave</t>
         </is>
       </c>
       <c r="I93" s="11" t="n"/>
@@ -4777,42 +4777,42 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>7 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 50</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/unit/festering-chantor</t>
         </is>
       </c>
       <c r="I94" s="11" t="n"/>
@@ -4821,42 +4821,42 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Plague Lord</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Plague Lord</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 100</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: A 5-&gt;4</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/unit/plague-lord</t>
         </is>
       </c>
       <c r="I95" s="11" t="n"/>
@@ -4865,42 +4865,42 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 70</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: I 6-&gt;4</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I96" s="11" t="n"/>
@@ -4909,42 +4909,42 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Warlock Engineer</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Warlock Master</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>6 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: WS 4-&gt;3, T 4-&gt;3, W 3-&gt;2, I 5-&gt;4, A 2-&gt;1, Ld 7-&gt;5</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/unit/warlock-engineer</t>
         </is>
       </c>
       <c r="I97" s="11" t="n"/>
@@ -4953,3222 +4953,54 @@
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Empathy</t>
+          <t>Skeleton Crew</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Chariots &gt; Chariot</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Tomb Kings.cat</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>2 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 90</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>wiki: 10</t>
+          <t>wiki: WS 3-&gt;2, Ld 7-&gt;3</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-empathy</t>
+          <t>https://6th.whfb.app/unit/skeleton-crew</t>
         </is>
       </c>
       <c r="I98" s="11" t="n"/>
       <c r="J98" s="11" t="n"/>
     </row>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of Heroism</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 80</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 40</t>
-        </is>
-      </c>
-      <c r="H99" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-heroism</t>
-        </is>
-      </c>
-      <c r="I99" s="11" t="n"/>
-      <c r="J99" s="11" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of Knightly Temper</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 80</t>
-        </is>
-      </c>
-      <c r="G100" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 40</t>
-        </is>
-      </c>
-      <c r="H100" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-knightly-temper</t>
-        </is>
-      </c>
-      <c r="I100" s="11" t="n"/>
-      <c r="J100" s="11" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of Noble Disdain</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E101" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 40</t>
-        </is>
-      </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 20</t>
-        </is>
-      </c>
-      <c r="H101" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
-        </is>
-      </c>
-      <c r="I101" s="11" t="n"/>
-      <c r="J101" s="11" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of Noble Disdain</t>
-        </is>
-      </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 60</t>
-        </is>
-      </c>
-      <c r="G102" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 20</t>
-        </is>
-      </c>
-      <c r="H102" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
-        </is>
-      </c>
-      <c r="I102" s="11" t="n"/>
-      <c r="J102" s="11" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of Noble Disdain</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 80</t>
-        </is>
-      </c>
-      <c r="G103" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 20</t>
-        </is>
-      </c>
-      <c r="H103" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
-        </is>
-      </c>
-      <c r="I103" s="11" t="n"/>
-      <c r="J103" s="11" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of Noble Disdain</t>
-        </is>
-      </c>
-      <c r="C104" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F104" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 100</t>
-        </is>
-      </c>
-      <c r="G104" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 20</t>
-        </is>
-      </c>
-      <c r="H104" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-noble-disdain</t>
-        </is>
-      </c>
-      <c r="I104" s="11" t="n"/>
-      <c r="J104" s="11" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of Purity</t>
-        </is>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F105" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 40</t>
-        </is>
-      </c>
-      <c r="G105" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 20</t>
-        </is>
-      </c>
-      <c r="H105" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
-        </is>
-      </c>
-      <c r="I105" s="11" t="n"/>
-      <c r="J105" s="11" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of Purity</t>
-        </is>
-      </c>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E106" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F106" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 60</t>
-        </is>
-      </c>
-      <c r="G106" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 20</t>
-        </is>
-      </c>
-      <c r="H106" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
-        </is>
-      </c>
-      <c r="I106" s="11" t="n"/>
-      <c r="J106" s="11" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of Purity</t>
-        </is>
-      </c>
-      <c r="C107" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E107" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 100</t>
-        </is>
-      </c>
-      <c r="G107" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 20</t>
-        </is>
-      </c>
-      <c r="H107" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
-        </is>
-      </c>
-      <c r="I107" s="11" t="n"/>
-      <c r="J107" s="11" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of Purity</t>
-        </is>
-      </c>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F108" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 80</t>
-        </is>
-      </c>
-      <c r="G108" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 20</t>
-        </is>
-      </c>
-      <c r="H108" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-purity</t>
-        </is>
-      </c>
-      <c r="I108" s="11" t="n"/>
-      <c r="J108" s="11" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of Stoicism</t>
-        </is>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F109" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 80</t>
-        </is>
-      </c>
-      <c r="G109" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 35</t>
-        </is>
-      </c>
-      <c r="H109" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
-        </is>
-      </c>
-      <c r="I109" s="11" t="n"/>
-      <c r="J109" s="11" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of Stoicism</t>
-        </is>
-      </c>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 40</t>
-        </is>
-      </c>
-      <c r="G110" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 35</t>
-        </is>
-      </c>
-      <c r="H110" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
-        </is>
-      </c>
-      <c r="I110" s="11" t="n"/>
-      <c r="J110" s="11" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of the Ideal</t>
-        </is>
-      </c>
-      <c r="C111" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E111" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F111" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 70</t>
-        </is>
-      </c>
-      <c r="G111" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 35</t>
-        </is>
-      </c>
-      <c r="H111" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-ideal</t>
-        </is>
-      </c>
-      <c r="I111" s="11" t="n"/>
-      <c r="J111" s="11" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of the Impetuous Knight</t>
-        </is>
-      </c>
-      <c r="C112" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E112" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 70</t>
-        </is>
-      </c>
-      <c r="G112" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 35</t>
-        </is>
-      </c>
-      <c r="H112" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-impetuous-knight</t>
-        </is>
-      </c>
-      <c r="I112" s="11" t="n"/>
-      <c r="J112" s="11" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of the Joust</t>
-        </is>
-      </c>
-      <c r="C113" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E113" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 50</t>
-        </is>
-      </c>
-      <c r="G113" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 25</t>
-        </is>
-      </c>
-      <c r="H113" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
-        </is>
-      </c>
-      <c r="I113" s="11" t="n"/>
-      <c r="J113" s="11" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of the Joust</t>
-        </is>
-      </c>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E114" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F114" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 75</t>
-        </is>
-      </c>
-      <c r="G114" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 25</t>
-        </is>
-      </c>
-      <c r="H114" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
-        </is>
-      </c>
-      <c r="I114" s="11" t="n"/>
-      <c r="J114" s="11" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of the Joust</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F115" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 100</t>
-        </is>
-      </c>
-      <c r="G115" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 25</t>
-        </is>
-      </c>
-      <c r="H115" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-joust</t>
-        </is>
-      </c>
-      <c r="I115" s="11" t="n"/>
-      <c r="J115" s="11" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>Virtue of the Penitent</t>
-        </is>
-      </c>
-      <c r="C116" s="9" t="inlineStr">
-        <is>
-          <t>Chivalric Virtues</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E116" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F116" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 80</t>
-        </is>
-      </c>
-      <c r="G116" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 40</t>
-        </is>
-      </c>
-      <c r="H116" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-the-penitent</t>
-        </is>
-      </c>
-      <c r="I116" s="11" t="n"/>
-      <c r="J116" s="11" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>Power Stone</t>
-        </is>
-      </c>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>Arcane Items &gt; Unique Items</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="inlineStr">
-        <is>
-          <t>High Elves.cat</t>
-        </is>
-      </c>
-      <c r="E117" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F117" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 0</t>
-        </is>
-      </c>
-      <c r="G117" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 25</t>
-        </is>
-      </c>
-      <c r="H117" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/power-stone</t>
-        </is>
-      </c>
-      <c r="I117" s="11" t="n"/>
-      <c r="J117" s="11" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B118" s="8" t="inlineStr">
-        <is>
-          <t>Pure of Heart</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>Honours</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="inlineStr">
-        <is>
-          <t>High Elves.cat</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 0</t>
-        </is>
-      </c>
-      <c r="G118" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 500</t>
-        </is>
-      </c>
-      <c r="H118" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/pure-of-heart</t>
-        </is>
-      </c>
-      <c r="I118" s="11" t="n"/>
-      <c r="J118" s="11" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B119" s="8" t="inlineStr">
-        <is>
-          <t>Ghal Maraz</t>
-        </is>
-      </c>
-      <c r="C119" s="9" t="inlineStr">
-        <is>
-          <t>Emperor Karl Franz &gt; Weapon</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="inlineStr">
-        <is>
-          <t>The Empire.cat</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 180</t>
-        </is>
-      </c>
-      <c r="G119" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 0</t>
-        </is>
-      </c>
-      <c r="H119" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/ghal-maraz</t>
-        </is>
-      </c>
-      <c r="I119" s="11" t="n"/>
-      <c r="J119" s="11" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>Horn of the Wild Hunt</t>
-        </is>
-      </c>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>Orion, the King in the Woods</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="inlineStr">
-        <is>
-          <t>Wood Elves.cat</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 0</t>
-        </is>
-      </c>
-      <c r="G120" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 10</t>
-        </is>
-      </c>
-      <c r="H120" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/horn-of-the-wild-hunt</t>
-        </is>
-      </c>
-      <c r="I120" s="11" t="n"/>
-      <c r="J120" s="11" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B121" s="8" t="inlineStr">
-        <is>
-          <t>Pegasus</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>Pegasus Knights &gt; Pegasus Knight</t>
-        </is>
-      </c>
-      <c r="D121" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 7-&gt;6</t>
-        </is>
-      </c>
-      <c r="H121" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/pegasus</t>
-        </is>
-      </c>
-      <c r="I121" s="11" t="n"/>
-      <c r="J121" s="11" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B122" s="8" t="inlineStr">
-        <is>
-          <t>Villein</t>
-        </is>
-      </c>
-      <c r="C122" s="9" t="inlineStr">
-        <is>
-          <t>Peasant Bowmen &gt; Command &gt; Villein</t>
-        </is>
-      </c>
-      <c r="D122" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E122" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F122" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G122" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;2, A 1-&gt;2</t>
-        </is>
-      </c>
-      <c r="H122" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/villein</t>
-        </is>
-      </c>
-      <c r="I122" s="11" t="n"/>
-      <c r="J122" s="11" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B123" s="8" t="inlineStr">
-        <is>
-          <t>Bull Centaur Hero</t>
-        </is>
-      </c>
-      <c r="C123" s="9" t="inlineStr">
-        <is>
-          <t>Bull Centaur Hero</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="inlineStr">
-        <is>
-          <t>Chaos Dwarves.cat</t>
-        </is>
-      </c>
-      <c r="E123" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F123" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G123" s="9" t="inlineStr">
-        <is>
-          <t>wiki: T 4-&gt;5</t>
-        </is>
-      </c>
-      <c r="H123" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/bull-centaur-hero</t>
-        </is>
-      </c>
-      <c r="I123" s="11" t="n"/>
-      <c r="J123" s="11" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>Chaos Dwarf Sorcerer</t>
-        </is>
-      </c>
-      <c r="C124" s="9" t="inlineStr">
-        <is>
-          <t>Sorcerer Lord</t>
-        </is>
-      </c>
-      <c r="D124" s="8" t="inlineStr">
-        <is>
-          <t>Chaos Dwarves.cat</t>
-        </is>
-      </c>
-      <c r="E124" s="9" t="inlineStr">
-        <is>
-          <t>5 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F124" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G124" s="9" t="inlineStr">
-        <is>
-          <t>wiki: S 4-&gt;3, T 5-&gt;4, W 3-&gt;2, I 1-&gt;2, Ld 10-&gt;9</t>
-        </is>
-      </c>
-      <c r="H124" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/chaos-dwarf-sorcerer</t>
-        </is>
-      </c>
-      <c r="I124" s="11" t="n"/>
-      <c r="J124" s="11" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B125" s="8" t="inlineStr">
-        <is>
-          <t>Hobgoblin Crew</t>
-        </is>
-      </c>
-      <c r="C125" s="9" t="inlineStr">
-        <is>
-          <t>Hobgoblin Bolt Thrower &gt; Hobgoblin Bolt Thrower</t>
-        </is>
-      </c>
-      <c r="D125" s="8" t="inlineStr">
-        <is>
-          <t>Chaos Dwarves.cat</t>
-        </is>
-      </c>
-      <c r="E125" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F125" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G125" s="9" t="inlineStr">
-        <is>
-          <t>wiki: M 3-&gt;4</t>
-        </is>
-      </c>
-      <c r="H125" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/hobgoblin-crew</t>
-        </is>
-      </c>
-      <c r="I125" s="11" t="n"/>
-      <c r="J125" s="11" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B126" s="8" t="inlineStr">
-        <is>
-          <t>Bloodletter</t>
-        </is>
-      </c>
-      <c r="C126" s="9" t="inlineStr">
-        <is>
-          <t>Bloodletters &gt; Bloodletters</t>
-        </is>
-      </c>
-      <c r="D126" s="8" t="inlineStr">
-        <is>
-          <t>Daemonic Legions.cat</t>
-        </is>
-      </c>
-      <c r="E126" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F126" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G126" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 9-&gt;8</t>
-        </is>
-      </c>
-      <c r="H126" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/bloodletter</t>
-        </is>
-      </c>
-      <c r="I126" s="11" t="n"/>
-      <c r="J126" s="11" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B127" s="8" t="inlineStr">
-        <is>
-          <t>Daemonette</t>
-        </is>
-      </c>
-      <c r="C127" s="9" t="inlineStr">
-        <is>
-          <t>Daemonettes &gt; Daemonettes</t>
-        </is>
-      </c>
-      <c r="D127" s="8" t="inlineStr">
-        <is>
-          <t>Daemonic Legions.cat</t>
-        </is>
-      </c>
-      <c r="E127" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F127" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G127" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 9-&gt;8</t>
-        </is>
-      </c>
-      <c r="H127" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/daemonette</t>
-        </is>
-      </c>
-      <c r="I127" s="11" t="n"/>
-      <c r="J127" s="11" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B128" s="8" t="inlineStr">
-        <is>
-          <t>Daemonette</t>
-        </is>
-      </c>
-      <c r="C128" s="9" t="inlineStr">
-        <is>
-          <t>Mounted Daemonettes &gt; Mounted Daemonette</t>
-        </is>
-      </c>
-      <c r="D128" s="8" t="inlineStr">
-        <is>
-          <t>Daemonic Legions.cat</t>
-        </is>
-      </c>
-      <c r="E128" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F128" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G128" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 9-&gt;8</t>
-        </is>
-      </c>
-      <c r="H128" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/daemonette</t>
-        </is>
-      </c>
-      <c r="I128" s="11" t="n"/>
-      <c r="J128" s="11" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B129" s="8" t="inlineStr">
-        <is>
-          <t>Flamer</t>
-        </is>
-      </c>
-      <c r="C129" s="9" t="inlineStr">
-        <is>
-          <t>Flamers &gt; Flamer</t>
-        </is>
-      </c>
-      <c r="D129" s="8" t="inlineStr">
-        <is>
-          <t>Daemonic Legions.cat</t>
-        </is>
-      </c>
-      <c r="E129" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F129" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G129" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 9-&gt;8</t>
-        </is>
-      </c>
-      <c r="H129" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/flamer</t>
-        </is>
-      </c>
-      <c r="I129" s="11" t="n"/>
-      <c r="J129" s="11" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B130" s="8" t="inlineStr">
-        <is>
-          <t>Flesh Hound</t>
-        </is>
-      </c>
-      <c r="C130" s="9" t="inlineStr">
-        <is>
-          <t>Flesh Hounds &gt; Flesh Hounds</t>
-        </is>
-      </c>
-      <c r="D130" s="8" t="inlineStr">
-        <is>
-          <t>Daemonic Legions.cat</t>
-        </is>
-      </c>
-      <c r="E130" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F130" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G130" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 9-&gt;8</t>
-        </is>
-      </c>
-      <c r="H130" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/flesh-hound</t>
-        </is>
-      </c>
-      <c r="I130" s="11" t="n"/>
-      <c r="J130" s="11" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B131" s="8" t="inlineStr">
-        <is>
-          <t>Horror</t>
-        </is>
-      </c>
-      <c r="C131" s="9" t="inlineStr">
-        <is>
-          <t>Horrors &gt; Horrors</t>
-        </is>
-      </c>
-      <c r="D131" s="8" t="inlineStr">
-        <is>
-          <t>Daemonic Legions.cat</t>
-        </is>
-      </c>
-      <c r="E131" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F131" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G131" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 9-&gt;8</t>
-        </is>
-      </c>
-      <c r="H131" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/horror</t>
-        </is>
-      </c>
-      <c r="I131" s="11" t="n"/>
-      <c r="J131" s="11" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>Nurglings</t>
-        </is>
-      </c>
-      <c r="C132" s="9" t="inlineStr">
-        <is>
-          <t>Nurglings &gt; Nurglings</t>
-        </is>
-      </c>
-      <c r="D132" s="8" t="inlineStr">
-        <is>
-          <t>Daemonic Legions.cat</t>
-        </is>
-      </c>
-      <c r="E132" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G132" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 9-&gt;8</t>
-        </is>
-      </c>
-      <c r="H132" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/nurglings</t>
-        </is>
-      </c>
-      <c r="I132" s="11" t="n"/>
-      <c r="J132" s="11" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B133" s="8" t="inlineStr">
-        <is>
-          <t>Plaguebearer</t>
-        </is>
-      </c>
-      <c r="C133" s="9" t="inlineStr">
-        <is>
-          <t>Plaguebearers &gt; Plaguebearers</t>
-        </is>
-      </c>
-      <c r="D133" s="8" t="inlineStr">
-        <is>
-          <t>Daemonic Legions.cat</t>
-        </is>
-      </c>
-      <c r="E133" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G133" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 9-&gt;8</t>
-        </is>
-      </c>
-      <c r="H133" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/plaguebearer</t>
-        </is>
-      </c>
-      <c r="I133" s="11" t="n"/>
-      <c r="J133" s="11" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B134" s="8" t="inlineStr">
-        <is>
-          <t>Screamer</t>
-        </is>
-      </c>
-      <c r="C134" s="9" t="inlineStr">
-        <is>
-          <t>Screamers of Tzeentch &gt; Screamer</t>
-        </is>
-      </c>
-      <c r="D134" s="8" t="inlineStr">
-        <is>
-          <t>Daemonic Legions.cat</t>
-        </is>
-      </c>
-      <c r="E134" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F134" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G134" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 9-&gt;8</t>
-        </is>
-      </c>
-      <c r="H134" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/screamer</t>
-        </is>
-      </c>
-      <c r="I134" s="11" t="n"/>
-      <c r="J134" s="11" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B135" s="8" t="inlineStr">
-        <is>
-          <t>Hag</t>
-        </is>
-      </c>
-      <c r="C135" s="9" t="inlineStr">
-        <is>
-          <t>Cauldron of Blood</t>
-        </is>
-      </c>
-      <c r="D135" s="8" t="inlineStr">
-        <is>
-          <t>Dark Elves.cat</t>
-        </is>
-      </c>
-      <c r="E135" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F135" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G135" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 4-&gt;5</t>
-        </is>
-      </c>
-      <c r="H135" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/hag</t>
-        </is>
-      </c>
-      <c r="I135" s="11" t="n"/>
-      <c r="J135" s="11" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B136" s="8" t="inlineStr">
-        <is>
-          <t>Keeper of Secrets</t>
-        </is>
-      </c>
-      <c r="C136" s="9" t="inlineStr">
-        <is>
-          <t>Keeper of Secrets</t>
-        </is>
-      </c>
-      <c r="D136" s="8" t="inlineStr">
-        <is>
-          <t>Dark Elves.cat</t>
-        </is>
-      </c>
-      <c r="E136" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F136" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G136" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
-        </is>
-      </c>
-      <c r="H136" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
-        </is>
-      </c>
-      <c r="I136" s="11" t="n"/>
-      <c r="J136" s="11" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="inlineStr">
-        <is>
-          <t>Knight</t>
-        </is>
-      </c>
-      <c r="C137" s="9" t="inlineStr">
-        <is>
-          <t>Cold One Knights &gt; Cold One Knights</t>
-        </is>
-      </c>
-      <c r="D137" s="8" t="inlineStr">
-        <is>
-          <t>Dark Elves.cat</t>
-        </is>
-      </c>
-      <c r="E137" s="9" t="inlineStr">
-        <is>
-          <t>5 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F137" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G137" s="9" t="inlineStr">
-        <is>
-          <t>wiki: M 5-&gt;4, WS 5-&gt;4, BS 4-&gt;3, I 5-&gt;3, Ld 9-&gt;8</t>
-        </is>
-      </c>
-      <c r="H137" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/knight</t>
-        </is>
-      </c>
-      <c r="I137" s="11" t="n"/>
-      <c r="J137" s="11" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>Knight</t>
-        </is>
-      </c>
-      <c r="C138" s="9" t="inlineStr">
-        <is>
-          <t>Knights of Chaos &gt; Knights</t>
-        </is>
-      </c>
-      <c r="D138" s="8" t="inlineStr">
-        <is>
-          <t>Dark Elves.cat</t>
-        </is>
-      </c>
-      <c r="E138" s="9" t="inlineStr">
-        <is>
-          <t>4 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F138" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G138" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
-        </is>
-      </c>
-      <c r="H138" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/knight</t>
-        </is>
-      </c>
-      <c r="I138" s="11" t="n"/>
-      <c r="J138" s="11" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B139" s="8" t="inlineStr">
-        <is>
-          <t>Steed of Slaanesh</t>
-        </is>
-      </c>
-      <c r="C139" s="9" t="inlineStr">
-        <is>
-          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
-        </is>
-      </c>
-      <c r="D139" s="8" t="inlineStr">
-        <is>
-          <t>Dark Elves.cat</t>
-        </is>
-      </c>
-      <c r="E139" s="9" t="inlineStr">
-        <is>
-          <t>5 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F139" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G139" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
-        </is>
-      </c>
-      <c r="H139" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
-        </is>
-      </c>
-      <c r="I139" s="11" t="n"/>
-      <c r="J139" s="11" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>Daddallo</t>
-        </is>
-      </c>
-      <c r="C140" s="9" t="inlineStr">
-        <is>
-          <t>Birdmen of Catrazza &gt; Daddallo</t>
-        </is>
-      </c>
-      <c r="D140" s="8" t="inlineStr">
-        <is>
-          <t>Dogs of War.cat</t>
-        </is>
-      </c>
-      <c r="E140" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F140" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G140" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 2-&gt;1</t>
-        </is>
-      </c>
-      <c r="H140" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/daddallo</t>
-        </is>
-      </c>
-      <c r="I140" s="11" t="n"/>
-      <c r="J140" s="11" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B141" s="8" t="inlineStr">
-        <is>
-          <t>Warhorse</t>
-        </is>
-      </c>
-      <c r="C141" s="9" t="inlineStr">
-        <is>
-          <t>shared; used by Al Muktar's Desert Dogs, Bronzino's Galloper Guns</t>
-        </is>
-      </c>
-      <c r="D141" s="8" t="inlineStr">
-        <is>
-          <t>Dogs of War.cat</t>
-        </is>
-      </c>
-      <c r="E141" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F141" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G141" s="9" t="inlineStr">
-        <is>
-          <t>wiki: BS 3-&gt;0</t>
-        </is>
-      </c>
-      <c r="H141" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/warhorse</t>
-        </is>
-      </c>
-      <c r="I141" s="11" t="n"/>
-      <c r="J141" s="11" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="D142" s="8" t="inlineStr">
-        <is>
-          <t>Dwarfs.cat</t>
-        </is>
-      </c>
-      <c r="E142" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F142" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G142" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 2-&gt;1</t>
-        </is>
-      </c>
-      <c r="H142" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/engineer</t>
-        </is>
-      </c>
-      <c r="I142" s="11" t="n"/>
-      <c r="J142" s="11" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="inlineStr">
-        <is>
-          <t>Bloodthirster</t>
-        </is>
-      </c>
-      <c r="C143" s="9" t="inlineStr">
-        <is>
-          <t>Bloodthirster</t>
-        </is>
-      </c>
-      <c r="D143" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E143" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F143" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G143" s="9" t="inlineStr">
-        <is>
-          <t>wiki: S 7-&gt;6(7)</t>
-        </is>
-      </c>
-      <c r="H143" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/bloodthirster</t>
-        </is>
-      </c>
-      <c r="I143" s="11" t="n"/>
-      <c r="J143" s="11" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="inlineStr">
-        <is>
-          <t>Centigor</t>
-        </is>
-      </c>
-      <c r="C144" s="9" t="inlineStr">
-        <is>
-          <t>Minotaurs &gt; Minotaurs</t>
-        </is>
-      </c>
-      <c r="D144" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E144" s="9" t="inlineStr">
-        <is>
-          <t>5 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F144" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G144" s="9" t="inlineStr">
-        <is>
-          <t>wiki: M 6-&gt;8, W 3-&gt;1, I 4-&gt;2, A 3-&gt;1(2), Ld 8-&gt;7</t>
-        </is>
-      </c>
-      <c r="H144" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/centigor</t>
-        </is>
-      </c>
-      <c r="I144" s="11" t="n"/>
-      <c r="J144" s="11" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B145" s="8" t="inlineStr">
-        <is>
-          <t>Chaos Giant</t>
-        </is>
-      </c>
-      <c r="C145" s="9" t="inlineStr">
-        <is>
-          <t>Chaos Giant</t>
-        </is>
-      </c>
-      <c r="D145" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E145" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F145" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G145" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A Special-&gt;*</t>
-        </is>
-      </c>
-      <c r="H145" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/chaos-giant</t>
-        </is>
-      </c>
-      <c r="I145" s="11" t="n"/>
-      <c r="J145" s="11" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B146" s="8" t="inlineStr">
-        <is>
-          <t>Keeper of Secrets</t>
-        </is>
-      </c>
-      <c r="C146" s="9" t="inlineStr">
-        <is>
-          <t>Lord of Change</t>
-        </is>
-      </c>
-      <c r="D146" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E146" s="9" t="inlineStr">
-        <is>
-          <t>4 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F146" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G146" s="9" t="inlineStr">
-        <is>
-          <t>wiki: M 6-&gt;8, WS 6-&gt;9, A 5-&gt;10, Ld 9-&gt;6</t>
-        </is>
-      </c>
-      <c r="H146" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
-        </is>
-      </c>
-      <c r="I146" s="11" t="n"/>
-      <c r="J146" s="11" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B147" s="8" t="inlineStr">
-        <is>
-          <t>Keeper of Secrets</t>
-        </is>
-      </c>
-      <c r="C147" s="9" t="inlineStr">
-        <is>
-          <t>Keeper of Secrets</t>
-        </is>
-      </c>
-      <c r="D147" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E147" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F147" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G147" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
-        </is>
-      </c>
-      <c r="H147" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
-        </is>
-      </c>
-      <c r="I147" s="11" t="n"/>
-      <c r="J147" s="11" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B148" s="8" t="inlineStr">
-        <is>
-          <t>Knight</t>
-        </is>
-      </c>
-      <c r="C148" s="9" t="inlineStr">
-        <is>
-          <t>Knights of Chaos &gt; Knights</t>
-        </is>
-      </c>
-      <c r="D148" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E148" s="9" t="inlineStr">
-        <is>
-          <t>4 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F148" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G148" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 5-&gt;4, S 5-&gt;3, T 4-&gt;3, I 5-&gt;3</t>
-        </is>
-      </c>
-      <c r="H148" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/knight</t>
-        </is>
-      </c>
-      <c r="I148" s="11" t="n"/>
-      <c r="J148" s="11" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B149" s="8" t="inlineStr">
-        <is>
-          <t>Steed of Slaanesh</t>
-        </is>
-      </c>
-      <c r="C149" s="9" t="inlineStr">
-        <is>
-          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
-        </is>
-      </c>
-      <c r="D149" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E149" s="9" t="inlineStr">
-        <is>
-          <t>5 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F149" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G149" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
-        </is>
-      </c>
-      <c r="H149" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
-        </is>
-      </c>
-      <c r="I149" s="11" t="n"/>
-      <c r="J149" s="11" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B150" s="8" t="inlineStr">
-        <is>
-          <t>Troll</t>
-        </is>
-      </c>
-      <c r="C150" s="9" t="inlineStr">
-        <is>
-          <t>Chaos Trolls &gt; Trolls</t>
-        </is>
-      </c>
-      <c r="D150" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E150" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F150" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G150" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 4-&gt;3</t>
-        </is>
-      </c>
-      <c r="H150" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/troll</t>
-        </is>
-      </c>
-      <c r="I150" s="11" t="n"/>
-      <c r="J150" s="11" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B151" s="8" t="inlineStr">
-        <is>
-          <t>Tuskgor</t>
-        </is>
-      </c>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>Gorthor the Beastlord</t>
-        </is>
-      </c>
-      <c r="D151" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E151" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F151" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G151" s="9" t="inlineStr">
-        <is>
-          <t>wiki: S 4-&gt;3</t>
-        </is>
-      </c>
-      <c r="H151" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/tuskgor</t>
-        </is>
-      </c>
-      <c r="I151" s="11" t="n"/>
-      <c r="J151" s="11" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B152" s="8" t="inlineStr">
-        <is>
-          <t>Ungor</t>
-        </is>
-      </c>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>Beast Herd &gt; Ungors</t>
-        </is>
-      </c>
-      <c r="D152" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E152" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F152" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G152" s="9" t="inlineStr">
-        <is>
-          <t>wiki: T 4-&gt;3</t>
-        </is>
-      </c>
-      <c r="H152" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/ungor</t>
-        </is>
-      </c>
-      <c r="I152" s="11" t="n"/>
-      <c r="J152" s="11" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B153" s="8" t="inlineStr">
-        <is>
-          <t>Ungor</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>Tuskgor Chariot</t>
-        </is>
-      </c>
-      <c r="D153" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E153" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F153" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G153" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 4-&gt;3</t>
-        </is>
-      </c>
-      <c r="H153" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/ungor</t>
-        </is>
-      </c>
-      <c r="I153" s="11" t="n"/>
-      <c r="J153" s="11" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B154" s="8" t="inlineStr">
-        <is>
-          <t>Bladelord</t>
-        </is>
-      </c>
-      <c r="C154" s="9" t="inlineStr">
-        <is>
-          <t>Phoenix Guard &gt; Command &gt; Keeper of the Flame</t>
-        </is>
-      </c>
-      <c r="D154" s="8" t="inlineStr">
-        <is>
-          <t>High Elves.cat</t>
-        </is>
-      </c>
-      <c r="E154" s="9" t="inlineStr">
-        <is>
-          <t>3 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F154" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G154" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 5-&gt;6, I 6-&gt;5, Ld 9-&gt;8</t>
-        </is>
-      </c>
-      <c r="H154" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/bladelord</t>
-        </is>
-      </c>
-      <c r="I154" s="11" t="n"/>
-      <c r="J154" s="11" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B155" s="8" t="inlineStr">
-        <is>
-          <t>Ellyrian Reaver</t>
-        </is>
-      </c>
-      <c r="C155" s="9" t="inlineStr">
-        <is>
-          <t>Ellyrian Reavers &gt; Ellyrian Reavers</t>
-        </is>
-      </c>
-      <c r="D155" s="8" t="inlineStr">
-        <is>
-          <t>High Elves.cat</t>
-        </is>
-      </c>
-      <c r="E155" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F155" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G155" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 1-&gt;2</t>
-        </is>
-      </c>
-      <c r="H155" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/ellyrian-reaver</t>
-        </is>
-      </c>
-      <c r="I155" s="11" t="n"/>
-      <c r="J155" s="11" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B156" s="8" t="inlineStr">
-        <is>
-          <t>Harbinger</t>
-        </is>
-      </c>
-      <c r="C156" s="9" t="inlineStr">
-        <is>
-          <t>Ellyrian Reavers &gt; Command &gt; Harbinger</t>
-        </is>
-      </c>
-      <c r="D156" s="8" t="inlineStr">
-        <is>
-          <t>High Elves.cat</t>
-        </is>
-      </c>
-      <c r="E156" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F156" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G156" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 1-&gt;2</t>
-        </is>
-      </c>
-      <c r="H156" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/harbinger</t>
-        </is>
-      </c>
-      <c r="I156" s="11" t="n"/>
-      <c r="J156" s="11" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B157" s="8" t="inlineStr">
-        <is>
-          <t>Greyback</t>
-        </is>
-      </c>
-      <c r="C157" s="9" t="inlineStr">
-        <is>
-          <t>Yheetees &gt; Greyback</t>
-        </is>
-      </c>
-      <c r="D157" s="8" t="inlineStr">
-        <is>
-          <t>Ogre Kingdoms.cat</t>
-        </is>
-      </c>
-      <c r="E157" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F157" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G157" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 4-&gt;3</t>
-        </is>
-      </c>
-      <c r="H157" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/greyback</t>
-        </is>
-      </c>
-      <c r="I157" s="11" t="n"/>
-      <c r="J157" s="11" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B158" s="8" t="inlineStr">
-        <is>
-          <t>Rhinox</t>
-        </is>
-      </c>
-      <c r="C158" s="9" t="inlineStr">
-        <is>
-          <t>Rhinox Cavalry &gt; Rhinox Riders</t>
-        </is>
-      </c>
-      <c r="D158" s="8" t="inlineStr">
-        <is>
-          <t>Ogre Kingdoms.cat</t>
-        </is>
-      </c>
-      <c r="E158" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F158" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G158" s="9" t="inlineStr">
-        <is>
-          <t>wiki: M 7-&gt;6</t>
-        </is>
-      </c>
-      <c r="H158" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
-        </is>
-      </c>
-      <c r="I158" s="11" t="n"/>
-      <c r="J158" s="11" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B159" s="8" t="inlineStr">
-        <is>
-          <t>Thunderfist</t>
-        </is>
-      </c>
-      <c r="C159" s="9" t="inlineStr">
-        <is>
-          <t>Leadbelchers &gt; Command &gt; Thunderfist</t>
-        </is>
-      </c>
-      <c r="D159" s="8" t="inlineStr">
-        <is>
-          <t>Ogre Kingdoms.cat</t>
-        </is>
-      </c>
-      <c r="E159" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F159" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G159" s="9" t="inlineStr">
-        <is>
-          <t>wiki: BS 2-&gt;3</t>
-        </is>
-      </c>
-      <c r="H159" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/thunderfist</t>
-        </is>
-      </c>
-      <c r="I159" s="11" t="n"/>
-      <c r="J159" s="11" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B160" s="8" t="inlineStr">
-        <is>
-          <t>Boar Chariot</t>
-        </is>
-      </c>
-      <c r="C160" s="9" t="inlineStr">
-        <is>
-          <t>Savage Orc Boar Chariot</t>
-        </is>
-      </c>
-      <c r="D160" s="8" t="inlineStr">
-        <is>
-          <t>Orcs and Goblins.cat</t>
-        </is>
-      </c>
-      <c r="E160" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F160" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G160" s="9" t="inlineStr">
-        <is>
-          <t>wiki: S 5-&gt;3</t>
-        </is>
-      </c>
-      <c r="H160" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/boar-chariot</t>
-        </is>
-      </c>
-      <c r="I160" s="11" t="n"/>
-      <c r="J160" s="11" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B161" s="8" t="inlineStr">
-        <is>
-          <t>Giant</t>
-        </is>
-      </c>
-      <c r="C161" s="9" t="inlineStr">
-        <is>
-          <t>Giant</t>
-        </is>
-      </c>
-      <c r="D161" s="8" t="inlineStr">
-        <is>
-          <t>Orcs and Goblins.cat</t>
-        </is>
-      </c>
-      <c r="E161" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F161" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G161" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A Special-&gt;*</t>
-        </is>
-      </c>
-      <c r="H161" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/giant</t>
-        </is>
-      </c>
-      <c r="I161" s="11" t="n"/>
-      <c r="J161" s="11" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B162" s="8" t="inlineStr">
-        <is>
-          <t>Squig Hopper</t>
-        </is>
-      </c>
-      <c r="C162" s="9" t="inlineStr">
-        <is>
-          <t>Night Goblin Squig Herd &gt; Unit &gt; Squig Hopper</t>
-        </is>
-      </c>
-      <c r="D162" s="8" t="inlineStr">
-        <is>
-          <t>Orcs and Goblins.cat</t>
-        </is>
-      </c>
-      <c r="E162" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F162" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G162" s="9" t="inlineStr">
-        <is>
-          <t>wiki: W 2-&gt;1</t>
-        </is>
-      </c>
-      <c r="H162" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/squig-hopper</t>
-        </is>
-      </c>
-      <c r="I162" s="11" t="n"/>
-      <c r="J162" s="11" t="n"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B163" s="8" t="inlineStr">
-        <is>
-          <t>Clanrat Slave</t>
-        </is>
-      </c>
-      <c r="C163" s="9" t="inlineStr">
-        <is>
-          <t>Clanrat Slaves &gt; Clanrat Slaves</t>
-        </is>
-      </c>
-      <c r="D163" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E163" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F163" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G163" s="9" t="inlineStr">
-        <is>
-          <t>wiki: M 6-&gt;5, I 5-&gt;4</t>
-        </is>
-      </c>
-      <c r="H163" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/clanrat-slave</t>
-        </is>
-      </c>
-      <c r="I163" s="11" t="n"/>
-      <c r="J163" s="11" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B164" s="8" t="inlineStr">
-        <is>
-          <t>Festering Chantor</t>
-        </is>
-      </c>
-      <c r="C164" s="9" t="inlineStr">
-        <is>
-          <t>Festering Chantor</t>
-        </is>
-      </c>
-      <c r="D164" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E164" s="9" t="inlineStr">
-        <is>
-          <t>7 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F164" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G164" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
-        </is>
-      </c>
-      <c r="H164" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/festering-chantor</t>
-        </is>
-      </c>
-      <c r="I164" s="11" t="n"/>
-      <c r="J164" s="11" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B165" s="8" t="inlineStr">
-        <is>
-          <t>Plague Lord</t>
-        </is>
-      </c>
-      <c r="C165" s="9" t="inlineStr">
-        <is>
-          <t>Plague Lord</t>
-        </is>
-      </c>
-      <c r="D165" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E165" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F165" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G165" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 5-&gt;4</t>
-        </is>
-      </c>
-      <c r="H165" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/plague-lord</t>
-        </is>
-      </c>
-      <c r="I165" s="11" t="n"/>
-      <c r="J165" s="11" t="n"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B166" s="8" t="inlineStr">
-        <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="C166" s="9" t="inlineStr">
-        <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="D166" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E166" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F166" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G166" s="9" t="inlineStr">
-        <is>
-          <t>wiki: I 6-&gt;4</t>
-        </is>
-      </c>
-      <c r="H166" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
-        </is>
-      </c>
-      <c r="I166" s="11" t="n"/>
-      <c r="J166" s="11" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B167" s="8" t="inlineStr">
-        <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="C167" s="9" t="inlineStr">
-        <is>
-          <t>Warlock Master</t>
-        </is>
-      </c>
-      <c r="D167" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E167" s="9" t="inlineStr">
-        <is>
-          <t>6 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F167" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G167" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 4-&gt;3, T 4-&gt;3, W 3-&gt;2, I 5-&gt;4, A 2-&gt;1, Ld 7-&gt;5</t>
-        </is>
-      </c>
-      <c r="H167" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
-        </is>
-      </c>
-      <c r="I167" s="11" t="n"/>
-      <c r="J167" s="11" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B168" s="8" t="inlineStr">
-        <is>
-          <t>Skeleton</t>
-        </is>
-      </c>
-      <c r="C168" s="9" t="inlineStr">
-        <is>
-          <t>Skeleton Light Horsemen &gt; Skeleton Horseman</t>
-        </is>
-      </c>
-      <c r="D168" s="8" t="inlineStr">
-        <is>
-          <t>Tomb Kings.cat</t>
-        </is>
-      </c>
-      <c r="E168" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F168" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G168" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 5-&gt;3</t>
-        </is>
-      </c>
-      <c r="H168" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/skeleton</t>
-        </is>
-      </c>
-      <c r="I168" s="11" t="n"/>
-      <c r="J168" s="11" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B169" s="8" t="inlineStr">
-        <is>
-          <t>Skeleton</t>
-        </is>
-      </c>
-      <c r="C169" s="9" t="inlineStr">
-        <is>
-          <t>Skeleton Heavy Horsemen &gt; Skeleton Horseman</t>
-        </is>
-      </c>
-      <c r="D169" s="8" t="inlineStr">
-        <is>
-          <t>Tomb Kings.cat</t>
-        </is>
-      </c>
-      <c r="E169" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F169" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G169" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 5-&gt;3</t>
-        </is>
-      </c>
-      <c r="H169" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/skeleton</t>
-        </is>
-      </c>
-      <c r="I169" s="11" t="n"/>
-      <c r="J169" s="11" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B170" s="8" t="inlineStr">
-        <is>
-          <t>Skeleton Crew</t>
-        </is>
-      </c>
-      <c r="C170" s="9" t="inlineStr">
-        <is>
-          <t>Chariots &gt; Chariot</t>
-        </is>
-      </c>
-      <c r="D170" s="8" t="inlineStr">
-        <is>
-          <t>Tomb Kings.cat</t>
-        </is>
-      </c>
-      <c r="E170" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F170" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G170" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;2, Ld 7-&gt;3</t>
-        </is>
-      </c>
-      <c r="H170" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/skeleton-crew</t>
-        </is>
-      </c>
-      <c r="I170" s="11" t="n"/>
-      <c r="J170" s="11" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:J170"/>
+  <autoFilter ref="A2:J98"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4:I170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Option A,Option B,Leave as is,Rename catalogue,Needs more thought"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8182,60 +5014,60 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId66"/>
@@ -8255,78 +5087,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId154"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/judgement-calls.xlsx
+++ b/docs/judgement-calls.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Decisions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B29" s="4">
-        <f>COUNTBLANK(Decisions!$I$4:$I$98)</f>
+        <f>COUNTBLANK(Decisions!$I$4:$I$71)</f>
         <v/>
       </c>
     </row>
@@ -704,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3499,8 +3499,16 @@
           <t>https://6th.whfb.app/special-rules/ethereal</t>
         </is>
       </c>
-      <c r="I64" s="11" t="n"/>
-      <c r="J64" s="11" t="n"/>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>Needs more thought</t>
+        </is>
+      </c>
+      <c r="J64" s="12" t="inlineStr">
+        <is>
+          <t>The wiki's Black Knight has only Undead and Wight Blades - no ethereal steeds - so there is nothing to copy and the intent is unclear.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -3682,17 +3690,17 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Stoicism</t>
+          <t>Ghal Maraz</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Emperor Karl Franz &gt; Weapon</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -3702,17 +3710,17 @@
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 80</t>
+          <t>catalogue: 180</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: 0</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
+          <t>https://6th.whfb.app/magic-item/ghal-maraz</t>
         </is>
       </c>
       <c r="I69" s="11" t="n"/>
@@ -3721,1286 +3729,114 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Virtue of Stoicism</t>
+          <t>Steed of Slaanesh</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Chivalric Virtues</t>
+          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Bretonnians.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>5 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 40</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>wiki: 35</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/virtue-of-stoicism</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="n"/>
-      <c r="J70" s="11" t="n"/>
+          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="inlineStr">
+        <is>
+          <t>Needs more thought</t>
+        </is>
+      </c>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>The catalogue's is the ridden mount's line; the wiki page is the standalone Daemon creature. Probably not the same thing.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Ghal Maraz</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Emperor Karl Franz &gt; Weapon</t>
+          <t>Festering Chantor</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Skaven.cat</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>7 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 180</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>wiki: 0</t>
+          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/ghal-maraz</t>
-        </is>
-      </c>
-      <c r="I71" s="11" t="n"/>
-      <c r="J71" s="11" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Villein</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>Peasant Bowmen &gt; Command &gt; Villein</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Bretonnians.cat</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;2, A 1-&gt;2</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/villein</t>
-        </is>
-      </c>
-      <c r="I72" s="11" t="n"/>
-      <c r="J72" s="11" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Bull Centaur Hero</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>Bull Centaur Hero</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>Chaos Dwarves.cat</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>wiki: T 4-&gt;5</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/bull-centaur-hero</t>
-        </is>
-      </c>
-      <c r="I73" s="11" t="n"/>
-      <c r="J73" s="11" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Chaos Dwarf Sorcerer</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>Sorcerer Lord</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>Chaos Dwarves.cat</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>5 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>wiki: S 4-&gt;3, T 5-&gt;4, W 3-&gt;2, I 1-&gt;2, Ld 10-&gt;9</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/chaos-dwarf-sorcerer</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="n"/>
-      <c r="J74" s="11" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>Hobgoblin Crew</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>Hobgoblin Bolt Thrower &gt; Hobgoblin Bolt Thrower</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>Chaos Dwarves.cat</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>wiki: M 3-&gt;4</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/hobgoblin-crew</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="n"/>
-      <c r="J75" s="11" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Hag</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>Cauldron of Blood</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Dark Elves.cat</t>
-        </is>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 4-&gt;5</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/hag</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="n"/>
-      <c r="J76" s="11" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>Daddallo</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>Birdmen of Catrazza &gt; Daddallo</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>Dogs of War.cat</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 2-&gt;1</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/daddallo</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="n"/>
-      <c r="J77" s="11" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Warhorse</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>shared; used by Al Muktar's Desert Dogs, Bronzino's Galloper Guns</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>Dogs of War.cat</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>wiki: BS 3-&gt;0</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/warhorse</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="n"/>
-      <c r="J78" s="11" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>Dwarfs.cat</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 2-&gt;1</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/engineer</t>
-        </is>
-      </c>
-      <c r="I79" s="11" t="n"/>
-      <c r="J79" s="11" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>Keeper of Secrets</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>Keeper of Secrets</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 6-&gt;10, Ld 9-&gt;6</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/keeper-of-secrets</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="n"/>
-      <c r="J80" s="11" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Steed of Slaanesh</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>5 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
-        </is>
-      </c>
-      <c r="I81" s="11" t="n"/>
-      <c r="J81" s="11" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Tuskgor</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>Gorthor the Beastlord</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>wiki: S 4-&gt;3</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/tuskgor</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="n"/>
-      <c r="J82" s="11" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Ungor</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>Beast Herd &gt; Ungors</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>wiki: T 4-&gt;3</t>
-        </is>
-      </c>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/ungor</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="n"/>
-      <c r="J83" s="11" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Ungor</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>Tuskgor Chariot</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 4-&gt;3</t>
-        </is>
-      </c>
-      <c r="H84" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/ungor</t>
-        </is>
-      </c>
-      <c r="I84" s="11" t="n"/>
-      <c r="J84" s="11" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Bladelord</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>Phoenix Guard &gt; Command &gt; Keeper of the Flame</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>High Elves.cat</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>3 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 5-&gt;6, I 6-&gt;5, Ld 9-&gt;8</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/bladelord</t>
-        </is>
-      </c>
-      <c r="I85" s="11" t="n"/>
-      <c r="J85" s="11" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>Ellyrian Reaver</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t>Ellyrian Reavers &gt; Ellyrian Reavers</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>High Elves.cat</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G86" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 1-&gt;2</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/ellyrian-reaver</t>
-        </is>
-      </c>
-      <c r="I86" s="11" t="n"/>
-      <c r="J86" s="11" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>Harbinger</t>
-        </is>
-      </c>
-      <c r="C87" s="9" t="inlineStr">
-        <is>
-          <t>Ellyrian Reavers &gt; Command &gt; Harbinger</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>High Elves.cat</t>
-        </is>
-      </c>
-      <c r="E87" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G87" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 1-&gt;2</t>
-        </is>
-      </c>
-      <c r="H87" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/harbinger</t>
-        </is>
-      </c>
-      <c r="I87" s="11" t="n"/>
-      <c r="J87" s="11" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>Greyback</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>Yheetees &gt; Greyback</t>
-        </is>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>Ogre Kingdoms.cat</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 4-&gt;3</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/greyback</t>
-        </is>
-      </c>
-      <c r="I88" s="11" t="n"/>
-      <c r="J88" s="11" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Rhinox</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>Rhinox Cavalry &gt; Rhinox Riders</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>Ogre Kingdoms.cat</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>wiki: M 7-&gt;6</t>
-        </is>
-      </c>
-      <c r="H89" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/rhinox</t>
-        </is>
-      </c>
-      <c r="I89" s="11" t="n"/>
-      <c r="J89" s="11" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>Thunderfist</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>Leadbelchers &gt; Command &gt; Thunderfist</t>
-        </is>
-      </c>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Ogre Kingdoms.cat</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>wiki: BS 2-&gt;3</t>
-        </is>
-      </c>
-      <c r="H90" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/thunderfist</t>
-        </is>
-      </c>
-      <c r="I90" s="11" t="n"/>
-      <c r="J90" s="11" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>Boar Chariot</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>Savage Orc Boar Chariot</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t>Orcs and Goblins.cat</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F91" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>wiki: S 5-&gt;3</t>
-        </is>
-      </c>
-      <c r="H91" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/boar-chariot</t>
-        </is>
-      </c>
-      <c r="I91" s="11" t="n"/>
-      <c r="J91" s="11" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Squig Hopper</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>Night Goblin Squig Herd &gt; Unit &gt; Squig Hopper</t>
-        </is>
-      </c>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>Orcs and Goblins.cat</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>wiki: W 2-&gt;1</t>
-        </is>
-      </c>
-      <c r="H92" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/squig-hopper</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="n"/>
-      <c r="J92" s="11" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Clanrat Slave</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>Clanrat Slaves &gt; Clanrat Slaves</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>wiki: M 6-&gt;5, I 5-&gt;4</t>
-        </is>
-      </c>
-      <c r="H93" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/clanrat-slave</t>
-        </is>
-      </c>
-      <c r="I93" s="11" t="n"/>
-      <c r="J93" s="11" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>Festering Chantor</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>Festering Chantor</t>
-        </is>
-      </c>
-      <c r="D94" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>7 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
-        </is>
-      </c>
-      <c r="H94" s="10" t="inlineStr">
-        <is>
           <t>https://6th.whfb.app/unit/festering-chantor</t>
         </is>
       </c>
-      <c r="I94" s="11" t="n"/>
-      <c r="J94" s="11" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>Plague Lord</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>Plague Lord</t>
-        </is>
-      </c>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr">
-        <is>
-          <t>wiki: A 5-&gt;4</t>
-        </is>
-      </c>
-      <c r="H95" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/plague-lord</t>
-        </is>
-      </c>
-      <c r="I95" s="11" t="n"/>
-      <c r="J95" s="11" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>wiki: I 6-&gt;4</t>
-        </is>
-      </c>
-      <c r="H96" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
-        </is>
-      </c>
-      <c r="I96" s="11" t="n"/>
-      <c r="J96" s="11" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>Warlock Engineer</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>Warlock Master</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>6 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 4-&gt;3, T 4-&gt;3, W 3-&gt;2, I 5-&gt;4, A 2-&gt;1, Ld 7-&gt;5</t>
-        </is>
-      </c>
-      <c r="H97" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
-        </is>
-      </c>
-      <c r="I97" s="11" t="n"/>
-      <c r="J97" s="11" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>Skeleton Crew</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>Chariots &gt; Chariot</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>Tomb Kings.cat</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>2 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;2, Ld 7-&gt;3</t>
-        </is>
-      </c>
-      <c r="H98" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/skeleton-crew</t>
-        </is>
-      </c>
-      <c r="I98" s="11" t="n"/>
-      <c r="J98" s="11" t="n"/>
+      <c r="I71" s="12" t="inlineStr">
+        <is>
+          <t>Needs more thought</t>
+        </is>
+      </c>
+      <c r="J71" s="12" t="inlineStr">
+        <is>
+          <t>Every one of seven characteristics is exactly 1 lower than the wiki's, which looks like a different tier of the model rather than a typo. Worth checking the book.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J98"/>
+  <autoFilter ref="A2:J71"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4:I98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Option A,Option B,Leave as is,Rename catalogue,Needs more thought"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5060,33 +3896,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/judgement-calls.xlsx
+++ b/docs/judgement-calls.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Decisions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B29" s="4">
-        <f>COUNTBLANK(Decisions!$I$4:$I$71)</f>
+        <f>COUNTBLANK(Decisions!$I$4:$I$69)</f>
         <v/>
       </c>
     </row>
@@ -704,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3466,17 +3466,17 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Ethereal Steeds</t>
+          <t>Fly</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Black Knights</t>
+          <t>shared; nothing links to it</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Vampire Counts.cat</t>
+          <t>Warhammer Fantasy 6th Edition.gst</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3491,24 +3491,16 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>/special-rules/ethereal (0.90)</t>
+          <t>/faq/flyers (0.90)</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/special-rules/ethereal</t>
-        </is>
-      </c>
-      <c r="I64" s="12" t="inlineStr">
-        <is>
-          <t>Needs more thought</t>
-        </is>
-      </c>
-      <c r="J64" s="12" t="inlineStr">
-        <is>
-          <t>The wiki's Black Knight has only Undead and Wight Blades - no ethereal steeds - so there is nothing to copy and the intent is unclear.</t>
-        </is>
-      </c>
+          <t>https://6th.whfb.app/faq/flyers</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="11" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -3518,7 +3510,7 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Fly</t>
+          <t>Stone Thrower</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -3543,12 +3535,12 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>/faq/flyers (0.90)</t>
+          <t>/unit/stone-thrower (1.00)</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/faq/flyers</t>
+          <t>https://6th.whfb.app/unit/stone-thrower</t>
         </is>
       </c>
       <c r="I65" s="11" t="n"/>
@@ -3562,17 +3554,17 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Stone Thrower</t>
+          <t>Alter Kindred</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>shared; nothing links to it</t>
+          <t>Wood Elf Kindred &gt; Alter Kindred</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Warhammer Fantasy 6th Edition.gst</t>
+          <t>Wood Elves.cat</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -3587,12 +3579,12 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>/unit/stone-thrower (1.00)</t>
+          <t>/magic-item/the-alter-kindreds (0.80)</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/stone-thrower</t>
+          <t>https://6th.whfb.app/magic-item/the-alter-kindreds</t>
         </is>
       </c>
       <c r="I66" s="11" t="n"/>
@@ -3606,12 +3598,12 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Alter Kindred</t>
+          <t>Strangle-Roots</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Wood Elf Kindred &gt; Alter Kindred</t>
+          <t>shared; used by Treeman, Treeman Ancient</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -3631,212 +3623,108 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>/magic-item/the-alter-kindreds (0.80)</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/the-alter-kindreds</t>
-        </is>
-      </c>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr"/>
       <c r="I67" s="11" t="n"/>
       <c r="J67" s="11" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>No wiki coverage</t>
+          <t>Points cost</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Strangle-Roots</t>
+          <t>Ghal Maraz</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>shared; used by Treeman, Treeman Ancient</t>
+          <t>Emperor Karl Franz &gt; Weapon</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Wood Elves.cat</t>
+          <t>The Empire.cat</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>no confident match; nearest candidate is not applied</t>
+          <t>catalogue and wiki disagree on cost</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>leave as is</t>
+          <t>catalogue: 180</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>no candidate</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr"/>
+          <t>wiki: 0</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/magic-item/ghal-maraz</t>
+        </is>
+      </c>
       <c r="I68" s="11" t="n"/>
       <c r="J68" s="11" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>Points cost</t>
+          <t>Unit statline</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Ghal Maraz</t>
+          <t>Mount of Slaanesh</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Emperor Karl Franz &gt; Weapon</t>
+          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>The Empire.cat</t>
+          <t>Forces of Chaos.cat</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>catalogue and wiki disagree on cost</t>
+          <t>1 characteristic(s) differ</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>catalogue: 180</t>
+          <t>catalogue as is</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>wiki: 0</t>
+          <t>wiki: Ld 8-&gt;9</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/magic-item/ghal-maraz</t>
+          <t>https://6th.whfb.app/unit/mount-of-slaanesh</t>
         </is>
       </c>
       <c r="I69" s="11" t="n"/>
       <c r="J69" s="11" t="n"/>
     </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Steed of Slaanesh</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>5 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 3-&gt;4, W 1-&gt;3, A 1-&gt;2</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/steed-of-slaanesh</t>
-        </is>
-      </c>
-      <c r="I70" s="12" t="inlineStr">
-        <is>
-          <t>Needs more thought</t>
-        </is>
-      </c>
-      <c r="J70" s="12" t="inlineStr">
-        <is>
-          <t>The catalogue's is the ridden mount's line; the wiki page is the standalone Daemon creature. Probably not the same thing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Festering Chantor</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>Festering Chantor</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>Skaven.cat</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>7 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>wiki: WS 3-&gt;4, S 3-&gt;4, T 4-&gt;5, W 2-&gt;3, I 3-&gt;4, A 1-&gt;2, Ld 5-&gt;6</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/festering-chantor</t>
-        </is>
-      </c>
-      <c r="I71" s="12" t="inlineStr">
-        <is>
-          <t>Needs more thought</t>
-        </is>
-      </c>
-      <c r="J71" s="12" t="inlineStr">
-        <is>
-          <t>Every one of seven characteristics is exactly 1 lower than the wiki's, which looks like a different tier of the model rather than a typo. Worth checking the book.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:J71"/>
+  <autoFilter ref="A2:J69"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4:I71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Option A,Option B,Leave as is,Rename catalogue,Needs more thought"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3892,10 +3780,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/judgement-calls.xlsx
+++ b/docs/judgement-calls.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Decisions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B29" s="4">
-        <f>COUNTBLANK(Decisions!$I$4:$I$69)</f>
+        <f>COUNTBLANK(Decisions!$I$4:$I$67)</f>
         <v/>
       </c>
     </row>
@@ -704,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Warlock Engineer</t>
+          <t>Warlock Master</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>/unit/warlock-engineer (1.00)</t>
+          <t>/unit/master (0.80)</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>https://6th.whfb.app/unit/warlock-engineer</t>
+          <t>https://6th.whfb.app/unit/master</t>
         </is>
       </c>
       <c r="I54" s="11" t="n"/>
@@ -3630,101 +3630,13 @@
       <c r="I67" s="11" t="n"/>
       <c r="J67" s="11" t="n"/>
     </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>Points cost</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Ghal Maraz</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>Emperor Karl Franz &gt; Weapon</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>The Empire.cat</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>catalogue and wiki disagree on cost</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>catalogue: 180</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>wiki: 0</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/magic-item/ghal-maraz</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="n"/>
-      <c r="J68" s="11" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>Unit statline</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Mount of Slaanesh</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>Mounted Daemonettes &gt; Mounted Daemonettes</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>Forces of Chaos.cat</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>1 characteristic(s) differ</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>catalogue as is</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>wiki: Ld 8-&gt;9</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
-        <is>
-          <t>https://6th.whfb.app/unit/mount-of-slaanesh</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="n"/>
-      <c r="J69" s="11" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:J69"/>
+  <autoFilter ref="A2:J67"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4:I69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Option A,Option B,Leave as is,Rename catalogue,Needs more thought"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3780,8 +3692,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/judgement-calls.xlsx
+++ b/docs/judgement-calls.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Decisions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$2:$J$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,6 +120,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -688,7 +689,7 @@
         </is>
       </c>
       <c r="B29" s="4">
-        <f>COUNTBLANK(Decisions!$I$4:$I$9)</f>
+        <f>COUNTBLANK(Decisions!$I$4:$I$11)</f>
         <v/>
       </c>
     </row>
@@ -703,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1093,57 +1094,141 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
+          <t>Single-Minded</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Rhinox Cavalry</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Ogre Kingdoms.cat</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>no confident match; nearest candidate is not applied</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>leave as is</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>no candidate</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>No wiki coverage</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
           <t>Parent and Detachment Units</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>shared; nothing links to it</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>The Empire.cat</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>no confident match; nearest candidate is not applied</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>leave as is</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>/warhammer-glossary/unit-warhammer-glossary (0.80)</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>https://6th.whfb.app/warhammer-glossary/unit-warhammer-glossary</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Needs more thought</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>The wiki's Detachment Rules page is 6,618 characters, the longest in the repo. Held back with the other long rules to be summarised rather than copied; the catalogue's 5,933-character version stands meanwhile.</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Unit statline</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Rhinox</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Rhinox Cavalry &gt; Rhinox Riders</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Ogre Kingdoms.cat</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>1 characteristic(s) differ</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>catalogue as is</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>wiki: M 7-&gt;6</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>https://6th.whfb.app/unit/rhinox</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:J9"/>
+  <autoFilter ref="A2:J11"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4:I9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Option A,Option B,Leave as is,Rename catalogue,Needs more thought"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1153,7 +1238,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
